--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -10101,464 +10101,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1232,6 +1232,15 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -6578,7 +6587,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9804,6 +9813,10 @@
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10024,7 +10037,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10220,7 +10233,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10311,7 +10324,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10344,7 +10357,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -11709,8 +11722,8 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E1:M1"/>
     <mergeCell ref="L7:M7"/>
-    <mergeCell ref="E1:M1"/>
     <mergeCell ref="A32:M32"/>
     <mergeCell ref="A23:M23"/>
     <mergeCell ref="A8:M8"/>
@@ -11758,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y163"/>
+  <dimension ref="A1:Y164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="587" min="1" max="1"/>
@@ -12069,7 +12082,7 @@
       </c>
       <c r="E9" s="288" t="inlineStr">
         <is>
-          <t>Localización y Replanteo</t>
+          <t>Replanteo general de ejes y niveles</t>
         </is>
       </c>
       <c r="F9" s="289" t="n"/>
@@ -12077,7 +12090,7 @@
       <c r="H9" s="289" t="n"/>
       <c r="I9" s="287" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="J9" s="1294" t="n">
@@ -12108,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="1294">
-        <f>IF(I9="","",ROUND(IF(OR(I9="m²",I9="m2"),J9*IF(K9=0,1,K9)*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="m³",I9="m3"),J9*K9*L9*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="ml",I9="ML"),J9*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="und",I9="UND"),IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(I9="kg",J9*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,0))))),3))</f>
+        <f>IF(I9="","",ROUND(IF(OR(I9="m²",I9="m2"),J9*IF(K9=0,1,K9)*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="m³",I9="m3"),J9*K9*L9*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="ml",I9="ML"),J9*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="und",I9="UND"),IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(I9="kg",J9*IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,IF(OR(I9="gl",I9="GL",I9="gb",I9="GB",I9="Gl",I9="Gb"),IF(N9=0,1,N9)*IF(O9=0,1,O9)*P9-Q9,0)))))),3))</f>
         <v/>
       </c>
       <c r="T9" s="1294">
@@ -12191,7 +12204,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="1294">
-        <f>IF(I10="","",ROUND(IF(OR(I10="m²",I10="m2"),J10*IF(K10=0,1,K10)*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="m³",I10="m3"),J10*K10*L10*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="ml",I10="ML"),J10*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="und",I10="UND"),IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(I10="kg",J10*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,0))))),3))</f>
+        <f>IF(I10="","",ROUND(IF(OR(I10="m²",I10="m2"),J10*IF(K10=0,1,K10)*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="m³",I10="m3"),J10*K10*L10*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="ml",I10="ML"),J10*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="und",I10="UND"),IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(I10="kg",J10*IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,IF(OR(I10="gl",I10="GL",I10="gb",I10="GB",I10="Gl",I10="Gb"),IF(N10=0,1,N10)*IF(O10=0,1,O10)*P10-Q10,0)))))),3))</f>
         <v/>
       </c>
       <c r="T10" s="1294">
@@ -12274,7 +12287,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="1294">
-        <f>IF(I11="","",ROUND(IF(OR(I11="m²",I11="m2"),J11*IF(K11=0,1,K11)*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="m³",I11="m3"),J11*K11*L11*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="ml",I11="ML"),J11*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="und",I11="UND"),IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(I11="kg",J11*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,0))))),3))</f>
+        <f>IF(I11="","",ROUND(IF(OR(I11="m²",I11="m2"),J11*IF(K11=0,1,K11)*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="m³",I11="m3"),J11*K11*L11*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="ml",I11="ML"),J11*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="und",I11="UND"),IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(I11="kg",J11*IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,IF(OR(I11="gl",I11="GL",I11="gb",I11="GB",I11="Gl",I11="Gb"),IF(N11=0,1,N11)*IF(O11=0,1,O11)*P11-Q11,0)))))),3))</f>
         <v/>
       </c>
       <c r="T11" s="1294">
@@ -12357,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="1294">
-        <f>IF(I12="","",ROUND(IF(OR(I12="m²",I12="m2"),J12*IF(K12=0,1,K12)*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="m³",I12="m3"),J12*K12*L12*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="ml",I12="ML"),J12*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="und",I12="UND"),IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(I12="kg",J12*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,0))))),3))</f>
+        <f>IF(I12="","",ROUND(IF(OR(I12="m²",I12="m2"),J12*IF(K12=0,1,K12)*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="m³",I12="m3"),J12*K12*L12*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="ml",I12="ML"),J12*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="und",I12="UND"),IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(I12="kg",J12*IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,IF(OR(I12="gl",I12="GL",I12="gb",I12="GB",I12="Gl",I12="Gb"),IF(N12=0,1,N12)*IF(O12=0,1,O12)*P12-Q12,0)))))),3))</f>
         <v/>
       </c>
       <c r="T12" s="1294">
@@ -12440,7 +12453,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="1294">
-        <f>IF(I13="","",ROUND(IF(OR(I13="m²",I13="m2"),J13*IF(K13=0,1,K13)*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="m³",I13="m3"),J13*K13*L13*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="ml",I13="ML"),J13*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="und",I13="UND"),IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(I13="kg",J13*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,0))))),3))</f>
+        <f>IF(I13="","",ROUND(IF(OR(I13="m²",I13="m2"),J13*IF(K13=0,1,K13)*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="m³",I13="m3"),J13*K13*L13*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="ml",I13="ML"),J13*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="und",I13="UND"),IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(I13="kg",J13*IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,IF(OR(I13="gl",I13="GL",I13="gb",I13="GB",I13="Gl",I13="Gb"),IF(N13=0,1,N13)*IF(O13=0,1,O13)*P13-Q13,0)))))),3))</f>
         <v/>
       </c>
       <c r="T13" s="1294">
@@ -12523,7 +12536,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1294">
-        <f>IF(I14="","",ROUND(IF(OR(I14="m²",I14="m2"),J14*IF(K14=0,1,K14)*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="m³",I14="m3"),J14*K14*L14*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="ml",I14="ML"),J14*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="und",I14="UND"),IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(I14="kg",J14*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,0))))),3))</f>
+        <f>IF(I14="","",ROUND(IF(OR(I14="m²",I14="m2"),J14*IF(K14=0,1,K14)*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="m³",I14="m3"),J14*K14*L14*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="ml",I14="ML"),J14*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="und",I14="UND"),IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(I14="kg",J14*IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,IF(OR(I14="gl",I14="GL",I14="gb",I14="GB",I14="Gl",I14="Gb"),IF(N14=0,1,N14)*IF(O14=0,1,O14)*P14-Q14,0)))))),3))</f>
         <v/>
       </c>
       <c r="T14" s="1294">
@@ -12606,7 +12619,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="1294">
-        <f>IF(I15="","",ROUND(IF(OR(I15="m²",I15="m2"),J15*IF(K15=0,1,K15)*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="m³",I15="m3"),J15*K15*L15*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="ml",I15="ML"),J15*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="und",I15="UND"),IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(I15="kg",J15*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,0))))),3))</f>
+        <f>IF(I15="","",ROUND(IF(OR(I15="m²",I15="m2"),J15*IF(K15=0,1,K15)*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="m³",I15="m3"),J15*K15*L15*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="ml",I15="ML"),J15*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="und",I15="UND"),IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(I15="kg",J15*IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,IF(OR(I15="gl",I15="GL",I15="gb",I15="GB",I15="Gl",I15="Gb"),IF(N15=0,1,N15)*IF(O15=0,1,O15)*P15-Q15,0)))))),3))</f>
         <v/>
       </c>
       <c r="T15" s="1294">
@@ -12689,7 +12702,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="1294">
-        <f>IF(I16="","",ROUND(IF(OR(I16="m²",I16="m2"),J16*IF(K16=0,1,K16)*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="m³",I16="m3"),J16*K16*L16*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="ml",I16="ML"),J16*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="und",I16="UND"),IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(I16="kg",J16*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,0))))),3))</f>
+        <f>IF(I16="","",ROUND(IF(OR(I16="m²",I16="m2"),J16*IF(K16=0,1,K16)*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="m³",I16="m3"),J16*K16*L16*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="ml",I16="ML"),J16*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="und",I16="UND"),IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(I16="kg",J16*IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,IF(OR(I16="gl",I16="GL",I16="gb",I16="GB",I16="Gl",I16="Gb"),IF(N16=0,1,N16)*IF(O16=0,1,O16)*P16-Q16,0)))))),3))</f>
         <v/>
       </c>
       <c r="T16" s="1294">
@@ -12772,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="1294">
-        <f>IF(I17="","",ROUND(IF(OR(I17="m²",I17="m2"),J17*IF(K17=0,1,K17)*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="m³",I17="m3"),J17*K17*L17*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="ml",I17="ML"),J17*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="und",I17="UND"),IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(I17="kg",J17*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,0))))),3))</f>
+        <f>IF(I17="","",ROUND(IF(OR(I17="m²",I17="m2"),J17*IF(K17=0,1,K17)*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="m³",I17="m3"),J17*K17*L17*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="ml",I17="ML"),J17*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="und",I17="UND"),IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(I17="kg",J17*IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,IF(OR(I17="gl",I17="GL",I17="gb",I17="GB",I17="Gl",I17="Gb"),IF(N17=0,1,N17)*IF(O17=0,1,O17)*P17-Q17,0)))))),3))</f>
         <v/>
       </c>
       <c r="T17" s="1294">
@@ -12855,7 +12868,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="1294">
-        <f>IF(I18="","",ROUND(IF(OR(I18="m²",I18="m2"),J18*IF(K18=0,1,K18)*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="m³",I18="m3"),J18*K18*L18*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="ml",I18="ML"),J18*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="und",I18="UND"),IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(I18="kg",J18*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,0))))),3))</f>
+        <f>IF(I18="","",ROUND(IF(OR(I18="m²",I18="m2"),J18*IF(K18=0,1,K18)*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="m³",I18="m3"),J18*K18*L18*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="ml",I18="ML"),J18*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="und",I18="UND"),IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(I18="kg",J18*IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,IF(OR(I18="gl",I18="GL",I18="gb",I18="GB",I18="Gl",I18="Gb"),IF(N18=0,1,N18)*IF(O18=0,1,O18)*P18-Q18,0)))))),3))</f>
         <v/>
       </c>
       <c r="T18" s="1294">
@@ -12938,7 +12951,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="1294">
-        <f>IF(I19="","",ROUND(IF(OR(I19="m²",I19="m2"),J19*IF(K19=0,1,K19)*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="m³",I19="m3"),J19*K19*L19*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="ml",I19="ML"),J19*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="und",I19="UND"),IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(I19="kg",J19*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,0))))),3))</f>
+        <f>IF(I19="","",ROUND(IF(OR(I19="m²",I19="m2"),J19*IF(K19=0,1,K19)*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="m³",I19="m3"),J19*K19*L19*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="ml",I19="ML"),J19*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="und",I19="UND"),IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(I19="kg",J19*IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,IF(OR(I19="gl",I19="GL",I19="gb",I19="GB",I19="Gl",I19="Gb"),IF(N19=0,1,N19)*IF(O19=0,1,O19)*P19-Q19,0)))))),3))</f>
         <v/>
       </c>
       <c r="T19" s="1294">
@@ -13021,7 +13034,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="1294">
-        <f>IF(I20="","",ROUND(IF(OR(I20="m²",I20="m2"),J20*IF(K20=0,1,K20)*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="m³",I20="m3"),J20*K20*L20*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="ml",I20="ML"),J20*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="und",I20="UND"),IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(I20="kg",J20*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,0))))),3))</f>
+        <f>IF(I20="","",ROUND(IF(OR(I20="m²",I20="m2"),J20*IF(K20=0,1,K20)*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="m³",I20="m3"),J20*K20*L20*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="ml",I20="ML"),J20*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="und",I20="UND"),IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(I20="kg",J20*IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,IF(OR(I20="gl",I20="GL",I20="gb",I20="GB",I20="Gl",I20="Gb"),IF(N20=0,1,N20)*IF(O20=0,1,O20)*P20-Q20,0)))))),3))</f>
         <v/>
       </c>
       <c r="T20" s="1294">
@@ -13104,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="1294">
-        <f>IF(I21="","",ROUND(IF(OR(I21="m²",I21="m2"),J21*IF(K21=0,1,K21)*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="m³",I21="m3"),J21*K21*L21*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="ml",I21="ML"),J21*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="und",I21="UND"),IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(I21="kg",J21*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,0))))),3))</f>
+        <f>IF(I21="","",ROUND(IF(OR(I21="m²",I21="m2"),J21*IF(K21=0,1,K21)*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="m³",I21="m3"),J21*K21*L21*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="ml",I21="ML"),J21*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="und",I21="UND"),IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(I21="kg",J21*IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,IF(OR(I21="gl",I21="GL",I21="gb",I21="GB",I21="Gl",I21="Gb"),IF(N21=0,1,N21)*IF(O21=0,1,O21)*P21-Q21,0)))))),3))</f>
         <v/>
       </c>
       <c r="T21" s="1294">
@@ -13187,7 +13200,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="1294">
-        <f>IF(I22="","",ROUND(IF(OR(I22="m²",I22="m2"),J22*IF(K22=0,1,K22)*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="m³",I22="m3"),J22*K22*L22*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="ml",I22="ML"),J22*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="und",I22="UND"),IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(I22="kg",J22*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,0))))),3))</f>
+        <f>IF(I22="","",ROUND(IF(OR(I22="m²",I22="m2"),J22*IF(K22=0,1,K22)*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="m³",I22="m3"),J22*K22*L22*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="ml",I22="ML"),J22*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="und",I22="UND"),IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(I22="kg",J22*IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,IF(OR(I22="gl",I22="GL",I22="gb",I22="GB",I22="Gl",I22="Gb"),IF(N22=0,1,N22)*IF(O22=0,1,O22)*P22-Q22,0)))))),3))</f>
         <v/>
       </c>
       <c r="T22" s="1294">
@@ -13270,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="1294">
-        <f>IF(I23="","",ROUND(IF(OR(I23="m²",I23="m2"),J23*IF(K23=0,1,K23)*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="m³",I23="m3"),J23*K23*L23*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="ml",I23="ML"),J23*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="und",I23="UND"),IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(I23="kg",J23*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,0))))),3))</f>
+        <f>IF(I23="","",ROUND(IF(OR(I23="m²",I23="m2"),J23*IF(K23=0,1,K23)*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="m³",I23="m3"),J23*K23*L23*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="ml",I23="ML"),J23*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="und",I23="UND"),IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(I23="kg",J23*IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,IF(OR(I23="gl",I23="GL",I23="gb",I23="GB",I23="Gl",I23="Gb"),IF(N23=0,1,N23)*IF(O23=0,1,O23)*P23-Q23,0)))))),3))</f>
         <v/>
       </c>
       <c r="T23" s="1294">
@@ -13353,7 +13366,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="1294">
-        <f>IF(I24="","",ROUND(IF(OR(I24="m²",I24="m2"),J24*IF(K24=0,1,K24)*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="m³",I24="m3"),J24*K24*L24*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="ml",I24="ML"),J24*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="und",I24="UND"),IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(I24="kg",J24*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,0))))),3))</f>
+        <f>IF(I24="","",ROUND(IF(OR(I24="m²",I24="m2"),J24*IF(K24=0,1,K24)*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="m³",I24="m3"),J24*K24*L24*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="ml",I24="ML"),J24*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="und",I24="UND"),IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(I24="kg",J24*IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,IF(OR(I24="gl",I24="GL",I24="gb",I24="GB",I24="Gl",I24="Gb"),IF(N24=0,1,N24)*IF(O24=0,1,O24)*P24-Q24,0)))))),3))</f>
         <v/>
       </c>
       <c r="T24" s="1294">
@@ -13436,7 +13449,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="1294">
-        <f>IF(I25="","",ROUND(IF(OR(I25="m²",I25="m2"),J25*IF(K25=0,1,K25)*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="m³",I25="m3"),J25*K25*L25*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="ml",I25="ML"),J25*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="und",I25="UND"),IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(I25="kg",J25*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,0))))),3))</f>
+        <f>IF(I25="","",ROUND(IF(OR(I25="m²",I25="m2"),J25*IF(K25=0,1,K25)*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="m³",I25="m3"),J25*K25*L25*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="ml",I25="ML"),J25*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="und",I25="UND"),IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(I25="kg",J25*IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,IF(OR(I25="gl",I25="GL",I25="gb",I25="GB",I25="Gl",I25="Gb"),IF(N25=0,1,N25)*IF(O25=0,1,O25)*P25-Q25,0)))))),3))</f>
         <v/>
       </c>
       <c r="T25" s="1294">
@@ -13519,7 +13532,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="1294">
-        <f>IF(I26="","",ROUND(IF(OR(I26="m²",I26="m2"),J26*IF(K26=0,1,K26)*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="m³",I26="m3"),J26*K26*L26*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="ml",I26="ML"),J26*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="und",I26="UND"),IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(I26="kg",J26*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,0))))),3))</f>
+        <f>IF(I26="","",ROUND(IF(OR(I26="m²",I26="m2"),J26*IF(K26=0,1,K26)*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="m³",I26="m3"),J26*K26*L26*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="ml",I26="ML"),J26*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="und",I26="UND"),IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(I26="kg",J26*IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,IF(OR(I26="gl",I26="GL",I26="gb",I26="GB",I26="Gl",I26="Gb"),IF(N26=0,1,N26)*IF(O26=0,1,O26)*P26-Q26,0)))))),3))</f>
         <v/>
       </c>
       <c r="T26" s="1294">
@@ -13602,7 +13615,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="1294">
-        <f>IF(I27="","",ROUND(IF(OR(I27="m²",I27="m2"),J27*IF(K27=0,1,K27)*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="m³",I27="m3"),J27*K27*L27*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="ml",I27="ML"),J27*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="und",I27="UND"),IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(I27="kg",J27*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,0))))),3))</f>
+        <f>IF(I27="","",ROUND(IF(OR(I27="m²",I27="m2"),J27*IF(K27=0,1,K27)*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="m³",I27="m3"),J27*K27*L27*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="ml",I27="ML"),J27*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="und",I27="UND"),IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(I27="kg",J27*IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,IF(OR(I27="gl",I27="GL",I27="gb",I27="GB",I27="Gl",I27="Gb"),IF(N27=0,1,N27)*IF(O27=0,1,O27)*P27-Q27,0)))))),3))</f>
         <v/>
       </c>
       <c r="T27" s="1294">
@@ -13685,7 +13698,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="1294">
-        <f>IF(I28="","",ROUND(IF(OR(I28="m²",I28="m2"),J28*IF(K28=0,1,K28)*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="m³",I28="m3"),J28*K28*L28*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="ml",I28="ML"),J28*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="und",I28="UND"),IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(I28="kg",J28*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,0))))),3))</f>
+        <f>IF(I28="","",ROUND(IF(OR(I28="m²",I28="m2"),J28*IF(K28=0,1,K28)*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="m³",I28="m3"),J28*K28*L28*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="ml",I28="ML"),J28*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="und",I28="UND"),IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(I28="kg",J28*IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,IF(OR(I28="gl",I28="GL",I28="gb",I28="GB",I28="Gl",I28="Gb"),IF(N28=0,1,N28)*IF(O28=0,1,O28)*P28-Q28,0)))))),3))</f>
         <v/>
       </c>
       <c r="T28" s="1294">
@@ -13768,7 +13781,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="1294">
-        <f>IF(I29="","",ROUND(IF(OR(I29="m²",I29="m2"),J29*IF(K29=0,1,K29)*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="m³",I29="m3"),J29*K29*L29*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="ml",I29="ML"),J29*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="und",I29="UND"),IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(I29="kg",J29*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,0))))),3))</f>
+        <f>IF(I29="","",ROUND(IF(OR(I29="m²",I29="m2"),J29*IF(K29=0,1,K29)*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="m³",I29="m3"),J29*K29*L29*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="ml",I29="ML"),J29*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="und",I29="UND"),IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(I29="kg",J29*IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,IF(OR(I29="gl",I29="GL",I29="gb",I29="GB",I29="Gl",I29="Gb"),IF(N29=0,1,N29)*IF(O29=0,1,O29)*P29-Q29,0)))))),3))</f>
         <v/>
       </c>
       <c r="T29" s="1294">
@@ -13851,7 +13864,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="1294">
-        <f>IF(I30="","",ROUND(IF(OR(I30="m²",I30="m2"),J30*IF(K30=0,1,K30)*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="m³",I30="m3"),J30*K30*L30*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="ml",I30="ML"),J30*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="und",I30="UND"),IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(I30="kg",J30*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,0))))),3))</f>
+        <f>IF(I30="","",ROUND(IF(OR(I30="m²",I30="m2"),J30*IF(K30=0,1,K30)*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="m³",I30="m3"),J30*K30*L30*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="ml",I30="ML"),J30*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="und",I30="UND"),IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(I30="kg",J30*IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,IF(OR(I30="gl",I30="GL",I30="gb",I30="GB",I30="Gl",I30="Gb"),IF(N30=0,1,N30)*IF(O30=0,1,O30)*P30-Q30,0)))))),3))</f>
         <v/>
       </c>
       <c r="T30" s="1294">
@@ -13934,7 +13947,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="1294">
-        <f>IF(I31="","",ROUND(IF(OR(I31="m²",I31="m2"),J31*IF(K31=0,1,K31)*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="m³",I31="m3"),J31*K31*L31*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="ml",I31="ML"),J31*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="und",I31="UND"),IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(I31="kg",J31*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,0))))),3))</f>
+        <f>IF(I31="","",ROUND(IF(OR(I31="m²",I31="m2"),J31*IF(K31=0,1,K31)*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="m³",I31="m3"),J31*K31*L31*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="ml",I31="ML"),J31*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="und",I31="UND"),IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(I31="kg",J31*IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,IF(OR(I31="gl",I31="GL",I31="gb",I31="GB",I31="Gl",I31="Gb"),IF(N31=0,1,N31)*IF(O31=0,1,O31)*P31-Q31,0)))))),3))</f>
         <v/>
       </c>
       <c r="T31" s="1294">
@@ -14017,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="1294">
-        <f>IF(I32="","",ROUND(IF(OR(I32="m²",I32="m2"),J32*IF(K32=0,1,K32)*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="m³",I32="m3"),J32*K32*L32*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="ml",I32="ML"),J32*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="und",I32="UND"),IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(I32="kg",J32*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,0))))),3))</f>
+        <f>IF(I32="","",ROUND(IF(OR(I32="m²",I32="m2"),J32*IF(K32=0,1,K32)*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="m³",I32="m3"),J32*K32*L32*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="ml",I32="ML"),J32*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="und",I32="UND"),IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(I32="kg",J32*IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,IF(OR(I32="gl",I32="GL",I32="gb",I32="GB",I32="Gl",I32="Gb"),IF(N32=0,1,N32)*IF(O32=0,1,O32)*P32-Q32,0)))))),3))</f>
         <v/>
       </c>
       <c r="T32" s="1294">
@@ -14100,7 +14113,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="1294">
-        <f>IF(I33="","",ROUND(IF(OR(I33="m²",I33="m2"),J33*IF(K33=0,1,K33)*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="m³",I33="m3"),J33*K33*L33*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="ml",I33="ML"),J33*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="und",I33="UND"),IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(I33="kg",J33*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,0))))),3))</f>
+        <f>IF(I33="","",ROUND(IF(OR(I33="m²",I33="m2"),J33*IF(K33=0,1,K33)*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="m³",I33="m3"),J33*K33*L33*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="ml",I33="ML"),J33*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="und",I33="UND"),IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(I33="kg",J33*IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,IF(OR(I33="gl",I33="GL",I33="gb",I33="GB",I33="Gl",I33="Gb"),IF(N33=0,1,N33)*IF(O33=0,1,O33)*P33-Q33,0)))))),3))</f>
         <v/>
       </c>
       <c r="T33" s="1294">
@@ -14183,7 +14196,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="1294">
-        <f>IF(I34="","",ROUND(IF(OR(I34="m²",I34="m2"),J34*IF(K34=0,1,K34)*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="m³",I34="m3"),J34*K34*L34*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="ml",I34="ML"),J34*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="und",I34="UND"),IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(I34="kg",J34*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,0))))),3))</f>
+        <f>IF(I34="","",ROUND(IF(OR(I34="m²",I34="m2"),J34*IF(K34=0,1,K34)*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="m³",I34="m3"),J34*K34*L34*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="ml",I34="ML"),J34*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="und",I34="UND"),IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(I34="kg",J34*IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,IF(OR(I34="gl",I34="GL",I34="gb",I34="GB",I34="Gl",I34="Gb"),IF(N34=0,1,N34)*IF(O34=0,1,O34)*P34-Q34,0)))))),3))</f>
         <v/>
       </c>
       <c r="T34" s="1294">
@@ -14266,7 +14279,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="1294">
-        <f>IF(I35="","",ROUND(IF(OR(I35="m²",I35="m2"),J35*IF(K35=0,1,K35)*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="m³",I35="m3"),J35*K35*L35*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="ml",I35="ML"),J35*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="und",I35="UND"),IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(I35="kg",J35*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,0))))),3))</f>
+        <f>IF(I35="","",ROUND(IF(OR(I35="m²",I35="m2"),J35*IF(K35=0,1,K35)*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="m³",I35="m3"),J35*K35*L35*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="ml",I35="ML"),J35*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="und",I35="UND"),IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(I35="kg",J35*IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,IF(OR(I35="gl",I35="GL",I35="gb",I35="GB",I35="Gl",I35="Gb"),IF(N35=0,1,N35)*IF(O35=0,1,O35)*P35-Q35,0)))))),3))</f>
         <v/>
       </c>
       <c r="T35" s="1294">
@@ -14349,7 +14362,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="1294">
-        <f>IF(I36="","",ROUND(IF(OR(I36="m²",I36="m2"),J36*IF(K36=0,1,K36)*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="m³",I36="m3"),J36*K36*L36*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="ml",I36="ML"),J36*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="und",I36="UND"),IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(I36="kg",J36*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,0))))),3))</f>
+        <f>IF(I36="","",ROUND(IF(OR(I36="m²",I36="m2"),J36*IF(K36=0,1,K36)*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="m³",I36="m3"),J36*K36*L36*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="ml",I36="ML"),J36*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="und",I36="UND"),IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(I36="kg",J36*IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,IF(OR(I36="gl",I36="GL",I36="gb",I36="GB",I36="Gl",I36="Gb"),IF(N36=0,1,N36)*IF(O36=0,1,O36)*P36-Q36,0)))))),3))</f>
         <v/>
       </c>
       <c r="T36" s="1294">
@@ -14432,7 +14445,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="1294">
-        <f>IF(I37="","",ROUND(IF(OR(I37="m²",I37="m2"),J37*IF(K37=0,1,K37)*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="m³",I37="m3"),J37*K37*L37*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="ml",I37="ML"),J37*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="und",I37="UND"),IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(I37="kg",J37*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,0))))),3))</f>
+        <f>IF(I37="","",ROUND(IF(OR(I37="m²",I37="m2"),J37*IF(K37=0,1,K37)*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="m³",I37="m3"),J37*K37*L37*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="ml",I37="ML"),J37*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="und",I37="UND"),IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(I37="kg",J37*IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,IF(OR(I37="gl",I37="GL",I37="gb",I37="GB",I37="Gl",I37="Gb"),IF(N37=0,1,N37)*IF(O37=0,1,O37)*P37-Q37,0)))))),3))</f>
         <v/>
       </c>
       <c r="T37" s="1294">
@@ -14515,7 +14528,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="1294">
-        <f>IF(I38="","",ROUND(IF(OR(I38="m²",I38="m2"),J38*IF(K38=0,1,K38)*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="m³",I38="m3"),J38*K38*L38*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="ml",I38="ML"),J38*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="und",I38="UND"),IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(I38="kg",J38*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,0))))),3))</f>
+        <f>IF(I38="","",ROUND(IF(OR(I38="m²",I38="m2"),J38*IF(K38=0,1,K38)*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="m³",I38="m3"),J38*K38*L38*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="ml",I38="ML"),J38*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="und",I38="UND"),IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(I38="kg",J38*IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,IF(OR(I38="gl",I38="GL",I38="gb",I38="GB",I38="Gl",I38="Gb"),IF(N38=0,1,N38)*IF(O38=0,1,O38)*P38-Q38,0)))))),3))</f>
         <v/>
       </c>
       <c r="T38" s="1294">
@@ -14598,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="1294">
-        <f>IF(I39="","",ROUND(IF(OR(I39="m²",I39="m2"),J39*IF(K39=0,1,K39)*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="m³",I39="m3"),J39*K39*L39*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="ml",I39="ML"),J39*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="und",I39="UND"),IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(I39="kg",J39*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,0))))),3))</f>
+        <f>IF(I39="","",ROUND(IF(OR(I39="m²",I39="m2"),J39*IF(K39=0,1,K39)*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="m³",I39="m3"),J39*K39*L39*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="ml",I39="ML"),J39*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="und",I39="UND"),IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(I39="kg",J39*IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,IF(OR(I39="gl",I39="GL",I39="gb",I39="GB",I39="Gl",I39="Gb"),IF(N39=0,1,N39)*IF(O39=0,1,O39)*P39-Q39,0)))))),3))</f>
         <v/>
       </c>
       <c r="T39" s="1294">
@@ -14681,7 +14694,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="1294">
-        <f>IF(I40="","",ROUND(IF(OR(I40="m²",I40="m2"),J40*IF(K40=0,1,K40)*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="m³",I40="m3"),J40*K40*L40*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="ml",I40="ML"),J40*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="und",I40="UND"),IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(I40="kg",J40*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,0))))),3))</f>
+        <f>IF(I40="","",ROUND(IF(OR(I40="m²",I40="m2"),J40*IF(K40=0,1,K40)*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="m³",I40="m3"),J40*K40*L40*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="ml",I40="ML"),J40*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="und",I40="UND"),IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(I40="kg",J40*IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,IF(OR(I40="gl",I40="GL",I40="gb",I40="GB",I40="Gl",I40="Gb"),IF(N40=0,1,N40)*IF(O40=0,1,O40)*P40-Q40,0)))))),3))</f>
         <v/>
       </c>
       <c r="T40" s="1294">
@@ -14764,7 +14777,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="1294">
-        <f>IF(I41="","",ROUND(IF(OR(I41="m²",I41="m2"),J41*IF(K41=0,1,K41)*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="m³",I41="m3"),J41*K41*L41*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="ml",I41="ML"),J41*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="und",I41="UND"),IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(I41="kg",J41*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,0))))),3))</f>
+        <f>IF(I41="","",ROUND(IF(OR(I41="m²",I41="m2"),J41*IF(K41=0,1,K41)*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="m³",I41="m3"),J41*K41*L41*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="ml",I41="ML"),J41*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="und",I41="UND"),IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(I41="kg",J41*IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,IF(OR(I41="gl",I41="GL",I41="gb",I41="GB",I41="Gl",I41="Gb"),IF(N41=0,1,N41)*IF(O41=0,1,O41)*P41-Q41,0)))))),3))</f>
         <v/>
       </c>
       <c r="T41" s="1294">
@@ -14847,7 +14860,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="1294">
-        <f>IF(I42="","",ROUND(IF(OR(I42="m²",I42="m2"),J42*IF(K42=0,1,K42)*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="m³",I42="m3"),J42*K42*L42*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="ml",I42="ML"),J42*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="und",I42="UND"),IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(I42="kg",J42*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,0))))),3))</f>
+        <f>IF(I42="","",ROUND(IF(OR(I42="m²",I42="m2"),J42*IF(K42=0,1,K42)*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="m³",I42="m3"),J42*K42*L42*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="ml",I42="ML"),J42*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="und",I42="UND"),IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(I42="kg",J42*IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,IF(OR(I42="gl",I42="GL",I42="gb",I42="GB",I42="Gl",I42="Gb"),IF(N42=0,1,N42)*IF(O42=0,1,O42)*P42-Q42,0)))))),3))</f>
         <v/>
       </c>
       <c r="T42" s="1294">
@@ -14930,7 +14943,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="1294">
-        <f>IF(I43="","",ROUND(IF(OR(I43="m²",I43="m2"),J43*IF(K43=0,1,K43)*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="m³",I43="m3"),J43*K43*L43*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="ml",I43="ML"),J43*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="und",I43="UND"),IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(I43="kg",J43*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,0))))),3))</f>
+        <f>IF(I43="","",ROUND(IF(OR(I43="m²",I43="m2"),J43*IF(K43=0,1,K43)*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="m³",I43="m3"),J43*K43*L43*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="ml",I43="ML"),J43*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="und",I43="UND"),IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(I43="kg",J43*IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,IF(OR(I43="gl",I43="GL",I43="gb",I43="GB",I43="Gl",I43="Gb"),IF(N43=0,1,N43)*IF(O43=0,1,O43)*P43-Q43,0)))))),3))</f>
         <v/>
       </c>
       <c r="T43" s="1294">
@@ -15013,7 +15026,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="1294">
-        <f>IF(I44="","",ROUND(IF(OR(I44="m²",I44="m2"),J44*IF(K44=0,1,K44)*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="m³",I44="m3"),J44*K44*L44*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="ml",I44="ML"),J44*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="und",I44="UND"),IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(I44="kg",J44*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,0))))),3))</f>
+        <f>IF(I44="","",ROUND(IF(OR(I44="m²",I44="m2"),J44*IF(K44=0,1,K44)*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="m³",I44="m3"),J44*K44*L44*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="ml",I44="ML"),J44*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="und",I44="UND"),IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(I44="kg",J44*IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,IF(OR(I44="gl",I44="GL",I44="gb",I44="GB",I44="Gl",I44="Gb"),IF(N44=0,1,N44)*IF(O44=0,1,O44)*P44-Q44,0)))))),3))</f>
         <v/>
       </c>
       <c r="T44" s="1294">
@@ -15096,7 +15109,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="1294">
-        <f>IF(I45="","",ROUND(IF(OR(I45="m²",I45="m2"),J45*IF(K45=0,1,K45)*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="m³",I45="m3"),J45*K45*L45*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="ml",I45="ML"),J45*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="und",I45="UND"),IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(I45="kg",J45*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,0))))),3))</f>
+        <f>IF(I45="","",ROUND(IF(OR(I45="m²",I45="m2"),J45*IF(K45=0,1,K45)*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="m³",I45="m3"),J45*K45*L45*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="ml",I45="ML"),J45*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="und",I45="UND"),IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(I45="kg",J45*IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,IF(OR(I45="gl",I45="GL",I45="gb",I45="GB",I45="Gl",I45="Gb"),IF(N45=0,1,N45)*IF(O45=0,1,O45)*P45-Q45,0)))))),3))</f>
         <v/>
       </c>
       <c r="T45" s="1294">
@@ -15179,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="1294">
-        <f>IF(I46="","",ROUND(IF(OR(I46="m²",I46="m2"),J46*IF(K46=0,1,K46)*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="m³",I46="m3"),J46*K46*L46*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="ml",I46="ML"),J46*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="und",I46="UND"),IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(I46="kg",J46*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,0))))),3))</f>
+        <f>IF(I46="","",ROUND(IF(OR(I46="m²",I46="m2"),J46*IF(K46=0,1,K46)*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="m³",I46="m3"),J46*K46*L46*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="ml",I46="ML"),J46*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="und",I46="UND"),IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(I46="kg",J46*IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,IF(OR(I46="gl",I46="GL",I46="gb",I46="GB",I46="Gl",I46="Gb"),IF(N46=0,1,N46)*IF(O46=0,1,O46)*P46-Q46,0)))))),3))</f>
         <v/>
       </c>
       <c r="T46" s="1294">
@@ -15262,7 +15275,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="1294">
-        <f>IF(I47="","",ROUND(IF(OR(I47="m²",I47="m2"),J47*IF(K47=0,1,K47)*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="m³",I47="m3"),J47*K47*L47*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="ml",I47="ML"),J47*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="und",I47="UND"),IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(I47="kg",J47*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,0))))),3))</f>
+        <f>IF(I47="","",ROUND(IF(OR(I47="m²",I47="m2"),J47*IF(K47=0,1,K47)*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="m³",I47="m3"),J47*K47*L47*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="ml",I47="ML"),J47*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="und",I47="UND"),IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(I47="kg",J47*IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,IF(OR(I47="gl",I47="GL",I47="gb",I47="GB",I47="Gl",I47="Gb"),IF(N47=0,1,N47)*IF(O47=0,1,O47)*P47-Q47,0)))))),3))</f>
         <v/>
       </c>
       <c r="T47" s="1294">
@@ -15345,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="1294">
-        <f>IF(I48="","",ROUND(IF(OR(I48="m²",I48="m2"),J48*IF(K48=0,1,K48)*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="m³",I48="m3"),J48*K48*L48*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="ml",I48="ML"),J48*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="und",I48="UND"),IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(I48="kg",J48*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,0))))),3))</f>
+        <f>IF(I48="","",ROUND(IF(OR(I48="m²",I48="m2"),J48*IF(K48=0,1,K48)*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="m³",I48="m3"),J48*K48*L48*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="ml",I48="ML"),J48*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="und",I48="UND"),IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(I48="kg",J48*IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,IF(OR(I48="gl",I48="GL",I48="gb",I48="GB",I48="Gl",I48="Gb"),IF(N48=0,1,N48)*IF(O48=0,1,O48)*P48-Q48,0)))))),3))</f>
         <v/>
       </c>
       <c r="T48" s="1294">
@@ -15428,7 +15441,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="1294">
-        <f>IF(I49="","",ROUND(IF(OR(I49="m²",I49="m2"),J49*IF(K49=0,1,K49)*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="m³",I49="m3"),J49*K49*L49*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="ml",I49="ML"),J49*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="und",I49="UND"),IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(I49="kg",J49*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,0))))),3))</f>
+        <f>IF(I49="","",ROUND(IF(OR(I49="m²",I49="m2"),J49*IF(K49=0,1,K49)*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="m³",I49="m3"),J49*K49*L49*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="ml",I49="ML"),J49*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="und",I49="UND"),IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(I49="kg",J49*IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,IF(OR(I49="gl",I49="GL",I49="gb",I49="GB",I49="Gl",I49="Gb"),IF(N49=0,1,N49)*IF(O49=0,1,O49)*P49-Q49,0)))))),3))</f>
         <v/>
       </c>
       <c r="T49" s="1294">
@@ -15511,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="1294">
-        <f>IF(I50="","",ROUND(IF(OR(I50="m²",I50="m2"),J50*IF(K50=0,1,K50)*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="m³",I50="m3"),J50*K50*L50*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="ml",I50="ML"),J50*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="und",I50="UND"),IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(I50="kg",J50*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,0))))),3))</f>
+        <f>IF(I50="","",ROUND(IF(OR(I50="m²",I50="m2"),J50*IF(K50=0,1,K50)*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="m³",I50="m3"),J50*K50*L50*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="ml",I50="ML"),J50*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="und",I50="UND"),IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(I50="kg",J50*IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,IF(OR(I50="gl",I50="GL",I50="gb",I50="GB",I50="Gl",I50="Gb"),IF(N50=0,1,N50)*IF(O50=0,1,O50)*P50-Q50,0)))))),3))</f>
         <v/>
       </c>
       <c r="T50" s="1294">
@@ -15594,7 +15607,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="1294">
-        <f>IF(I51="","",ROUND(IF(OR(I51="m²",I51="m2"),J51*IF(K51=0,1,K51)*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="m³",I51="m3"),J51*K51*L51*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="ml",I51="ML"),J51*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="und",I51="UND"),IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(I51="kg",J51*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,0))))),3))</f>
+        <f>IF(I51="","",ROUND(IF(OR(I51="m²",I51="m2"),J51*IF(K51=0,1,K51)*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="m³",I51="m3"),J51*K51*L51*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="ml",I51="ML"),J51*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="und",I51="UND"),IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(I51="kg",J51*IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,IF(OR(I51="gl",I51="GL",I51="gb",I51="GB",I51="Gl",I51="Gb"),IF(N51=0,1,N51)*IF(O51=0,1,O51)*P51-Q51,0)))))),3))</f>
         <v/>
       </c>
       <c r="T51" s="1294">
@@ -15677,7 +15690,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="1294">
-        <f>IF(I52="","",ROUND(IF(OR(I52="m²",I52="m2"),J52*IF(K52=0,1,K52)*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="m³",I52="m3"),J52*K52*L52*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="ml",I52="ML"),J52*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="und",I52="UND"),IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(I52="kg",J52*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,0))))),3))</f>
+        <f>IF(I52="","",ROUND(IF(OR(I52="m²",I52="m2"),J52*IF(K52=0,1,K52)*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="m³",I52="m3"),J52*K52*L52*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="ml",I52="ML"),J52*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="und",I52="UND"),IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(I52="kg",J52*IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,IF(OR(I52="gl",I52="GL",I52="gb",I52="GB",I52="Gl",I52="Gb"),IF(N52=0,1,N52)*IF(O52=0,1,O52)*P52-Q52,0)))))),3))</f>
         <v/>
       </c>
       <c r="T52" s="1294">
@@ -15760,7 +15773,7 @@
         <v>0</v>
       </c>
       <c r="S53" s="1294">
-        <f>IF(I53="","",ROUND(IF(OR(I53="m²",I53="m2"),J53*IF(K53=0,1,K53)*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="m³",I53="m3"),J53*K53*L53*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="ml",I53="ML"),J53*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="und",I53="UND"),IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(I53="kg",J53*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,0))))),3))</f>
+        <f>IF(I53="","",ROUND(IF(OR(I53="m²",I53="m2"),J53*IF(K53=0,1,K53)*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="m³",I53="m3"),J53*K53*L53*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="ml",I53="ML"),J53*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="und",I53="UND"),IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(I53="kg",J53*IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,IF(OR(I53="gl",I53="GL",I53="gb",I53="GB",I53="Gl",I53="Gb"),IF(N53=0,1,N53)*IF(O53=0,1,O53)*P53-Q53,0)))))),3))</f>
         <v/>
       </c>
       <c r="T53" s="1294">
@@ -15843,7 +15856,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="1294">
-        <f>IF(I54="","",ROUND(IF(OR(I54="m²",I54="m2"),J54*IF(K54=0,1,K54)*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="m³",I54="m3"),J54*K54*L54*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="ml",I54="ML"),J54*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="und",I54="UND"),IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(I54="kg",J54*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,0))))),3))</f>
+        <f>IF(I54="","",ROUND(IF(OR(I54="m²",I54="m2"),J54*IF(K54=0,1,K54)*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="m³",I54="m3"),J54*K54*L54*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="ml",I54="ML"),J54*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="und",I54="UND"),IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(I54="kg",J54*IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,IF(OR(I54="gl",I54="GL",I54="gb",I54="GB",I54="Gl",I54="Gb"),IF(N54=0,1,N54)*IF(O54=0,1,O54)*P54-Q54,0)))))),3))</f>
         <v/>
       </c>
       <c r="T54" s="1294">
@@ -15926,7 +15939,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="1294">
-        <f>IF(I55="","",ROUND(IF(OR(I55="m²",I55="m2"),J55*IF(K55=0,1,K55)*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="m³",I55="m3"),J55*K55*L55*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="ml",I55="ML"),J55*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="und",I55="UND"),IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(I55="kg",J55*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,0))))),3))</f>
+        <f>IF(I55="","",ROUND(IF(OR(I55="m²",I55="m2"),J55*IF(K55=0,1,K55)*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="m³",I55="m3"),J55*K55*L55*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="ml",I55="ML"),J55*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="und",I55="UND"),IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(I55="kg",J55*IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,IF(OR(I55="gl",I55="GL",I55="gb",I55="GB",I55="Gl",I55="Gb"),IF(N55=0,1,N55)*IF(O55=0,1,O55)*P55-Q55,0)))))),3))</f>
         <v/>
       </c>
       <c r="T55" s="1294">
@@ -16009,7 +16022,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="1294">
-        <f>IF(I56="","",ROUND(IF(OR(I56="m²",I56="m2"),J56*IF(K56=0,1,K56)*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="m³",I56="m3"),J56*K56*L56*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="ml",I56="ML"),J56*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="und",I56="UND"),IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(I56="kg",J56*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,0))))),3))</f>
+        <f>IF(I56="","",ROUND(IF(OR(I56="m²",I56="m2"),J56*IF(K56=0,1,K56)*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="m³",I56="m3"),J56*K56*L56*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="ml",I56="ML"),J56*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="und",I56="UND"),IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(I56="kg",J56*IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,IF(OR(I56="gl",I56="GL",I56="gb",I56="GB",I56="Gl",I56="Gb"),IF(N56=0,1,N56)*IF(O56=0,1,O56)*P56-Q56,0)))))),3))</f>
         <v/>
       </c>
       <c r="T56" s="1294">
@@ -16092,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="1294">
-        <f>IF(I57="","",ROUND(IF(OR(I57="m²",I57="m2"),J57*IF(K57=0,1,K57)*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="m³",I57="m3"),J57*K57*L57*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="ml",I57="ML"),J57*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="und",I57="UND"),IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(I57="kg",J57*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,0))))),3))</f>
+        <f>IF(I57="","",ROUND(IF(OR(I57="m²",I57="m2"),J57*IF(K57=0,1,K57)*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="m³",I57="m3"),J57*K57*L57*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="ml",I57="ML"),J57*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="und",I57="UND"),IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(I57="kg",J57*IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,IF(OR(I57="gl",I57="GL",I57="gb",I57="GB",I57="Gl",I57="Gb"),IF(N57=0,1,N57)*IF(O57=0,1,O57)*P57-Q57,0)))))),3))</f>
         <v/>
       </c>
       <c r="T57" s="1294">
@@ -16175,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="1294">
-        <f>IF(I58="","",ROUND(IF(OR(I58="m²",I58="m2"),J58*IF(K58=0,1,K58)*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="m³",I58="m3"),J58*K58*L58*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="ml",I58="ML"),J58*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="und",I58="UND"),IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(I58="kg",J58*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,0))))),3))</f>
+        <f>IF(I58="","",ROUND(IF(OR(I58="m²",I58="m2"),J58*IF(K58=0,1,K58)*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="m³",I58="m3"),J58*K58*L58*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="ml",I58="ML"),J58*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="und",I58="UND"),IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(I58="kg",J58*IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,IF(OR(I58="gl",I58="GL",I58="gb",I58="GB",I58="Gl",I58="Gb"),IF(N58=0,1,N58)*IF(O58=0,1,O58)*P58-Q58,0)))))),3))</f>
         <v/>
       </c>
       <c r="T58" s="1294">
@@ -16258,7 +16271,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="1294">
-        <f>IF(I59="","",ROUND(IF(OR(I59="m²",I59="m2"),J59*IF(K59=0,1,K59)*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="m³",I59="m3"),J59*K59*L59*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="ml",I59="ML"),J59*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="und",I59="UND"),IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(I59="kg",J59*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,0))))),3))</f>
+        <f>IF(I59="","",ROUND(IF(OR(I59="m²",I59="m2"),J59*IF(K59=0,1,K59)*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="m³",I59="m3"),J59*K59*L59*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="ml",I59="ML"),J59*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="und",I59="UND"),IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(I59="kg",J59*IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,IF(OR(I59="gl",I59="GL",I59="gb",I59="GB",I59="Gl",I59="Gb"),IF(N59=0,1,N59)*IF(O59=0,1,O59)*P59-Q59,0)))))),3))</f>
         <v/>
       </c>
       <c r="T59" s="1294">
@@ -16341,7 +16354,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="1294">
-        <f>IF(I60="","",ROUND(IF(OR(I60="m²",I60="m2"),J60*IF(K60=0,1,K60)*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="m³",I60="m3"),J60*K60*L60*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="ml",I60="ML"),J60*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="und",I60="UND"),IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(I60="kg",J60*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,0))))),3))</f>
+        <f>IF(I60="","",ROUND(IF(OR(I60="m²",I60="m2"),J60*IF(K60=0,1,K60)*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="m³",I60="m3"),J60*K60*L60*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="ml",I60="ML"),J60*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="und",I60="UND"),IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(I60="kg",J60*IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,IF(OR(I60="gl",I60="GL",I60="gb",I60="GB",I60="Gl",I60="Gb"),IF(N60=0,1,N60)*IF(O60=0,1,O60)*P60-Q60,0)))))),3))</f>
         <v/>
       </c>
       <c r="T60" s="1294">
@@ -16424,7 +16437,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="1294">
-        <f>IF(I61="","",ROUND(IF(OR(I61="m²",I61="m2"),J61*IF(K61=0,1,K61)*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="m³",I61="m3"),J61*K61*L61*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="ml",I61="ML"),J61*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="und",I61="UND"),IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(I61="kg",J61*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,0))))),3))</f>
+        <f>IF(I61="","",ROUND(IF(OR(I61="m²",I61="m2"),J61*IF(K61=0,1,K61)*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="m³",I61="m3"),J61*K61*L61*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="ml",I61="ML"),J61*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="und",I61="UND"),IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(I61="kg",J61*IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,IF(OR(I61="gl",I61="GL",I61="gb",I61="GB",I61="Gl",I61="Gb"),IF(N61=0,1,N61)*IF(O61=0,1,O61)*P61-Q61,0)))))),3))</f>
         <v/>
       </c>
       <c r="T61" s="1294">
@@ -16507,7 +16520,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="1294">
-        <f>IF(I62="","",ROUND(IF(OR(I62="m²",I62="m2"),J62*IF(K62=0,1,K62)*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="m³",I62="m3"),J62*K62*L62*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="ml",I62="ML"),J62*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="und",I62="UND"),IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(I62="kg",J62*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,0))))),3))</f>
+        <f>IF(I62="","",ROUND(IF(OR(I62="m²",I62="m2"),J62*IF(K62=0,1,K62)*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="m³",I62="m3"),J62*K62*L62*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="ml",I62="ML"),J62*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="und",I62="UND"),IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(I62="kg",J62*IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,IF(OR(I62="gl",I62="GL",I62="gb",I62="GB",I62="Gl",I62="Gb"),IF(N62=0,1,N62)*IF(O62=0,1,O62)*P62-Q62,0)))))),3))</f>
         <v/>
       </c>
       <c r="T62" s="1294">
@@ -16590,7 +16603,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="1294">
-        <f>IF(I63="","",ROUND(IF(OR(I63="m²",I63="m2"),J63*IF(K63=0,1,K63)*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="m³",I63="m3"),J63*K63*L63*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="ml",I63="ML"),J63*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="und",I63="UND"),IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(I63="kg",J63*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,0))))),3))</f>
+        <f>IF(I63="","",ROUND(IF(OR(I63="m²",I63="m2"),J63*IF(K63=0,1,K63)*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="m³",I63="m3"),J63*K63*L63*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="ml",I63="ML"),J63*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="und",I63="UND"),IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(I63="kg",J63*IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,IF(OR(I63="gl",I63="GL",I63="gb",I63="GB",I63="Gl",I63="Gb"),IF(N63=0,1,N63)*IF(O63=0,1,O63)*P63-Q63,0)))))),3))</f>
         <v/>
       </c>
       <c r="T63" s="1294">
@@ -16673,7 +16686,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="1294">
-        <f>IF(I64="","",ROUND(IF(OR(I64="m²",I64="m2"),J64*IF(K64=0,1,K64)*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="m³",I64="m3"),J64*K64*L64*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="ml",I64="ML"),J64*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="und",I64="UND"),IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(I64="kg",J64*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,0))))),3))</f>
+        <f>IF(I64="","",ROUND(IF(OR(I64="m²",I64="m2"),J64*IF(K64=0,1,K64)*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="m³",I64="m3"),J64*K64*L64*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="ml",I64="ML"),J64*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="und",I64="UND"),IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(I64="kg",J64*IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,IF(OR(I64="gl",I64="GL",I64="gb",I64="GB",I64="Gl",I64="Gb"),IF(N64=0,1,N64)*IF(O64=0,1,O64)*P64-Q64,0)))))),3))</f>
         <v/>
       </c>
       <c r="T64" s="1294">
@@ -16756,7 +16769,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="1294">
-        <f>IF(I65="","",ROUND(IF(OR(I65="m²",I65="m2"),J65*IF(K65=0,1,K65)*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="m³",I65="m3"),J65*K65*L65*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="ml",I65="ML"),J65*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="und",I65="UND"),IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(I65="kg",J65*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,0))))),3))</f>
+        <f>IF(I65="","",ROUND(IF(OR(I65="m²",I65="m2"),J65*IF(K65=0,1,K65)*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="m³",I65="m3"),J65*K65*L65*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="ml",I65="ML"),J65*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="und",I65="UND"),IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(I65="kg",J65*IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,IF(OR(I65="gl",I65="GL",I65="gb",I65="GB",I65="Gl",I65="Gb"),IF(N65=0,1,N65)*IF(O65=0,1,O65)*P65-Q65,0)))))),3))</f>
         <v/>
       </c>
       <c r="T65" s="1294">
@@ -16839,7 +16852,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="1294">
-        <f>IF(I66="","",ROUND(IF(OR(I66="m²",I66="m2"),J66*IF(K66=0,1,K66)*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="m³",I66="m3"),J66*K66*L66*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="ml",I66="ML"),J66*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="und",I66="UND"),IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(I66="kg",J66*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,0))))),3))</f>
+        <f>IF(I66="","",ROUND(IF(OR(I66="m²",I66="m2"),J66*IF(K66=0,1,K66)*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="m³",I66="m3"),J66*K66*L66*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="ml",I66="ML"),J66*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="und",I66="UND"),IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(I66="kg",J66*IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,IF(OR(I66="gl",I66="GL",I66="gb",I66="GB",I66="Gl",I66="Gb"),IF(N66=0,1,N66)*IF(O66=0,1,O66)*P66-Q66,0)))))),3))</f>
         <v/>
       </c>
       <c r="T66" s="1294">
@@ -16922,7 +16935,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="1294">
-        <f>IF(I67="","",ROUND(IF(OR(I67="m²",I67="m2"),J67*IF(K67=0,1,K67)*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="m³",I67="m3"),J67*K67*L67*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="ml",I67="ML"),J67*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="und",I67="UND"),IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(I67="kg",J67*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,0))))),3))</f>
+        <f>IF(I67="","",ROUND(IF(OR(I67="m²",I67="m2"),J67*IF(K67=0,1,K67)*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="m³",I67="m3"),J67*K67*L67*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="ml",I67="ML"),J67*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="und",I67="UND"),IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(I67="kg",J67*IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,IF(OR(I67="gl",I67="GL",I67="gb",I67="GB",I67="Gl",I67="Gb"),IF(N67=0,1,N67)*IF(O67=0,1,O67)*P67-Q67,0)))))),3))</f>
         <v/>
       </c>
       <c r="T67" s="1294">
@@ -17005,7 +17018,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="1294">
-        <f>IF(I68="","",ROUND(IF(OR(I68="m²",I68="m2"),J68*IF(K68=0,1,K68)*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="m³",I68="m3"),J68*K68*L68*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="ml",I68="ML"),J68*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="und",I68="UND"),IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(I68="kg",J68*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,0))))),3))</f>
+        <f>IF(I68="","",ROUND(IF(OR(I68="m²",I68="m2"),J68*IF(K68=0,1,K68)*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="m³",I68="m3"),J68*K68*L68*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="ml",I68="ML"),J68*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="und",I68="UND"),IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(I68="kg",J68*IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,IF(OR(I68="gl",I68="GL",I68="gb",I68="GB",I68="Gl",I68="Gb"),IF(N68=0,1,N68)*IF(O68=0,1,O68)*P68-Q68,0)))))),3))</f>
         <v/>
       </c>
       <c r="T68" s="1294">
@@ -17088,7 +17101,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="1294">
-        <f>IF(I69="","",ROUND(IF(OR(I69="m²",I69="m2"),J69*IF(K69=0,1,K69)*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="m³",I69="m3"),J69*K69*L69*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="ml",I69="ML"),J69*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="und",I69="UND"),IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(I69="kg",J69*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,0))))),3))</f>
+        <f>IF(I69="","",ROUND(IF(OR(I69="m²",I69="m2"),J69*IF(K69=0,1,K69)*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="m³",I69="m3"),J69*K69*L69*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="ml",I69="ML"),J69*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="und",I69="UND"),IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(I69="kg",J69*IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,IF(OR(I69="gl",I69="GL",I69="gb",I69="GB",I69="Gl",I69="Gb"),IF(N69=0,1,N69)*IF(O69=0,1,O69)*P69-Q69,0)))))),3))</f>
         <v/>
       </c>
       <c r="T69" s="1294">
@@ -17171,7 +17184,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="1294">
-        <f>IF(I70="","",ROUND(IF(OR(I70="m²",I70="m2"),J70*IF(K70=0,1,K70)*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="m³",I70="m3"),J70*K70*L70*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="ml",I70="ML"),J70*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="und",I70="UND"),IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(I70="kg",J70*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,0))))),3))</f>
+        <f>IF(I70="","",ROUND(IF(OR(I70="m²",I70="m2"),J70*IF(K70=0,1,K70)*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="m³",I70="m3"),J70*K70*L70*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="ml",I70="ML"),J70*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="und",I70="UND"),IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(I70="kg",J70*IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,IF(OR(I70="gl",I70="GL",I70="gb",I70="GB",I70="Gl",I70="Gb"),IF(N70=0,1,N70)*IF(O70=0,1,O70)*P70-Q70,0)))))),3))</f>
         <v/>
       </c>
       <c r="T70" s="1294">
@@ -17254,7 +17267,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="1294">
-        <f>IF(I71="","",ROUND(IF(OR(I71="m²",I71="m2"),J71*IF(K71=0,1,K71)*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="m³",I71="m3"),J71*K71*L71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="ml",I71="ML"),J71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="und",I71="UND"),IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(I71="kg",J71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,0))))),3))</f>
+        <f>IF(I71="","",ROUND(IF(OR(I71="m²",I71="m2"),J71*IF(K71=0,1,K71)*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="m³",I71="m3"),J71*K71*L71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="ml",I71="ML"),J71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="und",I71="UND"),IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(I71="kg",J71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="gl",I71="GL",I71="gb",I71="GB",I71="Gl",I71="Gb"),IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,0)))))),3))</f>
         <v/>
       </c>
       <c r="T71" s="1294">
@@ -17337,7 +17350,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="1294">
-        <f>IF(I72="","",ROUND(IF(OR(I72="m²",I72="m2"),J72*IF(K72=0,1,K72)*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="m³",I72="m3"),J72*K72*L72*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="ml",I72="ML"),J72*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="und",I72="UND"),IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(I72="kg",J72*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,0))))),3))</f>
+        <f>IF(I72="","",ROUND(IF(OR(I72="m²",I72="m2"),J72*IF(K72=0,1,K72)*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="m³",I72="m3"),J72*K72*L72*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="ml",I72="ML"),J72*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="und",I72="UND"),IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(I72="kg",J72*IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,IF(OR(I72="gl",I72="GL",I72="gb",I72="GB",I72="Gl",I72="Gb"),IF(N72=0,1,N72)*IF(O72=0,1,O72)*P72-Q72,0)))))),3))</f>
         <v/>
       </c>
       <c r="T72" s="1294">
@@ -17420,7 +17433,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="1294">
-        <f>IF(I73="","",ROUND(IF(OR(I73="m²",I73="m2"),J73*IF(K73=0,1,K73)*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="m³",I73="m3"),J73*K73*L73*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="ml",I73="ML"),J73*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="und",I73="UND"),IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(I73="kg",J73*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,0))))),3))</f>
+        <f>IF(I73="","",ROUND(IF(OR(I73="m²",I73="m2"),J73*IF(K73=0,1,K73)*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="m³",I73="m3"),J73*K73*L73*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="ml",I73="ML"),J73*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="und",I73="UND"),IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(I73="kg",J73*IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,IF(OR(I73="gl",I73="GL",I73="gb",I73="GB",I73="Gl",I73="Gb"),IF(N73=0,1,N73)*IF(O73=0,1,O73)*P73-Q73,0)))))),3))</f>
         <v/>
       </c>
       <c r="T73" s="1294">
@@ -17503,7 +17516,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="1294">
-        <f>IF(I74="","",ROUND(IF(OR(I74="m²",I74="m2"),J74*IF(K74=0,1,K74)*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="m³",I74="m3"),J74*K74*L74*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="ml",I74="ML"),J74*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="und",I74="UND"),IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(I74="kg",J74*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,0))))),3))</f>
+        <f>IF(I74="","",ROUND(IF(OR(I74="m²",I74="m2"),J74*IF(K74=0,1,K74)*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="m³",I74="m3"),J74*K74*L74*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="ml",I74="ML"),J74*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="und",I74="UND"),IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(I74="kg",J74*IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,IF(OR(I74="gl",I74="GL",I74="gb",I74="GB",I74="Gl",I74="Gb"),IF(N74=0,1,N74)*IF(O74=0,1,O74)*P74-Q74,0)))))),3))</f>
         <v/>
       </c>
       <c r="T74" s="1294">
@@ -17586,7 +17599,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="1294">
-        <f>IF(I75="","",ROUND(IF(OR(I75="m²",I75="m2"),J75*IF(K75=0,1,K75)*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="m³",I75="m3"),J75*K75*L75*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="ml",I75="ML"),J75*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="und",I75="UND"),IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(I75="kg",J75*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,0))))),3))</f>
+        <f>IF(I75="","",ROUND(IF(OR(I75="m²",I75="m2"),J75*IF(K75=0,1,K75)*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="m³",I75="m3"),J75*K75*L75*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="ml",I75="ML"),J75*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="und",I75="UND"),IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(I75="kg",J75*IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,IF(OR(I75="gl",I75="GL",I75="gb",I75="GB",I75="Gl",I75="Gb"),IF(N75=0,1,N75)*IF(O75=0,1,O75)*P75-Q75,0)))))),3))</f>
         <v/>
       </c>
       <c r="T75" s="1294">
@@ -17669,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="1294">
-        <f>IF(I76="","",ROUND(IF(OR(I76="m²",I76="m2"),J76*IF(K76=0,1,K76)*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="m³",I76="m3"),J76*K76*L76*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="ml",I76="ML"),J76*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="und",I76="UND"),IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(I76="kg",J76*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,0))))),3))</f>
+        <f>IF(I76="","",ROUND(IF(OR(I76="m²",I76="m2"),J76*IF(K76=0,1,K76)*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="m³",I76="m3"),J76*K76*L76*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="ml",I76="ML"),J76*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="und",I76="UND"),IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(I76="kg",J76*IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,IF(OR(I76="gl",I76="GL",I76="gb",I76="GB",I76="Gl",I76="Gb"),IF(N76=0,1,N76)*IF(O76=0,1,O76)*P76-Q76,0)))))),3))</f>
         <v/>
       </c>
       <c r="T76" s="1294">
@@ -17752,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="1294">
-        <f>IF(I77="","",ROUND(IF(OR(I77="m²",I77="m2"),J77*IF(K77=0,1,K77)*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="m³",I77="m3"),J77*K77*L77*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="ml",I77="ML"),J77*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="und",I77="UND"),IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(I77="kg",J77*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,0))))),3))</f>
+        <f>IF(I77="","",ROUND(IF(OR(I77="m²",I77="m2"),J77*IF(K77=0,1,K77)*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="m³",I77="m3"),J77*K77*L77*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="ml",I77="ML"),J77*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="und",I77="UND"),IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(I77="kg",J77*IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,IF(OR(I77="gl",I77="GL",I77="gb",I77="GB",I77="Gl",I77="Gb"),IF(N77=0,1,N77)*IF(O77=0,1,O77)*P77-Q77,0)))))),3))</f>
         <v/>
       </c>
       <c r="T77" s="1294">
@@ -17835,7 +17848,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="1294">
-        <f>IF(I78="","",ROUND(IF(OR(I78="m²",I78="m2"),J78*IF(K78=0,1,K78)*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="m³",I78="m3"),J78*K78*L78*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="ml",I78="ML"),J78*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="und",I78="UND"),IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(I78="kg",J78*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,0))))),3))</f>
+        <f>IF(I78="","",ROUND(IF(OR(I78="m²",I78="m2"),J78*IF(K78=0,1,K78)*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="m³",I78="m3"),J78*K78*L78*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="ml",I78="ML"),J78*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="und",I78="UND"),IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(I78="kg",J78*IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,IF(OR(I78="gl",I78="GL",I78="gb",I78="GB",I78="Gl",I78="Gb"),IF(N78=0,1,N78)*IF(O78=0,1,O78)*P78-Q78,0)))))),3))</f>
         <v/>
       </c>
       <c r="T78" s="1294">
@@ -17918,7 +17931,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="1294">
-        <f>IF(I79="","",ROUND(IF(OR(I79="m²",I79="m2"),J79*IF(K79=0,1,K79)*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="m³",I79="m3"),J79*K79*L79*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="ml",I79="ML"),J79*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="und",I79="UND"),IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(I79="kg",J79*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,0))))),3))</f>
+        <f>IF(I79="","",ROUND(IF(OR(I79="m²",I79="m2"),J79*IF(K79=0,1,K79)*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="m³",I79="m3"),J79*K79*L79*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="ml",I79="ML"),J79*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="und",I79="UND"),IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(I79="kg",J79*IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,IF(OR(I79="gl",I79="GL",I79="gb",I79="GB",I79="Gl",I79="Gb"),IF(N79=0,1,N79)*IF(O79=0,1,O79)*P79-Q79,0)))))),3))</f>
         <v/>
       </c>
       <c r="T79" s="1294">
@@ -18001,7 +18014,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="1294">
-        <f>IF(I80="","",ROUND(IF(OR(I80="m²",I80="m2"),J80*IF(K80=0,1,K80)*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="m³",I80="m3"),J80*K80*L80*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="ml",I80="ML"),J80*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="und",I80="UND"),IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(I80="kg",J80*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,0))))),3))</f>
+        <f>IF(I80="","",ROUND(IF(OR(I80="m²",I80="m2"),J80*IF(K80=0,1,K80)*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="m³",I80="m3"),J80*K80*L80*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="ml",I80="ML"),J80*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="und",I80="UND"),IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(I80="kg",J80*IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,IF(OR(I80="gl",I80="GL",I80="gb",I80="GB",I80="Gl",I80="Gb"),IF(N80=0,1,N80)*IF(O80=0,1,O80)*P80-Q80,0)))))),3))</f>
         <v/>
       </c>
       <c r="T80" s="1294">
@@ -18084,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="1294">
-        <f>IF(I81="","",ROUND(IF(OR(I81="m²",I81="m2"),J81*IF(K81=0,1,K81)*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="m³",I81="m3"),J81*K81*L81*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="ml",I81="ML"),J81*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="und",I81="UND"),IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(I81="kg",J81*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,0))))),3))</f>
+        <f>IF(I81="","",ROUND(IF(OR(I81="m²",I81="m2"),J81*IF(K81=0,1,K81)*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="m³",I81="m3"),J81*K81*L81*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="ml",I81="ML"),J81*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="und",I81="UND"),IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(I81="kg",J81*IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,IF(OR(I81="gl",I81="GL",I81="gb",I81="GB",I81="Gl",I81="Gb"),IF(N81=0,1,N81)*IF(O81=0,1,O81)*P81-Q81,0)))))),3))</f>
         <v/>
       </c>
       <c r="T81" s="1294">
@@ -18167,7 +18180,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="1294">
-        <f>IF(I82="","",ROUND(IF(OR(I82="m²",I82="m2"),J82*IF(K82=0,1,K82)*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="m³",I82="m3"),J82*K82*L82*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="ml",I82="ML"),J82*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="und",I82="UND"),IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(I82="kg",J82*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,0))))),3))</f>
+        <f>IF(I82="","",ROUND(IF(OR(I82="m²",I82="m2"),J82*IF(K82=0,1,K82)*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="m³",I82="m3"),J82*K82*L82*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="ml",I82="ML"),J82*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="und",I82="UND"),IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(I82="kg",J82*IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,IF(OR(I82="gl",I82="GL",I82="gb",I82="GB",I82="Gl",I82="Gb"),IF(N82=0,1,N82)*IF(O82=0,1,O82)*P82-Q82,0)))))),3))</f>
         <v/>
       </c>
       <c r="T82" s="1294">
@@ -18250,7 +18263,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="1294">
-        <f>IF(I83="","",ROUND(IF(OR(I83="m²",I83="m2"),J83*IF(K83=0,1,K83)*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="m³",I83="m3"),J83*K83*L83*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="ml",I83="ML"),J83*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="und",I83="UND"),IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(I83="kg",J83*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,0))))),3))</f>
+        <f>IF(I83="","",ROUND(IF(OR(I83="m²",I83="m2"),J83*IF(K83=0,1,K83)*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="m³",I83="m3"),J83*K83*L83*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="ml",I83="ML"),J83*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="und",I83="UND"),IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(I83="kg",J83*IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,IF(OR(I83="gl",I83="GL",I83="gb",I83="GB",I83="Gl",I83="Gb"),IF(N83=0,1,N83)*IF(O83=0,1,O83)*P83-Q83,0)))))),3))</f>
         <v/>
       </c>
       <c r="T83" s="1294">
@@ -18333,7 +18346,7 @@
         <v>0</v>
       </c>
       <c r="S84" s="1294">
-        <f>IF(I84="","",ROUND(IF(OR(I84="m²",I84="m2"),J84*IF(K84=0,1,K84)*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="m³",I84="m3"),J84*K84*L84*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="ml",I84="ML"),J84*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="und",I84="UND"),IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(I84="kg",J84*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,0))))),3))</f>
+        <f>IF(I84="","",ROUND(IF(OR(I84="m²",I84="m2"),J84*IF(K84=0,1,K84)*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="m³",I84="m3"),J84*K84*L84*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="ml",I84="ML"),J84*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="und",I84="UND"),IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(I84="kg",J84*IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,IF(OR(I84="gl",I84="GL",I84="gb",I84="GB",I84="Gl",I84="Gb"),IF(N84=0,1,N84)*IF(O84=0,1,O84)*P84-Q84,0)))))),3))</f>
         <v/>
       </c>
       <c r="T84" s="1294">
@@ -18416,7 +18429,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="1294">
-        <f>IF(I85="","",ROUND(IF(OR(I85="m²",I85="m2"),J85*IF(K85=0,1,K85)*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="m³",I85="m3"),J85*K85*L85*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="ml",I85="ML"),J85*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="und",I85="UND"),IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(I85="kg",J85*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,0))))),3))</f>
+        <f>IF(I85="","",ROUND(IF(OR(I85="m²",I85="m2"),J85*IF(K85=0,1,K85)*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="m³",I85="m3"),J85*K85*L85*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="ml",I85="ML"),J85*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="und",I85="UND"),IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(I85="kg",J85*IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,IF(OR(I85="gl",I85="GL",I85="gb",I85="GB",I85="Gl",I85="Gb"),IF(N85=0,1,N85)*IF(O85=0,1,O85)*P85-Q85,0)))))),3))</f>
         <v/>
       </c>
       <c r="T85" s="1294">
@@ -18499,7 +18512,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="1294">
-        <f>IF(I86="","",ROUND(IF(OR(I86="m²",I86="m2"),J86*IF(K86=0,1,K86)*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="m³",I86="m3"),J86*K86*L86*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="ml",I86="ML"),J86*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="und",I86="UND"),IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(I86="kg",J86*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,0))))),3))</f>
+        <f>IF(I86="","",ROUND(IF(OR(I86="m²",I86="m2"),J86*IF(K86=0,1,K86)*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="m³",I86="m3"),J86*K86*L86*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="ml",I86="ML"),J86*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="und",I86="UND"),IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(I86="kg",J86*IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,IF(OR(I86="gl",I86="GL",I86="gb",I86="GB",I86="Gl",I86="Gb"),IF(N86=0,1,N86)*IF(O86=0,1,O86)*P86-Q86,0)))))),3))</f>
         <v/>
       </c>
       <c r="T86" s="1294">
@@ -18582,7 +18595,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="1294">
-        <f>IF(I87="","",ROUND(IF(OR(I87="m²",I87="m2"),J87*IF(K87=0,1,K87)*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="m³",I87="m3"),J87*K87*L87*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="ml",I87="ML"),J87*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="und",I87="UND"),IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(I87="kg",J87*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,0))))),3))</f>
+        <f>IF(I87="","",ROUND(IF(OR(I87="m²",I87="m2"),J87*IF(K87=0,1,K87)*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="m³",I87="m3"),J87*K87*L87*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="ml",I87="ML"),J87*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="und",I87="UND"),IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(I87="kg",J87*IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,IF(OR(I87="gl",I87="GL",I87="gb",I87="GB",I87="Gl",I87="Gb"),IF(N87=0,1,N87)*IF(O87=0,1,O87)*P87-Q87,0)))))),3))</f>
         <v/>
       </c>
       <c r="T87" s="1294">
@@ -18665,7 +18678,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="1294">
-        <f>IF(I88="","",ROUND(IF(OR(I88="m²",I88="m2"),J88*IF(K88=0,1,K88)*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="m³",I88="m3"),J88*K88*L88*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="ml",I88="ML"),J88*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="und",I88="UND"),IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(I88="kg",J88*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,0))))),3))</f>
+        <f>IF(I88="","",ROUND(IF(OR(I88="m²",I88="m2"),J88*IF(K88=0,1,K88)*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="m³",I88="m3"),J88*K88*L88*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="ml",I88="ML"),J88*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="und",I88="UND"),IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(I88="kg",J88*IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,IF(OR(I88="gl",I88="GL",I88="gb",I88="GB",I88="Gl",I88="Gb"),IF(N88=0,1,N88)*IF(O88=0,1,O88)*P88-Q88,0)))))),3))</f>
         <v/>
       </c>
       <c r="T88" s="1294">
@@ -18748,7 +18761,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="1294">
-        <f>IF(I89="","",ROUND(IF(OR(I89="m²",I89="m2"),J89*IF(K89=0,1,K89)*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="m³",I89="m3"),J89*K89*L89*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="ml",I89="ML"),J89*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="und",I89="UND"),IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(I89="kg",J89*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,0))))),3))</f>
+        <f>IF(I89="","",ROUND(IF(OR(I89="m²",I89="m2"),J89*IF(K89=0,1,K89)*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="m³",I89="m3"),J89*K89*L89*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="ml",I89="ML"),J89*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="und",I89="UND"),IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(I89="kg",J89*IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,IF(OR(I89="gl",I89="GL",I89="gb",I89="GB",I89="Gl",I89="Gb"),IF(N89=0,1,N89)*IF(O89=0,1,O89)*P89-Q89,0)))))),3))</f>
         <v/>
       </c>
       <c r="T89" s="1294">
@@ -18831,7 +18844,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="1294">
-        <f>IF(I90="","",ROUND(IF(OR(I90="m²",I90="m2"),J90*IF(K90=0,1,K90)*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="m³",I90="m3"),J90*K90*L90*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="ml",I90="ML"),J90*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="und",I90="UND"),IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(I90="kg",J90*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,0))))),3))</f>
+        <f>IF(I90="","",ROUND(IF(OR(I90="m²",I90="m2"),J90*IF(K90=0,1,K90)*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="m³",I90="m3"),J90*K90*L90*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="ml",I90="ML"),J90*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="und",I90="UND"),IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(I90="kg",J90*IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,IF(OR(I90="gl",I90="GL",I90="gb",I90="GB",I90="Gl",I90="Gb"),IF(N90=0,1,N90)*IF(O90=0,1,O90)*P90-Q90,0)))))),3))</f>
         <v/>
       </c>
       <c r="T90" s="1294">
@@ -18914,7 +18927,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="1294">
-        <f>IF(I91="","",ROUND(IF(OR(I91="m²",I91="m2"),J91*IF(K91=0,1,K91)*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="m³",I91="m3"),J91*K91*L91*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="ml",I91="ML"),J91*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="und",I91="UND"),IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(I91="kg",J91*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,0))))),3))</f>
+        <f>IF(I91="","",ROUND(IF(OR(I91="m²",I91="m2"),J91*IF(K91=0,1,K91)*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="m³",I91="m3"),J91*K91*L91*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="ml",I91="ML"),J91*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="und",I91="UND"),IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(I91="kg",J91*IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,IF(OR(I91="gl",I91="GL",I91="gb",I91="GB",I91="Gl",I91="Gb"),IF(N91=0,1,N91)*IF(O91=0,1,O91)*P91-Q91,0)))))),3))</f>
         <v/>
       </c>
       <c r="T91" s="1294">
@@ -18997,7 +19010,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="1294">
-        <f>IF(I92="","",ROUND(IF(OR(I92="m²",I92="m2"),J92*IF(K92=0,1,K92)*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="m³",I92="m3"),J92*K92*L92*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="ml",I92="ML"),J92*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="und",I92="UND"),IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(I92="kg",J92*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,0))))),3))</f>
+        <f>IF(I92="","",ROUND(IF(OR(I92="m²",I92="m2"),J92*IF(K92=0,1,K92)*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="m³",I92="m3"),J92*K92*L92*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="ml",I92="ML"),J92*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="und",I92="UND"),IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(I92="kg",J92*IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,IF(OR(I92="gl",I92="GL",I92="gb",I92="GB",I92="Gl",I92="Gb"),IF(N92=0,1,N92)*IF(O92=0,1,O92)*P92-Q92,0)))))),3))</f>
         <v/>
       </c>
       <c r="T92" s="1294">
@@ -19080,7 +19093,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="1294">
-        <f>IF(I93="","",ROUND(IF(OR(I93="m²",I93="m2"),J93*IF(K93=0,1,K93)*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="m³",I93="m3"),J93*K93*L93*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="ml",I93="ML"),J93*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="und",I93="UND"),IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(I93="kg",J93*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,0))))),3))</f>
+        <f>IF(I93="","",ROUND(IF(OR(I93="m²",I93="m2"),J93*IF(K93=0,1,K93)*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="m³",I93="m3"),J93*K93*L93*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="ml",I93="ML"),J93*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="und",I93="UND"),IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(I93="kg",J93*IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,IF(OR(I93="gl",I93="GL",I93="gb",I93="GB",I93="Gl",I93="Gb"),IF(N93=0,1,N93)*IF(O93=0,1,O93)*P93-Q93,0)))))),3))</f>
         <v/>
       </c>
       <c r="T93" s="1294">
@@ -19163,7 +19176,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="1294">
-        <f>IF(I94="","",ROUND(IF(OR(I94="m²",I94="m2"),J94*IF(K94=0,1,K94)*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="m³",I94="m3"),J94*K94*L94*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="ml",I94="ML"),J94*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="und",I94="UND"),IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(I94="kg",J94*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,0))))),3))</f>
+        <f>IF(I94="","",ROUND(IF(OR(I94="m²",I94="m2"),J94*IF(K94=0,1,K94)*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="m³",I94="m3"),J94*K94*L94*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="ml",I94="ML"),J94*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="und",I94="UND"),IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(I94="kg",J94*IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,IF(OR(I94="gl",I94="GL",I94="gb",I94="GB",I94="Gl",I94="Gb"),IF(N94=0,1,N94)*IF(O94=0,1,O94)*P94-Q94,0)))))),3))</f>
         <v/>
       </c>
       <c r="T94" s="1294">
@@ -19246,7 +19259,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="1294">
-        <f>IF(I95="","",ROUND(IF(OR(I95="m²",I95="m2"),J95*IF(K95=0,1,K95)*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="m³",I95="m3"),J95*K95*L95*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="ml",I95="ML"),J95*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="und",I95="UND"),IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(I95="kg",J95*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,0))))),3))</f>
+        <f>IF(I95="","",ROUND(IF(OR(I95="m²",I95="m2"),J95*IF(K95=0,1,K95)*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="m³",I95="m3"),J95*K95*L95*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="ml",I95="ML"),J95*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="und",I95="UND"),IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(I95="kg",J95*IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,IF(OR(I95="gl",I95="GL",I95="gb",I95="GB",I95="Gl",I95="Gb"),IF(N95=0,1,N95)*IF(O95=0,1,O95)*P95-Q95,0)))))),3))</f>
         <v/>
       </c>
       <c r="T95" s="1294">
@@ -19329,7 +19342,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="1294">
-        <f>IF(I96="","",ROUND(IF(OR(I96="m²",I96="m2"),J96*IF(K96=0,1,K96)*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="m³",I96="m3"),J96*K96*L96*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="ml",I96="ML"),J96*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="und",I96="UND"),IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(I96="kg",J96*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,0))))),3))</f>
+        <f>IF(I96="","",ROUND(IF(OR(I96="m²",I96="m2"),J96*IF(K96=0,1,K96)*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="m³",I96="m3"),J96*K96*L96*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="ml",I96="ML"),J96*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="und",I96="UND"),IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(I96="kg",J96*IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,IF(OR(I96="gl",I96="GL",I96="gb",I96="GB",I96="Gl",I96="Gb"),IF(N96=0,1,N96)*IF(O96=0,1,O96)*P96-Q96,0)))))),3))</f>
         <v/>
       </c>
       <c r="T96" s="1294">
@@ -19412,7 +19425,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="1294">
-        <f>IF(I97="","",ROUND(IF(OR(I97="m²",I97="m2"),J97*IF(K97=0,1,K97)*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="m³",I97="m3"),J97*K97*L97*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="ml",I97="ML"),J97*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="und",I97="UND"),IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(I97="kg",J97*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,0))))),3))</f>
+        <f>IF(I97="","",ROUND(IF(OR(I97="m²",I97="m2"),J97*IF(K97=0,1,K97)*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="m³",I97="m3"),J97*K97*L97*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="ml",I97="ML"),J97*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="und",I97="UND"),IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(I97="kg",J97*IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,IF(OR(I97="gl",I97="GL",I97="gb",I97="GB",I97="Gl",I97="Gb"),IF(N97=0,1,N97)*IF(O97=0,1,O97)*P97-Q97,0)))))),3))</f>
         <v/>
       </c>
       <c r="T97" s="1294">
@@ -19495,7 +19508,7 @@
         <v>0</v>
       </c>
       <c r="S98" s="1294">
-        <f>IF(I98="","",ROUND(IF(OR(I98="m²",I98="m2"),J98*IF(K98=0,1,K98)*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="m³",I98="m3"),J98*K98*L98*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="ml",I98="ML"),J98*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="und",I98="UND"),IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(I98="kg",J98*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,0))))),3))</f>
+        <f>IF(I98="","",ROUND(IF(OR(I98="m²",I98="m2"),J98*IF(K98=0,1,K98)*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="m³",I98="m3"),J98*K98*L98*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="ml",I98="ML"),J98*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="und",I98="UND"),IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(I98="kg",J98*IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,IF(OR(I98="gl",I98="GL",I98="gb",I98="GB",I98="Gl",I98="Gb"),IF(N98=0,1,N98)*IF(O98=0,1,O98)*P98-Q98,0)))))),3))</f>
         <v/>
       </c>
       <c r="T98" s="1294">
@@ -19578,7 +19591,7 @@
         <v>0</v>
       </c>
       <c r="S99" s="1294">
-        <f>IF(I99="","",ROUND(IF(OR(I99="m²",I99="m2"),J99*IF(K99=0,1,K99)*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="m³",I99="m3"),J99*K99*L99*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="ml",I99="ML"),J99*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="und",I99="UND"),IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(I99="kg",J99*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,0))))),3))</f>
+        <f>IF(I99="","",ROUND(IF(OR(I99="m²",I99="m2"),J99*IF(K99=0,1,K99)*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="m³",I99="m3"),J99*K99*L99*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="ml",I99="ML"),J99*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="und",I99="UND"),IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(I99="kg",J99*IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,IF(OR(I99="gl",I99="GL",I99="gb",I99="GB",I99="Gl",I99="Gb"),IF(N99=0,1,N99)*IF(O99=0,1,O99)*P99-Q99,0)))))),3))</f>
         <v/>
       </c>
       <c r="T99" s="1294">
@@ -19661,7 +19674,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="1294">
-        <f>IF(I100="","",ROUND(IF(OR(I100="m²",I100="m2"),J100*IF(K100=0,1,K100)*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="m³",I100="m3"),J100*K100*L100*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="ml",I100="ML"),J100*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="und",I100="UND"),IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(I100="kg",J100*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,0))))),3))</f>
+        <f>IF(I100="","",ROUND(IF(OR(I100="m²",I100="m2"),J100*IF(K100=0,1,K100)*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="m³",I100="m3"),J100*K100*L100*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="ml",I100="ML"),J100*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="und",I100="UND"),IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(I100="kg",J100*IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,IF(OR(I100="gl",I100="GL",I100="gb",I100="GB",I100="Gl",I100="Gb"),IF(N100=0,1,N100)*IF(O100=0,1,O100)*P100-Q100,0)))))),3))</f>
         <v/>
       </c>
       <c r="T100" s="1294">
@@ -19744,7 +19757,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="1294">
-        <f>IF(I101="","",ROUND(IF(OR(I101="m²",I101="m2"),J101*IF(K101=0,1,K101)*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="m³",I101="m3"),J101*K101*L101*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="ml",I101="ML"),J101*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="und",I101="UND"),IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(I101="kg",J101*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,0))))),3))</f>
+        <f>IF(I101="","",ROUND(IF(OR(I101="m²",I101="m2"),J101*IF(K101=0,1,K101)*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="m³",I101="m3"),J101*K101*L101*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="ml",I101="ML"),J101*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="und",I101="UND"),IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(I101="kg",J101*IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,IF(OR(I101="gl",I101="GL",I101="gb",I101="GB",I101="Gl",I101="Gb"),IF(N101=0,1,N101)*IF(O101=0,1,O101)*P101-Q101,0)))))),3))</f>
         <v/>
       </c>
       <c r="T101" s="1294">
@@ -19827,7 +19840,7 @@
         <v>0</v>
       </c>
       <c r="S102" s="1294">
-        <f>IF(I102="","",ROUND(IF(OR(I102="m²",I102="m2"),J102*IF(K102=0,1,K102)*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="m³",I102="m3"),J102*K102*L102*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="ml",I102="ML"),J102*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="und",I102="UND"),IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(I102="kg",J102*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,0))))),3))</f>
+        <f>IF(I102="","",ROUND(IF(OR(I102="m²",I102="m2"),J102*IF(K102=0,1,K102)*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="m³",I102="m3"),J102*K102*L102*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="ml",I102="ML"),J102*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="und",I102="UND"),IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(I102="kg",J102*IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,IF(OR(I102="gl",I102="GL",I102="gb",I102="GB",I102="Gl",I102="Gb"),IF(N102=0,1,N102)*IF(O102=0,1,O102)*P102-Q102,0)))))),3))</f>
         <v/>
       </c>
       <c r="T102" s="1294">
@@ -19910,7 +19923,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="1294">
-        <f>IF(I103="","",ROUND(IF(OR(I103="m²",I103="m2"),J103*IF(K103=0,1,K103)*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="m³",I103="m3"),J103*K103*L103*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="ml",I103="ML"),J103*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="und",I103="UND"),IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(I103="kg",J103*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,0))))),3))</f>
+        <f>IF(I103="","",ROUND(IF(OR(I103="m²",I103="m2"),J103*IF(K103=0,1,K103)*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="m³",I103="m3"),J103*K103*L103*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="ml",I103="ML"),J103*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="und",I103="UND"),IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(I103="kg",J103*IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,IF(OR(I103="gl",I103="GL",I103="gb",I103="GB",I103="Gl",I103="Gb"),IF(N103=0,1,N103)*IF(O103=0,1,O103)*P103-Q103,0)))))),3))</f>
         <v/>
       </c>
       <c r="T103" s="1294">
@@ -19993,7 +20006,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="1294">
-        <f>IF(I104="","",ROUND(IF(OR(I104="m²",I104="m2"),J104*IF(K104=0,1,K104)*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="m³",I104="m3"),J104*K104*L104*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="ml",I104="ML"),J104*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="und",I104="UND"),IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(I104="kg",J104*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,0))))),3))</f>
+        <f>IF(I104="","",ROUND(IF(OR(I104="m²",I104="m2"),J104*IF(K104=0,1,K104)*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="m³",I104="m3"),J104*K104*L104*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="ml",I104="ML"),J104*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="und",I104="UND"),IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(I104="kg",J104*IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,IF(OR(I104="gl",I104="GL",I104="gb",I104="GB",I104="Gl",I104="Gb"),IF(N104=0,1,N104)*IF(O104=0,1,O104)*P104-Q104,0)))))),3))</f>
         <v/>
       </c>
       <c r="T104" s="1294">
@@ -20076,7 +20089,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="1294">
-        <f>IF(I105="","",ROUND(IF(OR(I105="m²",I105="m2"),J105*IF(K105=0,1,K105)*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="m³",I105="m3"),J105*K105*L105*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="ml",I105="ML"),J105*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="und",I105="UND"),IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(I105="kg",J105*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,0))))),3))</f>
+        <f>IF(I105="","",ROUND(IF(OR(I105="m²",I105="m2"),J105*IF(K105=0,1,K105)*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="m³",I105="m3"),J105*K105*L105*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="ml",I105="ML"),J105*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="und",I105="UND"),IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(I105="kg",J105*IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,IF(OR(I105="gl",I105="GL",I105="gb",I105="GB",I105="Gl",I105="Gb"),IF(N105=0,1,N105)*IF(O105=0,1,O105)*P105-Q105,0)))))),3))</f>
         <v/>
       </c>
       <c r="T105" s="1294">
@@ -20159,7 +20172,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="1294">
-        <f>IF(I106="","",ROUND(IF(OR(I106="m²",I106="m2"),J106*IF(K106=0,1,K106)*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="m³",I106="m3"),J106*K106*L106*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="ml",I106="ML"),J106*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="und",I106="UND"),IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(I106="kg",J106*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,0))))),3))</f>
+        <f>IF(I106="","",ROUND(IF(OR(I106="m²",I106="m2"),J106*IF(K106=0,1,K106)*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="m³",I106="m3"),J106*K106*L106*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="ml",I106="ML"),J106*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="und",I106="UND"),IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(I106="kg",J106*IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,IF(OR(I106="gl",I106="GL",I106="gb",I106="GB",I106="Gl",I106="Gb"),IF(N106=0,1,N106)*IF(O106=0,1,O106)*P106-Q106,0)))))),3))</f>
         <v/>
       </c>
       <c r="T106" s="1294">
@@ -20242,7 +20255,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="1294">
-        <f>IF(I107="","",ROUND(IF(OR(I107="m²",I107="m2"),J107*IF(K107=0,1,K107)*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="m³",I107="m3"),J107*K107*L107*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="ml",I107="ML"),J107*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="und",I107="UND"),IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(I107="kg",J107*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,0))))),3))</f>
+        <f>IF(I107="","",ROUND(IF(OR(I107="m²",I107="m2"),J107*IF(K107=0,1,K107)*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="m³",I107="m3"),J107*K107*L107*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="ml",I107="ML"),J107*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="und",I107="UND"),IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(I107="kg",J107*IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,IF(OR(I107="gl",I107="GL",I107="gb",I107="GB",I107="Gl",I107="Gb"),IF(N107=0,1,N107)*IF(O107=0,1,O107)*P107-Q107,0)))))),3))</f>
         <v/>
       </c>
       <c r="T107" s="1294">
@@ -20325,7 +20338,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="1294">
-        <f>IF(I108="","",ROUND(IF(OR(I108="m²",I108="m2"),J108*IF(K108=0,1,K108)*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="m³",I108="m3"),J108*K108*L108*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="ml",I108="ML"),J108*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="und",I108="UND"),IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(I108="kg",J108*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,0))))),3))</f>
+        <f>IF(I108="","",ROUND(IF(OR(I108="m²",I108="m2"),J108*IF(K108=0,1,K108)*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="m³",I108="m3"),J108*K108*L108*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="ml",I108="ML"),J108*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="und",I108="UND"),IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(I108="kg",J108*IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,IF(OR(I108="gl",I108="GL",I108="gb",I108="GB",I108="Gl",I108="Gb"),IF(N108=0,1,N108)*IF(O108=0,1,O108)*P108-Q108,0)))))),3))</f>
         <v/>
       </c>
       <c r="T108" s="1294">
@@ -20408,7 +20421,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="1294">
-        <f>IF(I109="","",ROUND(IF(OR(I109="m²",I109="m2"),J109*IF(K109=0,1,K109)*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="m³",I109="m3"),J109*K109*L109*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="ml",I109="ML"),J109*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="und",I109="UND"),IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(I109="kg",J109*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,0))))),3))</f>
+        <f>IF(I109="","",ROUND(IF(OR(I109="m²",I109="m2"),J109*IF(K109=0,1,K109)*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="m³",I109="m3"),J109*K109*L109*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="ml",I109="ML"),J109*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="und",I109="UND"),IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(I109="kg",J109*IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,IF(OR(I109="gl",I109="GL",I109="gb",I109="GB",I109="Gl",I109="Gb"),IF(N109=0,1,N109)*IF(O109=0,1,O109)*P109-Q109,0)))))),3))</f>
         <v/>
       </c>
       <c r="T109" s="1294">
@@ -20491,7 +20504,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="1294">
-        <f>IF(I110="","",ROUND(IF(OR(I110="m²",I110="m2"),J110*IF(K110=0,1,K110)*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="m³",I110="m3"),J110*K110*L110*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="ml",I110="ML"),J110*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="und",I110="UND"),IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(I110="kg",J110*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,0))))),3))</f>
+        <f>IF(I110="","",ROUND(IF(OR(I110="m²",I110="m2"),J110*IF(K110=0,1,K110)*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="m³",I110="m3"),J110*K110*L110*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="ml",I110="ML"),J110*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="und",I110="UND"),IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(I110="kg",J110*IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,IF(OR(I110="gl",I110="GL",I110="gb",I110="GB",I110="Gl",I110="Gb"),IF(N110=0,1,N110)*IF(O110=0,1,O110)*P110-Q110,0)))))),3))</f>
         <v/>
       </c>
       <c r="T110" s="1294">
@@ -20574,7 +20587,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="1294">
-        <f>IF(I111="","",ROUND(IF(OR(I111="m²",I111="m2"),J111*IF(K111=0,1,K111)*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="m³",I111="m3"),J111*K111*L111*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="ml",I111="ML"),J111*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="und",I111="UND"),IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(I111="kg",J111*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,0))))),3))</f>
+        <f>IF(I111="","",ROUND(IF(OR(I111="m²",I111="m2"),J111*IF(K111=0,1,K111)*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="m³",I111="m3"),J111*K111*L111*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="ml",I111="ML"),J111*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="und",I111="UND"),IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(I111="kg",J111*IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,IF(OR(I111="gl",I111="GL",I111="gb",I111="GB",I111="Gl",I111="Gb"),IF(N111=0,1,N111)*IF(O111=0,1,O111)*P111-Q111,0)))))),3))</f>
         <v/>
       </c>
       <c r="T111" s="1294">
@@ -20657,7 +20670,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="1294">
-        <f>IF(I112="","",ROUND(IF(OR(I112="m²",I112="m2"),J112*IF(K112=0,1,K112)*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="m³",I112="m3"),J112*K112*L112*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="ml",I112="ML"),J112*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="und",I112="UND"),IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(I112="kg",J112*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,0))))),3))</f>
+        <f>IF(I112="","",ROUND(IF(OR(I112="m²",I112="m2"),J112*IF(K112=0,1,K112)*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="m³",I112="m3"),J112*K112*L112*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="ml",I112="ML"),J112*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="und",I112="UND"),IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(I112="kg",J112*IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,IF(OR(I112="gl",I112="GL",I112="gb",I112="GB",I112="Gl",I112="Gb"),IF(N112=0,1,N112)*IF(O112=0,1,O112)*P112-Q112,0)))))),3))</f>
         <v/>
       </c>
       <c r="T112" s="1294">
@@ -20740,7 +20753,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="1294">
-        <f>IF(I113="","",ROUND(IF(OR(I113="m²",I113="m2"),J113*IF(K113=0,1,K113)*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="m³",I113="m3"),J113*K113*L113*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="ml",I113="ML"),J113*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="und",I113="UND"),IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(I113="kg",J113*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,0))))),3))</f>
+        <f>IF(I113="","",ROUND(IF(OR(I113="m²",I113="m2"),J113*IF(K113=0,1,K113)*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="m³",I113="m3"),J113*K113*L113*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="ml",I113="ML"),J113*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="und",I113="UND"),IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(I113="kg",J113*IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,IF(OR(I113="gl",I113="GL",I113="gb",I113="GB",I113="Gl",I113="Gb"),IF(N113=0,1,N113)*IF(O113=0,1,O113)*P113-Q113,0)))))),3))</f>
         <v/>
       </c>
       <c r="T113" s="1294">
@@ -20823,7 +20836,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="1294">
-        <f>IF(I114="","",ROUND(IF(OR(I114="m²",I114="m2"),J114*IF(K114=0,1,K114)*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="m³",I114="m3"),J114*K114*L114*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="ml",I114="ML"),J114*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="und",I114="UND"),IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(I114="kg",J114*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,0))))),3))</f>
+        <f>IF(I114="","",ROUND(IF(OR(I114="m²",I114="m2"),J114*IF(K114=0,1,K114)*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="m³",I114="m3"),J114*K114*L114*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="ml",I114="ML"),J114*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="und",I114="UND"),IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(I114="kg",J114*IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,IF(OR(I114="gl",I114="GL",I114="gb",I114="GB",I114="Gl",I114="Gb"),IF(N114=0,1,N114)*IF(O114=0,1,O114)*P114-Q114,0)))))),3))</f>
         <v/>
       </c>
       <c r="T114" s="1294">
@@ -20906,7 +20919,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="1294">
-        <f>IF(I115="","",ROUND(IF(OR(I115="m²",I115="m2"),J115*IF(K115=0,1,K115)*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="m³",I115="m3"),J115*K115*L115*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="ml",I115="ML"),J115*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="und",I115="UND"),IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(I115="kg",J115*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,0))))),3))</f>
+        <f>IF(I115="","",ROUND(IF(OR(I115="m²",I115="m2"),J115*IF(K115=0,1,K115)*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="m³",I115="m3"),J115*K115*L115*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="ml",I115="ML"),J115*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="und",I115="UND"),IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(I115="kg",J115*IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,IF(OR(I115="gl",I115="GL",I115="gb",I115="GB",I115="Gl",I115="Gb"),IF(N115=0,1,N115)*IF(O115=0,1,O115)*P115-Q115,0)))))),3))</f>
         <v/>
       </c>
       <c r="T115" s="1294">
@@ -20989,7 +21002,7 @@
         <v>0</v>
       </c>
       <c r="S116" s="1294">
-        <f>IF(I116="","",ROUND(IF(OR(I116="m²",I116="m2"),J116*IF(K116=0,1,K116)*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="m³",I116="m3"),J116*K116*L116*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="ml",I116="ML"),J116*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="und",I116="UND"),IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(I116="kg",J116*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,0))))),3))</f>
+        <f>IF(I116="","",ROUND(IF(OR(I116="m²",I116="m2"),J116*IF(K116=0,1,K116)*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="m³",I116="m3"),J116*K116*L116*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="ml",I116="ML"),J116*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="und",I116="UND"),IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(I116="kg",J116*IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,IF(OR(I116="gl",I116="GL",I116="gb",I116="GB",I116="Gl",I116="Gb"),IF(N116=0,1,N116)*IF(O116=0,1,O116)*P116-Q116,0)))))),3))</f>
         <v/>
       </c>
       <c r="T116" s="1294">
@@ -21072,7 +21085,7 @@
         <v>0</v>
       </c>
       <c r="S117" s="1294">
-        <f>IF(I117="","",ROUND(IF(OR(I117="m²",I117="m2"),J117*IF(K117=0,1,K117)*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="m³",I117="m3"),J117*K117*L117*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="ml",I117="ML"),J117*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="und",I117="UND"),IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(I117="kg",J117*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,0))))),3))</f>
+        <f>IF(I117="","",ROUND(IF(OR(I117="m²",I117="m2"),J117*IF(K117=0,1,K117)*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="m³",I117="m3"),J117*K117*L117*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="ml",I117="ML"),J117*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="und",I117="UND"),IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(I117="kg",J117*IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,IF(OR(I117="gl",I117="GL",I117="gb",I117="GB",I117="Gl",I117="Gb"),IF(N117=0,1,N117)*IF(O117=0,1,O117)*P117-Q117,0)))))),3))</f>
         <v/>
       </c>
       <c r="T117" s="1294">
@@ -21155,7 +21168,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="1294">
-        <f>IF(I118="","",ROUND(IF(OR(I118="m²",I118="m2"),J118*IF(K118=0,1,K118)*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="m³",I118="m3"),J118*K118*L118*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="ml",I118="ML"),J118*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="und",I118="UND"),IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(I118="kg",J118*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,0))))),3))</f>
+        <f>IF(I118="","",ROUND(IF(OR(I118="m²",I118="m2"),J118*IF(K118=0,1,K118)*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="m³",I118="m3"),J118*K118*L118*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="ml",I118="ML"),J118*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="und",I118="UND"),IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(I118="kg",J118*IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,IF(OR(I118="gl",I118="GL",I118="gb",I118="GB",I118="Gl",I118="Gb"),IF(N118=0,1,N118)*IF(O118=0,1,O118)*P118-Q118,0)))))),3))</f>
         <v/>
       </c>
       <c r="T118" s="1294">
@@ -21238,7 +21251,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="1294">
-        <f>IF(I119="","",ROUND(IF(OR(I119="m²",I119="m2"),J119*IF(K119=0,1,K119)*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="m³",I119="m3"),J119*K119*L119*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="ml",I119="ML"),J119*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="und",I119="UND"),IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(I119="kg",J119*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,0))))),3))</f>
+        <f>IF(I119="","",ROUND(IF(OR(I119="m²",I119="m2"),J119*IF(K119=0,1,K119)*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="m³",I119="m3"),J119*K119*L119*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="ml",I119="ML"),J119*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="und",I119="UND"),IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(I119="kg",J119*IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,IF(OR(I119="gl",I119="GL",I119="gb",I119="GB",I119="Gl",I119="Gb"),IF(N119=0,1,N119)*IF(O119=0,1,O119)*P119-Q119,0)))))),3))</f>
         <v/>
       </c>
       <c r="T119" s="1294">
@@ -21321,7 +21334,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="1294">
-        <f>IF(I120="","",ROUND(IF(OR(I120="m²",I120="m2"),J120*IF(K120=0,1,K120)*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="m³",I120="m3"),J120*K120*L120*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="ml",I120="ML"),J120*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="und",I120="UND"),IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(I120="kg",J120*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,0))))),3))</f>
+        <f>IF(I120="","",ROUND(IF(OR(I120="m²",I120="m2"),J120*IF(K120=0,1,K120)*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="m³",I120="m3"),J120*K120*L120*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="ml",I120="ML"),J120*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="und",I120="UND"),IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(I120="kg",J120*IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,IF(OR(I120="gl",I120="GL",I120="gb",I120="GB",I120="Gl",I120="Gb"),IF(N120=0,1,N120)*IF(O120=0,1,O120)*P120-Q120,0)))))),3))</f>
         <v/>
       </c>
       <c r="T120" s="1294">
@@ -21404,7 +21417,7 @@
         <v>0</v>
       </c>
       <c r="S121" s="1294">
-        <f>IF(I121="","",ROUND(IF(OR(I121="m²",I121="m2"),J121*IF(K121=0,1,K121)*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="m³",I121="m3"),J121*K121*L121*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="ml",I121="ML"),J121*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="und",I121="UND"),IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(I121="kg",J121*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,0))))),3))</f>
+        <f>IF(I121="","",ROUND(IF(OR(I121="m²",I121="m2"),J121*IF(K121=0,1,K121)*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="m³",I121="m3"),J121*K121*L121*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="ml",I121="ML"),J121*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="und",I121="UND"),IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(I121="kg",J121*IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,IF(OR(I121="gl",I121="GL",I121="gb",I121="GB",I121="Gl",I121="Gb"),IF(N121=0,1,N121)*IF(O121=0,1,O121)*P121-Q121,0)))))),3))</f>
         <v/>
       </c>
       <c r="T121" s="1294">
@@ -21487,7 +21500,7 @@
         <v>0</v>
       </c>
       <c r="S122" s="1294">
-        <f>IF(I122="","",ROUND(IF(OR(I122="m²",I122="m2"),J122*IF(K122=0,1,K122)*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="m³",I122="m3"),J122*K122*L122*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="ml",I122="ML"),J122*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="und",I122="UND"),IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(I122="kg",J122*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,0))))),3))</f>
+        <f>IF(I122="","",ROUND(IF(OR(I122="m²",I122="m2"),J122*IF(K122=0,1,K122)*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="m³",I122="m3"),J122*K122*L122*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="ml",I122="ML"),J122*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="und",I122="UND"),IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(I122="kg",J122*IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,IF(OR(I122="gl",I122="GL",I122="gb",I122="GB",I122="Gl",I122="Gb"),IF(N122=0,1,N122)*IF(O122=0,1,O122)*P122-Q122,0)))))),3))</f>
         <v/>
       </c>
       <c r="T122" s="1294">
@@ -21570,7 +21583,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="1294">
-        <f>IF(I123="","",ROUND(IF(OR(I123="m²",I123="m2"),J123*IF(K123=0,1,K123)*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="m³",I123="m3"),J123*K123*L123*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="ml",I123="ML"),J123*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="und",I123="UND"),IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(I123="kg",J123*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,0))))),3))</f>
+        <f>IF(I123="","",ROUND(IF(OR(I123="m²",I123="m2"),J123*IF(K123=0,1,K123)*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="m³",I123="m3"),J123*K123*L123*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="ml",I123="ML"),J123*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="und",I123="UND"),IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(I123="kg",J123*IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,IF(OR(I123="gl",I123="GL",I123="gb",I123="GB",I123="Gl",I123="Gb"),IF(N123=0,1,N123)*IF(O123=0,1,O123)*P123-Q123,0)))))),3))</f>
         <v/>
       </c>
       <c r="T123" s="1294">
@@ -21653,7 +21666,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="1294">
-        <f>IF(I124="","",ROUND(IF(OR(I124="m²",I124="m2"),J124*IF(K124=0,1,K124)*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="m³",I124="m3"),J124*K124*L124*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="ml",I124="ML"),J124*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="und",I124="UND"),IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(I124="kg",J124*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,0))))),3))</f>
+        <f>IF(I124="","",ROUND(IF(OR(I124="m²",I124="m2"),J124*IF(K124=0,1,K124)*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="m³",I124="m3"),J124*K124*L124*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="ml",I124="ML"),J124*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="und",I124="UND"),IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(I124="kg",J124*IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,IF(OR(I124="gl",I124="GL",I124="gb",I124="GB",I124="Gl",I124="Gb"),IF(N124=0,1,N124)*IF(O124=0,1,O124)*P124-Q124,0)))))),3))</f>
         <v/>
       </c>
       <c r="T124" s="1294">
@@ -21736,7 +21749,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="1294">
-        <f>IF(I125="","",ROUND(IF(OR(I125="m²",I125="m2"),J125*IF(K125=0,1,K125)*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="m³",I125="m3"),J125*K125*L125*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="ml",I125="ML"),J125*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="und",I125="UND"),IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(I125="kg",J125*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,0))))),3))</f>
+        <f>IF(I125="","",ROUND(IF(OR(I125="m²",I125="m2"),J125*IF(K125=0,1,K125)*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="m³",I125="m3"),J125*K125*L125*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="ml",I125="ML"),J125*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="und",I125="UND"),IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(I125="kg",J125*IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,IF(OR(I125="gl",I125="GL",I125="gb",I125="GB",I125="Gl",I125="Gb"),IF(N125=0,1,N125)*IF(O125=0,1,O125)*P125-Q125,0)))))),3))</f>
         <v/>
       </c>
       <c r="T125" s="1294">
@@ -21819,7 +21832,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="1294">
-        <f>IF(I126="","",ROUND(IF(OR(I126="m²",I126="m2"),J126*IF(K126=0,1,K126)*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="m³",I126="m3"),J126*K126*L126*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="ml",I126="ML"),J126*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="und",I126="UND"),IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(I126="kg",J126*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,0))))),3))</f>
+        <f>IF(I126="","",ROUND(IF(OR(I126="m²",I126="m2"),J126*IF(K126=0,1,K126)*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="m³",I126="m3"),J126*K126*L126*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="ml",I126="ML"),J126*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="und",I126="UND"),IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(I126="kg",J126*IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,IF(OR(I126="gl",I126="GL",I126="gb",I126="GB",I126="Gl",I126="Gb"),IF(N126=0,1,N126)*IF(O126=0,1,O126)*P126-Q126,0)))))),3))</f>
         <v/>
       </c>
       <c r="T126" s="1294">
@@ -21902,7 +21915,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="1294">
-        <f>IF(I127="","",ROUND(IF(OR(I127="m²",I127="m2"),J127*IF(K127=0,1,K127)*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="m³",I127="m3"),J127*K127*L127*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="ml",I127="ML"),J127*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="und",I127="UND"),IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(I127="kg",J127*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,0))))),3))</f>
+        <f>IF(I127="","",ROUND(IF(OR(I127="m²",I127="m2"),J127*IF(K127=0,1,K127)*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="m³",I127="m3"),J127*K127*L127*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="ml",I127="ML"),J127*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="und",I127="UND"),IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(I127="kg",J127*IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,IF(OR(I127="gl",I127="GL",I127="gb",I127="GB",I127="Gl",I127="Gb"),IF(N127=0,1,N127)*IF(O127=0,1,O127)*P127-Q127,0)))))),3))</f>
         <v/>
       </c>
       <c r="T127" s="1294">
@@ -21985,7 +21998,7 @@
         <v>0</v>
       </c>
       <c r="S128" s="1294">
-        <f>IF(I128="","",ROUND(IF(OR(I128="m²",I128="m2"),J128*IF(K128=0,1,K128)*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="m³",I128="m3"),J128*K128*L128*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="ml",I128="ML"),J128*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="und",I128="UND"),IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(I128="kg",J128*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,0))))),3))</f>
+        <f>IF(I128="","",ROUND(IF(OR(I128="m²",I128="m2"),J128*IF(K128=0,1,K128)*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="m³",I128="m3"),J128*K128*L128*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="ml",I128="ML"),J128*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="und",I128="UND"),IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(I128="kg",J128*IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,IF(OR(I128="gl",I128="GL",I128="gb",I128="GB",I128="Gl",I128="Gb"),IF(N128=0,1,N128)*IF(O128=0,1,O128)*P128-Q128,0)))))),3))</f>
         <v/>
       </c>
       <c r="T128" s="1294">
@@ -22068,7 +22081,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="1294">
-        <f>IF(I129="","",ROUND(IF(OR(I129="m²",I129="m2"),J129*IF(K129=0,1,K129)*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="m³",I129="m3"),J129*K129*L129*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="ml",I129="ML"),J129*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="und",I129="UND"),IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(I129="kg",J129*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,0))))),3))</f>
+        <f>IF(I129="","",ROUND(IF(OR(I129="m²",I129="m2"),J129*IF(K129=0,1,K129)*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="m³",I129="m3"),J129*K129*L129*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="ml",I129="ML"),J129*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="und",I129="UND"),IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(I129="kg",J129*IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,IF(OR(I129="gl",I129="GL",I129="gb",I129="GB",I129="Gl",I129="Gb"),IF(N129=0,1,N129)*IF(O129=0,1,O129)*P129-Q129,0)))))),3))</f>
         <v/>
       </c>
       <c r="T129" s="1294">
@@ -22151,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="S130" s="1294">
-        <f>IF(I130="","",ROUND(IF(OR(I130="m²",I130="m2"),J130*IF(K130=0,1,K130)*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="m³",I130="m3"),J130*K130*L130*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="ml",I130="ML"),J130*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="und",I130="UND"),IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(I130="kg",J130*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,0))))),3))</f>
+        <f>IF(I130="","",ROUND(IF(OR(I130="m²",I130="m2"),J130*IF(K130=0,1,K130)*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="m³",I130="m3"),J130*K130*L130*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="ml",I130="ML"),J130*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="und",I130="UND"),IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(I130="kg",J130*IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,IF(OR(I130="gl",I130="GL",I130="gb",I130="GB",I130="Gl",I130="Gb"),IF(N130=0,1,N130)*IF(O130=0,1,O130)*P130-Q130,0)))))),3))</f>
         <v/>
       </c>
       <c r="T130" s="1294">
@@ -22234,7 +22247,7 @@
         <v>0</v>
       </c>
       <c r="S131" s="1294">
-        <f>IF(I131="","",ROUND(IF(OR(I131="m²",I131="m2"),J131*IF(K131=0,1,K131)*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="m³",I131="m3"),J131*K131*L131*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="ml",I131="ML"),J131*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="und",I131="UND"),IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(I131="kg",J131*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,0))))),3))</f>
+        <f>IF(I131="","",ROUND(IF(OR(I131="m²",I131="m2"),J131*IF(K131=0,1,K131)*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="m³",I131="m3"),J131*K131*L131*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="ml",I131="ML"),J131*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="und",I131="UND"),IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(I131="kg",J131*IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,IF(OR(I131="gl",I131="GL",I131="gb",I131="GB",I131="Gl",I131="Gb"),IF(N131=0,1,N131)*IF(O131=0,1,O131)*P131-Q131,0)))))),3))</f>
         <v/>
       </c>
       <c r="T131" s="1294">
@@ -22317,7 +22330,7 @@
         <v>0</v>
       </c>
       <c r="S132" s="1294">
-        <f>IF(I132="","",ROUND(IF(OR(I132="m²",I132="m2"),J132*IF(K132=0,1,K132)*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="m³",I132="m3"),J132*K132*L132*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="ml",I132="ML"),J132*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="und",I132="UND"),IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(I132="kg",J132*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,0))))),3))</f>
+        <f>IF(I132="","",ROUND(IF(OR(I132="m²",I132="m2"),J132*IF(K132=0,1,K132)*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="m³",I132="m3"),J132*K132*L132*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="ml",I132="ML"),J132*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="und",I132="UND"),IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(I132="kg",J132*IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,IF(OR(I132="gl",I132="GL",I132="gb",I132="GB",I132="Gl",I132="Gb"),IF(N132=0,1,N132)*IF(O132=0,1,O132)*P132-Q132,0)))))),3))</f>
         <v/>
       </c>
       <c r="T132" s="1294">
@@ -22400,7 +22413,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="1294">
-        <f>IF(I133="","",ROUND(IF(OR(I133="m²",I133="m2"),J133*IF(K133=0,1,K133)*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="m³",I133="m3"),J133*K133*L133*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="ml",I133="ML"),J133*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="und",I133="UND"),IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(I133="kg",J133*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,0))))),3))</f>
+        <f>IF(I133="","",ROUND(IF(OR(I133="m²",I133="m2"),J133*IF(K133=0,1,K133)*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="m³",I133="m3"),J133*K133*L133*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="ml",I133="ML"),J133*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="und",I133="UND"),IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(I133="kg",J133*IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,IF(OR(I133="gl",I133="GL",I133="gb",I133="GB",I133="Gl",I133="Gb"),IF(N133=0,1,N133)*IF(O133=0,1,O133)*P133-Q133,0)))))),3))</f>
         <v/>
       </c>
       <c r="T133" s="1294">
@@ -22483,7 +22496,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="1294">
-        <f>IF(I134="","",ROUND(IF(OR(I134="m²",I134="m2"),J134*IF(K134=0,1,K134)*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="m³",I134="m3"),J134*K134*L134*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="ml",I134="ML"),J134*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="und",I134="UND"),IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(I134="kg",J134*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,0))))),3))</f>
+        <f>IF(I134="","",ROUND(IF(OR(I134="m²",I134="m2"),J134*IF(K134=0,1,K134)*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="m³",I134="m3"),J134*K134*L134*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="ml",I134="ML"),J134*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="und",I134="UND"),IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(I134="kg",J134*IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,IF(OR(I134="gl",I134="GL",I134="gb",I134="GB",I134="Gl",I134="Gb"),IF(N134=0,1,N134)*IF(O134=0,1,O134)*P134-Q134,0)))))),3))</f>
         <v/>
       </c>
       <c r="T134" s="1294">
@@ -22566,7 +22579,7 @@
         <v>0</v>
       </c>
       <c r="S135" s="1294">
-        <f>IF(I135="","",ROUND(IF(OR(I135="m²",I135="m2"),J135*IF(K135=0,1,K135)*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="m³",I135="m3"),J135*K135*L135*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="ml",I135="ML"),J135*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="und",I135="UND"),IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(I135="kg",J135*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,0))))),3))</f>
+        <f>IF(I135="","",ROUND(IF(OR(I135="m²",I135="m2"),J135*IF(K135=0,1,K135)*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="m³",I135="m3"),J135*K135*L135*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="ml",I135="ML"),J135*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="und",I135="UND"),IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(I135="kg",J135*IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,IF(OR(I135="gl",I135="GL",I135="gb",I135="GB",I135="Gl",I135="Gb"),IF(N135=0,1,N135)*IF(O135=0,1,O135)*P135-Q135,0)))))),3))</f>
         <v/>
       </c>
       <c r="T135" s="1294">
@@ -22649,7 +22662,7 @@
         <v>0</v>
       </c>
       <c r="S136" s="1294">
-        <f>IF(I136="","",ROUND(IF(OR(I136="m²",I136="m2"),J136*IF(K136=0,1,K136)*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="m³",I136="m3"),J136*K136*L136*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="ml",I136="ML"),J136*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="und",I136="UND"),IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(I136="kg",J136*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,0))))),3))</f>
+        <f>IF(I136="","",ROUND(IF(OR(I136="m²",I136="m2"),J136*IF(K136=0,1,K136)*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="m³",I136="m3"),J136*K136*L136*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="ml",I136="ML"),J136*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="und",I136="UND"),IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(I136="kg",J136*IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,IF(OR(I136="gl",I136="GL",I136="gb",I136="GB",I136="Gl",I136="Gb"),IF(N136=0,1,N136)*IF(O136=0,1,O136)*P136-Q136,0)))))),3))</f>
         <v/>
       </c>
       <c r="T136" s="1294">
@@ -22732,7 +22745,7 @@
         <v>0</v>
       </c>
       <c r="S137" s="1294">
-        <f>IF(I137="","",ROUND(IF(OR(I137="m²",I137="m2"),J137*IF(K137=0,1,K137)*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="m³",I137="m3"),J137*K137*L137*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="ml",I137="ML"),J137*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="und",I137="UND"),IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(I137="kg",J137*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,0))))),3))</f>
+        <f>IF(I137="","",ROUND(IF(OR(I137="m²",I137="m2"),J137*IF(K137=0,1,K137)*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="m³",I137="m3"),J137*K137*L137*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="ml",I137="ML"),J137*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="und",I137="UND"),IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(I137="kg",J137*IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,IF(OR(I137="gl",I137="GL",I137="gb",I137="GB",I137="Gl",I137="Gb"),IF(N137=0,1,N137)*IF(O137=0,1,O137)*P137-Q137,0)))))),3))</f>
         <v/>
       </c>
       <c r="T137" s="1294">
@@ -22815,7 +22828,7 @@
         <v>0</v>
       </c>
       <c r="S138" s="1294">
-        <f>IF(I138="","",ROUND(IF(OR(I138="m²",I138="m2"),J138*IF(K138=0,1,K138)*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="m³",I138="m3"),J138*K138*L138*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="ml",I138="ML"),J138*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="und",I138="UND"),IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(I138="kg",J138*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,0))))),3))</f>
+        <f>IF(I138="","",ROUND(IF(OR(I138="m²",I138="m2"),J138*IF(K138=0,1,K138)*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="m³",I138="m3"),J138*K138*L138*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="ml",I138="ML"),J138*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="und",I138="UND"),IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(I138="kg",J138*IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,IF(OR(I138="gl",I138="GL",I138="gb",I138="GB",I138="Gl",I138="Gb"),IF(N138=0,1,N138)*IF(O138=0,1,O138)*P138-Q138,0)))))),3))</f>
         <v/>
       </c>
       <c r="T138" s="1294">
@@ -22898,7 +22911,7 @@
         <v>0</v>
       </c>
       <c r="S139" s="1294">
-        <f>IF(I139="","",ROUND(IF(OR(I139="m²",I139="m2"),J139*IF(K139=0,1,K139)*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="m³",I139="m3"),J139*K139*L139*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="ml",I139="ML"),J139*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="und",I139="UND"),IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(I139="kg",J139*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,0))))),3))</f>
+        <f>IF(I139="","",ROUND(IF(OR(I139="m²",I139="m2"),J139*IF(K139=0,1,K139)*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="m³",I139="m3"),J139*K139*L139*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="ml",I139="ML"),J139*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="und",I139="UND"),IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(I139="kg",J139*IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,IF(OR(I139="gl",I139="GL",I139="gb",I139="GB",I139="Gl",I139="Gb"),IF(N139=0,1,N139)*IF(O139=0,1,O139)*P139-Q139,0)))))),3))</f>
         <v/>
       </c>
       <c r="T139" s="1294">
@@ -22981,7 +22994,7 @@
         <v>0</v>
       </c>
       <c r="S140" s="1294">
-        <f>IF(I140="","",ROUND(IF(OR(I140="m²",I140="m2"),J140*IF(K140=0,1,K140)*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="m³",I140="m3"),J140*K140*L140*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="ml",I140="ML"),J140*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="und",I140="UND"),IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(I140="kg",J140*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,0))))),3))</f>
+        <f>IF(I140="","",ROUND(IF(OR(I140="m²",I140="m2"),J140*IF(K140=0,1,K140)*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="m³",I140="m3"),J140*K140*L140*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="ml",I140="ML"),J140*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="und",I140="UND"),IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(I140="kg",J140*IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,IF(OR(I140="gl",I140="GL",I140="gb",I140="GB",I140="Gl",I140="Gb"),IF(N140=0,1,N140)*IF(O140=0,1,O140)*P140-Q140,0)))))),3))</f>
         <v/>
       </c>
       <c r="T140" s="1294">
@@ -23064,7 +23077,7 @@
         <v>0</v>
       </c>
       <c r="S141" s="1294">
-        <f>IF(I141="","",ROUND(IF(OR(I141="m²",I141="m2"),J141*IF(K141=0,1,K141)*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="m³",I141="m3"),J141*K141*L141*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="ml",I141="ML"),J141*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="und",I141="UND"),IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(I141="kg",J141*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,0))))),3))</f>
+        <f>IF(I141="","",ROUND(IF(OR(I141="m²",I141="m2"),J141*IF(K141=0,1,K141)*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="m³",I141="m3"),J141*K141*L141*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="ml",I141="ML"),J141*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="und",I141="UND"),IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(I141="kg",J141*IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,IF(OR(I141="gl",I141="GL",I141="gb",I141="GB",I141="Gl",I141="Gb"),IF(N141=0,1,N141)*IF(O141=0,1,O141)*P141-Q141,0)))))),3))</f>
         <v/>
       </c>
       <c r="T141" s="1294">
@@ -23147,7 +23160,7 @@
         <v>0</v>
       </c>
       <c r="S142" s="1294">
-        <f>IF(I142="","",ROUND(IF(OR(I142="m²",I142="m2"),J142*IF(K142=0,1,K142)*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="m³",I142="m3"),J142*K142*L142*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="ml",I142="ML"),J142*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="und",I142="UND"),IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(I142="kg",J142*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,0))))),3))</f>
+        <f>IF(I142="","",ROUND(IF(OR(I142="m²",I142="m2"),J142*IF(K142=0,1,K142)*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="m³",I142="m3"),J142*K142*L142*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="ml",I142="ML"),J142*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="und",I142="UND"),IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(I142="kg",J142*IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,IF(OR(I142="gl",I142="GL",I142="gb",I142="GB",I142="Gl",I142="Gb"),IF(N142=0,1,N142)*IF(O142=0,1,O142)*P142-Q142,0)))))),3))</f>
         <v/>
       </c>
       <c r="T142" s="1294">
@@ -23230,7 +23243,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="1294">
-        <f>IF(I143="","",ROUND(IF(OR(I143="m²",I143="m2"),J143*IF(K143=0,1,K143)*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="m³",I143="m3"),J143*K143*L143*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="ml",I143="ML"),J143*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="und",I143="UND"),IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(I143="kg",J143*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,0))))),3))</f>
+        <f>IF(I143="","",ROUND(IF(OR(I143="m²",I143="m2"),J143*IF(K143=0,1,K143)*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="m³",I143="m3"),J143*K143*L143*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="ml",I143="ML"),J143*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="und",I143="UND"),IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(I143="kg",J143*IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,IF(OR(I143="gl",I143="GL",I143="gb",I143="GB",I143="Gl",I143="Gb"),IF(N143=0,1,N143)*IF(O143=0,1,O143)*P143-Q143,0)))))),3))</f>
         <v/>
       </c>
       <c r="T143" s="1294">
@@ -23313,7 +23326,7 @@
         <v>0</v>
       </c>
       <c r="S144" s="1294">
-        <f>IF(I144="","",ROUND(IF(OR(I144="m²",I144="m2"),J144*IF(K144=0,1,K144)*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="m³",I144="m3"),J144*K144*L144*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="ml",I144="ML"),J144*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="und",I144="UND"),IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(I144="kg",J144*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,0))))),3))</f>
+        <f>IF(I144="","",ROUND(IF(OR(I144="m²",I144="m2"),J144*IF(K144=0,1,K144)*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="m³",I144="m3"),J144*K144*L144*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="ml",I144="ML"),J144*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="und",I144="UND"),IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(I144="kg",J144*IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,IF(OR(I144="gl",I144="GL",I144="gb",I144="GB",I144="Gl",I144="Gb"),IF(N144=0,1,N144)*IF(O144=0,1,O144)*P144-Q144,0)))))),3))</f>
         <v/>
       </c>
       <c r="T144" s="1294">
@@ -23396,7 +23409,7 @@
         <v>0</v>
       </c>
       <c r="S145" s="1294">
-        <f>IF(I145="","",ROUND(IF(OR(I145="m²",I145="m2"),J145*IF(K145=0,1,K145)*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="m³",I145="m3"),J145*K145*L145*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="ml",I145="ML"),J145*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="und",I145="UND"),IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(I145="kg",J145*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,0))))),3))</f>
+        <f>IF(I145="","",ROUND(IF(OR(I145="m²",I145="m2"),J145*IF(K145=0,1,K145)*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="m³",I145="m3"),J145*K145*L145*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="ml",I145="ML"),J145*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="und",I145="UND"),IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(I145="kg",J145*IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,IF(OR(I145="gl",I145="GL",I145="gb",I145="GB",I145="Gl",I145="Gb"),IF(N145=0,1,N145)*IF(O145=0,1,O145)*P145-Q145,0)))))),3))</f>
         <v/>
       </c>
       <c r="T145" s="1294">
@@ -23949,7 +23962,38 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="526" t="inlineStr">
+      <c r="A163" s="284" t="inlineStr">
+        <is>
+          <t>MQ-155</t>
+        </is>
+      </c>
+      <c r="B163" s="285" t="inlineStr">
+        <is>
+          <t>ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C163" s="286" t="n"/>
+      <c r="D163" s="287" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="E163" s="288" t="inlineStr">
+        <is>
+          <t>Concreto premezclado o de planta (suministro)</t>
+        </is>
+      </c>
+      <c r="F163" s="289" t="n"/>
+      <c r="G163" s="289" t="n"/>
+      <c r="H163" s="289" t="n"/>
+      <c r="I163" s="287" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1308" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -28,6 +28,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="170">
     <font>
@@ -1693,7 +1694,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6579,6 +6580,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
@@ -6587,7 +6602,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1309">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9817,6 +9832,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10857,7 +10884,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I34"/>
@@ -11455,7 +11481,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M33"/>
@@ -11768,7 +11793,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y164"/>
@@ -24025,7 +24049,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N49"/>
@@ -25084,7 +25107,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U146"/>
@@ -37422,7 +37444,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I176"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -10408,31 +10408,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -10869,7 +10869,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I34"/>
@@ -11467,7 +11466,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M33"/>
@@ -11780,7 +11778,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y164"/>
@@ -24037,7 +24034,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N49"/>
@@ -25096,7 +25092,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U146"/>
@@ -28522,7 +28517,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I176"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cantidades de Obra" sheetId="1" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId7"/>
-    <sheet name="Cálculo Detallado" sheetId="3" r:id="rId8"/>
-    <sheet name="Catalogo de Actividades" sheetId="4" r:id="rId9"/>
-    <sheet name="Planos" sheetId="5" r:id="rId10"/>
-    <sheet name="Instructivo" sheetId="6" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantidades de Obra" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cálculo Detallado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de Actividades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructivo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -9985,440 +9986,187 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>18300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>80025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2952000" cy="1404000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>10785</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171949</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2808000" cy="1368000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1104300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>160575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="3276000" cy="1656000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>49483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2880000" cy="1368000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10463,7 +10211,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10493,186 +10241,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3060000" cy="1476000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>18300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>80025</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2952000" cy="1404000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>10785</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>171949</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2808000" cy="1368000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1104300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>160575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="3276000" cy="1656000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>20360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>49483</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2880000" cy="1368000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -10865,916 +10433,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF1565C0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.77734375" customWidth="1" style="1223" min="1" max="2"/>
-    <col width="25.77734375" customWidth="1" style="1223" min="3" max="3"/>
-    <col width="12" customWidth="1" style="1223" min="4" max="4"/>
-    <col width="14" customWidth="1" style="1223" min="5" max="5"/>
-    <col width="48" customWidth="1" style="1223" min="7" max="7"/>
-    <col width="20" customWidth="1" style="1223" min="8" max="8"/>
-    <col width="38" customWidth="1" style="1223" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="1223">
-      <c r="A1" s="1253" t="n"/>
-      <c r="B1" s="1258" t="n"/>
-      <c r="C1" s="1258" t="n"/>
-      <c r="D1" s="667" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PLANOS Y REVISIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4.95" customHeight="1" s="1223">
-      <c r="A2" s="1258" t="n"/>
-      <c r="B2" s="1258" t="n"/>
-      <c r="C2" s="1258" t="n"/>
-      <c r="D2" s="664" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="1223">
-      <c r="A3" s="1258" t="n"/>
-      <c r="B3" s="1258" t="n"/>
-      <c r="C3" s="1258" t="n"/>
-      <c r="D3" s="665" t="n"/>
-      <c r="H3" s="662" t="inlineStr">
-        <is>
-          <t>CONTROL DOCUMENTAL</t>
-        </is>
-      </c>
-      <c r="I3" s="663" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="1223">
-      <c r="A4" s="1258" t="n"/>
-      <c r="B4" s="1258" t="n"/>
-      <c r="C4" s="1258" t="n"/>
-      <c r="D4" s="600" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="G4" s="546" t="n"/>
-      <c r="H4" s="274" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="I4" s="275" t="inlineStr">
-        <is>
-          <t>RYR-CO-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="1223">
-      <c r="A5" s="1258" t="n"/>
-      <c r="B5" s="1258" t="n"/>
-      <c r="C5" s="1258" t="n"/>
-      <c r="D5" s="656" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="G5" s="546" t="n"/>
-      <c r="H5" s="246" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="I5" s="243" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="1223">
-      <c r="A6" s="1258" t="n"/>
-      <c r="B6" s="1258" t="n"/>
-      <c r="C6" s="1258" t="n"/>
-      <c r="D6" s="666" t="n"/>
-      <c r="H6" s="246" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="I6" s="243" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1258" t="n"/>
-      <c r="B7" s="1258" t="n"/>
-      <c r="C7" s="1258" t="n"/>
-      <c r="D7" s="607" t="n"/>
-      <c r="E7" s="607" t="n"/>
-      <c r="F7" s="607" t="n"/>
-      <c r="G7" s="607" t="n"/>
-      <c r="H7" s="244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Página </t>
-        </is>
-      </c>
-      <c r="I7" s="245" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customFormat="1" customHeight="1" s="587">
-      <c r="A8" s="1252" t="inlineStr">
-        <is>
-          <t>Código plano</t>
-        </is>
-      </c>
-      <c r="B8" s="1252" t="inlineStr">
-        <is>
-          <t>Disciplina</t>
-        </is>
-      </c>
-      <c r="C8" s="1252" t="inlineStr">
-        <is>
-          <t>Título</t>
-        </is>
-      </c>
-      <c r="D8" s="249" t="inlineStr">
-        <is>
-          <t>Revisión</t>
-        </is>
-      </c>
-      <c r="E8" s="249" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="F8" s="249" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="G8" s="249" t="inlineStr">
-        <is>
-          <t>Actividades relacionadas</t>
-        </is>
-      </c>
-      <c r="H8" s="249" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="I8" s="249" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="655">
-      <c r="A9" s="253" t="inlineStr">
-        <is>
-          <t>ARQ-001</t>
-        </is>
-      </c>
-      <c r="B9" s="254" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="C9" s="250" t="inlineStr">
-        <is>
-          <t>Planta general</t>
-        </is>
-      </c>
-      <c r="D9" s="251" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="E9" s="476" t="n">
-        <v>46266</v>
-      </c>
-      <c r="F9" s="251" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G9" s="250" t="inlineStr">
-        <is>
-          <t>Preliminares / mampostería / acabados</t>
-        </is>
-      </c>
-      <c r="H9" s="250" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I9" s="252" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="655">
-      <c r="A10" s="253" t="inlineStr">
-        <is>
-          <t>EST-101</t>
-        </is>
-      </c>
-      <c r="B10" s="254" t="inlineStr">
-        <is>
-          <t>Estructural</t>
-        </is>
-      </c>
-      <c r="C10" s="250" t="inlineStr">
-        <is>
-          <t>Cimentación</t>
-        </is>
-      </c>
-      <c r="D10" s="251" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="E10" s="476" t="n">
-        <v>46254</v>
-      </c>
-      <c r="F10" s="251" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G10" s="250" t="inlineStr">
-        <is>
-          <t>Cimentaciones / estructura</t>
-        </is>
-      </c>
-      <c r="H10" s="250" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I10" s="252" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="655">
-      <c r="A11" s="253" t="inlineStr">
-        <is>
-          <t>HID-201</t>
-        </is>
-      </c>
-      <c r="B11" s="254" t="inlineStr">
-        <is>
-          <t>Hidrosanitaria</t>
-        </is>
-      </c>
-      <c r="C11" s="250" t="inlineStr">
-        <is>
-          <t>Redes hidrosanitarias</t>
-        </is>
-      </c>
-      <c r="D11" s="251" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="E11" s="476" t="n">
-        <v>46262</v>
-      </c>
-      <c r="F11" s="251" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G11" s="250" t="inlineStr">
-        <is>
-          <t>Instalaciones hidrosanitarias</t>
-        </is>
-      </c>
-      <c r="H11" s="250" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I11" s="252" t="n"/>
-    </row>
-    <row r="12" customFormat="1" s="655">
-      <c r="A12" s="253" t="inlineStr">
-        <is>
-          <t>ELE-301</t>
-        </is>
-      </c>
-      <c r="B12" s="254" t="inlineStr">
-        <is>
-          <t>Eléctrica</t>
-        </is>
-      </c>
-      <c r="C12" s="250" t="inlineStr">
-        <is>
-          <t>Fuerza e iluminación</t>
-        </is>
-      </c>
-      <c r="D12" s="251" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="E12" s="476" t="n">
-        <v>46267</v>
-      </c>
-      <c r="F12" s="251" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G12" s="250" t="inlineStr">
-        <is>
-          <t>Instalaciones eléctricas</t>
-        </is>
-      </c>
-      <c r="H12" s="250" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I12" s="252" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="248" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="247" t="n"/>
-      <c r="C13" s="247" t="n"/>
-      <c r="D13" s="247" t="n"/>
-      <c r="E13" s="247" t="n"/>
-      <c r="F13" s="247" t="n"/>
-      <c r="G13" s="247" t="n"/>
-      <c r="H13" s="247" t="n"/>
-      <c r="I13" s="349">
-        <f>I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="247" t="n"/>
-      <c r="B14" s="247" t="n"/>
-      <c r="C14" s="247" t="n"/>
-      <c r="D14" s="247" t="n"/>
-      <c r="E14" s="247" t="n"/>
-      <c r="F14" s="247" t="n"/>
-      <c r="G14" s="247" t="n"/>
-      <c r="H14" s="247" t="n"/>
-      <c r="I14" s="247" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="247" t="n"/>
-      <c r="B15" s="247" t="n"/>
-      <c r="C15" s="247" t="n"/>
-      <c r="D15" s="247" t="n"/>
-      <c r="E15" s="247" t="n"/>
-      <c r="F15" s="247" t="n"/>
-      <c r="G15" s="247" t="n"/>
-      <c r="H15" s="247" t="n"/>
-      <c r="I15" s="247" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="247" t="n"/>
-      <c r="B16" s="247" t="n"/>
-      <c r="C16" s="247" t="n"/>
-      <c r="D16" s="247" t="n"/>
-      <c r="E16" s="247" t="n"/>
-      <c r="F16" s="247" t="n"/>
-      <c r="G16" s="247" t="n"/>
-      <c r="H16" s="247" t="n"/>
-      <c r="I16" s="247" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="247" t="n"/>
-      <c r="B17" s="247" t="n"/>
-      <c r="C17" s="247" t="n"/>
-      <c r="D17" s="247" t="n"/>
-      <c r="E17" s="247" t="n"/>
-      <c r="F17" s="247" t="n"/>
-      <c r="G17" s="247" t="n"/>
-      <c r="H17" s="247" t="n"/>
-      <c r="I17" s="247" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="247" t="n"/>
-      <c r="B18" s="247" t="n"/>
-      <c r="C18" s="247" t="n"/>
-      <c r="D18" s="247" t="n"/>
-      <c r="E18" s="247" t="n"/>
-      <c r="F18" s="247" t="n"/>
-      <c r="G18" s="247" t="n"/>
-      <c r="H18" s="247" t="n"/>
-      <c r="I18" s="247" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="247" t="n"/>
-      <c r="B19" s="247" t="n"/>
-      <c r="C19" s="247" t="n"/>
-      <c r="D19" s="247" t="n"/>
-      <c r="E19" s="247" t="n"/>
-      <c r="F19" s="247" t="n"/>
-      <c r="G19" s="247" t="n"/>
-      <c r="H19" s="247" t="n"/>
-      <c r="I19" s="247" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="247" t="n"/>
-      <c r="B20" s="247" t="n"/>
-      <c r="C20" s="247" t="n"/>
-      <c r="D20" s="247" t="n"/>
-      <c r="E20" s="247" t="n"/>
-      <c r="F20" s="247" t="n"/>
-      <c r="G20" s="247" t="n"/>
-      <c r="H20" s="247" t="n"/>
-      <c r="I20" s="247" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="247" t="n"/>
-      <c r="B21" s="247" t="n"/>
-      <c r="C21" s="247" t="n"/>
-      <c r="D21" s="247" t="n"/>
-      <c r="E21" s="247" t="n"/>
-      <c r="F21" s="247" t="n"/>
-      <c r="G21" s="247" t="n"/>
-      <c r="H21" s="247" t="n"/>
-      <c r="I21" s="247" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="247" t="n"/>
-      <c r="B22" s="247" t="n"/>
-      <c r="C22" s="247" t="n"/>
-      <c r="D22" s="247" t="n"/>
-      <c r="E22" s="247" t="n"/>
-      <c r="F22" s="247" t="n"/>
-      <c r="G22" s="247" t="n"/>
-      <c r="H22" s="247" t="n"/>
-      <c r="I22" s="247" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="247" t="n"/>
-      <c r="B23" s="247" t="n"/>
-      <c r="C23" s="247" t="n"/>
-      <c r="D23" s="247" t="n"/>
-      <c r="E23" s="247" t="n"/>
-      <c r="F23" s="247" t="n"/>
-      <c r="G23" s="247" t="n"/>
-      <c r="H23" s="247" t="n"/>
-      <c r="I23" s="247" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="247" t="n"/>
-      <c r="B24" s="247" t="n"/>
-      <c r="C24" s="247" t="n"/>
-      <c r="D24" s="247" t="n"/>
-      <c r="E24" s="247" t="n"/>
-      <c r="F24" s="247" t="n"/>
-      <c r="G24" s="247" t="n"/>
-      <c r="H24" s="247" t="n"/>
-      <c r="I24" s="247" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="247" t="n"/>
-      <c r="B25" s="247" t="n"/>
-      <c r="C25" s="247" t="n"/>
-      <c r="D25" s="247" t="n"/>
-      <c r="E25" s="247" t="n"/>
-      <c r="F25" s="247" t="n"/>
-      <c r="G25" s="247" t="n"/>
-      <c r="H25" s="247" t="n"/>
-      <c r="I25" s="247" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="281" t="n"/>
-      <c r="B26" s="281" t="n"/>
-      <c r="C26" s="281" t="n"/>
-      <c r="D26" s="281" t="n"/>
-      <c r="E26" s="281" t="n"/>
-      <c r="F26" s="281" t="n"/>
-      <c r="G26" s="281" t="n"/>
-      <c r="H26" s="281" t="n"/>
-      <c r="I26" s="281" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="281" t="n"/>
-      <c r="B27" s="281" t="n"/>
-      <c r="C27" s="281" t="n"/>
-      <c r="D27" s="281" t="n"/>
-      <c r="E27" s="281" t="n"/>
-      <c r="F27" s="281" t="n"/>
-      <c r="G27" s="281" t="n"/>
-      <c r="H27" s="281" t="n"/>
-      <c r="I27" s="281" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="281" t="n"/>
-      <c r="B28" s="281" t="n"/>
-      <c r="C28" s="281" t="n"/>
-      <c r="D28" s="281" t="n"/>
-      <c r="E28" s="281" t="n"/>
-      <c r="F28" s="281" t="n"/>
-      <c r="G28" s="281" t="n"/>
-      <c r="H28" s="281" t="n"/>
-      <c r="I28" s="281" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="281" t="n"/>
-      <c r="B29" s="281" t="n"/>
-      <c r="C29" s="281" t="n"/>
-      <c r="D29" s="281" t="n"/>
-      <c r="E29" s="281" t="n"/>
-      <c r="F29" s="281" t="n"/>
-      <c r="G29" s="281" t="n"/>
-      <c r="H29" s="281" t="n"/>
-      <c r="I29" s="281" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="281" t="n"/>
-      <c r="B30" s="281" t="n"/>
-      <c r="C30" s="281" t="n"/>
-      <c r="D30" s="281" t="n"/>
-      <c r="E30" s="281" t="n"/>
-      <c r="F30" s="281" t="n"/>
-      <c r="G30" s="281" t="n"/>
-      <c r="H30" s="281" t="n"/>
-      <c r="I30" s="281" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="281" t="n"/>
-      <c r="B31" s="281" t="n"/>
-      <c r="C31" s="281" t="n"/>
-      <c r="D31" s="281" t="n"/>
-      <c r="E31" s="281" t="n"/>
-      <c r="F31" s="281" t="n"/>
-      <c r="G31" s="281" t="n"/>
-      <c r="H31" s="281" t="n"/>
-      <c r="I31" s="281" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="281" t="n"/>
-      <c r="B32" s="281" t="n"/>
-      <c r="C32" s="281" t="n"/>
-      <c r="D32" s="281" t="n"/>
-      <c r="E32" s="281" t="n"/>
-      <c r="F32" s="281" t="n"/>
-      <c r="G32" s="281" t="n"/>
-      <c r="H32" s="281" t="n"/>
-      <c r="I32" s="281" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="281" t="n"/>
-      <c r="B33" s="281" t="n"/>
-      <c r="C33" s="281" t="n"/>
-      <c r="D33" s="281" t="n"/>
-      <c r="E33" s="281" t="n"/>
-      <c r="F33" s="281" t="n"/>
-      <c r="G33" s="281" t="n"/>
-      <c r="H33" s="281" t="n"/>
-      <c r="I33" s="281" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="281" t="n"/>
-      <c r="B34" s="281" t="n"/>
-      <c r="C34" s="281" t="n"/>
-      <c r="D34" s="281" t="n"/>
-      <c r="E34" s="281" t="n"/>
-      <c r="F34" s="281" t="n"/>
-      <c r="G34" s="281" t="n"/>
-      <c r="H34" s="281" t="n"/>
-      <c r="I34" s="281" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D6:G7"/>
-    <mergeCell ref="D1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF1565C0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="18" customWidth="1" style="1223" min="1" max="1"/>
-    <col width="15.77734375" customWidth="1" style="1223" min="11" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="1223">
-      <c r="A1" s="1250" t="n"/>
-      <c r="B1" s="1250" t="n"/>
-      <c r="C1" s="1250" t="n"/>
-      <c r="D1" s="1251" t="n"/>
-      <c r="E1" s="585" t="inlineStr">
-        <is>
-          <t>INSTRUCTIVO DE USO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4.95" customHeight="1" s="1223">
-      <c r="A2" s="1250" t="n"/>
-      <c r="B2" s="1250" t="n"/>
-      <c r="C2" s="1250" t="n"/>
-      <c r="D2" s="1258" t="n"/>
-      <c r="E2" s="671" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="1223">
-      <c r="A3" s="1250" t="n"/>
-      <c r="B3" s="1250" t="n"/>
-      <c r="C3" s="1250" t="n"/>
-      <c r="D3" s="1258" t="n"/>
-      <c r="E3" s="587" t="n"/>
-      <c r="K3" s="673" t="inlineStr">
-        <is>
-          <t>CONTROL DOCUMENTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="1223">
-      <c r="A4" s="1250" t="n"/>
-      <c r="B4" s="1250" t="n"/>
-      <c r="C4" s="1250" t="n"/>
-      <c r="D4" s="1258" t="n"/>
-      <c r="E4" s="600" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="J4" s="546" t="n"/>
-      <c r="K4" s="255" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="L4" s="668" t="inlineStr">
-        <is>
-          <t>RYR-CO-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="1223">
-      <c r="A5" s="1250" t="n"/>
-      <c r="B5" s="1250" t="n"/>
-      <c r="C5" s="1250" t="n"/>
-      <c r="D5" s="1258" t="n"/>
-      <c r="E5" s="656" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="J5" s="546" t="n"/>
-      <c r="K5" s="255" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="L5" s="668" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="14.4" customHeight="1" s="1223">
-      <c r="A6" s="1250" t="n"/>
-      <c r="B6" s="1250" t="n"/>
-      <c r="C6" s="1250" t="n"/>
-      <c r="D6" s="1258" t="n"/>
-      <c r="E6" s="587" t="n"/>
-      <c r="K6" s="255" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="L6" s="668" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="1223">
-      <c r="A7" s="1250" t="n"/>
-      <c r="B7" s="1250" t="n"/>
-      <c r="C7" s="1250" t="n"/>
-      <c r="D7" s="1258" t="n"/>
-      <c r="K7" s="255" t="inlineStr">
-        <is>
-          <t>Página</t>
-        </is>
-      </c>
-      <c r="L7" s="668" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="19.95" customHeight="1" s="1223">
-      <c r="A8" s="669" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES — INSTRUCTIVO DE CANTIDADES</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="1223">
-      <c r="A9" s="672" t="inlineStr">
-        <is>
-          <t>1. IDENTIFICAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="1223">
-      <c r="A10" s="670" t="inlineStr">
-        <is>
-          <t>Use el código y actividad específica del catálogo; defina ubicación/frente y plano/revisión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="1223"/>
-    <row r="12" ht="15" customHeight="1" s="1223">
-      <c r="A12" s="672" t="inlineStr">
-        <is>
-          <t>2. MEDIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="1223">
-      <c r="A13" s="670" t="inlineStr">
-        <is>
-          <t>Ingrese solo las dimensiones aplicables a la actividad: largo, ancho, alto/profundidad, espesor y número de elementos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="1223"/>
-    <row r="15" ht="15" customHeight="1" s="1223">
-      <c r="A15" s="672" t="inlineStr">
-        <is>
-          <t>3. REPETIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="1223">
-      <c r="A16" s="670" t="inlineStr">
-        <is>
-          <t>Use N° de elementos para componentes repetitivos y Repeticiones para módulos o conjuntos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="1223"/>
-    <row r="18" ht="15" customHeight="1" s="1223">
-      <c r="A18" s="672" t="inlineStr">
-        <is>
-          <t>4. DEDUCIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1223">
-      <c r="A19" s="670" t="inlineStr">
-        <is>
-          <t>Registre vanos, vacíos u otros descuentos en Deducción y explique el criterio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1223"/>
-    <row r="21" ht="15" customHeight="1" s="1223">
-      <c r="A21" s="672" t="inlineStr">
-        <is>
-          <t>5. DESPERDICIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="1223">
-      <c r="A22" s="670" t="inlineStr">
-        <is>
-          <t>Ingrese el porcentaje como decimal (5% = 0,05) solo si está técnicamente o contractualmente sustentado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1223"/>
-    <row r="24" ht="15" customHeight="1" s="1223">
-      <c r="A24" s="672" t="inlineStr">
-        <is>
-          <t>6. TRAZABILIDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="1223">
-      <c r="A25" s="670" t="inlineStr">
-        <is>
-          <t>Toda cantidad debe poder rastrearse a plano, detalle, especificación, medición de campo o documento contractual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="1223"/>
-    <row r="27">
-      <c r="A27" s="672" t="inlineStr">
-        <is>
-          <t>7. VALIDAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="14.4" customHeight="1" s="1223">
-      <c r="A28" s="670" t="inlineStr">
-        <is>
-          <t>Compare contra presupuesto, APU, planos y medición de campo; documente diferencias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="672" t="inlineStr">
-        <is>
-          <t>8. APROBAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="14.4" customHeight="1" s="1223">
-      <c r="A31" s="670" t="inlineStr">
-        <is>
-          <t>Cambie el Estado a Aprobada solo después de la revisión técnica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="206" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="206" t="n"/>
-      <c r="C33" s="206" t="n"/>
-      <c r="D33" s="206" t="n"/>
-      <c r="E33" s="206" t="n"/>
-      <c r="F33" s="206" t="n"/>
-      <c r="G33" s="206" t="n"/>
-      <c r="H33" s="206" t="n"/>
-      <c r="I33" s="206" t="n"/>
-      <c r="J33" s="206" t="n"/>
-      <c r="K33" s="206" t="n"/>
-      <c r="L33" s="206" t="n"/>
-      <c r="M33" s="205">
-        <f>L4</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="E1:M1"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="E2:M2"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="A25:M25"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="E6:J7"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A21:M21"/>
-    <mergeCell ref="E4:J4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -24030,7 +22689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -24048,7 +22707,7 @@
       <c r="A1" s="1255" t="n"/>
       <c r="B1" s="1259" t="inlineStr">
         <is>
-          <t>REFORMAS Y REMODELACIONES</t>
+          <t>DASHBOARD</t>
         </is>
       </c>
       <c r="C1" s="636" t="n"/>
@@ -25088,7 +23747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -28513,7 +27172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -33871,4 +32530,913 @@
   <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1565C0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="15.77734375" customWidth="1" style="1223" min="1" max="2"/>
+    <col width="25.77734375" customWidth="1" style="1223" min="3" max="3"/>
+    <col width="12" customWidth="1" style="1223" min="4" max="4"/>
+    <col width="14" customWidth="1" style="1223" min="5" max="5"/>
+    <col width="48" customWidth="1" style="1223" min="7" max="7"/>
+    <col width="20" customWidth="1" style="1223" min="8" max="8"/>
+    <col width="38" customWidth="1" style="1223" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40.05" customHeight="1" s="1223">
+      <c r="A1" s="1253" t="n"/>
+      <c r="B1" s="1258" t="n"/>
+      <c r="C1" s="1258" t="n"/>
+      <c r="D1" s="667" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PLANOS Y REVISIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4.95" customHeight="1" s="1223">
+      <c r="A2" s="1258" t="n"/>
+      <c r="B2" s="1258" t="n"/>
+      <c r="C2" s="1258" t="n"/>
+      <c r="D2" s="664" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="1223">
+      <c r="A3" s="1258" t="n"/>
+      <c r="B3" s="1258" t="n"/>
+      <c r="C3" s="1258" t="n"/>
+      <c r="D3" s="665" t="n"/>
+      <c r="H3" s="662" t="inlineStr">
+        <is>
+          <t>CONTROL DOCUMENTAL</t>
+        </is>
+      </c>
+      <c r="I3" s="663" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="1223">
+      <c r="A4" s="1258" t="n"/>
+      <c r="B4" s="1258" t="n"/>
+      <c r="C4" s="1258" t="n"/>
+      <c r="D4" s="600" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="G4" s="546" t="n"/>
+      <c r="H4" s="274" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="I4" s="275" t="inlineStr">
+        <is>
+          <t>RYR-CO-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="1223">
+      <c r="A5" s="1258" t="n"/>
+      <c r="B5" s="1258" t="n"/>
+      <c r="C5" s="1258" t="n"/>
+      <c r="D5" s="656" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="G5" s="546" t="n"/>
+      <c r="H5" s="246" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="I5" s="243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="1223">
+      <c r="A6" s="1258" t="n"/>
+      <c r="B6" s="1258" t="n"/>
+      <c r="C6" s="1258" t="n"/>
+      <c r="D6" s="666" t="n"/>
+      <c r="H6" s="246" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="I6" s="243" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1258" t="n"/>
+      <c r="B7" s="1258" t="n"/>
+      <c r="C7" s="1258" t="n"/>
+      <c r="D7" s="607" t="n"/>
+      <c r="E7" s="607" t="n"/>
+      <c r="F7" s="607" t="n"/>
+      <c r="G7" s="607" t="n"/>
+      <c r="H7" s="244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Página </t>
+        </is>
+      </c>
+      <c r="I7" s="245" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customFormat="1" customHeight="1" s="587">
+      <c r="A8" s="1252" t="inlineStr">
+        <is>
+          <t>Código plano</t>
+        </is>
+      </c>
+      <c r="B8" s="1252" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="C8" s="1252" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="D8" s="249" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="E8" s="249" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="F8" s="249" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="G8" s="249" t="inlineStr">
+        <is>
+          <t>Actividades relacionadas</t>
+        </is>
+      </c>
+      <c r="H8" s="249" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="I8" s="249" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="655">
+      <c r="A9" s="253" t="inlineStr">
+        <is>
+          <t>ARQ-001</t>
+        </is>
+      </c>
+      <c r="B9" s="254" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="C9" s="250" t="inlineStr">
+        <is>
+          <t>Planta general</t>
+        </is>
+      </c>
+      <c r="D9" s="251" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E9" s="476" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F9" s="251" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G9" s="250" t="inlineStr">
+        <is>
+          <t>Preliminares / mampostería / acabados</t>
+        </is>
+      </c>
+      <c r="H9" s="250" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I9" s="252" t="n"/>
+    </row>
+    <row r="10" customFormat="1" s="655">
+      <c r="A10" s="253" t="inlineStr">
+        <is>
+          <t>EST-101</t>
+        </is>
+      </c>
+      <c r="B10" s="254" t="inlineStr">
+        <is>
+          <t>Estructural</t>
+        </is>
+      </c>
+      <c r="C10" s="250" t="inlineStr">
+        <is>
+          <t>Cimentación</t>
+        </is>
+      </c>
+      <c r="D10" s="251" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="E10" s="476" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F10" s="251" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G10" s="250" t="inlineStr">
+        <is>
+          <t>Cimentaciones / estructura</t>
+        </is>
+      </c>
+      <c r="H10" s="250" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I10" s="252" t="n"/>
+    </row>
+    <row r="11" customFormat="1" s="655">
+      <c r="A11" s="253" t="inlineStr">
+        <is>
+          <t>HID-201</t>
+        </is>
+      </c>
+      <c r="B11" s="254" t="inlineStr">
+        <is>
+          <t>Hidrosanitaria</t>
+        </is>
+      </c>
+      <c r="C11" s="250" t="inlineStr">
+        <is>
+          <t>Redes hidrosanitarias</t>
+        </is>
+      </c>
+      <c r="D11" s="251" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E11" s="476" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F11" s="251" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G11" s="250" t="inlineStr">
+        <is>
+          <t>Instalaciones hidrosanitarias</t>
+        </is>
+      </c>
+      <c r="H11" s="250" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I11" s="252" t="n"/>
+    </row>
+    <row r="12" customFormat="1" s="655">
+      <c r="A12" s="253" t="inlineStr">
+        <is>
+          <t>ELE-301</t>
+        </is>
+      </c>
+      <c r="B12" s="254" t="inlineStr">
+        <is>
+          <t>Eléctrica</t>
+        </is>
+      </c>
+      <c r="C12" s="250" t="inlineStr">
+        <is>
+          <t>Fuerza e iluminación</t>
+        </is>
+      </c>
+      <c r="D12" s="251" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E12" s="476" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F12" s="251" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G12" s="250" t="inlineStr">
+        <is>
+          <t>Instalaciones eléctricas</t>
+        </is>
+      </c>
+      <c r="H12" s="250" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I12" s="252" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="248" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="247" t="n"/>
+      <c r="C13" s="247" t="n"/>
+      <c r="D13" s="247" t="n"/>
+      <c r="E13" s="247" t="n"/>
+      <c r="F13" s="247" t="n"/>
+      <c r="G13" s="247" t="n"/>
+      <c r="H13" s="247" t="n"/>
+      <c r="I13" s="349">
+        <f>I4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="247" t="n"/>
+      <c r="B14" s="247" t="n"/>
+      <c r="C14" s="247" t="n"/>
+      <c r="D14" s="247" t="n"/>
+      <c r="E14" s="247" t="n"/>
+      <c r="F14" s="247" t="n"/>
+      <c r="G14" s="247" t="n"/>
+      <c r="H14" s="247" t="n"/>
+      <c r="I14" s="247" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="247" t="n"/>
+      <c r="B15" s="247" t="n"/>
+      <c r="C15" s="247" t="n"/>
+      <c r="D15" s="247" t="n"/>
+      <c r="E15" s="247" t="n"/>
+      <c r="F15" s="247" t="n"/>
+      <c r="G15" s="247" t="n"/>
+      <c r="H15" s="247" t="n"/>
+      <c r="I15" s="247" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="247" t="n"/>
+      <c r="B16" s="247" t="n"/>
+      <c r="C16" s="247" t="n"/>
+      <c r="D16" s="247" t="n"/>
+      <c r="E16" s="247" t="n"/>
+      <c r="F16" s="247" t="n"/>
+      <c r="G16" s="247" t="n"/>
+      <c r="H16" s="247" t="n"/>
+      <c r="I16" s="247" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="247" t="n"/>
+      <c r="B17" s="247" t="n"/>
+      <c r="C17" s="247" t="n"/>
+      <c r="D17" s="247" t="n"/>
+      <c r="E17" s="247" t="n"/>
+      <c r="F17" s="247" t="n"/>
+      <c r="G17" s="247" t="n"/>
+      <c r="H17" s="247" t="n"/>
+      <c r="I17" s="247" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="247" t="n"/>
+      <c r="B18" s="247" t="n"/>
+      <c r="C18" s="247" t="n"/>
+      <c r="D18" s="247" t="n"/>
+      <c r="E18" s="247" t="n"/>
+      <c r="F18" s="247" t="n"/>
+      <c r="G18" s="247" t="n"/>
+      <c r="H18" s="247" t="n"/>
+      <c r="I18" s="247" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="247" t="n"/>
+      <c r="B19" s="247" t="n"/>
+      <c r="C19" s="247" t="n"/>
+      <c r="D19" s="247" t="n"/>
+      <c r="E19" s="247" t="n"/>
+      <c r="F19" s="247" t="n"/>
+      <c r="G19" s="247" t="n"/>
+      <c r="H19" s="247" t="n"/>
+      <c r="I19" s="247" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="247" t="n"/>
+      <c r="B20" s="247" t="n"/>
+      <c r="C20" s="247" t="n"/>
+      <c r="D20" s="247" t="n"/>
+      <c r="E20" s="247" t="n"/>
+      <c r="F20" s="247" t="n"/>
+      <c r="G20" s="247" t="n"/>
+      <c r="H20" s="247" t="n"/>
+      <c r="I20" s="247" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="247" t="n"/>
+      <c r="B21" s="247" t="n"/>
+      <c r="C21" s="247" t="n"/>
+      <c r="D21" s="247" t="n"/>
+      <c r="E21" s="247" t="n"/>
+      <c r="F21" s="247" t="n"/>
+      <c r="G21" s="247" t="n"/>
+      <c r="H21" s="247" t="n"/>
+      <c r="I21" s="247" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="247" t="n"/>
+      <c r="B22" s="247" t="n"/>
+      <c r="C22" s="247" t="n"/>
+      <c r="D22" s="247" t="n"/>
+      <c r="E22" s="247" t="n"/>
+      <c r="F22" s="247" t="n"/>
+      <c r="G22" s="247" t="n"/>
+      <c r="H22" s="247" t="n"/>
+      <c r="I22" s="247" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="247" t="n"/>
+      <c r="B23" s="247" t="n"/>
+      <c r="C23" s="247" t="n"/>
+      <c r="D23" s="247" t="n"/>
+      <c r="E23" s="247" t="n"/>
+      <c r="F23" s="247" t="n"/>
+      <c r="G23" s="247" t="n"/>
+      <c r="H23" s="247" t="n"/>
+      <c r="I23" s="247" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="247" t="n"/>
+      <c r="B24" s="247" t="n"/>
+      <c r="C24" s="247" t="n"/>
+      <c r="D24" s="247" t="n"/>
+      <c r="E24" s="247" t="n"/>
+      <c r="F24" s="247" t="n"/>
+      <c r="G24" s="247" t="n"/>
+      <c r="H24" s="247" t="n"/>
+      <c r="I24" s="247" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="247" t="n"/>
+      <c r="B25" s="247" t="n"/>
+      <c r="C25" s="247" t="n"/>
+      <c r="D25" s="247" t="n"/>
+      <c r="E25" s="247" t="n"/>
+      <c r="F25" s="247" t="n"/>
+      <c r="G25" s="247" t="n"/>
+      <c r="H25" s="247" t="n"/>
+      <c r="I25" s="247" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="281" t="n"/>
+      <c r="B26" s="281" t="n"/>
+      <c r="C26" s="281" t="n"/>
+      <c r="D26" s="281" t="n"/>
+      <c r="E26" s="281" t="n"/>
+      <c r="F26" s="281" t="n"/>
+      <c r="G26" s="281" t="n"/>
+      <c r="H26" s="281" t="n"/>
+      <c r="I26" s="281" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="281" t="n"/>
+      <c r="B27" s="281" t="n"/>
+      <c r="C27" s="281" t="n"/>
+      <c r="D27" s="281" t="n"/>
+      <c r="E27" s="281" t="n"/>
+      <c r="F27" s="281" t="n"/>
+      <c r="G27" s="281" t="n"/>
+      <c r="H27" s="281" t="n"/>
+      <c r="I27" s="281" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="281" t="n"/>
+      <c r="B28" s="281" t="n"/>
+      <c r="C28" s="281" t="n"/>
+      <c r="D28" s="281" t="n"/>
+      <c r="E28" s="281" t="n"/>
+      <c r="F28" s="281" t="n"/>
+      <c r="G28" s="281" t="n"/>
+      <c r="H28" s="281" t="n"/>
+      <c r="I28" s="281" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="281" t="n"/>
+      <c r="B29" s="281" t="n"/>
+      <c r="C29" s="281" t="n"/>
+      <c r="D29" s="281" t="n"/>
+      <c r="E29" s="281" t="n"/>
+      <c r="F29" s="281" t="n"/>
+      <c r="G29" s="281" t="n"/>
+      <c r="H29" s="281" t="n"/>
+      <c r="I29" s="281" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="281" t="n"/>
+      <c r="B30" s="281" t="n"/>
+      <c r="C30" s="281" t="n"/>
+      <c r="D30" s="281" t="n"/>
+      <c r="E30" s="281" t="n"/>
+      <c r="F30" s="281" t="n"/>
+      <c r="G30" s="281" t="n"/>
+      <c r="H30" s="281" t="n"/>
+      <c r="I30" s="281" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="281" t="n"/>
+      <c r="B31" s="281" t="n"/>
+      <c r="C31" s="281" t="n"/>
+      <c r="D31" s="281" t="n"/>
+      <c r="E31" s="281" t="n"/>
+      <c r="F31" s="281" t="n"/>
+      <c r="G31" s="281" t="n"/>
+      <c r="H31" s="281" t="n"/>
+      <c r="I31" s="281" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="281" t="n"/>
+      <c r="B32" s="281" t="n"/>
+      <c r="C32" s="281" t="n"/>
+      <c r="D32" s="281" t="n"/>
+      <c r="E32" s="281" t="n"/>
+      <c r="F32" s="281" t="n"/>
+      <c r="G32" s="281" t="n"/>
+      <c r="H32" s="281" t="n"/>
+      <c r="I32" s="281" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="281" t="n"/>
+      <c r="B33" s="281" t="n"/>
+      <c r="C33" s="281" t="n"/>
+      <c r="D33" s="281" t="n"/>
+      <c r="E33" s="281" t="n"/>
+      <c r="F33" s="281" t="n"/>
+      <c r="G33" s="281" t="n"/>
+      <c r="H33" s="281" t="n"/>
+      <c r="I33" s="281" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="281" t="n"/>
+      <c r="B34" s="281" t="n"/>
+      <c r="C34" s="281" t="n"/>
+      <c r="D34" s="281" t="n"/>
+      <c r="E34" s="281" t="n"/>
+      <c r="F34" s="281" t="n"/>
+      <c r="G34" s="281" t="n"/>
+      <c r="H34" s="281" t="n"/>
+      <c r="I34" s="281" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:G7"/>
+    <mergeCell ref="D1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1565C0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18" customWidth="1" style="1223" min="1" max="1"/>
+    <col width="15.77734375" customWidth="1" style="1223" min="11" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40.05" customHeight="1" s="1223">
+      <c r="A1" s="1250" t="n"/>
+      <c r="B1" s="1250" t="n"/>
+      <c r="C1" s="1250" t="n"/>
+      <c r="D1" s="1251" t="n"/>
+      <c r="E1" s="585" t="inlineStr">
+        <is>
+          <t>INSTRUCTIVO DE USO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4.95" customHeight="1" s="1223">
+      <c r="A2" s="1250" t="n"/>
+      <c r="B2" s="1250" t="n"/>
+      <c r="C2" s="1250" t="n"/>
+      <c r="D2" s="1258" t="n"/>
+      <c r="E2" s="671" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="1223">
+      <c r="A3" s="1250" t="n"/>
+      <c r="B3" s="1250" t="n"/>
+      <c r="C3" s="1250" t="n"/>
+      <c r="D3" s="1258" t="n"/>
+      <c r="E3" s="587" t="n"/>
+      <c r="K3" s="673" t="inlineStr">
+        <is>
+          <t>CONTROL DOCUMENTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="1223">
+      <c r="A4" s="1250" t="n"/>
+      <c r="B4" s="1250" t="n"/>
+      <c r="C4" s="1250" t="n"/>
+      <c r="D4" s="1258" t="n"/>
+      <c r="E4" s="600" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="J4" s="546" t="n"/>
+      <c r="K4" s="255" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="L4" s="668" t="inlineStr">
+        <is>
+          <t>RYR-CO-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="1223">
+      <c r="A5" s="1250" t="n"/>
+      <c r="B5" s="1250" t="n"/>
+      <c r="C5" s="1250" t="n"/>
+      <c r="D5" s="1258" t="n"/>
+      <c r="E5" s="656" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="J5" s="546" t="n"/>
+      <c r="K5" s="255" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="L5" s="668" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1" s="1223">
+      <c r="A6" s="1250" t="n"/>
+      <c r="B6" s="1250" t="n"/>
+      <c r="C6" s="1250" t="n"/>
+      <c r="D6" s="1258" t="n"/>
+      <c r="E6" s="587" t="n"/>
+      <c r="K6" s="255" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="L6" s="668" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="1223">
+      <c r="A7" s="1250" t="n"/>
+      <c r="B7" s="1250" t="n"/>
+      <c r="C7" s="1250" t="n"/>
+      <c r="D7" s="1258" t="n"/>
+      <c r="K7" s="255" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="L7" s="668" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.95" customHeight="1" s="1223">
+      <c r="A8" s="669" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES — INSTRUCTIVO DE CANTIDADES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="1223">
+      <c r="A9" s="672" t="inlineStr">
+        <is>
+          <t>1. IDENTIFICAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="1223">
+      <c r="A10" s="670" t="inlineStr">
+        <is>
+          <t>Use el código y actividad específica del catálogo; defina ubicación/frente y plano/revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="1223"/>
+    <row r="12" ht="15" customHeight="1" s="1223">
+      <c r="A12" s="672" t="inlineStr">
+        <is>
+          <t>2. MEDIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1223">
+      <c r="A13" s="670" t="inlineStr">
+        <is>
+          <t>Ingrese solo las dimensiones aplicables a la actividad: largo, ancho, alto/profundidad, espesor y número de elementos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="1223"/>
+    <row r="15" ht="15" customHeight="1" s="1223">
+      <c r="A15" s="672" t="inlineStr">
+        <is>
+          <t>3. REPETIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="1223">
+      <c r="A16" s="670" t="inlineStr">
+        <is>
+          <t>Use N° de elementos para componentes repetitivos y Repeticiones para módulos o conjuntos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="1223"/>
+    <row r="18" ht="15" customHeight="1" s="1223">
+      <c r="A18" s="672" t="inlineStr">
+        <is>
+          <t>4. DEDUCIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="1223">
+      <c r="A19" s="670" t="inlineStr">
+        <is>
+          <t>Registre vanos, vacíos u otros descuentos en Deducción y explique el criterio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="1223"/>
+    <row r="21" ht="15" customHeight="1" s="1223">
+      <c r="A21" s="672" t="inlineStr">
+        <is>
+          <t>5. DESPERDICIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="1223">
+      <c r="A22" s="670" t="inlineStr">
+        <is>
+          <t>Ingrese el porcentaje como decimal (5% = 0,05) solo si está técnicamente o contractualmente sustentado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="1223"/>
+    <row r="24" ht="15" customHeight="1" s="1223">
+      <c r="A24" s="672" t="inlineStr">
+        <is>
+          <t>6. TRAZABILIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="1223">
+      <c r="A25" s="670" t="inlineStr">
+        <is>
+          <t>Toda cantidad debe poder rastrearse a plano, detalle, especificación, medición de campo o documento contractual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="1223"/>
+    <row r="27">
+      <c r="A27" s="672" t="inlineStr">
+        <is>
+          <t>7. VALIDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14.4" customHeight="1" s="1223">
+      <c r="A28" s="670" t="inlineStr">
+        <is>
+          <t>Compare contra presupuesto, APU, planos y medición de campo; documente diferencias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="672" t="inlineStr">
+        <is>
+          <t>8. APROBAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14.4" customHeight="1" s="1223">
+      <c r="A31" s="670" t="inlineStr">
+        <is>
+          <t>Cambie el Estado a Aprobada solo después de la revisión técnica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="206" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="206" t="n"/>
+      <c r="C33" s="206" t="n"/>
+      <c r="D33" s="206" t="n"/>
+      <c r="E33" s="206" t="n"/>
+      <c r="F33" s="206" t="n"/>
+      <c r="G33" s="206" t="n"/>
+      <c r="H33" s="206" t="n"/>
+      <c r="I33" s="206" t="n"/>
+      <c r="J33" s="206" t="n"/>
+      <c r="K33" s="206" t="n"/>
+      <c r="L33" s="206" t="n"/>
+      <c r="M33" s="205">
+        <f>L4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="E2:M2"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="E6:J7"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="E4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="171" formatCode="\$\ #,##0"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="166">
+  <fonts count="167">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1219,6 +1219,10 @@
       <color rgb="006B7280"/>
       <sz val="8"/>
     </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6684,7 +6688,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1446">
+  <cellXfs count="1447">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10283,6 +10287,7 @@
     <xf numFmtId="2" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11776,7 +11781,7 @@
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y164"/>
+  <dimension ref="A1:Y169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="615" min="1" max="1"/>
@@ -12087,7 +12092,7 @@
       </c>
       <c r="E9" s="284" t="inlineStr">
         <is>
-          <t>Replanteo general de ejes y niveles</t>
+          <t>Localización y Replanteo</t>
         </is>
       </c>
       <c r="F9" s="285" t="n"/>
@@ -19391,7 +19396,7 @@
       </c>
       <c r="E97" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="F97" s="285" t="n"/>
@@ -21964,7 +21969,7 @@
       </c>
       <c r="E128" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="F128" s="285" t="n"/>
@@ -23998,7 +24003,162 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="539" t="inlineStr">
+      <c r="A164" s="280" t="inlineStr">
+        <is>
+          <t>MQ-157</t>
+        </is>
+      </c>
+      <c r="B164" s="281" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C164" s="282" t="n"/>
+      <c r="D164" s="283" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="E164" s="284" t="inlineStr">
+        <is>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+        </is>
+      </c>
+      <c r="F164" s="285" t="n"/>
+      <c r="G164" s="285" t="n"/>
+      <c r="H164" s="285" t="n"/>
+      <c r="I164" s="283" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="280" t="inlineStr">
+        <is>
+          <t>MQ-158</t>
+        </is>
+      </c>
+      <c r="B165" s="281" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C165" s="282" t="n"/>
+      <c r="D165" s="283" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="E165" s="284" t="inlineStr">
+        <is>
+          <t>Estudio de suelos y geotecnia</t>
+        </is>
+      </c>
+      <c r="F165" s="285" t="n"/>
+      <c r="G165" s="285" t="n"/>
+      <c r="H165" s="285" t="n"/>
+      <c r="I165" s="283" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="280" t="inlineStr">
+        <is>
+          <t>MQ-159</t>
+        </is>
+      </c>
+      <c r="B166" s="281" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C166" s="282" t="n"/>
+      <c r="D166" s="283" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="E166" s="284" t="inlineStr">
+        <is>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
+        </is>
+      </c>
+      <c r="F166" s="285" t="n"/>
+      <c r="G166" s="285" t="n"/>
+      <c r="H166" s="285" t="n"/>
+      <c r="I166" s="283" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="280" t="inlineStr">
+        <is>
+          <t>MQ-160</t>
+        </is>
+      </c>
+      <c r="B167" s="281" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C167" s="282" t="n"/>
+      <c r="D167" s="283" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="E167" s="284" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="F167" s="285" t="n"/>
+      <c r="G167" s="285" t="n"/>
+      <c r="H167" s="285" t="n"/>
+      <c r="I167" s="283" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="280" t="inlineStr">
+        <is>
+          <t>MQ-161</t>
+        </is>
+      </c>
+      <c r="B168" s="281" t="inlineStr">
+        <is>
+          <t>ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C168" s="282" t="n"/>
+      <c r="D168" s="283" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="E168" s="284" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de ascensor eléctrico</t>
+        </is>
+      </c>
+      <c r="F168" s="285" t="n"/>
+      <c r="G168" s="285" t="n"/>
+      <c r="H168" s="285" t="n"/>
+      <c r="I168" s="283" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1446" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cantidades de Obra" sheetId="1" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId7"/>
-    <sheet name="Cálculo Detallado" sheetId="3" r:id="rId8"/>
-    <sheet name="Catalogo de Actividades" sheetId="4" r:id="rId9"/>
-    <sheet name="Planos" sheetId="5" r:id="rId10"/>
-    <sheet name="Instructivo" sheetId="6" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantidades de Obra" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cálculo Detallado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de Actividades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructivo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -10419,7 +10420,187 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>18300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>80025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2952000" cy="1404000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>10785</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171949</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2808000" cy="1368000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1104300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>160575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="3276000" cy="1656000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>49483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2880000" cy="1368000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10464,7 +10645,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10494,186 +10675,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3060000" cy="1476000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>18300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>80025</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2952000" cy="1404000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>10785</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>171949</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2808000" cy="1368000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1104300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>160575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="3276000" cy="1656000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>20360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>49483</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2880000" cy="1368000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -10866,922 +10867,13 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.77734375" customWidth="1" style="550" min="1" max="2"/>
-    <col width="25.77734375" customWidth="1" style="550" min="3" max="3"/>
-    <col width="12" customWidth="1" style="550" min="4" max="4"/>
-    <col width="14" customWidth="1" style="550" min="5" max="5"/>
-    <col width="48" customWidth="1" style="550" min="7" max="7"/>
-    <col width="20" customWidth="1" style="550" min="8" max="8"/>
-    <col width="38" customWidth="1" style="550" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="550">
-      <c r="A1" s="508" t="n"/>
-      <c r="B1" s="618" t="n"/>
-      <c r="C1" s="618" t="n"/>
-      <c r="D1" s="696" t="inlineStr">
-        <is>
-          <t>REGISTRO DE PLANOS Y REVISIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4.95" customHeight="1" s="550">
-      <c r="A2" s="618" t="n"/>
-      <c r="B2" s="618" t="n"/>
-      <c r="C2" s="618" t="n"/>
-      <c r="D2" s="693" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="550">
-      <c r="A3" s="618" t="n"/>
-      <c r="B3" s="618" t="n"/>
-      <c r="C3" s="618" t="n"/>
-      <c r="D3" s="694" t="n"/>
-      <c r="H3" s="691" t="inlineStr">
-        <is>
-          <t>CONTROL DOCUMENTAL</t>
-        </is>
-      </c>
-      <c r="I3" s="692" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="550">
-      <c r="A4" s="618" t="n"/>
-      <c r="B4" s="618" t="n"/>
-      <c r="C4" s="618" t="n"/>
-      <c r="D4" s="564" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="G4" s="562" t="n"/>
-      <c r="H4" s="270" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="I4" s="271" t="inlineStr">
-        <is>
-          <t>RYR-CO-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="550">
-      <c r="A5" s="618" t="n"/>
-      <c r="B5" s="618" t="n"/>
-      <c r="C5" s="618" t="n"/>
-      <c r="D5" s="683" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="G5" s="562" t="n"/>
-      <c r="H5" s="242" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="I5" s="239" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="550">
-      <c r="A6" s="618" t="n"/>
-      <c r="B6" s="618" t="n"/>
-      <c r="C6" s="618" t="n"/>
-      <c r="D6" s="695" t="n"/>
-      <c r="H6" s="242" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="I6" s="239" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="618" t="n"/>
-      <c r="B7" s="618" t="n"/>
-      <c r="C7" s="618" t="n"/>
-      <c r="D7" s="633" t="n"/>
-      <c r="E7" s="633" t="n"/>
-      <c r="F7" s="633" t="n"/>
-      <c r="G7" s="633" t="n"/>
-      <c r="H7" s="240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Página </t>
-        </is>
-      </c>
-      <c r="I7" s="241" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customFormat="1" customHeight="1" s="615">
-      <c r="A8" s="507" t="inlineStr">
-        <is>
-          <t>Código plano</t>
-        </is>
-      </c>
-      <c r="B8" s="507" t="inlineStr">
-        <is>
-          <t>Disciplina</t>
-        </is>
-      </c>
-      <c r="C8" s="507" t="inlineStr">
-        <is>
-          <t>Título</t>
-        </is>
-      </c>
-      <c r="D8" s="245" t="inlineStr">
-        <is>
-          <t>Revisión</t>
-        </is>
-      </c>
-      <c r="E8" s="245" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="F8" s="245" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="G8" s="245" t="inlineStr">
-        <is>
-          <t>Actividades relacionadas</t>
-        </is>
-      </c>
-      <c r="H8" s="245" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="I8" s="245" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="690">
-      <c r="A9" s="249" t="inlineStr">
-        <is>
-          <t>ARQ-001</t>
-        </is>
-      </c>
-      <c r="B9" s="250" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="C9" s="246" t="inlineStr">
-        <is>
-          <t>Planta general</t>
-        </is>
-      </c>
-      <c r="D9" s="247" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="E9" s="1309" t="n">
-        <v>46266</v>
-      </c>
-      <c r="F9" s="247" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G9" s="246" t="inlineStr">
-        <is>
-          <t>Preliminares / mampostería / acabados</t>
-        </is>
-      </c>
-      <c r="H9" s="246" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I9" s="248" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="690">
-      <c r="A10" s="249" t="inlineStr">
-        <is>
-          <t>EST-101</t>
-        </is>
-      </c>
-      <c r="B10" s="250" t="inlineStr">
-        <is>
-          <t>Estructural</t>
-        </is>
-      </c>
-      <c r="C10" s="246" t="inlineStr">
-        <is>
-          <t>Cimentación</t>
-        </is>
-      </c>
-      <c r="D10" s="247" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="E10" s="1309" t="n">
-        <v>46254</v>
-      </c>
-      <c r="F10" s="247" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G10" s="246" t="inlineStr">
-        <is>
-          <t>Cimentaciones / estructura</t>
-        </is>
-      </c>
-      <c r="H10" s="246" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I10" s="248" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="690">
-      <c r="A11" s="249" t="inlineStr">
-        <is>
-          <t>HID-201</t>
-        </is>
-      </c>
-      <c r="B11" s="250" t="inlineStr">
-        <is>
-          <t>Hidrosanitaria</t>
-        </is>
-      </c>
-      <c r="C11" s="246" t="inlineStr">
-        <is>
-          <t>Redes hidrosanitarias</t>
-        </is>
-      </c>
-      <c r="D11" s="247" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="E11" s="1309" t="n">
-        <v>46262</v>
-      </c>
-      <c r="F11" s="247" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G11" s="246" t="inlineStr">
-        <is>
-          <t>Instalaciones hidrosanitarias</t>
-        </is>
-      </c>
-      <c r="H11" s="246" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I11" s="248" t="n"/>
-    </row>
-    <row r="12" customFormat="1" s="690">
-      <c r="A12" s="249" t="inlineStr">
-        <is>
-          <t>ELE-301</t>
-        </is>
-      </c>
-      <c r="B12" s="250" t="inlineStr">
-        <is>
-          <t>Eléctrica</t>
-        </is>
-      </c>
-      <c r="C12" s="246" t="inlineStr">
-        <is>
-          <t>Fuerza e iluminación</t>
-        </is>
-      </c>
-      <c r="D12" s="247" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="E12" s="1309" t="n">
-        <v>46267</v>
-      </c>
-      <c r="F12" s="247" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G12" s="246" t="inlineStr">
-        <is>
-          <t>Instalaciones eléctricas</t>
-        </is>
-      </c>
-      <c r="H12" s="246" t="inlineStr">
-        <is>
-          <t>Ing. Residente</t>
-        </is>
-      </c>
-      <c r="I12" s="248" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="244" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="243" t="n"/>
-      <c r="C13" s="243" t="n"/>
-      <c r="D13" s="243" t="n"/>
-      <c r="E13" s="243" t="n"/>
-      <c r="F13" s="243" t="n"/>
-      <c r="G13" s="243" t="n"/>
-      <c r="H13" s="243" t="n"/>
-      <c r="I13" s="344">
-        <f>I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="243" t="n"/>
-      <c r="B14" s="243" t="n"/>
-      <c r="C14" s="243" t="n"/>
-      <c r="D14" s="243" t="n"/>
-      <c r="E14" s="243" t="n"/>
-      <c r="F14" s="243" t="n"/>
-      <c r="G14" s="243" t="n"/>
-      <c r="H14" s="243" t="n"/>
-      <c r="I14" s="243" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="243" t="n"/>
-      <c r="B15" s="243" t="n"/>
-      <c r="C15" s="243" t="n"/>
-      <c r="D15" s="243" t="n"/>
-      <c r="E15" s="243" t="n"/>
-      <c r="F15" s="243" t="n"/>
-      <c r="G15" s="243" t="n"/>
-      <c r="H15" s="243" t="n"/>
-      <c r="I15" s="243" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="243" t="n"/>
-      <c r="B16" s="243" t="n"/>
-      <c r="C16" s="243" t="n"/>
-      <c r="D16" s="243" t="n"/>
-      <c r="E16" s="243" t="n"/>
-      <c r="F16" s="243" t="n"/>
-      <c r="G16" s="243" t="n"/>
-      <c r="H16" s="243" t="n"/>
-      <c r="I16" s="243" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="243" t="n"/>
-      <c r="B17" s="243" t="n"/>
-      <c r="C17" s="243" t="n"/>
-      <c r="D17" s="243" t="n"/>
-      <c r="E17" s="243" t="n"/>
-      <c r="F17" s="243" t="n"/>
-      <c r="G17" s="243" t="n"/>
-      <c r="H17" s="243" t="n"/>
-      <c r="I17" s="243" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="243" t="n"/>
-      <c r="B18" s="243" t="n"/>
-      <c r="C18" s="243" t="n"/>
-      <c r="D18" s="243" t="n"/>
-      <c r="E18" s="243" t="n"/>
-      <c r="F18" s="243" t="n"/>
-      <c r="G18" s="243" t="n"/>
-      <c r="H18" s="243" t="n"/>
-      <c r="I18" s="243" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="243" t="n"/>
-      <c r="B19" s="243" t="n"/>
-      <c r="C19" s="243" t="n"/>
-      <c r="D19" s="243" t="n"/>
-      <c r="E19" s="243" t="n"/>
-      <c r="F19" s="243" t="n"/>
-      <c r="G19" s="243" t="n"/>
-      <c r="H19" s="243" t="n"/>
-      <c r="I19" s="243" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="243" t="n"/>
-      <c r="B20" s="243" t="n"/>
-      <c r="C20" s="243" t="n"/>
-      <c r="D20" s="243" t="n"/>
-      <c r="E20" s="243" t="n"/>
-      <c r="F20" s="243" t="n"/>
-      <c r="G20" s="243" t="n"/>
-      <c r="H20" s="243" t="n"/>
-      <c r="I20" s="243" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="243" t="n"/>
-      <c r="B21" s="243" t="n"/>
-      <c r="C21" s="243" t="n"/>
-      <c r="D21" s="243" t="n"/>
-      <c r="E21" s="243" t="n"/>
-      <c r="F21" s="243" t="n"/>
-      <c r="G21" s="243" t="n"/>
-      <c r="H21" s="243" t="n"/>
-      <c r="I21" s="243" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="243" t="n"/>
-      <c r="B22" s="243" t="n"/>
-      <c r="C22" s="243" t="n"/>
-      <c r="D22" s="243" t="n"/>
-      <c r="E22" s="243" t="n"/>
-      <c r="F22" s="243" t="n"/>
-      <c r="G22" s="243" t="n"/>
-      <c r="H22" s="243" t="n"/>
-      <c r="I22" s="243" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="243" t="n"/>
-      <c r="B23" s="243" t="n"/>
-      <c r="C23" s="243" t="n"/>
-      <c r="D23" s="243" t="n"/>
-      <c r="E23" s="243" t="n"/>
-      <c r="F23" s="243" t="n"/>
-      <c r="G23" s="243" t="n"/>
-      <c r="H23" s="243" t="n"/>
-      <c r="I23" s="243" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="243" t="n"/>
-      <c r="B24" s="243" t="n"/>
-      <c r="C24" s="243" t="n"/>
-      <c r="D24" s="243" t="n"/>
-      <c r="E24" s="243" t="n"/>
-      <c r="F24" s="243" t="n"/>
-      <c r="G24" s="243" t="n"/>
-      <c r="H24" s="243" t="n"/>
-      <c r="I24" s="243" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="243" t="n"/>
-      <c r="B25" s="243" t="n"/>
-      <c r="C25" s="243" t="n"/>
-      <c r="D25" s="243" t="n"/>
-      <c r="E25" s="243" t="n"/>
-      <c r="F25" s="243" t="n"/>
-      <c r="G25" s="243" t="n"/>
-      <c r="H25" s="243" t="n"/>
-      <c r="I25" s="243" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="277" t="n"/>
-      <c r="B26" s="277" t="n"/>
-      <c r="C26" s="277" t="n"/>
-      <c r="D26" s="277" t="n"/>
-      <c r="E26" s="277" t="n"/>
-      <c r="F26" s="277" t="n"/>
-      <c r="G26" s="277" t="n"/>
-      <c r="H26" s="277" t="n"/>
-      <c r="I26" s="277" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="277" t="n"/>
-      <c r="B27" s="277" t="n"/>
-      <c r="C27" s="277" t="n"/>
-      <c r="D27" s="277" t="n"/>
-      <c r="E27" s="277" t="n"/>
-      <c r="F27" s="277" t="n"/>
-      <c r="G27" s="277" t="n"/>
-      <c r="H27" s="277" t="n"/>
-      <c r="I27" s="277" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="277" t="n"/>
-      <c r="B28" s="277" t="n"/>
-      <c r="C28" s="277" t="n"/>
-      <c r="D28" s="277" t="n"/>
-      <c r="E28" s="277" t="n"/>
-      <c r="F28" s="277" t="n"/>
-      <c r="G28" s="277" t="n"/>
-      <c r="H28" s="277" t="n"/>
-      <c r="I28" s="277" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="277" t="n"/>
-      <c r="B29" s="277" t="n"/>
-      <c r="C29" s="277" t="n"/>
-      <c r="D29" s="277" t="n"/>
-      <c r="E29" s="277" t="n"/>
-      <c r="F29" s="277" t="n"/>
-      <c r="G29" s="277" t="n"/>
-      <c r="H29" s="277" t="n"/>
-      <c r="I29" s="277" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="277" t="n"/>
-      <c r="B30" s="277" t="n"/>
-      <c r="C30" s="277" t="n"/>
-      <c r="D30" s="277" t="n"/>
-      <c r="E30" s="277" t="n"/>
-      <c r="F30" s="277" t="n"/>
-      <c r="G30" s="277" t="n"/>
-      <c r="H30" s="277" t="n"/>
-      <c r="I30" s="277" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="277" t="n"/>
-      <c r="B31" s="277" t="n"/>
-      <c r="C31" s="277" t="n"/>
-      <c r="D31" s="277" t="n"/>
-      <c r="E31" s="277" t="n"/>
-      <c r="F31" s="277" t="n"/>
-      <c r="G31" s="277" t="n"/>
-      <c r="H31" s="277" t="n"/>
-      <c r="I31" s="277" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="277" t="n"/>
-      <c r="B32" s="277" t="n"/>
-      <c r="C32" s="277" t="n"/>
-      <c r="D32" s="277" t="n"/>
-      <c r="E32" s="277" t="n"/>
-      <c r="F32" s="277" t="n"/>
-      <c r="G32" s="277" t="n"/>
-      <c r="H32" s="277" t="n"/>
-      <c r="I32" s="277" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="277" t="n"/>
-      <c r="B33" s="277" t="n"/>
-      <c r="C33" s="277" t="n"/>
-      <c r="D33" s="277" t="n"/>
-      <c r="E33" s="277" t="n"/>
-      <c r="F33" s="277" t="n"/>
-      <c r="G33" s="277" t="n"/>
-      <c r="H33" s="277" t="n"/>
-      <c r="I33" s="277" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="277" t="n"/>
-      <c r="B34" s="277" t="n"/>
-      <c r="C34" s="277" t="n"/>
-      <c r="D34" s="277" t="n"/>
-      <c r="E34" s="277" t="n"/>
-      <c r="F34" s="277" t="n"/>
-      <c r="G34" s="277" t="n"/>
-      <c r="H34" s="277" t="n"/>
-      <c r="I34" s="277" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D6:G7"/>
-    <mergeCell ref="D4:G4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF1565C0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="18" customWidth="1" style="550" min="1" max="1"/>
-    <col width="15.77734375" customWidth="1" style="550" min="11" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="550">
-      <c r="A1" s="505" t="n"/>
-      <c r="B1" s="505" t="n"/>
-      <c r="C1" s="505" t="n"/>
-      <c r="D1" s="506" t="n"/>
-      <c r="E1" s="613" t="inlineStr">
-        <is>
-          <t>INSTRUCTIVO DE USO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4.95" customHeight="1" s="550">
-      <c r="A2" s="505" t="n"/>
-      <c r="B2" s="505" t="n"/>
-      <c r="C2" s="505" t="n"/>
-      <c r="D2" s="618" t="n"/>
-      <c r="E2" s="700" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="550">
-      <c r="A3" s="505" t="n"/>
-      <c r="B3" s="505" t="n"/>
-      <c r="C3" s="505" t="n"/>
-      <c r="D3" s="618" t="n"/>
-      <c r="E3" s="615" t="n"/>
-      <c r="K3" s="702" t="inlineStr">
-        <is>
-          <t>CONTROL DOCUMENTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="550">
-      <c r="A4" s="505" t="n"/>
-      <c r="B4" s="505" t="n"/>
-      <c r="C4" s="505" t="n"/>
-      <c r="D4" s="618" t="n"/>
-      <c r="E4" s="564" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="J4" s="562" t="n"/>
-      <c r="K4" s="251" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="L4" s="697" t="inlineStr">
-        <is>
-          <t>RYR-CO-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="550">
-      <c r="A5" s="505" t="n"/>
-      <c r="B5" s="505" t="n"/>
-      <c r="C5" s="505" t="n"/>
-      <c r="D5" s="618" t="n"/>
-      <c r="E5" s="683" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="J5" s="562" t="n"/>
-      <c r="K5" s="251" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="L5" s="697" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="14.4" customHeight="1" s="550">
-      <c r="A6" s="505" t="n"/>
-      <c r="B6" s="505" t="n"/>
-      <c r="C6" s="505" t="n"/>
-      <c r="D6" s="618" t="n"/>
-      <c r="E6" s="615" t="n"/>
-      <c r="K6" s="251" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="L6" s="697" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="550">
-      <c r="A7" s="505" t="n"/>
-      <c r="B7" s="505" t="n"/>
-      <c r="C7" s="505" t="n"/>
-      <c r="D7" s="618" t="n"/>
-      <c r="K7" s="251" t="inlineStr">
-        <is>
-          <t>Página</t>
-        </is>
-      </c>
-      <c r="L7" s="697" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="19.95" customHeight="1" s="550">
-      <c r="A8" s="698" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES — INSTRUCTIVO DE CANTIDADES</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="550">
-      <c r="A9" s="701" t="inlineStr">
-        <is>
-          <t>1. IDENTIFICAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="550">
-      <c r="A10" s="699" t="inlineStr">
-        <is>
-          <t>Use el código y actividad específica del catálogo; defina ubicación/frente y plano/revisión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="550"/>
-    <row r="12" ht="15" customHeight="1" s="550">
-      <c r="A12" s="701" t="inlineStr">
-        <is>
-          <t>2. MEDIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="550">
-      <c r="A13" s="699" t="inlineStr">
-        <is>
-          <t>Ingrese solo las dimensiones aplicables a la actividad: largo, ancho, alto/profundidad, espesor y número de elementos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="550"/>
-    <row r="15" ht="15" customHeight="1" s="550">
-      <c r="A15" s="701" t="inlineStr">
-        <is>
-          <t>3. REPETIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="550">
-      <c r="A16" s="699" t="inlineStr">
-        <is>
-          <t>Use N° de elementos para componentes repetitivos y Repeticiones para módulos o conjuntos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="550"/>
-    <row r="18" ht="15" customHeight="1" s="550">
-      <c r="A18" s="701" t="inlineStr">
-        <is>
-          <t>4. DEDUCIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="550">
-      <c r="A19" s="699" t="inlineStr">
-        <is>
-          <t>Registre vanos, vacíos u otros descuentos en Deducción y explique el criterio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="550"/>
-    <row r="21" ht="15" customHeight="1" s="550">
-      <c r="A21" s="701" t="inlineStr">
-        <is>
-          <t>5. DESPERDICIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="550">
-      <c r="A22" s="699" t="inlineStr">
-        <is>
-          <t>Ingrese el porcentaje como decimal (5% = 0,05) solo si está técnicamente o contractualmente sustentado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="550"/>
-    <row r="24" ht="15" customHeight="1" s="550">
-      <c r="A24" s="701" t="inlineStr">
-        <is>
-          <t>6. TRAZABILIDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="550">
-      <c r="A25" s="699" t="inlineStr">
-        <is>
-          <t>Toda cantidad debe poder rastrearse a plano, detalle, especificación, medición de campo o documento contractual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="550"/>
-    <row r="27">
-      <c r="A27" s="701" t="inlineStr">
-        <is>
-          <t>7. VALIDAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="14.4" customHeight="1" s="550">
-      <c r="A28" s="699" t="inlineStr">
-        <is>
-          <t>Compare contra presupuesto, APU, planos y medición de campo; documente diferencias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="701" t="inlineStr">
-        <is>
-          <t>8. APROBAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="14.4" customHeight="1" s="550">
-      <c r="A31" s="699" t="inlineStr">
-        <is>
-          <t>Cambie el Estado a Aprobada solo después de la revisión técnica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="203" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="203" t="n"/>
-      <c r="C33" s="203" t="n"/>
-      <c r="D33" s="203" t="n"/>
-      <c r="E33" s="203" t="n"/>
-      <c r="F33" s="203" t="n"/>
-      <c r="G33" s="203" t="n"/>
-      <c r="H33" s="203" t="n"/>
-      <c r="I33" s="203" t="n"/>
-      <c r="J33" s="203" t="n"/>
-      <c r="K33" s="203" t="n"/>
-      <c r="L33" s="203" t="n"/>
-      <c r="M33" s="202">
-        <f>L4</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="E1:M1"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="E2:M2"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="A25:M25"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="E6:J7"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A21:M21"/>
-    <mergeCell ref="E4:J4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF1565C0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y169"/>
+  <dimension ref="A1:Y170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="615" min="1" max="1"/>
@@ -17140,7 +16232,7 @@
       </c>
       <c r="B70" s="281" t="inlineStr">
         <is>
-          <t>PAÑETES Y REVOQUES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C70" s="282" t="inlineStr">
@@ -17155,7 +16247,7 @@
       </c>
       <c r="E70" s="284" t="inlineStr">
         <is>
-          <t>Estuco plástico o tradicional</t>
+          <t>Estuco plástico</t>
         </is>
       </c>
       <c r="F70" s="285" t="n"/>
@@ -17215,30 +16307,22 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="71">
       <c r="A71" s="280" t="inlineStr">
         <is>
-          <t>MQ-063</t>
+          <t>MQ-062B</t>
         </is>
       </c>
       <c r="B71" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C71" s="282" t="inlineStr">
-        <is>
-          <t>Pisos</t>
-        </is>
-      </c>
-      <c r="D71" s="283" t="inlineStr">
-        <is>
-          <t>09.01.01</t>
-        </is>
-      </c>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="C71" s="282" t="n"/>
+      <c r="D71" s="283" t="n"/>
       <c r="E71" s="284" t="inlineStr">
         <is>
-          <t>Mortero de nivelación</t>
+          <t>Estuco tradicional</t>
         </is>
       </c>
       <c r="F71" s="285" t="n"/>
@@ -17249,59 +16333,11 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J71" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="1438">
-        <f>IF(I71="","",ROUND(IF(OR(I71="m²",I71="m2"),J71*IF(K71=0,1,K71)*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="m³",I71="m3"),J71*K71*L71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="ml",I71="ML"),J71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="und",I71="UND"),IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(I71="kg",J71*IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,IF(OR(I71="gl",I71="GL",I71="gb",I71="GB",I71="Gl",I71="Gb"),IF(N71=0,1,N71)*IF(O71=0,1,O71)*P71-Q71,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="T71" s="1438">
-        <f>IF(S71="","",ROUND(S71*(1+R71),3))</f>
-        <v/>
-      </c>
-      <c r="U71" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="V71" s="285" t="n"/>
-      <c r="W71" s="285" t="n"/>
-      <c r="X71" s="1304" t="n"/>
-      <c r="Y71" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
     </row>
     <row r="72" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A72" s="280" t="inlineStr">
         <is>
-          <t>MQ-064</t>
+          <t>MQ-063</t>
         </is>
       </c>
       <c r="B72" s="281" t="inlineStr">
@@ -17316,12 +16352,12 @@
       </c>
       <c r="D72" s="283" t="inlineStr">
         <is>
-          <t>09.01.02</t>
+          <t>09.01.01</t>
         </is>
       </c>
       <c r="E72" s="284" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="F72" s="285" t="n"/>
@@ -17384,7 +16420,7 @@
     <row r="73" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A73" s="280" t="inlineStr">
         <is>
-          <t>MQ-065</t>
+          <t>MQ-064</t>
         </is>
       </c>
       <c r="B73" s="281" t="inlineStr">
@@ -17399,12 +16435,12 @@
       </c>
       <c r="D73" s="283" t="inlineStr">
         <is>
-          <t>09.01.03</t>
+          <t>09.01.02</t>
         </is>
       </c>
       <c r="E73" s="284" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="F73" s="285" t="n"/>
@@ -17467,7 +16503,7 @@
     <row r="74" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A74" s="280" t="inlineStr">
         <is>
-          <t>MQ-066</t>
+          <t>MQ-065</t>
         </is>
       </c>
       <c r="B74" s="281" t="inlineStr">
@@ -17482,12 +16518,12 @@
       </c>
       <c r="D74" s="283" t="inlineStr">
         <is>
-          <t>09.01.04</t>
+          <t>09.01.03</t>
         </is>
       </c>
       <c r="E74" s="284" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="F74" s="285" t="n"/>
@@ -17550,7 +16586,7 @@
     <row r="75" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A75" s="280" t="inlineStr">
         <is>
-          <t>MQ-067</t>
+          <t>MQ-066</t>
         </is>
       </c>
       <c r="B75" s="281" t="inlineStr">
@@ -17565,12 +16601,12 @@
       </c>
       <c r="D75" s="283" t="inlineStr">
         <is>
-          <t>09.01.05</t>
+          <t>09.01.04</t>
         </is>
       </c>
       <c r="E75" s="284" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="F75" s="285" t="n"/>
@@ -17633,7 +16669,7 @@
     <row r="76" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A76" s="280" t="inlineStr">
         <is>
-          <t>MQ-068</t>
+          <t>MQ-067</t>
         </is>
       </c>
       <c r="B76" s="281" t="inlineStr">
@@ -17643,17 +16679,17 @@
       </c>
       <c r="C76" s="282" t="inlineStr">
         <is>
-          <t>Enchapes</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="D76" s="283" t="inlineStr">
         <is>
-          <t>09.02.01</t>
+          <t>09.01.05</t>
         </is>
       </c>
       <c r="E76" s="284" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="F76" s="285" t="n"/>
@@ -17716,7 +16752,7 @@
     <row r="77" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A77" s="280" t="inlineStr">
         <is>
-          <t>MQ-069</t>
+          <t>MQ-068</t>
         </is>
       </c>
       <c r="B77" s="281" t="inlineStr">
@@ -17731,12 +16767,12 @@
       </c>
       <c r="D77" s="283" t="inlineStr">
         <is>
-          <t>09.02.02</t>
+          <t>09.02.01</t>
         </is>
       </c>
       <c r="E77" s="284" t="inlineStr">
         <is>
-          <t>Guardaescoba</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="F77" s="285" t="n"/>
@@ -17744,7 +16780,7 @@
       <c r="H77" s="285" t="n"/>
       <c r="I77" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J77" s="1438" t="n">
@@ -17784,7 +16820,7 @@
       </c>
       <c r="U77" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V77" s="285" t="n"/>
@@ -17799,7 +16835,7 @@
     <row r="78" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A78" s="280" t="inlineStr">
         <is>
-          <t>MQ-070</t>
+          <t>MQ-069</t>
         </is>
       </c>
       <c r="B78" s="281" t="inlineStr">
@@ -17814,12 +16850,12 @@
       </c>
       <c r="D78" s="283" t="inlineStr">
         <is>
-          <t>09.02.03</t>
+          <t>09.02.02</t>
         </is>
       </c>
       <c r="E78" s="284" t="inlineStr">
         <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="F78" s="285" t="n"/>
@@ -17882,27 +16918,27 @@
     <row r="79" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A79" s="280" t="inlineStr">
         <is>
-          <t>MQ-071</t>
+          <t>MQ-070</t>
         </is>
       </c>
       <c r="B79" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C79" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Enchapes</t>
         </is>
       </c>
       <c r="D79" s="283" t="inlineStr">
         <is>
-          <t>10.01.01</t>
+          <t>09.02.03</t>
         </is>
       </c>
       <c r="E79" s="284" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="F79" s="285" t="n"/>
@@ -17910,7 +16946,7 @@
       <c r="H79" s="285" t="n"/>
       <c r="I79" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J79" s="1438" t="n">
@@ -17950,7 +16986,7 @@
       </c>
       <c r="U79" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V79" s="285" t="n"/>
@@ -17965,7 +17001,7 @@
     <row r="80" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A80" s="280" t="inlineStr">
         <is>
-          <t>MQ-072</t>
+          <t>MQ-071</t>
         </is>
       </c>
       <c r="B80" s="281" t="inlineStr">
@@ -17980,12 +17016,12 @@
       </c>
       <c r="D80" s="283" t="inlineStr">
         <is>
-          <t>10.01.02</t>
+          <t>10.01.01</t>
         </is>
       </c>
       <c r="E80" s="284" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="F80" s="285" t="n"/>
@@ -18048,7 +17084,7 @@
     <row r="81" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A81" s="280" t="inlineStr">
         <is>
-          <t>MQ-073</t>
+          <t>MQ-072</t>
         </is>
       </c>
       <c r="B81" s="281" t="inlineStr">
@@ -18063,12 +17099,12 @@
       </c>
       <c r="D81" s="283" t="inlineStr">
         <is>
-          <t>10.01.03</t>
+          <t>10.01.02</t>
         </is>
       </c>
       <c r="E81" s="284" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="F81" s="285" t="n"/>
@@ -18131,7 +17167,7 @@
     <row r="82" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A82" s="280" t="inlineStr">
         <is>
-          <t>MQ-074</t>
+          <t>MQ-073</t>
         </is>
       </c>
       <c r="B82" s="281" t="inlineStr">
@@ -18146,12 +17182,12 @@
       </c>
       <c r="D82" s="283" t="inlineStr">
         <is>
-          <t>10.01.04</t>
+          <t>10.01.03</t>
         </is>
       </c>
       <c r="E82" s="284" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="F82" s="285" t="n"/>
@@ -18214,7 +17250,7 @@
     <row r="83" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A83" s="280" t="inlineStr">
         <is>
-          <t>MQ-075</t>
+          <t>MQ-074</t>
         </is>
       </c>
       <c r="B83" s="281" t="inlineStr">
@@ -18229,12 +17265,12 @@
       </c>
       <c r="D83" s="283" t="inlineStr">
         <is>
-          <t>10.01.05</t>
+          <t>10.01.04</t>
         </is>
       </c>
       <c r="E83" s="284" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="F83" s="285" t="n"/>
@@ -18297,27 +17333,27 @@
     <row r="84" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A84" s="280" t="inlineStr">
         <is>
-          <t>MQ-076</t>
+          <t>MQ-075</t>
         </is>
       </c>
       <c r="B84" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C84" s="282" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D84" s="283" t="inlineStr">
         <is>
-          <t>11.01.01</t>
+          <t>10.01.05</t>
         </is>
       </c>
       <c r="E84" s="284" t="inlineStr">
         <is>
-          <t>Puertas de madera</t>
+          <t>Sellador / imprimante</t>
         </is>
       </c>
       <c r="F84" s="285" t="n"/>
@@ -18325,7 +17361,7 @@
       <c r="H84" s="285" t="n"/>
       <c r="I84" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J84" s="1438" t="n">
@@ -18365,7 +17401,7 @@
       </c>
       <c r="U84" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V84" s="285" t="n"/>
@@ -18380,7 +17416,7 @@
     <row r="85" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A85" s="280" t="inlineStr">
         <is>
-          <t>MQ-077</t>
+          <t>MQ-076</t>
         </is>
       </c>
       <c r="B85" s="281" t="inlineStr">
@@ -18395,12 +17431,12 @@
       </c>
       <c r="D85" s="283" t="inlineStr">
         <is>
-          <t>11.01.02</t>
+          <t>11.01.01</t>
         </is>
       </c>
       <c r="E85" s="284" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="F85" s="285" t="n"/>
@@ -18408,7 +17444,7 @@
       <c r="H85" s="285" t="n"/>
       <c r="I85" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J85" s="1438" t="n">
@@ -18448,7 +17484,7 @@
       </c>
       <c r="U85" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V85" s="285" t="n"/>
@@ -18463,7 +17499,7 @@
     <row r="86" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A86" s="280" t="inlineStr">
         <is>
-          <t>MQ-078</t>
+          <t>MQ-077</t>
         </is>
       </c>
       <c r="B86" s="281" t="inlineStr">
@@ -18473,17 +17509,17 @@
       </c>
       <c r="C86" s="282" t="inlineStr">
         <is>
-          <t>Metálica</t>
+          <t>Madera</t>
         </is>
       </c>
       <c r="D86" s="283" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>11.01.02</t>
         </is>
       </c>
       <c r="E86" s="284" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="F86" s="285" t="n"/>
@@ -18491,7 +17527,7 @@
       <c r="H86" s="285" t="n"/>
       <c r="I86" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J86" s="1438" t="n">
@@ -18531,7 +17567,7 @@
       </c>
       <c r="U86" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V86" s="285" t="n"/>
@@ -18546,7 +17582,7 @@
     <row r="87" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A87" s="280" t="inlineStr">
         <is>
-          <t>MQ-079</t>
+          <t>MQ-078</t>
         </is>
       </c>
       <c r="B87" s="281" t="inlineStr">
@@ -18561,12 +17597,12 @@
       </c>
       <c r="D87" s="283" t="inlineStr">
         <is>
-          <t>11.02.02</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="E87" s="284" t="inlineStr">
         <is>
-          <t>Barandas metálicas</t>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="F87" s="285" t="n"/>
@@ -18574,7 +17610,7 @@
       <c r="H87" s="285" t="n"/>
       <c r="I87" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J87" s="1438" t="n">
@@ -18614,7 +17650,7 @@
       </c>
       <c r="U87" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V87" s="285" t="n"/>
@@ -18629,7 +17665,7 @@
     <row r="88" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A88" s="280" t="inlineStr">
         <is>
-          <t>MQ-080</t>
+          <t>MQ-079</t>
         </is>
       </c>
       <c r="B88" s="281" t="inlineStr">
@@ -18644,12 +17680,12 @@
       </c>
       <c r="D88" s="283" t="inlineStr">
         <is>
-          <t>11.02.03</t>
+          <t>11.02.02</t>
         </is>
       </c>
       <c r="E88" s="284" t="inlineStr">
         <is>
-          <t>Pasamanos</t>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="F88" s="285" t="n"/>
@@ -18712,7 +17748,7 @@
     <row r="89" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A89" s="280" t="inlineStr">
         <is>
-          <t>MQ-081</t>
+          <t>MQ-080</t>
         </is>
       </c>
       <c r="B89" s="281" t="inlineStr">
@@ -18722,17 +17758,17 @@
       </c>
       <c r="C89" s="282" t="inlineStr">
         <is>
-          <t>Aluminio</t>
+          <t>Metálica</t>
         </is>
       </c>
       <c r="D89" s="283" t="inlineStr">
         <is>
-          <t>11.03.01</t>
+          <t>11.02.03</t>
         </is>
       </c>
       <c r="E89" s="284" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="F89" s="285" t="n"/>
@@ -18740,7 +17776,7 @@
       <c r="H89" s="285" t="n"/>
       <c r="I89" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J89" s="1438" t="n">
@@ -18780,7 +17816,7 @@
       </c>
       <c r="U89" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V89" s="285" t="n"/>
@@ -18795,7 +17831,7 @@
     <row r="90" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A90" s="280" t="inlineStr">
         <is>
-          <t>MQ-082</t>
+          <t>MQ-081</t>
         </is>
       </c>
       <c r="B90" s="281" t="inlineStr">
@@ -18810,12 +17846,12 @@
       </c>
       <c r="D90" s="283" t="inlineStr">
         <is>
-          <t>11.03.02</t>
+          <t>11.03.01</t>
         </is>
       </c>
       <c r="E90" s="284" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="F90" s="285" t="n"/>
@@ -18878,27 +17914,27 @@
     <row r="91" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A91" s="280" t="inlineStr">
         <is>
-          <t>MQ-083</t>
+          <t>MQ-082</t>
         </is>
       </c>
       <c r="B91" s="281" t="inlineStr">
         <is>
-          <t>VIDRIOS</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C91" s="282" t="inlineStr">
         <is>
-          <t>Vidriería</t>
+          <t>Aluminio</t>
         </is>
       </c>
       <c r="D91" s="283" t="inlineStr">
         <is>
-          <t>12.01.01</t>
+          <t>11.03.02</t>
         </is>
       </c>
       <c r="E91" s="284" t="inlineStr">
         <is>
-          <t>Vidrio templado</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="F91" s="285" t="n"/>
@@ -18961,7 +17997,7 @@
     <row r="92" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A92" s="280" t="inlineStr">
         <is>
-          <t>MQ-084</t>
+          <t>MQ-083</t>
         </is>
       </c>
       <c r="B92" s="281" t="inlineStr">
@@ -18976,12 +18012,12 @@
       </c>
       <c r="D92" s="283" t="inlineStr">
         <is>
-          <t>12.01.02</t>
+          <t>12.01.01</t>
         </is>
       </c>
       <c r="E92" s="284" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="F92" s="285" t="n"/>
@@ -19044,7 +18080,7 @@
     <row r="93" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A93" s="280" t="inlineStr">
         <is>
-          <t>MQ-085</t>
+          <t>MQ-084</t>
         </is>
       </c>
       <c r="B93" s="281" t="inlineStr">
@@ -19059,12 +18095,12 @@
       </c>
       <c r="D93" s="283" t="inlineStr">
         <is>
-          <t>12.01.03</t>
+          <t>12.01.02</t>
         </is>
       </c>
       <c r="E93" s="284" t="inlineStr">
         <is>
-          <t>Espejos</t>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="F93" s="285" t="n"/>
@@ -19127,7 +18163,7 @@
     <row r="94" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A94" s="280" t="inlineStr">
         <is>
-          <t>MQ-086</t>
+          <t>MQ-085</t>
         </is>
       </c>
       <c r="B94" s="281" t="inlineStr">
@@ -19142,12 +18178,12 @@
       </c>
       <c r="D94" s="283" t="inlineStr">
         <is>
-          <t>12.01.04</t>
+          <t>12.01.03</t>
         </is>
       </c>
       <c r="E94" s="284" t="inlineStr">
         <is>
-          <t>Sellos y silicona</t>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="F94" s="285" t="n"/>
@@ -19155,7 +18191,7 @@
       <c r="H94" s="285" t="n"/>
       <c r="I94" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J94" s="1438" t="n">
@@ -19195,7 +18231,7 @@
       </c>
       <c r="U94" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V94" s="285" t="n"/>
@@ -19210,27 +18246,27 @@
     <row r="95" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A95" s="280" t="inlineStr">
         <is>
-          <t>MQ-087</t>
+          <t>MQ-086</t>
         </is>
       </c>
       <c r="B95" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>VIDRIOS</t>
         </is>
       </c>
       <c r="C95" s="282" t="inlineStr">
         <is>
-          <t>Agua potable</t>
+          <t>Vidriería</t>
         </is>
       </c>
       <c r="D95" s="283" t="inlineStr">
         <is>
-          <t>13.01.01</t>
+          <t>12.01.04</t>
         </is>
       </c>
       <c r="E95" s="284" t="inlineStr">
         <is>
-          <t>Tubería de agua fría</t>
+          <t>Sellos y silicona</t>
         </is>
       </c>
       <c r="F95" s="285" t="n"/>
@@ -19293,7 +18329,7 @@
     <row r="96" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A96" s="280" t="inlineStr">
         <is>
-          <t>MQ-088</t>
+          <t>MQ-087</t>
         </is>
       </c>
       <c r="B96" s="281" t="inlineStr">
@@ -19308,12 +18344,12 @@
       </c>
       <c r="D96" s="283" t="inlineStr">
         <is>
-          <t>13.01.02</t>
+          <t>13.01.01</t>
         </is>
       </c>
       <c r="E96" s="284" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="F96" s="285" t="n"/>
@@ -19376,7 +18412,7 @@
     <row r="97" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A97" s="280" t="inlineStr">
         <is>
-          <t>MQ-089</t>
+          <t>MQ-088</t>
         </is>
       </c>
       <c r="B97" s="281" t="inlineStr">
@@ -19391,12 +18427,12 @@
       </c>
       <c r="D97" s="283" t="inlineStr">
         <is>
-          <t>13.01.03</t>
+          <t>13.01.02</t>
         </is>
       </c>
       <c r="E97" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios hidrosanitarios</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="F97" s="285" t="n"/>
@@ -19404,7 +18440,7 @@
       <c r="H97" s="285" t="n"/>
       <c r="I97" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J97" s="1438" t="n">
@@ -19444,7 +18480,7 @@
       </c>
       <c r="U97" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V97" s="285" t="n"/>
@@ -19459,7 +18495,7 @@
     <row r="98" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A98" s="280" t="inlineStr">
         <is>
-          <t>MQ-090</t>
+          <t>MQ-089</t>
         </is>
       </c>
       <c r="B98" s="281" t="inlineStr">
@@ -19469,17 +18505,17 @@
       </c>
       <c r="C98" s="282" t="inlineStr">
         <is>
-          <t>Desagües</t>
+          <t>Agua potable</t>
         </is>
       </c>
       <c r="D98" s="283" t="inlineStr">
         <is>
-          <t>13.02.01</t>
+          <t>13.01.03</t>
         </is>
       </c>
       <c r="E98" s="284" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="F98" s="285" t="n"/>
@@ -19487,7 +18523,7 @@
       <c r="H98" s="285" t="n"/>
       <c r="I98" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J98" s="1438" t="n">
@@ -19527,7 +18563,7 @@
       </c>
       <c r="U98" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V98" s="285" t="n"/>
@@ -19542,7 +18578,7 @@
     <row r="99" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A99" s="280" t="inlineStr">
         <is>
-          <t>MQ-091</t>
+          <t>MQ-090</t>
         </is>
       </c>
       <c r="B99" s="281" t="inlineStr">
@@ -19557,12 +18593,12 @@
       </c>
       <c r="D99" s="283" t="inlineStr">
         <is>
-          <t>13.02.02</t>
+          <t>13.02.01</t>
         </is>
       </c>
       <c r="E99" s="284" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="F99" s="285" t="n"/>
@@ -19625,7 +18661,7 @@
     <row r="100" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A100" s="280" t="inlineStr">
         <is>
-          <t>MQ-092</t>
+          <t>MQ-091</t>
         </is>
       </c>
       <c r="B100" s="281" t="inlineStr">
@@ -19640,12 +18676,12 @@
       </c>
       <c r="D100" s="283" t="inlineStr">
         <is>
-          <t>13.02.03</t>
+          <t>13.02.02</t>
         </is>
       </c>
       <c r="E100" s="284" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="F100" s="285" t="n"/>
@@ -19653,7 +18689,7 @@
       <c r="H100" s="285" t="n"/>
       <c r="I100" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J100" s="1438" t="n">
@@ -19693,7 +18729,7 @@
       </c>
       <c r="U100" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V100" s="285" t="n"/>
@@ -19708,7 +18744,7 @@
     <row r="101" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A101" s="280" t="inlineStr">
         <is>
-          <t>MQ-093</t>
+          <t>MQ-092</t>
         </is>
       </c>
       <c r="B101" s="281" t="inlineStr">
@@ -19718,17 +18754,17 @@
       </c>
       <c r="C101" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Desagües</t>
         </is>
       </c>
       <c r="D101" s="283" t="inlineStr">
         <is>
-          <t>13.03.01</t>
+          <t>13.02.03</t>
         </is>
       </c>
       <c r="E101" s="284" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="F101" s="285" t="n"/>
@@ -19791,7 +18827,7 @@
     <row r="102" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A102" s="280" t="inlineStr">
         <is>
-          <t>MQ-094</t>
+          <t>MQ-093</t>
         </is>
       </c>
       <c r="B102" s="281" t="inlineStr">
@@ -19806,12 +18842,12 @@
       </c>
       <c r="D102" s="283" t="inlineStr">
         <is>
-          <t>13.03.02</t>
+          <t>13.03.01</t>
         </is>
       </c>
       <c r="E102" s="284" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="F102" s="285" t="n"/>
@@ -19874,7 +18910,7 @@
     <row r="103" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A103" s="280" t="inlineStr">
         <is>
-          <t>MQ-095</t>
+          <t>MQ-094</t>
         </is>
       </c>
       <c r="B103" s="281" t="inlineStr">
@@ -19889,12 +18925,12 @@
       </c>
       <c r="D103" s="283" t="inlineStr">
         <is>
-          <t>13.03.03</t>
+          <t>13.03.02</t>
         </is>
       </c>
       <c r="E103" s="284" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="F103" s="285" t="n"/>
@@ -19957,7 +18993,7 @@
     <row r="104" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A104" s="280" t="inlineStr">
         <is>
-          <t>MQ-096</t>
+          <t>MQ-095</t>
         </is>
       </c>
       <c r="B104" s="281" t="inlineStr">
@@ -19972,12 +19008,12 @@
       </c>
       <c r="D104" s="283" t="inlineStr">
         <is>
-          <t>13.03.04</t>
+          <t>13.03.03</t>
         </is>
       </c>
       <c r="E104" s="284" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="F104" s="285" t="n"/>
@@ -20040,7 +19076,7 @@
     <row r="105" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A105" s="280" t="inlineStr">
         <is>
-          <t>MQ-097</t>
+          <t>MQ-096</t>
         </is>
       </c>
       <c r="B105" s="281" t="inlineStr">
@@ -20050,17 +19086,17 @@
       </c>
       <c r="C105" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D105" s="283" t="inlineStr">
         <is>
-          <t>13.04.01</t>
+          <t>13.03.04</t>
         </is>
       </c>
       <c r="E105" s="284" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="F105" s="285" t="n"/>
@@ -20068,7 +19104,7 @@
       <c r="H105" s="285" t="n"/>
       <c r="I105" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J105" s="1438" t="n">
@@ -20108,7 +19144,7 @@
       </c>
       <c r="U105" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V105" s="285" t="n"/>
@@ -20123,27 +19159,27 @@
     <row r="106" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A106" s="280" t="inlineStr">
         <is>
-          <t>MQ-098</t>
+          <t>MQ-097</t>
         </is>
       </c>
       <c r="B106" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C106" s="282" t="inlineStr">
         <is>
-          <t>Canalizaciones</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D106" s="283" t="inlineStr">
         <is>
-          <t>14.01.01</t>
+          <t>13.04.01</t>
         </is>
       </c>
       <c r="E106" s="284" t="inlineStr">
         <is>
-          <t>Tubería/conduit eléctrica</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="F106" s="285" t="n"/>
@@ -20151,7 +19187,7 @@
       <c r="H106" s="285" t="n"/>
       <c r="I106" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J106" s="1438" t="n">
@@ -20191,7 +19227,7 @@
       </c>
       <c r="U106" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="V106" s="285" t="n"/>
@@ -20206,7 +19242,7 @@
     <row r="107" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A107" s="280" t="inlineStr">
         <is>
-          <t>MQ-099</t>
+          <t>MQ-098</t>
         </is>
       </c>
       <c r="B107" s="281" t="inlineStr">
@@ -20221,12 +19257,12 @@
       </c>
       <c r="D107" s="283" t="inlineStr">
         <is>
-          <t>14.01.02</t>
+          <t>14.01.01</t>
         </is>
       </c>
       <c r="E107" s="284" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="F107" s="285" t="n"/>
@@ -20289,7 +19325,7 @@
     <row r="108" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A108" s="280" t="inlineStr">
         <is>
-          <t>MQ-100</t>
+          <t>MQ-099</t>
         </is>
       </c>
       <c r="B108" s="281" t="inlineStr">
@@ -20304,12 +19340,12 @@
       </c>
       <c r="D108" s="283" t="inlineStr">
         <is>
-          <t>14.01.03</t>
+          <t>14.01.02</t>
         </is>
       </c>
       <c r="E108" s="284" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="F108" s="285" t="n"/>
@@ -20317,7 +19353,7 @@
       <c r="H108" s="285" t="n"/>
       <c r="I108" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J108" s="1438" t="n">
@@ -20357,7 +19393,7 @@
       </c>
       <c r="U108" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V108" s="285" t="n"/>
@@ -20372,7 +19408,7 @@
     <row r="109" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A109" s="280" t="inlineStr">
         <is>
-          <t>MQ-101</t>
+          <t>MQ-100</t>
         </is>
       </c>
       <c r="B109" s="281" t="inlineStr">
@@ -20382,17 +19418,17 @@
       </c>
       <c r="C109" s="282" t="inlineStr">
         <is>
-          <t>Cableado</t>
+          <t>Canalizaciones</t>
         </is>
       </c>
       <c r="D109" s="283" t="inlineStr">
         <is>
-          <t>14.02.01</t>
+          <t>14.01.03</t>
         </is>
       </c>
       <c r="E109" s="284" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="F109" s="285" t="n"/>
@@ -20400,7 +19436,7 @@
       <c r="H109" s="285" t="n"/>
       <c r="I109" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J109" s="1438" t="n">
@@ -20440,7 +19476,7 @@
       </c>
       <c r="U109" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V109" s="285" t="n"/>
@@ -20455,7 +19491,7 @@
     <row r="110" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A110" s="280" t="inlineStr">
         <is>
-          <t>MQ-102</t>
+          <t>MQ-101</t>
         </is>
       </c>
       <c r="B110" s="281" t="inlineStr">
@@ -20470,12 +19506,12 @@
       </c>
       <c r="D110" s="283" t="inlineStr">
         <is>
-          <t>14.02.02</t>
+          <t>14.02.01</t>
         </is>
       </c>
       <c r="E110" s="284" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="F110" s="285" t="n"/>
@@ -20538,7 +19574,7 @@
     <row r="111" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A111" s="280" t="inlineStr">
         <is>
-          <t>MQ-103</t>
+          <t>MQ-102</t>
         </is>
       </c>
       <c r="B111" s="281" t="inlineStr">
@@ -20553,12 +19589,12 @@
       </c>
       <c r="D111" s="283" t="inlineStr">
         <is>
-          <t>14.02.03</t>
+          <t>14.02.02</t>
         </is>
       </c>
       <c r="E111" s="284" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="F111" s="285" t="n"/>
@@ -20566,7 +19602,7 @@
       <c r="H111" s="285" t="n"/>
       <c r="I111" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J111" s="1438" t="n">
@@ -20606,7 +19642,7 @@
       </c>
       <c r="U111" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V111" s="285" t="n"/>
@@ -20621,7 +19657,7 @@
     <row r="112" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A112" s="280" t="inlineStr">
         <is>
-          <t>MQ-104</t>
+          <t>MQ-103</t>
         </is>
       </c>
       <c r="B112" s="281" t="inlineStr">
@@ -20631,17 +19667,17 @@
       </c>
       <c r="C112" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Cableado</t>
         </is>
       </c>
       <c r="D112" s="283" t="inlineStr">
         <is>
-          <t>14.03.01</t>
+          <t>14.02.03</t>
         </is>
       </c>
       <c r="E112" s="284" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="F112" s="285" t="n"/>
@@ -20704,7 +19740,7 @@
     <row r="113" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A113" s="280" t="inlineStr">
         <is>
-          <t>MQ-105</t>
+          <t>MQ-104</t>
         </is>
       </c>
       <c r="B113" s="281" t="inlineStr">
@@ -20719,12 +19755,12 @@
       </c>
       <c r="D113" s="283" t="inlineStr">
         <is>
-          <t>14.03.02</t>
+          <t>14.03.01</t>
         </is>
       </c>
       <c r="E113" s="284" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="F113" s="285" t="n"/>
@@ -20787,7 +19823,7 @@
     <row r="114" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A114" s="280" t="inlineStr">
         <is>
-          <t>MQ-106</t>
+          <t>MQ-105</t>
         </is>
       </c>
       <c r="B114" s="281" t="inlineStr">
@@ -20802,12 +19838,12 @@
       </c>
       <c r="D114" s="283" t="inlineStr">
         <is>
-          <t>14.03.03</t>
+          <t>14.03.02</t>
         </is>
       </c>
       <c r="E114" s="284" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="F114" s="285" t="n"/>
@@ -20870,7 +19906,7 @@
     <row r="115" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A115" s="280" t="inlineStr">
         <is>
-          <t>MQ-107</t>
+          <t>MQ-106</t>
         </is>
       </c>
       <c r="B115" s="281" t="inlineStr">
@@ -20880,17 +19916,17 @@
       </c>
       <c r="C115" s="282" t="inlineStr">
         <is>
-          <t>Puesta a tierra</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D115" s="283" t="inlineStr">
         <is>
-          <t>14.04.01</t>
+          <t>14.03.03</t>
         </is>
       </c>
       <c r="E115" s="284" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="F115" s="285" t="n"/>
@@ -20898,7 +19934,7 @@
       <c r="H115" s="285" t="n"/>
       <c r="I115" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J115" s="1438" t="n">
@@ -20938,7 +19974,7 @@
       </c>
       <c r="U115" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V115" s="285" t="n"/>
@@ -20953,7 +19989,7 @@
     <row r="116" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A116" s="280" t="inlineStr">
         <is>
-          <t>MQ-108</t>
+          <t>MQ-107</t>
         </is>
       </c>
       <c r="B116" s="281" t="inlineStr">
@@ -20963,17 +19999,17 @@
       </c>
       <c r="C116" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Puesta a tierra</t>
         </is>
       </c>
       <c r="D116" s="283" t="inlineStr">
         <is>
-          <t>14.05.01</t>
+          <t>14.04.01</t>
         </is>
       </c>
       <c r="E116" s="284" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="F116" s="285" t="n"/>
@@ -21036,27 +20072,27 @@
     <row r="117" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A117" s="280" t="inlineStr">
         <is>
-          <t>MQ-109</t>
+          <t>MQ-108</t>
         </is>
       </c>
       <c r="B117" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C117" s="282" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D117" s="283" t="inlineStr">
         <is>
-          <t>15.01.01</t>
+          <t>14.05.01</t>
         </is>
       </c>
       <c r="E117" s="284" t="inlineStr">
         <is>
-          <t>Cableado estructurado de datos</t>
+          <t>Pruebas y certificaciones</t>
         </is>
       </c>
       <c r="F117" s="285" t="n"/>
@@ -21064,7 +20100,7 @@
       <c r="H117" s="285" t="n"/>
       <c r="I117" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J117" s="1438" t="n">
@@ -21104,7 +20140,7 @@
       </c>
       <c r="U117" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="V117" s="285" t="n"/>
@@ -21119,7 +20155,7 @@
     <row r="118" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A118" s="280" t="inlineStr">
         <is>
-          <t>MQ-110</t>
+          <t>MQ-109</t>
         </is>
       </c>
       <c r="B118" s="281" t="inlineStr">
@@ -21134,12 +20170,12 @@
       </c>
       <c r="D118" s="283" t="inlineStr">
         <is>
-          <t>15.01.02</t>
+          <t>15.01.01</t>
         </is>
       </c>
       <c r="E118" s="284" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="F118" s="285" t="n"/>
@@ -21147,7 +20183,7 @@
       <c r="H118" s="285" t="n"/>
       <c r="I118" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J118" s="1438" t="n">
@@ -21187,7 +20223,7 @@
       </c>
       <c r="U118" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V118" s="285" t="n"/>
@@ -21202,7 +20238,7 @@
     <row r="119" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A119" s="280" t="inlineStr">
         <is>
-          <t>MQ-111</t>
+          <t>MQ-110</t>
         </is>
       </c>
       <c r="B119" s="281" t="inlineStr">
@@ -21212,17 +20248,17 @@
       </c>
       <c r="C119" s="282" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Datos</t>
         </is>
       </c>
       <c r="D119" s="283" t="inlineStr">
         <is>
-          <t>15.02.01</t>
+          <t>15.01.02</t>
         </is>
       </c>
       <c r="E119" s="284" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="F119" s="285" t="n"/>
@@ -21285,7 +20321,7 @@
     <row r="120" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A120" s="280" t="inlineStr">
         <is>
-          <t>MQ-112</t>
+          <t>MQ-111</t>
         </is>
       </c>
       <c r="B120" s="281" t="inlineStr">
@@ -21300,12 +20336,12 @@
       </c>
       <c r="D120" s="283" t="inlineStr">
         <is>
-          <t>15.02.02</t>
+          <t>15.02.01</t>
         </is>
       </c>
       <c r="E120" s="284" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="F120" s="285" t="n"/>
@@ -21368,7 +20404,7 @@
     <row r="121" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A121" s="280" t="inlineStr">
         <is>
-          <t>MQ-113</t>
+          <t>MQ-112</t>
         </is>
       </c>
       <c r="B121" s="281" t="inlineStr">
@@ -21383,12 +20419,12 @@
       </c>
       <c r="D121" s="283" t="inlineStr">
         <is>
-          <t>15.02.03</t>
+          <t>15.02.02</t>
         </is>
       </c>
       <c r="E121" s="284" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="F121" s="285" t="n"/>
@@ -21451,7 +20487,7 @@
     <row r="122" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A122" s="280" t="inlineStr">
         <is>
-          <t>MQ-114</t>
+          <t>MQ-113</t>
         </is>
       </c>
       <c r="B122" s="281" t="inlineStr">
@@ -21461,17 +20497,17 @@
       </c>
       <c r="C122" s="282" t="inlineStr">
         <is>
-          <t>Detección</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D122" s="283" t="inlineStr">
         <is>
-          <t>15.03.01</t>
+          <t>15.02.03</t>
         </is>
       </c>
       <c r="E122" s="284" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="F122" s="285" t="n"/>
@@ -21479,7 +20515,7 @@
       <c r="H122" s="285" t="n"/>
       <c r="I122" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J122" s="1438" t="n">
@@ -21519,7 +20555,7 @@
       </c>
       <c r="U122" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V122" s="285" t="n"/>
@@ -21534,27 +20570,27 @@
     <row r="123" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A123" s="280" t="inlineStr">
         <is>
-          <t>MQ-115</t>
+          <t>MQ-114</t>
         </is>
       </c>
       <c r="B123" s="281" t="inlineStr">
         <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C123" s="282" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Detección</t>
         </is>
       </c>
       <c r="D123" s="283" t="inlineStr">
         <is>
-          <t>16.01.01</t>
+          <t>15.03.01</t>
         </is>
       </c>
       <c r="E123" s="284" t="inlineStr">
         <is>
-          <t>Equipos de aire acondicionado</t>
+          <t>Sistema de detección de incendios</t>
         </is>
       </c>
       <c r="F123" s="285" t="n"/>
@@ -21562,7 +20598,7 @@
       <c r="H123" s="285" t="n"/>
       <c r="I123" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J123" s="1438" t="n">
@@ -21602,7 +20638,7 @@
       </c>
       <c r="U123" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="V123" s="285" t="n"/>
@@ -21617,7 +20653,7 @@
     <row r="124" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A124" s="280" t="inlineStr">
         <is>
-          <t>MQ-116</t>
+          <t>MQ-115</t>
         </is>
       </c>
       <c r="B124" s="281" t="inlineStr">
@@ -21632,12 +20668,12 @@
       </c>
       <c r="D124" s="283" t="inlineStr">
         <is>
-          <t>16.01.02</t>
+          <t>16.01.01</t>
         </is>
       </c>
       <c r="E124" s="284" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="F124" s="285" t="n"/>
@@ -21645,7 +20681,7 @@
       <c r="H124" s="285" t="n"/>
       <c r="I124" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J124" s="1438" t="n">
@@ -21685,7 +20721,7 @@
       </c>
       <c r="U124" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V124" s="285" t="n"/>
@@ -21700,7 +20736,7 @@
     <row r="125" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A125" s="280" t="inlineStr">
         <is>
-          <t>MQ-117</t>
+          <t>MQ-116</t>
         </is>
       </c>
       <c r="B125" s="281" t="inlineStr">
@@ -21715,12 +20751,12 @@
       </c>
       <c r="D125" s="283" t="inlineStr">
         <is>
-          <t>16.01.03</t>
+          <t>16.01.02</t>
         </is>
       </c>
       <c r="E125" s="284" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="F125" s="285" t="n"/>
@@ -21728,7 +20764,7 @@
       <c r="H125" s="285" t="n"/>
       <c r="I125" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J125" s="1438" t="n">
@@ -21768,7 +20804,7 @@
       </c>
       <c r="U125" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V125" s="285" t="n"/>
@@ -21783,7 +20819,7 @@
     <row r="126" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A126" s="280" t="inlineStr">
         <is>
-          <t>MQ-118</t>
+          <t>MQ-117</t>
         </is>
       </c>
       <c r="B126" s="281" t="inlineStr">
@@ -21798,12 +20834,12 @@
       </c>
       <c r="D126" s="283" t="inlineStr">
         <is>
-          <t>16.01.04</t>
+          <t>16.01.03</t>
         </is>
       </c>
       <c r="E126" s="284" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="F126" s="285" t="n"/>
@@ -21811,7 +20847,7 @@
       <c r="H126" s="285" t="n"/>
       <c r="I126" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J126" s="1438" t="n">
@@ -21851,7 +20887,7 @@
       </c>
       <c r="U126" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V126" s="285" t="n"/>
@@ -21866,27 +20902,27 @@
     <row r="127" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A127" s="280" t="inlineStr">
         <is>
-          <t>MQ-119</t>
+          <t>MQ-118</t>
         </is>
       </c>
       <c r="B127" s="281" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C127" s="282" t="inlineStr">
         <is>
-          <t>Red de gas</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D127" s="283" t="inlineStr">
         <is>
-          <t>17.01.01</t>
+          <t>16.01.04</t>
         </is>
       </c>
       <c r="E127" s="284" t="inlineStr">
         <is>
-          <t>Red interna de gas</t>
+          <t>Rejillas y difusores</t>
         </is>
       </c>
       <c r="F127" s="285" t="n"/>
@@ -21894,7 +20930,7 @@
       <c r="H127" s="285" t="n"/>
       <c r="I127" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J127" s="1438" t="n">
@@ -21934,7 +20970,7 @@
       </c>
       <c r="U127" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V127" s="285" t="n"/>
@@ -21949,7 +20985,7 @@
     <row r="128" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A128" s="280" t="inlineStr">
         <is>
-          <t>MQ-120</t>
+          <t>MQ-119</t>
         </is>
       </c>
       <c r="B128" s="281" t="inlineStr">
@@ -21964,12 +21000,12 @@
       </c>
       <c r="D128" s="283" t="inlineStr">
         <is>
-          <t>17.01.02</t>
+          <t>17.01.01</t>
         </is>
       </c>
       <c r="E128" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios de gas</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="F128" s="285" t="n"/>
@@ -21977,7 +21013,7 @@
       <c r="H128" s="285" t="n"/>
       <c r="I128" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J128" s="1438" t="n">
@@ -22017,7 +21053,7 @@
       </c>
       <c r="U128" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V128" s="285" t="n"/>
@@ -22032,7 +21068,7 @@
     <row r="129" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A129" s="280" t="inlineStr">
         <is>
-          <t>MQ-121</t>
+          <t>MQ-120</t>
         </is>
       </c>
       <c r="B129" s="281" t="inlineStr">
@@ -22047,12 +21083,12 @@
       </c>
       <c r="D129" s="283" t="inlineStr">
         <is>
-          <t>17.01.03</t>
+          <t>17.01.02</t>
         </is>
       </c>
       <c r="E129" s="284" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="F129" s="285" t="n"/>
@@ -22060,7 +21096,7 @@
       <c r="H129" s="285" t="n"/>
       <c r="I129" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J129" s="1438" t="n">
@@ -22100,7 +21136,7 @@
       </c>
       <c r="U129" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V129" s="285" t="n"/>
@@ -22115,27 +21151,27 @@
     <row r="130" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A130" s="280" t="inlineStr">
         <is>
-          <t>MQ-122</t>
+          <t>MQ-121</t>
         </is>
       </c>
       <c r="B130" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="C130" s="282" t="inlineStr">
         <is>
-          <t>Pavimentos</t>
+          <t>Red de gas</t>
         </is>
       </c>
       <c r="D130" s="283" t="inlineStr">
         <is>
-          <t>18.01.01</t>
+          <t>17.01.03</t>
         </is>
       </c>
       <c r="E130" s="284" t="inlineStr">
         <is>
-          <t>Construcción de andenes</t>
+          <t>Pruebas y certificación</t>
         </is>
       </c>
       <c r="F130" s="285" t="n"/>
@@ -22143,7 +21179,7 @@
       <c r="H130" s="285" t="n"/>
       <c r="I130" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J130" s="1438" t="n">
@@ -22183,7 +21219,7 @@
       </c>
       <c r="U130" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="V130" s="285" t="n"/>
@@ -22198,7 +21234,7 @@
     <row r="131" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A131" s="280" t="inlineStr">
         <is>
-          <t>MQ-123</t>
+          <t>MQ-122</t>
         </is>
       </c>
       <c r="B131" s="281" t="inlineStr">
@@ -22213,12 +21249,12 @@
       </c>
       <c r="D131" s="283" t="inlineStr">
         <is>
-          <t>18.01.02</t>
+          <t>18.01.01</t>
         </is>
       </c>
       <c r="E131" s="284" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="F131" s="285" t="n"/>
@@ -22226,7 +21262,7 @@
       <c r="H131" s="285" t="n"/>
       <c r="I131" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J131" s="1438" t="n">
@@ -22266,7 +21302,7 @@
       </c>
       <c r="U131" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V131" s="285" t="n"/>
@@ -22281,7 +21317,7 @@
     <row r="132" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A132" s="280" t="inlineStr">
         <is>
-          <t>MQ-124</t>
+          <t>MQ-123</t>
         </is>
       </c>
       <c r="B132" s="281" t="inlineStr">
@@ -22296,12 +21332,12 @@
       </c>
       <c r="D132" s="283" t="inlineStr">
         <is>
-          <t>18.01.03</t>
+          <t>18.01.02</t>
         </is>
       </c>
       <c r="E132" s="284" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="F132" s="285" t="n"/>
@@ -22309,7 +21345,7 @@
       <c r="H132" s="285" t="n"/>
       <c r="I132" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="J132" s="1438" t="n">
@@ -22349,7 +21385,7 @@
       </c>
       <c r="U132" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="V132" s="285" t="n"/>
@@ -22364,7 +21400,7 @@
     <row r="133" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A133" s="280" t="inlineStr">
         <is>
-          <t>MQ-125</t>
+          <t>MQ-124</t>
         </is>
       </c>
       <c r="B133" s="281" t="inlineStr">
@@ -22374,17 +21410,17 @@
       </c>
       <c r="C133" s="282" t="inlineStr">
         <is>
-          <t>Bordillos</t>
+          <t>Pavimentos</t>
         </is>
       </c>
       <c r="D133" s="283" t="inlineStr">
         <is>
-          <t>18.02.01</t>
+          <t>18.01.03</t>
         </is>
       </c>
       <c r="E133" s="284" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="F133" s="285" t="n"/>
@@ -22392,7 +21428,7 @@
       <c r="H133" s="285" t="n"/>
       <c r="I133" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J133" s="1438" t="n">
@@ -22432,7 +21468,7 @@
       </c>
       <c r="U133" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V133" s="285" t="n"/>
@@ -22447,7 +21483,7 @@
     <row r="134" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A134" s="280" t="inlineStr">
         <is>
-          <t>MQ-126</t>
+          <t>MQ-125</t>
         </is>
       </c>
       <c r="B134" s="281" t="inlineStr">
@@ -22457,17 +21493,17 @@
       </c>
       <c r="C134" s="282" t="inlineStr">
         <is>
-          <t>Drenajes</t>
+          <t>Bordillos</t>
         </is>
       </c>
       <c r="D134" s="283" t="inlineStr">
         <is>
-          <t>18.03.01</t>
+          <t>18.02.01</t>
         </is>
       </c>
       <c r="E134" s="284" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="F134" s="285" t="n"/>
@@ -22475,7 +21511,7 @@
       <c r="H134" s="285" t="n"/>
       <c r="I134" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J134" s="1438" t="n">
@@ -22515,7 +21551,7 @@
       </c>
       <c r="U134" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V134" s="285" t="n"/>
@@ -22530,7 +21566,7 @@
     <row r="135" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A135" s="280" t="inlineStr">
         <is>
-          <t>MQ-127</t>
+          <t>MQ-126</t>
         </is>
       </c>
       <c r="B135" s="281" t="inlineStr">
@@ -22540,17 +21576,17 @@
       </c>
       <c r="C135" s="282" t="inlineStr">
         <is>
-          <t>Paisajismo</t>
+          <t>Drenajes</t>
         </is>
       </c>
       <c r="D135" s="283" t="inlineStr">
         <is>
-          <t>18.04.01</t>
+          <t>18.03.01</t>
         </is>
       </c>
       <c r="E135" s="284" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="F135" s="285" t="n"/>
@@ -22558,7 +21594,7 @@
       <c r="H135" s="285" t="n"/>
       <c r="I135" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J135" s="1438" t="n">
@@ -22598,7 +21634,7 @@
       </c>
       <c r="U135" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V135" s="285" t="n"/>
@@ -22613,7 +21649,7 @@
     <row r="136" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A136" s="280" t="inlineStr">
         <is>
-          <t>MQ-128</t>
+          <t>MQ-127</t>
         </is>
       </c>
       <c r="B136" s="281" t="inlineStr">
@@ -22628,12 +21664,12 @@
       </c>
       <c r="D136" s="283" t="inlineStr">
         <is>
-          <t>18.04.02</t>
+          <t>18.04.01</t>
         </is>
       </c>
       <c r="E136" s="284" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="F136" s="285" t="n"/>
@@ -22641,7 +21677,7 @@
       <c r="H136" s="285" t="n"/>
       <c r="I136" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="J136" s="1438" t="n">
@@ -22681,7 +21717,7 @@
       </c>
       <c r="U136" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="V136" s="285" t="n"/>
@@ -22696,27 +21732,27 @@
     <row r="137" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A137" s="280" t="inlineStr">
         <is>
-          <t>MQ-129</t>
+          <t>MQ-128</t>
         </is>
       </c>
       <c r="B137" s="281" t="inlineStr">
         <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C137" s="282" t="inlineStr">
         <is>
-          <t>Metálicas</t>
+          <t>Paisajismo</t>
         </is>
       </c>
       <c r="D137" s="283" t="inlineStr">
         <is>
-          <t>19.01.01</t>
+          <t>18.04.02</t>
         </is>
       </c>
       <c r="E137" s="284" t="inlineStr">
         <is>
-          <t>Rejas metálicas</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="F137" s="285" t="n"/>
@@ -22779,7 +21815,7 @@
     <row r="138" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A138" s="280" t="inlineStr">
         <is>
-          <t>MQ-130</t>
+          <t>MQ-129</t>
         </is>
       </c>
       <c r="B138" s="281" t="inlineStr">
@@ -22794,12 +21830,12 @@
       </c>
       <c r="D138" s="283" t="inlineStr">
         <is>
-          <t>19.01.02</t>
+          <t>19.01.01</t>
         </is>
       </c>
       <c r="E138" s="284" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="F138" s="285" t="n"/>
@@ -22807,7 +21843,7 @@
       <c r="H138" s="285" t="n"/>
       <c r="I138" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J138" s="1438" t="n">
@@ -22847,7 +21883,7 @@
       </c>
       <c r="U138" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V138" s="285" t="n"/>
@@ -22862,7 +21898,7 @@
     <row r="139" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A139" s="280" t="inlineStr">
         <is>
-          <t>MQ-131</t>
+          <t>MQ-130</t>
         </is>
       </c>
       <c r="B139" s="281" t="inlineStr">
@@ -22877,12 +21913,12 @@
       </c>
       <c r="D139" s="283" t="inlineStr">
         <is>
-          <t>19.01.03</t>
+          <t>19.01.02</t>
         </is>
       </c>
       <c r="E139" s="284" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="F139" s="285" t="n"/>
@@ -22945,7 +21981,7 @@
     <row r="140" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A140" s="280" t="inlineStr">
         <is>
-          <t>MQ-132</t>
+          <t>MQ-131</t>
         </is>
       </c>
       <c r="B140" s="281" t="inlineStr">
@@ -22955,17 +21991,17 @@
       </c>
       <c r="C140" s="282" t="inlineStr">
         <is>
-          <t>Mobiliario</t>
+          <t>Metálicas</t>
         </is>
       </c>
       <c r="D140" s="283" t="inlineStr">
         <is>
-          <t>19.02.01</t>
+          <t>19.01.03</t>
         </is>
       </c>
       <c r="E140" s="284" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="F140" s="285" t="n"/>
@@ -22973,7 +22009,7 @@
       <c r="H140" s="285" t="n"/>
       <c r="I140" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J140" s="1438" t="n">
@@ -23013,7 +22049,7 @@
       </c>
       <c r="U140" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="V140" s="285" t="n"/>
@@ -23028,27 +22064,27 @@
     <row r="141" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A141" s="280" t="inlineStr">
         <is>
-          <t>MQ-133</t>
+          <t>MQ-132</t>
         </is>
       </c>
       <c r="B141" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C141" s="282" t="inlineStr">
         <is>
-          <t>Limpieza</t>
+          <t>Mobiliario</t>
         </is>
       </c>
       <c r="D141" s="283" t="inlineStr">
         <is>
-          <t>20.01.01</t>
+          <t>19.02.01</t>
         </is>
       </c>
       <c r="E141" s="284" t="inlineStr">
         <is>
-          <t>Limpieza gruesa y fina de obra</t>
+          <t>Mobiliario fijo de obra</t>
         </is>
       </c>
       <c r="F141" s="285" t="n"/>
@@ -23056,7 +22092,7 @@
       <c r="H141" s="285" t="n"/>
       <c r="I141" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J141" s="1438" t="n">
@@ -23096,7 +22132,7 @@
       </c>
       <c r="U141" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="V141" s="285" t="n"/>
@@ -23111,7 +22147,7 @@
     <row r="142" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A142" s="280" t="inlineStr">
         <is>
-          <t>MQ-134</t>
+          <t>MQ-133</t>
         </is>
       </c>
       <c r="B142" s="281" t="inlineStr">
@@ -23126,12 +22162,12 @@
       </c>
       <c r="D142" s="283" t="inlineStr">
         <is>
-          <t>20.01.02</t>
+          <t>20.01.01</t>
         </is>
       </c>
       <c r="E142" s="284" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="F142" s="285" t="n"/>
@@ -23194,7 +22230,7 @@
     <row r="143" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A143" s="280" t="inlineStr">
         <is>
-          <t>MQ-135</t>
+          <t>MQ-134</t>
         </is>
       </c>
       <c r="B143" s="281" t="inlineStr">
@@ -23204,17 +22240,17 @@
       </c>
       <c r="C143" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Limpieza</t>
         </is>
       </c>
       <c r="D143" s="283" t="inlineStr">
         <is>
-          <t>20.02.01</t>
+          <t>20.01.02</t>
         </is>
       </c>
       <c r="E143" s="284" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="F143" s="285" t="n"/>
@@ -23222,7 +22258,7 @@
       <c r="H143" s="285" t="n"/>
       <c r="I143" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J143" s="1438" t="n">
@@ -23262,7 +22298,7 @@
       </c>
       <c r="U143" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="V143" s="285" t="n"/>
@@ -23277,7 +22313,7 @@
     <row r="144" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A144" s="280" t="inlineStr">
         <is>
-          <t>MQ-136</t>
+          <t>MQ-135</t>
         </is>
       </c>
       <c r="B144" s="281" t="inlineStr">
@@ -23287,7 +22323,7 @@
       </c>
       <c r="C144" s="282" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D144" s="283" t="inlineStr">
@@ -23297,7 +22333,7 @@
       </c>
       <c r="E144" s="284" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="F144" s="285" t="n"/>
@@ -23360,7 +22396,7 @@
     <row r="145" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A145" s="280" t="inlineStr">
         <is>
-          <t>MQ-137</t>
+          <t>MQ-136</t>
         </is>
       </c>
       <c r="B145" s="281" t="inlineStr">
@@ -23370,17 +22406,17 @@
       </c>
       <c r="C145" s="282" t="inlineStr">
         <is>
-          <t>Entrega</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D145" s="283" t="inlineStr">
         <is>
-          <t>20.02.02</t>
+          <t>20.02.01</t>
         </is>
       </c>
       <c r="E145" s="284" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="F145" s="285" t="n"/>
@@ -23440,26 +22476,30 @@
         </is>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A146" s="280" t="inlineStr">
         <is>
-          <t>MQ-138</t>
+          <t>MQ-137</t>
         </is>
       </c>
       <c r="B146" s="281" t="inlineStr">
         <is>
-          <t>PRELIMINARES</t>
-        </is>
-      </c>
-      <c r="C146" s="282" t="n"/>
+          <t>ASEO, ENTREGA Y CIERRE</t>
+        </is>
+      </c>
+      <c r="C146" s="282" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
       <c r="D146" s="283" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>20.02.02</t>
         </is>
       </c>
       <c r="E146" s="284" t="inlineStr">
         <is>
-          <t>Desmantelamiento de estructuras metálicas existentes</t>
+          <t>Entrega, manuales y acta de recibo</t>
         </is>
       </c>
       <c r="F146" s="285" t="n"/>
@@ -23467,34 +22507,78 @@
       <c r="H146" s="285" t="n"/>
       <c r="I146" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="Y146" s="336">
-        <f>I4</f>
-        <v/>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="J146" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q146" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" s="1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" s="1438">
+        <f>IF(I146="","",ROUND(IF(OR(I146="m²",I146="m2"),J146*IF(K146=0,1,K146)*IF(N146=0,1,N146)*IF(O146=0,1,O146)*P146-Q146,IF(OR(I146="m³",I146="m3"),J146*K146*L146*IF(N146=0,1,N146)*IF(O146=0,1,O146)*P146-Q146,IF(OR(I146="ml",I146="ML"),J146*IF(N146=0,1,N146)*IF(O146=0,1,O146)*P146-Q146,IF(OR(I146="und",I146="UND"),IF(N146=0,1,N146)*IF(O146=0,1,O146)*P146-Q146,IF(I146="kg",J146*IF(N146=0,1,N146)*IF(O146=0,1,O146)*P146-Q146,IF(OR(I146="gl",I146="GL",I146="gb",I146="GB",I146="Gl",I146="Gb"),IF(N146=0,1,N146)*IF(O146=0,1,O146)*P146-Q146,0)))))),3))</f>
+        <v/>
+      </c>
+      <c r="T146" s="1438">
+        <f>IF(S146="","",ROUND(S146*(1+R146),3))</f>
+        <v/>
+      </c>
+      <c r="U146" s="283" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="V146" s="285" t="n"/>
+      <c r="W146" s="285" t="n"/>
+      <c r="X146" s="1304" t="n"/>
+      <c r="Y146" s="285" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="280" t="inlineStr">
         <is>
-          <t>MQ-139</t>
+          <t>MQ-138</t>
         </is>
       </c>
       <c r="B147" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>PRELIMINARES</t>
         </is>
       </c>
       <c r="C147" s="282" t="n"/>
       <c r="D147" s="283" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E147" s="284" t="inlineStr">
         <is>
-          <t>Grouting cementoso para reparación estructural</t>
+          <t>Desmantelamiento de estructuras metálicas existentes</t>
         </is>
       </c>
       <c r="F147" s="285" t="n"/>
@@ -23502,14 +22586,18 @@
       <c r="H147" s="285" t="n"/>
       <c r="I147" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="Y147" s="336">
+        <f>I4</f>
+        <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="280" t="inlineStr">
         <is>
-          <t>MQ-140</t>
+          <t>MQ-139</t>
         </is>
       </c>
       <c r="B148" s="281" t="inlineStr">
@@ -23520,12 +22608,12 @@
       <c r="C148" s="282" t="n"/>
       <c r="D148" s="283" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="E148" s="284" t="inlineStr">
         <is>
-          <t>Grouting epóxico para reparación estructural</t>
+          <t>Grouting cementoso para reparación estructural</t>
         </is>
       </c>
       <c r="F148" s="285" t="n"/>
@@ -23540,23 +22628,23 @@
     <row r="149">
       <c r="A149" s="280" t="inlineStr">
         <is>
-          <t>MQ-141</t>
+          <t>MQ-140</t>
         </is>
       </c>
       <c r="B149" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>ESTRUCTURA</t>
         </is>
       </c>
       <c r="C149" s="282" t="n"/>
       <c r="D149" s="283" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E149" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Grouting epóxico para reparación estructural</t>
         </is>
       </c>
       <c r="F149" s="285" t="n"/>
@@ -23571,7 +22659,7 @@
     <row r="150">
       <c r="A150" s="280" t="inlineStr">
         <is>
-          <t>MQ-142</t>
+          <t>MQ-141</t>
         </is>
       </c>
       <c r="B150" s="281" t="inlineStr">
@@ -23582,12 +22670,12 @@
       <c r="C150" s="282" t="n"/>
       <c r="D150" s="283" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="E150" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="F150" s="285" t="n"/>
@@ -23602,23 +22690,23 @@
     <row r="151">
       <c r="A151" s="280" t="inlineStr">
         <is>
-          <t>MQ-143</t>
+          <t>MQ-142</t>
         </is>
       </c>
       <c r="B151" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C151" s="282" t="n"/>
       <c r="D151" s="283" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="E151" s="284" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
         </is>
       </c>
       <c r="F151" s="285" t="n"/>
@@ -23633,7 +22721,7 @@
     <row r="152">
       <c r="A152" s="280" t="inlineStr">
         <is>
-          <t>MQ-144</t>
+          <t>MQ-143</t>
         </is>
       </c>
       <c r="B152" s="281" t="inlineStr">
@@ -23644,12 +22732,12 @@
       <c r="C152" s="282" t="n"/>
       <c r="D152" s="283" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="E152" s="284" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="F152" s="285" t="n"/>
@@ -23664,23 +22752,23 @@
     <row r="153">
       <c r="A153" s="280" t="inlineStr">
         <is>
-          <t>MQ-145</t>
+          <t>MQ-144</t>
         </is>
       </c>
       <c r="B153" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C153" s="282" t="n"/>
       <c r="D153" s="283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="E153" s="284" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
         </is>
       </c>
       <c r="F153" s="285" t="n"/>
@@ -23695,23 +22783,23 @@
     <row r="154">
       <c r="A154" s="280" t="inlineStr">
         <is>
-          <t>MQ-146</t>
+          <t>MQ-145</t>
         </is>
       </c>
       <c r="B154" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C154" s="282" t="n"/>
       <c r="D154" s="283" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E154" s="284" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
         </is>
       </c>
       <c r="F154" s="285" t="n"/>
@@ -23726,7 +22814,7 @@
     <row r="155">
       <c r="A155" s="280" t="inlineStr">
         <is>
-          <t>MQ-147</t>
+          <t>MQ-146</t>
         </is>
       </c>
       <c r="B155" s="281" t="inlineStr">
@@ -23737,12 +22825,12 @@
       <c r="C155" s="282" t="n"/>
       <c r="D155" s="283" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="E155" s="284" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="F155" s="285" t="n"/>
@@ -23757,7 +22845,7 @@
     <row r="156">
       <c r="A156" s="280" t="inlineStr">
         <is>
-          <t>MQ-148</t>
+          <t>MQ-147</t>
         </is>
       </c>
       <c r="B156" s="281" t="inlineStr">
@@ -23768,12 +22856,12 @@
       <c r="C156" s="282" t="n"/>
       <c r="D156" s="283" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="E156" s="284" t="inlineStr">
         <is>
-          <t>Enchape en granito pulido</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="F156" s="285" t="n"/>
@@ -23788,23 +22876,23 @@
     <row r="157">
       <c r="A157" s="280" t="inlineStr">
         <is>
-          <t>MQ-149</t>
+          <t>MQ-148</t>
         </is>
       </c>
       <c r="B157" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C157" s="282" t="n"/>
       <c r="D157" s="283" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="E157" s="284" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Enchape en granito pulido</t>
         </is>
       </c>
       <c r="F157" s="285" t="n"/>
@@ -23812,30 +22900,30 @@
       <c r="H157" s="285" t="n"/>
       <c r="I157" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="280" t="inlineStr">
         <is>
-          <t>MQ-150</t>
+          <t>MQ-149</t>
         </is>
       </c>
       <c r="B158" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C158" s="282" t="n"/>
       <c r="D158" s="283" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="E158" s="284" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Puerta antipánico</t>
         </is>
       </c>
       <c r="F158" s="285" t="n"/>
@@ -23850,23 +22938,23 @@
     <row r="159">
       <c r="A159" s="280" t="inlineStr">
         <is>
-          <t>MQ-151</t>
+          <t>MQ-150</t>
         </is>
       </c>
       <c r="B159" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C159" s="282" t="n"/>
       <c r="D159" s="283" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="E159" s="284" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Orinal institucional</t>
         </is>
       </c>
       <c r="F159" s="285" t="n"/>
@@ -23874,14 +22962,14 @@
       <c r="H159" s="285" t="n"/>
       <c r="I159" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="280" t="inlineStr">
         <is>
-          <t>MQ-152</t>
+          <t>MQ-151</t>
         </is>
       </c>
       <c r="B160" s="281" t="inlineStr">
@@ -23892,12 +22980,12 @@
       <c r="C160" s="282" t="n"/>
       <c r="D160" s="283" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="E160" s="284" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="F160" s="285" t="n"/>
@@ -23905,14 +22993,14 @@
       <c r="H160" s="285" t="n"/>
       <c r="I160" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="280" t="inlineStr">
         <is>
-          <t>MQ-153</t>
+          <t>MQ-152</t>
         </is>
       </c>
       <c r="B161" s="281" t="inlineStr">
@@ -23923,12 +23011,12 @@
       <c r="C161" s="282" t="n"/>
       <c r="D161" s="283" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="E161" s="284" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="F161" s="285" t="n"/>
@@ -23936,14 +23024,14 @@
       <c r="H161" s="285" t="n"/>
       <c r="I161" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="280" t="inlineStr">
         <is>
-          <t>MQ-154</t>
+          <t>MQ-153</t>
         </is>
       </c>
       <c r="B162" s="281" t="inlineStr">
@@ -23954,12 +23042,12 @@
       <c r="C162" s="282" t="n"/>
       <c r="D162" s="283" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="E162" s="284" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="F162" s="285" t="n"/>
@@ -23967,30 +23055,30 @@
       <c r="H162" s="285" t="n"/>
       <c r="I162" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="280" t="inlineStr">
         <is>
-          <t>MQ-155</t>
+          <t>MQ-154</t>
         </is>
       </c>
       <c r="B163" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C163" s="282" t="n"/>
       <c r="D163" s="283" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="E163" s="284" t="inlineStr">
         <is>
-          <t>Concreto premezclado o de planta (suministro)</t>
+          <t>Revegetalización / empradización</t>
         </is>
       </c>
       <c r="F163" s="285" t="n"/>
@@ -23998,30 +23086,30 @@
       <c r="H163" s="285" t="n"/>
       <c r="I163" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="280" t="inlineStr">
         <is>
-          <t>MQ-157</t>
+          <t>MQ-155</t>
         </is>
       </c>
       <c r="B164" s="281" t="inlineStr">
         <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+          <t>ESTRUCTURA</t>
         </is>
       </c>
       <c r="C164" s="282" t="n"/>
       <c r="D164" s="283" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="E164" s="284" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Concreto premezclado o de planta (suministro)</t>
         </is>
       </c>
       <c r="F164" s="285" t="n"/>
@@ -24029,14 +23117,14 @@
       <c r="H164" s="285" t="n"/>
       <c r="I164" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="280" t="inlineStr">
         <is>
-          <t>MQ-158</t>
+          <t>MQ-157</t>
         </is>
       </c>
       <c r="B165" s="281" t="inlineStr">
@@ -24047,12 +23135,12 @@
       <c r="C165" s="282" t="n"/>
       <c r="D165" s="283" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="E165" s="284" t="inlineStr">
         <is>
-          <t>Estudio de suelos y geotecnia</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="F165" s="285" t="n"/>
@@ -24067,7 +23155,7 @@
     <row r="166">
       <c r="A166" s="280" t="inlineStr">
         <is>
-          <t>MQ-159</t>
+          <t>MQ-158</t>
         </is>
       </c>
       <c r="B166" s="281" t="inlineStr">
@@ -24078,12 +23166,12 @@
       <c r="C166" s="282" t="n"/>
       <c r="D166" s="283" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="E166" s="284" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="F166" s="285" t="n"/>
@@ -24098,7 +23186,7 @@
     <row r="167">
       <c r="A167" s="280" t="inlineStr">
         <is>
-          <t>MQ-160</t>
+          <t>MQ-159</t>
         </is>
       </c>
       <c r="B167" s="281" t="inlineStr">
@@ -24109,12 +23197,12 @@
       <c r="C167" s="282" t="n"/>
       <c r="D167" s="283" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E167" s="284" t="inlineStr">
         <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="F167" s="285" t="n"/>
@@ -24129,23 +23217,23 @@
     <row r="168">
       <c r="A168" s="280" t="inlineStr">
         <is>
-          <t>MQ-161</t>
+          <t>MQ-160</t>
         </is>
       </c>
       <c r="B168" s="281" t="inlineStr">
         <is>
-          <t>ASCENSORES</t>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C168" s="282" t="n"/>
       <c r="D168" s="283" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="E168" s="284" t="inlineStr">
         <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
         </is>
       </c>
       <c r="F168" s="285" t="n"/>
@@ -24153,12 +23241,43 @@
       <c r="H168" s="285" t="n"/>
       <c r="I168" s="283" t="inlineStr">
         <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="280" t="inlineStr">
+        <is>
+          <t>MQ-161</t>
+        </is>
+      </c>
+      <c r="B169" s="281" t="inlineStr">
+        <is>
+          <t>ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C169" s="282" t="n"/>
+      <c r="D169" s="283" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="E169" s="284" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de ascensor eléctrico</t>
+        </is>
+      </c>
+      <c r="F169" s="285" t="n"/>
+      <c r="G169" s="285" t="n"/>
+      <c r="H169" s="285" t="n"/>
+      <c r="I169" s="283" t="inlineStr">
+        <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="1446" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="1446" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
@@ -24186,7 +23305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -25244,7 +24363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -28669,7 +27788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1565C0"/>
@@ -34027,4 +33146,913 @@
   <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1565C0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="15.77734375" customWidth="1" style="550" min="1" max="2"/>
+    <col width="25.77734375" customWidth="1" style="550" min="3" max="3"/>
+    <col width="12" customWidth="1" style="550" min="4" max="4"/>
+    <col width="14" customWidth="1" style="550" min="5" max="5"/>
+    <col width="48" customWidth="1" style="550" min="7" max="7"/>
+    <col width="20" customWidth="1" style="550" min="8" max="8"/>
+    <col width="38" customWidth="1" style="550" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40.05" customHeight="1" s="550">
+      <c r="A1" s="508" t="n"/>
+      <c r="B1" s="618" t="n"/>
+      <c r="C1" s="618" t="n"/>
+      <c r="D1" s="696" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PLANOS Y REVISIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4.95" customHeight="1" s="550">
+      <c r="A2" s="618" t="n"/>
+      <c r="B2" s="618" t="n"/>
+      <c r="C2" s="618" t="n"/>
+      <c r="D2" s="693" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="550">
+      <c r="A3" s="618" t="n"/>
+      <c r="B3" s="618" t="n"/>
+      <c r="C3" s="618" t="n"/>
+      <c r="D3" s="694" t="n"/>
+      <c r="H3" s="691" t="inlineStr">
+        <is>
+          <t>CONTROL DOCUMENTAL</t>
+        </is>
+      </c>
+      <c r="I3" s="692" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="550">
+      <c r="A4" s="618" t="n"/>
+      <c r="B4" s="618" t="n"/>
+      <c r="C4" s="618" t="n"/>
+      <c r="D4" s="564" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="G4" s="562" t="n"/>
+      <c r="H4" s="270" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="I4" s="271" t="inlineStr">
+        <is>
+          <t>RYR-CO-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="550">
+      <c r="A5" s="618" t="n"/>
+      <c r="B5" s="618" t="n"/>
+      <c r="C5" s="618" t="n"/>
+      <c r="D5" s="683" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="G5" s="562" t="n"/>
+      <c r="H5" s="242" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="I5" s="239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="550">
+      <c r="A6" s="618" t="n"/>
+      <c r="B6" s="618" t="n"/>
+      <c r="C6" s="618" t="n"/>
+      <c r="D6" s="695" t="n"/>
+      <c r="H6" s="242" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="I6" s="239" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="618" t="n"/>
+      <c r="B7" s="618" t="n"/>
+      <c r="C7" s="618" t="n"/>
+      <c r="D7" s="633" t="n"/>
+      <c r="E7" s="633" t="n"/>
+      <c r="F7" s="633" t="n"/>
+      <c r="G7" s="633" t="n"/>
+      <c r="H7" s="240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Página </t>
+        </is>
+      </c>
+      <c r="I7" s="241" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customFormat="1" customHeight="1" s="615">
+      <c r="A8" s="507" t="inlineStr">
+        <is>
+          <t>Código plano</t>
+        </is>
+      </c>
+      <c r="B8" s="507" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="C8" s="507" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="D8" s="245" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="E8" s="245" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="F8" s="245" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="G8" s="245" t="inlineStr">
+        <is>
+          <t>Actividades relacionadas</t>
+        </is>
+      </c>
+      <c r="H8" s="245" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="I8" s="245" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="690">
+      <c r="A9" s="249" t="inlineStr">
+        <is>
+          <t>ARQ-001</t>
+        </is>
+      </c>
+      <c r="B9" s="250" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="C9" s="246" t="inlineStr">
+        <is>
+          <t>Planta general</t>
+        </is>
+      </c>
+      <c r="D9" s="247" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E9" s="1309" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F9" s="247" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G9" s="246" t="inlineStr">
+        <is>
+          <t>Preliminares / mampostería / acabados</t>
+        </is>
+      </c>
+      <c r="H9" s="246" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I9" s="248" t="n"/>
+    </row>
+    <row r="10" customFormat="1" s="690">
+      <c r="A10" s="249" t="inlineStr">
+        <is>
+          <t>EST-101</t>
+        </is>
+      </c>
+      <c r="B10" s="250" t="inlineStr">
+        <is>
+          <t>Estructural</t>
+        </is>
+      </c>
+      <c r="C10" s="246" t="inlineStr">
+        <is>
+          <t>Cimentación</t>
+        </is>
+      </c>
+      <c r="D10" s="247" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="E10" s="1309" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F10" s="247" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G10" s="246" t="inlineStr">
+        <is>
+          <t>Cimentaciones / estructura</t>
+        </is>
+      </c>
+      <c r="H10" s="246" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I10" s="248" t="n"/>
+    </row>
+    <row r="11" customFormat="1" s="690">
+      <c r="A11" s="249" t="inlineStr">
+        <is>
+          <t>HID-201</t>
+        </is>
+      </c>
+      <c r="B11" s="250" t="inlineStr">
+        <is>
+          <t>Hidrosanitaria</t>
+        </is>
+      </c>
+      <c r="C11" s="246" t="inlineStr">
+        <is>
+          <t>Redes hidrosanitarias</t>
+        </is>
+      </c>
+      <c r="D11" s="247" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E11" s="1309" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F11" s="247" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G11" s="246" t="inlineStr">
+        <is>
+          <t>Instalaciones hidrosanitarias</t>
+        </is>
+      </c>
+      <c r="H11" s="246" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I11" s="248" t="n"/>
+    </row>
+    <row r="12" customFormat="1" s="690">
+      <c r="A12" s="249" t="inlineStr">
+        <is>
+          <t>ELE-301</t>
+        </is>
+      </c>
+      <c r="B12" s="250" t="inlineStr">
+        <is>
+          <t>Eléctrica</t>
+        </is>
+      </c>
+      <c r="C12" s="246" t="inlineStr">
+        <is>
+          <t>Fuerza e iluminación</t>
+        </is>
+      </c>
+      <c r="D12" s="247" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E12" s="1309" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F12" s="247" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G12" s="246" t="inlineStr">
+        <is>
+          <t>Instalaciones eléctricas</t>
+        </is>
+      </c>
+      <c r="H12" s="246" t="inlineStr">
+        <is>
+          <t>Ing. Residente</t>
+        </is>
+      </c>
+      <c r="I12" s="248" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="244" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="243" t="n"/>
+      <c r="C13" s="243" t="n"/>
+      <c r="D13" s="243" t="n"/>
+      <c r="E13" s="243" t="n"/>
+      <c r="F13" s="243" t="n"/>
+      <c r="G13" s="243" t="n"/>
+      <c r="H13" s="243" t="n"/>
+      <c r="I13" s="344">
+        <f>I4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="243" t="n"/>
+      <c r="B14" s="243" t="n"/>
+      <c r="C14" s="243" t="n"/>
+      <c r="D14" s="243" t="n"/>
+      <c r="E14" s="243" t="n"/>
+      <c r="F14" s="243" t="n"/>
+      <c r="G14" s="243" t="n"/>
+      <c r="H14" s="243" t="n"/>
+      <c r="I14" s="243" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="243" t="n"/>
+      <c r="B15" s="243" t="n"/>
+      <c r="C15" s="243" t="n"/>
+      <c r="D15" s="243" t="n"/>
+      <c r="E15" s="243" t="n"/>
+      <c r="F15" s="243" t="n"/>
+      <c r="G15" s="243" t="n"/>
+      <c r="H15" s="243" t="n"/>
+      <c r="I15" s="243" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="243" t="n"/>
+      <c r="B16" s="243" t="n"/>
+      <c r="C16" s="243" t="n"/>
+      <c r="D16" s="243" t="n"/>
+      <c r="E16" s="243" t="n"/>
+      <c r="F16" s="243" t="n"/>
+      <c r="G16" s="243" t="n"/>
+      <c r="H16" s="243" t="n"/>
+      <c r="I16" s="243" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="243" t="n"/>
+      <c r="B17" s="243" t="n"/>
+      <c r="C17" s="243" t="n"/>
+      <c r="D17" s="243" t="n"/>
+      <c r="E17" s="243" t="n"/>
+      <c r="F17" s="243" t="n"/>
+      <c r="G17" s="243" t="n"/>
+      <c r="H17" s="243" t="n"/>
+      <c r="I17" s="243" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="243" t="n"/>
+      <c r="B18" s="243" t="n"/>
+      <c r="C18" s="243" t="n"/>
+      <c r="D18" s="243" t="n"/>
+      <c r="E18" s="243" t="n"/>
+      <c r="F18" s="243" t="n"/>
+      <c r="G18" s="243" t="n"/>
+      <c r="H18" s="243" t="n"/>
+      <c r="I18" s="243" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="243" t="n"/>
+      <c r="B19" s="243" t="n"/>
+      <c r="C19" s="243" t="n"/>
+      <c r="D19" s="243" t="n"/>
+      <c r="E19" s="243" t="n"/>
+      <c r="F19" s="243" t="n"/>
+      <c r="G19" s="243" t="n"/>
+      <c r="H19" s="243" t="n"/>
+      <c r="I19" s="243" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="243" t="n"/>
+      <c r="B20" s="243" t="n"/>
+      <c r="C20" s="243" t="n"/>
+      <c r="D20" s="243" t="n"/>
+      <c r="E20" s="243" t="n"/>
+      <c r="F20" s="243" t="n"/>
+      <c r="G20" s="243" t="n"/>
+      <c r="H20" s="243" t="n"/>
+      <c r="I20" s="243" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="243" t="n"/>
+      <c r="B21" s="243" t="n"/>
+      <c r="C21" s="243" t="n"/>
+      <c r="D21" s="243" t="n"/>
+      <c r="E21" s="243" t="n"/>
+      <c r="F21" s="243" t="n"/>
+      <c r="G21" s="243" t="n"/>
+      <c r="H21" s="243" t="n"/>
+      <c r="I21" s="243" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="243" t="n"/>
+      <c r="B22" s="243" t="n"/>
+      <c r="C22" s="243" t="n"/>
+      <c r="D22" s="243" t="n"/>
+      <c r="E22" s="243" t="n"/>
+      <c r="F22" s="243" t="n"/>
+      <c r="G22" s="243" t="n"/>
+      <c r="H22" s="243" t="n"/>
+      <c r="I22" s="243" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="243" t="n"/>
+      <c r="B23" s="243" t="n"/>
+      <c r="C23" s="243" t="n"/>
+      <c r="D23" s="243" t="n"/>
+      <c r="E23" s="243" t="n"/>
+      <c r="F23" s="243" t="n"/>
+      <c r="G23" s="243" t="n"/>
+      <c r="H23" s="243" t="n"/>
+      <c r="I23" s="243" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="243" t="n"/>
+      <c r="B24" s="243" t="n"/>
+      <c r="C24" s="243" t="n"/>
+      <c r="D24" s="243" t="n"/>
+      <c r="E24" s="243" t="n"/>
+      <c r="F24" s="243" t="n"/>
+      <c r="G24" s="243" t="n"/>
+      <c r="H24" s="243" t="n"/>
+      <c r="I24" s="243" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="243" t="n"/>
+      <c r="B25" s="243" t="n"/>
+      <c r="C25" s="243" t="n"/>
+      <c r="D25" s="243" t="n"/>
+      <c r="E25" s="243" t="n"/>
+      <c r="F25" s="243" t="n"/>
+      <c r="G25" s="243" t="n"/>
+      <c r="H25" s="243" t="n"/>
+      <c r="I25" s="243" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="277" t="n"/>
+      <c r="B26" s="277" t="n"/>
+      <c r="C26" s="277" t="n"/>
+      <c r="D26" s="277" t="n"/>
+      <c r="E26" s="277" t="n"/>
+      <c r="F26" s="277" t="n"/>
+      <c r="G26" s="277" t="n"/>
+      <c r="H26" s="277" t="n"/>
+      <c r="I26" s="277" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="277" t="n"/>
+      <c r="B27" s="277" t="n"/>
+      <c r="C27" s="277" t="n"/>
+      <c r="D27" s="277" t="n"/>
+      <c r="E27" s="277" t="n"/>
+      <c r="F27" s="277" t="n"/>
+      <c r="G27" s="277" t="n"/>
+      <c r="H27" s="277" t="n"/>
+      <c r="I27" s="277" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="277" t="n"/>
+      <c r="B28" s="277" t="n"/>
+      <c r="C28" s="277" t="n"/>
+      <c r="D28" s="277" t="n"/>
+      <c r="E28" s="277" t="n"/>
+      <c r="F28" s="277" t="n"/>
+      <c r="G28" s="277" t="n"/>
+      <c r="H28" s="277" t="n"/>
+      <c r="I28" s="277" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="277" t="n"/>
+      <c r="B29" s="277" t="n"/>
+      <c r="C29" s="277" t="n"/>
+      <c r="D29" s="277" t="n"/>
+      <c r="E29" s="277" t="n"/>
+      <c r="F29" s="277" t="n"/>
+      <c r="G29" s="277" t="n"/>
+      <c r="H29" s="277" t="n"/>
+      <c r="I29" s="277" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="277" t="n"/>
+      <c r="B30" s="277" t="n"/>
+      <c r="C30" s="277" t="n"/>
+      <c r="D30" s="277" t="n"/>
+      <c r="E30" s="277" t="n"/>
+      <c r="F30" s="277" t="n"/>
+      <c r="G30" s="277" t="n"/>
+      <c r="H30" s="277" t="n"/>
+      <c r="I30" s="277" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="277" t="n"/>
+      <c r="B31" s="277" t="n"/>
+      <c r="C31" s="277" t="n"/>
+      <c r="D31" s="277" t="n"/>
+      <c r="E31" s="277" t="n"/>
+      <c r="F31" s="277" t="n"/>
+      <c r="G31" s="277" t="n"/>
+      <c r="H31" s="277" t="n"/>
+      <c r="I31" s="277" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="277" t="n"/>
+      <c r="B32" s="277" t="n"/>
+      <c r="C32" s="277" t="n"/>
+      <c r="D32" s="277" t="n"/>
+      <c r="E32" s="277" t="n"/>
+      <c r="F32" s="277" t="n"/>
+      <c r="G32" s="277" t="n"/>
+      <c r="H32" s="277" t="n"/>
+      <c r="I32" s="277" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="277" t="n"/>
+      <c r="B33" s="277" t="n"/>
+      <c r="C33" s="277" t="n"/>
+      <c r="D33" s="277" t="n"/>
+      <c r="E33" s="277" t="n"/>
+      <c r="F33" s="277" t="n"/>
+      <c r="G33" s="277" t="n"/>
+      <c r="H33" s="277" t="n"/>
+      <c r="I33" s="277" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="277" t="n"/>
+      <c r="B34" s="277" t="n"/>
+      <c r="C34" s="277" t="n"/>
+      <c r="D34" s="277" t="n"/>
+      <c r="E34" s="277" t="n"/>
+      <c r="F34" s="277" t="n"/>
+      <c r="G34" s="277" t="n"/>
+      <c r="H34" s="277" t="n"/>
+      <c r="I34" s="277" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:G7"/>
+    <mergeCell ref="D4:G4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1565C0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18" customWidth="1" style="550" min="1" max="1"/>
+    <col width="15.77734375" customWidth="1" style="550" min="11" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40.05" customHeight="1" s="550">
+      <c r="A1" s="505" t="n"/>
+      <c r="B1" s="505" t="n"/>
+      <c r="C1" s="505" t="n"/>
+      <c r="D1" s="506" t="n"/>
+      <c r="E1" s="613" t="inlineStr">
+        <is>
+          <t>INSTRUCTIVO DE USO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4.95" customHeight="1" s="550">
+      <c r="A2" s="505" t="n"/>
+      <c r="B2" s="505" t="n"/>
+      <c r="C2" s="505" t="n"/>
+      <c r="D2" s="618" t="n"/>
+      <c r="E2" s="700" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="550">
+      <c r="A3" s="505" t="n"/>
+      <c r="B3" s="505" t="n"/>
+      <c r="C3" s="505" t="n"/>
+      <c r="D3" s="618" t="n"/>
+      <c r="E3" s="615" t="n"/>
+      <c r="K3" s="702" t="inlineStr">
+        <is>
+          <t>CONTROL DOCUMENTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="550">
+      <c r="A4" s="505" t="n"/>
+      <c r="B4" s="505" t="n"/>
+      <c r="C4" s="505" t="n"/>
+      <c r="D4" s="618" t="n"/>
+      <c r="E4" s="564" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="J4" s="562" t="n"/>
+      <c r="K4" s="251" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="L4" s="697" t="inlineStr">
+        <is>
+          <t>RYR-CO-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="550">
+      <c r="A5" s="505" t="n"/>
+      <c r="B5" s="505" t="n"/>
+      <c r="C5" s="505" t="n"/>
+      <c r="D5" s="618" t="n"/>
+      <c r="E5" s="683" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="J5" s="562" t="n"/>
+      <c r="K5" s="251" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="L5" s="697" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1" s="550">
+      <c r="A6" s="505" t="n"/>
+      <c r="B6" s="505" t="n"/>
+      <c r="C6" s="505" t="n"/>
+      <c r="D6" s="618" t="n"/>
+      <c r="E6" s="615" t="n"/>
+      <c r="K6" s="251" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="L6" s="697" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="550">
+      <c r="A7" s="505" t="n"/>
+      <c r="B7" s="505" t="n"/>
+      <c r="C7" s="505" t="n"/>
+      <c r="D7" s="618" t="n"/>
+      <c r="K7" s="251" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="L7" s="697" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.95" customHeight="1" s="550">
+      <c r="A8" s="698" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES — INSTRUCTIVO DE CANTIDADES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="550">
+      <c r="A9" s="701" t="inlineStr">
+        <is>
+          <t>1. IDENTIFICAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="550">
+      <c r="A10" s="699" t="inlineStr">
+        <is>
+          <t>Use el código y actividad específica del catálogo; defina ubicación/frente y plano/revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="550"/>
+    <row r="12" ht="15" customHeight="1" s="550">
+      <c r="A12" s="701" t="inlineStr">
+        <is>
+          <t>2. MEDIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="550">
+      <c r="A13" s="699" t="inlineStr">
+        <is>
+          <t>Ingrese solo las dimensiones aplicables a la actividad: largo, ancho, alto/profundidad, espesor y número de elementos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="550"/>
+    <row r="15" ht="15" customHeight="1" s="550">
+      <c r="A15" s="701" t="inlineStr">
+        <is>
+          <t>3. REPETIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="550">
+      <c r="A16" s="699" t="inlineStr">
+        <is>
+          <t>Use N° de elementos para componentes repetitivos y Repeticiones para módulos o conjuntos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="550"/>
+    <row r="18" ht="15" customHeight="1" s="550">
+      <c r="A18" s="701" t="inlineStr">
+        <is>
+          <t>4. DEDUCIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="550">
+      <c r="A19" s="699" t="inlineStr">
+        <is>
+          <t>Registre vanos, vacíos u otros descuentos en Deducción y explique el criterio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="550"/>
+    <row r="21" ht="15" customHeight="1" s="550">
+      <c r="A21" s="701" t="inlineStr">
+        <is>
+          <t>5. DESPERDICIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="550">
+      <c r="A22" s="699" t="inlineStr">
+        <is>
+          <t>Ingrese el porcentaje como decimal (5% = 0,05) solo si está técnicamente o contractualmente sustentado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="550"/>
+    <row r="24" ht="15" customHeight="1" s="550">
+      <c r="A24" s="701" t="inlineStr">
+        <is>
+          <t>6. TRAZABILIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="550">
+      <c r="A25" s="699" t="inlineStr">
+        <is>
+          <t>Toda cantidad debe poder rastrearse a plano, detalle, especificación, medición de campo o documento contractual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="550"/>
+    <row r="27">
+      <c r="A27" s="701" t="inlineStr">
+        <is>
+          <t>7. VALIDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14.4" customHeight="1" s="550">
+      <c r="A28" s="699" t="inlineStr">
+        <is>
+          <t>Compare contra presupuesto, APU, planos y medición de campo; documente diferencias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="701" t="inlineStr">
+        <is>
+          <t>8. APROBAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14.4" customHeight="1" s="550">
+      <c r="A31" s="699" t="inlineStr">
+        <is>
+          <t>Cambie el Estado a Aprobada solo después de la revisión técnica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="203" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="203" t="n"/>
+      <c r="C33" s="203" t="n"/>
+      <c r="D33" s="203" t="n"/>
+      <c r="E33" s="203" t="n"/>
+      <c r="F33" s="203" t="n"/>
+      <c r="G33" s="203" t="n"/>
+      <c r="H33" s="203" t="n"/>
+      <c r="I33" s="203" t="n"/>
+      <c r="J33" s="203" t="n"/>
+      <c r="K33" s="203" t="n"/>
+      <c r="L33" s="203" t="n"/>
+      <c r="M33" s="202">
+        <f>L4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="E2:M2"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="E6:J7"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="E4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planos" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructivo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$Y$169</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -23284,6 +23286,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A8:Y169"/>
   <mergeCells count="13">
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C7:G7"/>
@@ -34015,10 +34018,10 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="E1:M1"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A23:M23"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructivo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$Y$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$Z$169</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -10875,7 +10875,7 @@
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y170"/>
+  <dimension ref="A1:Z170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="615" min="1" max="1"/>
@@ -10902,6 +10902,7 @@
     <col width="18" customWidth="1" style="550" min="23" max="23"/>
     <col width="12" customWidth="1" style="550" min="24" max="24"/>
     <col width="15" customWidth="1" style="550" min="25" max="25"/>
+    <col width="15" customWidth="1" style="550" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="550">
@@ -11162,6 +11163,11 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="Z8" s="279" t="inlineStr">
+        <is>
+          <t>Peso (kg) - solo acero</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A9" s="280" t="inlineStr">
@@ -23286,7 +23292,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:Y169"/>
+  <autoFilter ref="A8:Z169"/>
   <mergeCells count="13">
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C7:G7"/>
@@ -24372,7 +24378,7 @@
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U146"/>
+  <dimension ref="A1:V146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.77734375" customWidth="1" style="614" min="1" max="1"/>
@@ -24393,6 +24399,7 @@
     <col width="52" customWidth="1" style="615" min="19" max="19"/>
     <col width="22" customWidth="1" style="615" min="20" max="20"/>
     <col width="50.77734375" customWidth="1" style="550" min="21" max="21"/>
+    <col width="50.77734375" customWidth="1" style="550" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="550">
@@ -24614,6 +24621,11 @@
       <c r="U8" s="297" t="inlineStr">
         <is>
           <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="V8" s="297" t="inlineStr">
+        <is>
+          <t>Peso (kg) - solo acero</t>
         </is>
       </c>
     </row>
@@ -34018,10 +34030,10 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E1:M1"/>
     <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="E1:M1"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructivo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$Z$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$AA$169</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -6702,7 +6702,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1448">
+  <cellXfs count="1449">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10303,6 +10303,7 @@
     </xf>
     <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="422" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10887,7 +10888,7 @@
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA170"/>
+  <dimension ref="A1:AB170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="615" min="1" max="1"/>
@@ -10910,11 +10911,11 @@
     <col width="14" customWidth="1" style="550" min="18" max="18"/>
     <col width="15" customWidth="1" style="550" min="19" max="19"/>
     <col width="12.77734375" customWidth="1" style="550" min="20" max="20"/>
-    <col width="52" customWidth="1" style="615" min="21" max="21"/>
-    <col width="42" customWidth="1" style="550" min="22" max="22"/>
+    <col width="13" customWidth="1" style="615" min="21" max="21"/>
+    <col width="20" customWidth="1" style="550" min="22" max="22"/>
     <col width="18" customWidth="1" style="550" min="23" max="23"/>
     <col width="12" customWidth="1" style="550" min="24" max="24"/>
-    <col width="15" customWidth="1" style="550" min="25" max="25"/>
+    <col width="18" customWidth="1" style="550" min="25" max="25"/>
     <col width="15" customWidth="1" style="550" min="26" max="26"/>
   </cols>
   <sheetData>
@@ -11054,6 +11055,7 @@
       <c r="X7" s="633" t="n"/>
       <c r="Y7" s="633" t="n"/>
       <c r="Z7" s="633" t="n"/>
+      <c r="AA7" s="633" t="n"/>
     </row>
     <row r="8" ht="19.95" customFormat="1" customHeight="1" s="685">
       <c r="A8" s="514" t="inlineStr">
@@ -11178,15 +11180,20 @@
       </c>
       <c r="Y8" s="279" t="inlineStr">
         <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="Z8" s="279" t="inlineStr">
+        <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="Z8" s="279" t="inlineStr">
+      <c r="AA8" s="279" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="AA8" s="279" t="n"/>
+      <c r="AB8" s="279" t="n"/>
     </row>
     <row r="9" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A9" s="280" t="inlineStr">
@@ -11222,6 +11229,7 @@
           <t>m2</t>
         </is>
       </c>
+      <c r="J9" s="1448" t="n"/>
       <c r="K9" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11264,8 +11272,9 @@
       </c>
       <c r="W9" s="285" t="n"/>
       <c r="X9" s="285" t="n"/>
-      <c r="Y9" s="1304" t="n"/>
-      <c r="Z9" s="285" t="inlineStr">
+      <c r="Y9" s="1448" t="n"/>
+      <c r="Z9" s="1304" t="n"/>
+      <c r="AA9" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11305,6 +11314,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J10" s="1448" t="n"/>
       <c r="K10" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11347,8 +11357,9 @@
       </c>
       <c r="W10" s="285" t="n"/>
       <c r="X10" s="285" t="n"/>
-      <c r="Y10" s="1304" t="n"/>
-      <c r="Z10" s="285" t="inlineStr">
+      <c r="Y10" s="1448" t="n"/>
+      <c r="Z10" s="1304" t="n"/>
+      <c r="AA10" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11388,6 +11399,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J11" s="1448" t="n"/>
       <c r="K11" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11430,8 +11442,9 @@
       </c>
       <c r="W11" s="285" t="n"/>
       <c r="X11" s="285" t="n"/>
-      <c r="Y11" s="1304" t="n"/>
-      <c r="Z11" s="285" t="inlineStr">
+      <c r="Y11" s="1448" t="n"/>
+      <c r="Z11" s="1304" t="n"/>
+      <c r="AA11" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11471,6 +11484,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J12" s="1448" t="n"/>
       <c r="K12" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11513,8 +11527,9 @@
       </c>
       <c r="W12" s="285" t="n"/>
       <c r="X12" s="285" t="n"/>
-      <c r="Y12" s="1304" t="n"/>
-      <c r="Z12" s="285" t="inlineStr">
+      <c r="Y12" s="1448" t="n"/>
+      <c r="Z12" s="1304" t="n"/>
+      <c r="AA12" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11554,6 +11569,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J13" s="1448" t="n"/>
       <c r="K13" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11596,8 +11612,9 @@
       </c>
       <c r="W13" s="285" t="n"/>
       <c r="X13" s="285" t="n"/>
-      <c r="Y13" s="1304" t="n"/>
-      <c r="Z13" s="285" t="inlineStr">
+      <c r="Y13" s="1448" t="n"/>
+      <c r="Z13" s="1304" t="n"/>
+      <c r="AA13" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11637,6 +11654,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J14" s="1448" t="n"/>
       <c r="K14" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11679,8 +11697,9 @@
       </c>
       <c r="W14" s="285" t="n"/>
       <c r="X14" s="285" t="n"/>
-      <c r="Y14" s="1304" t="n"/>
-      <c r="Z14" s="285" t="inlineStr">
+      <c r="Y14" s="1448" t="n"/>
+      <c r="Z14" s="1304" t="n"/>
+      <c r="AA14" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11720,6 +11739,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J15" s="1448" t="n"/>
       <c r="K15" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11762,8 +11782,9 @@
       </c>
       <c r="W15" s="285" t="n"/>
       <c r="X15" s="285" t="n"/>
-      <c r="Y15" s="1304" t="n"/>
-      <c r="Z15" s="285" t="inlineStr">
+      <c r="Y15" s="1448" t="n"/>
+      <c r="Z15" s="1304" t="n"/>
+      <c r="AA15" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11803,6 +11824,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J16" s="1448" t="n"/>
       <c r="K16" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11845,8 +11867,9 @@
       </c>
       <c r="W16" s="285" t="n"/>
       <c r="X16" s="285" t="n"/>
-      <c r="Y16" s="1304" t="n"/>
-      <c r="Z16" s="285" t="inlineStr">
+      <c r="Y16" s="1448" t="n"/>
+      <c r="Z16" s="1304" t="n"/>
+      <c r="AA16" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11886,6 +11909,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J17" s="1448" t="n"/>
       <c r="K17" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11928,8 +11952,9 @@
       </c>
       <c r="W17" s="285" t="n"/>
       <c r="X17" s="285" t="n"/>
-      <c r="Y17" s="1304" t="n"/>
-      <c r="Z17" s="285" t="inlineStr">
+      <c r="Y17" s="1448" t="n"/>
+      <c r="Z17" s="1304" t="n"/>
+      <c r="AA17" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -11969,6 +11994,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J18" s="1448" t="n"/>
       <c r="K18" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12011,8 +12037,9 @@
       </c>
       <c r="W18" s="285" t="n"/>
       <c r="X18" s="285" t="n"/>
-      <c r="Y18" s="1304" t="n"/>
-      <c r="Z18" s="285" t="inlineStr">
+      <c r="Y18" s="1448" t="n"/>
+      <c r="Z18" s="1304" t="n"/>
+      <c r="AA18" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12052,6 +12079,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J19" s="1448" t="n"/>
       <c r="K19" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12094,8 +12122,9 @@
       </c>
       <c r="W19" s="285" t="n"/>
       <c r="X19" s="285" t="n"/>
-      <c r="Y19" s="1304" t="n"/>
-      <c r="Z19" s="285" t="inlineStr">
+      <c r="Y19" s="1448" t="n"/>
+      <c r="Z19" s="1304" t="n"/>
+      <c r="AA19" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12135,6 +12164,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J20" s="1448" t="n"/>
       <c r="K20" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12177,8 +12207,9 @@
       </c>
       <c r="W20" s="285" t="n"/>
       <c r="X20" s="285" t="n"/>
-      <c r="Y20" s="1304" t="n"/>
-      <c r="Z20" s="285" t="inlineStr">
+      <c r="Y20" s="1448" t="n"/>
+      <c r="Z20" s="1304" t="n"/>
+      <c r="AA20" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12218,6 +12249,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J21" s="1448" t="n"/>
       <c r="K21" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12260,8 +12292,9 @@
       </c>
       <c r="W21" s="285" t="n"/>
       <c r="X21" s="285" t="n"/>
-      <c r="Y21" s="1304" t="n"/>
-      <c r="Z21" s="285" t="inlineStr">
+      <c r="Y21" s="1448" t="n"/>
+      <c r="Z21" s="1304" t="n"/>
+      <c r="AA21" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12301,6 +12334,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J22" s="1448" t="n"/>
       <c r="K22" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12343,8 +12377,9 @@
       </c>
       <c r="W22" s="285" t="n"/>
       <c r="X22" s="285" t="n"/>
-      <c r="Y22" s="1304" t="n"/>
-      <c r="Z22" s="285" t="inlineStr">
+      <c r="Y22" s="1448" t="n"/>
+      <c r="Z22" s="1304" t="n"/>
+      <c r="AA22" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12384,6 +12419,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J23" s="1448" t="n"/>
       <c r="K23" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12426,8 +12462,9 @@
       </c>
       <c r="W23" s="285" t="n"/>
       <c r="X23" s="285" t="n"/>
-      <c r="Y23" s="1304" t="n"/>
-      <c r="Z23" s="285" t="inlineStr">
+      <c r="Y23" s="1448" t="n"/>
+      <c r="Z23" s="1304" t="n"/>
+      <c r="AA23" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12467,6 +12504,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J24" s="1448" t="n"/>
       <c r="K24" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12509,8 +12547,9 @@
       </c>
       <c r="W24" s="285" t="n"/>
       <c r="X24" s="285" t="n"/>
-      <c r="Y24" s="1304" t="n"/>
-      <c r="Z24" s="285" t="inlineStr">
+      <c r="Y24" s="1448" t="n"/>
+      <c r="Z24" s="1304" t="n"/>
+      <c r="AA24" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12550,6 +12589,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J25" s="1448" t="n"/>
       <c r="K25" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12592,8 +12632,9 @@
       </c>
       <c r="W25" s="285" t="n"/>
       <c r="X25" s="285" t="n"/>
-      <c r="Y25" s="1304" t="n"/>
-      <c r="Z25" s="285" t="inlineStr">
+      <c r="Y25" s="1448" t="n"/>
+      <c r="Z25" s="1304" t="n"/>
+      <c r="AA25" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12633,6 +12674,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J26" s="1448" t="n"/>
       <c r="K26" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12675,8 +12717,9 @@
       </c>
       <c r="W26" s="285" t="n"/>
       <c r="X26" s="285" t="n"/>
-      <c r="Y26" s="1304" t="n"/>
-      <c r="Z26" s="285" t="inlineStr">
+      <c r="Y26" s="1448" t="n"/>
+      <c r="Z26" s="1304" t="n"/>
+      <c r="AA26" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12716,6 +12759,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J27" s="1448" t="n"/>
       <c r="K27" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12758,8 +12802,9 @@
       </c>
       <c r="W27" s="285" t="n"/>
       <c r="X27" s="285" t="n"/>
-      <c r="Y27" s="1304" t="n"/>
-      <c r="Z27" s="285" t="inlineStr">
+      <c r="Y27" s="1448" t="n"/>
+      <c r="Z27" s="1304" t="n"/>
+      <c r="AA27" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12799,6 +12844,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J28" s="1448" t="n"/>
       <c r="K28" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12841,8 +12887,9 @@
       </c>
       <c r="W28" s="285" t="n"/>
       <c r="X28" s="285" t="n"/>
-      <c r="Y28" s="1304" t="n"/>
-      <c r="Z28" s="285" t="inlineStr">
+      <c r="Y28" s="1448" t="n"/>
+      <c r="Z28" s="1304" t="n"/>
+      <c r="AA28" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12882,6 +12929,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J29" s="1448" t="n"/>
       <c r="K29" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12924,8 +12972,9 @@
       </c>
       <c r="W29" s="285" t="n"/>
       <c r="X29" s="285" t="n"/>
-      <c r="Y29" s="1304" t="n"/>
-      <c r="Z29" s="285" t="inlineStr">
+      <c r="Y29" s="1448" t="n"/>
+      <c r="Z29" s="1304" t="n"/>
+      <c r="AA29" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -12965,6 +13014,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J30" s="1448" t="n"/>
       <c r="K30" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13007,8 +13057,9 @@
       </c>
       <c r="W30" s="285" t="n"/>
       <c r="X30" s="285" t="n"/>
-      <c r="Y30" s="1304" t="n"/>
-      <c r="Z30" s="285" t="inlineStr">
+      <c r="Y30" s="1448" t="n"/>
+      <c r="Z30" s="1304" t="n"/>
+      <c r="AA30" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13048,6 +13099,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J31" s="1448" t="n"/>
       <c r="K31" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13090,8 +13142,9 @@
       </c>
       <c r="W31" s="285" t="n"/>
       <c r="X31" s="285" t="n"/>
-      <c r="Y31" s="1304" t="n"/>
-      <c r="Z31" s="285" t="inlineStr">
+      <c r="Y31" s="1448" t="n"/>
+      <c r="Z31" s="1304" t="n"/>
+      <c r="AA31" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13131,6 +13184,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J32" s="1448" t="n"/>
       <c r="K32" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13173,8 +13227,9 @@
       </c>
       <c r="W32" s="285" t="n"/>
       <c r="X32" s="285" t="n"/>
-      <c r="Y32" s="1304" t="n"/>
-      <c r="Z32" s="285" t="inlineStr">
+      <c r="Y32" s="1448" t="n"/>
+      <c r="Z32" s="1304" t="n"/>
+      <c r="AA32" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13214,6 +13269,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J33" s="1448" t="n"/>
       <c r="K33" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13256,8 +13312,9 @@
       </c>
       <c r="W33" s="285" t="n"/>
       <c r="X33" s="285" t="n"/>
-      <c r="Y33" s="1304" t="n"/>
-      <c r="Z33" s="285" t="inlineStr">
+      <c r="Y33" s="1448" t="n"/>
+      <c r="Z33" s="1304" t="n"/>
+      <c r="AA33" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13297,6 +13354,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J34" s="1448" t="n"/>
       <c r="K34" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13339,8 +13397,9 @@
       </c>
       <c r="W34" s="285" t="n"/>
       <c r="X34" s="285" t="n"/>
-      <c r="Y34" s="1304" t="n"/>
-      <c r="Z34" s="285" t="inlineStr">
+      <c r="Y34" s="1448" t="n"/>
+      <c r="Z34" s="1304" t="n"/>
+      <c r="AA34" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13380,6 +13439,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J35" s="1448" t="n"/>
       <c r="K35" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13422,8 +13482,9 @@
       </c>
       <c r="W35" s="285" t="n"/>
       <c r="X35" s="285" t="n"/>
-      <c r="Y35" s="1304" t="n"/>
-      <c r="Z35" s="285" t="inlineStr">
+      <c r="Y35" s="1448" t="n"/>
+      <c r="Z35" s="1304" t="n"/>
+      <c r="AA35" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13463,6 +13524,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J36" s="1448" t="n"/>
       <c r="K36" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13505,8 +13567,9 @@
       </c>
       <c r="W36" s="285" t="n"/>
       <c r="X36" s="285" t="n"/>
-      <c r="Y36" s="1304" t="n"/>
-      <c r="Z36" s="285" t="inlineStr">
+      <c r="Y36" s="1448" t="n"/>
+      <c r="Z36" s="1304" t="n"/>
+      <c r="AA36" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13546,6 +13609,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J37" s="1448" t="n"/>
       <c r="K37" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13588,8 +13652,9 @@
       </c>
       <c r="W37" s="285" t="n"/>
       <c r="X37" s="285" t="n"/>
-      <c r="Y37" s="1304" t="n"/>
-      <c r="Z37" s="285" t="inlineStr">
+      <c r="Y37" s="1448" t="n"/>
+      <c r="Z37" s="1304" t="n"/>
+      <c r="AA37" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13629,6 +13694,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J38" s="1448" t="n"/>
       <c r="K38" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13671,8 +13737,9 @@
       </c>
       <c r="W38" s="285" t="n"/>
       <c r="X38" s="285" t="n"/>
-      <c r="Y38" s="1304" t="n"/>
-      <c r="Z38" s="285" t="inlineStr">
+      <c r="Y38" s="1448" t="n"/>
+      <c r="Z38" s="1304" t="n"/>
+      <c r="AA38" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13712,6 +13779,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J39" s="1448" t="n"/>
       <c r="K39" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13754,8 +13822,9 @@
       </c>
       <c r="W39" s="285" t="n"/>
       <c r="X39" s="285" t="n"/>
-      <c r="Y39" s="1304" t="n"/>
-      <c r="Z39" s="285" t="inlineStr">
+      <c r="Y39" s="1448" t="n"/>
+      <c r="Z39" s="1304" t="n"/>
+      <c r="AA39" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13795,6 +13864,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J40" s="1448" t="n"/>
       <c r="K40" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13837,8 +13907,9 @@
       </c>
       <c r="W40" s="285" t="n"/>
       <c r="X40" s="285" t="n"/>
-      <c r="Y40" s="1304" t="n"/>
-      <c r="Z40" s="285" t="inlineStr">
+      <c r="Y40" s="1448" t="n"/>
+      <c r="Z40" s="1304" t="n"/>
+      <c r="AA40" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13878,6 +13949,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J41" s="1448" t="n"/>
       <c r="K41" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13920,8 +13992,9 @@
       </c>
       <c r="W41" s="285" t="n"/>
       <c r="X41" s="285" t="n"/>
-      <c r="Y41" s="1304" t="n"/>
-      <c r="Z41" s="285" t="inlineStr">
+      <c r="Y41" s="1448" t="n"/>
+      <c r="Z41" s="1304" t="n"/>
+      <c r="AA41" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -13961,6 +14034,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J42" s="1448" t="n"/>
       <c r="K42" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14003,8 +14077,9 @@
       </c>
       <c r="W42" s="285" t="n"/>
       <c r="X42" s="285" t="n"/>
-      <c r="Y42" s="1304" t="n"/>
-      <c r="Z42" s="285" t="inlineStr">
+      <c r="Y42" s="1448" t="n"/>
+      <c r="Z42" s="1304" t="n"/>
+      <c r="AA42" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14044,6 +14119,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J43" s="1448" t="n"/>
       <c r="K43" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14086,8 +14162,9 @@
       </c>
       <c r="W43" s="285" t="n"/>
       <c r="X43" s="285" t="n"/>
-      <c r="Y43" s="1304" t="n"/>
-      <c r="Z43" s="285" t="inlineStr">
+      <c r="Y43" s="1448" t="n"/>
+      <c r="Z43" s="1304" t="n"/>
+      <c r="AA43" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14127,6 +14204,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J44" s="1448" t="n"/>
       <c r="K44" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14169,8 +14247,9 @@
       </c>
       <c r="W44" s="285" t="n"/>
       <c r="X44" s="285" t="n"/>
-      <c r="Y44" s="1304" t="n"/>
-      <c r="Z44" s="285" t="inlineStr">
+      <c r="Y44" s="1448" t="n"/>
+      <c r="Z44" s="1304" t="n"/>
+      <c r="AA44" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14210,6 +14289,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J45" s="1448" t="n"/>
       <c r="K45" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14252,8 +14332,9 @@
       </c>
       <c r="W45" s="285" t="n"/>
       <c r="X45" s="285" t="n"/>
-      <c r="Y45" s="1304" t="n"/>
-      <c r="Z45" s="285" t="inlineStr">
+      <c r="Y45" s="1448" t="n"/>
+      <c r="Z45" s="1304" t="n"/>
+      <c r="AA45" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14293,6 +14374,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J46" s="1448" t="n"/>
       <c r="K46" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14335,8 +14417,9 @@
       </c>
       <c r="W46" s="285" t="n"/>
       <c r="X46" s="285" t="n"/>
-      <c r="Y46" s="1304" t="n"/>
-      <c r="Z46" s="285" t="inlineStr">
+      <c r="Y46" s="1448" t="n"/>
+      <c r="Z46" s="1304" t="n"/>
+      <c r="AA46" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14376,6 +14459,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J47" s="1448" t="n"/>
       <c r="K47" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14418,8 +14502,9 @@
       </c>
       <c r="W47" s="285" t="n"/>
       <c r="X47" s="285" t="n"/>
-      <c r="Y47" s="1304" t="n"/>
-      <c r="Z47" s="285" t="inlineStr">
+      <c r="Y47" s="1448" t="n"/>
+      <c r="Z47" s="1304" t="n"/>
+      <c r="AA47" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14459,6 +14544,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J48" s="1448" t="n"/>
       <c r="K48" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14501,8 +14587,9 @@
       </c>
       <c r="W48" s="285" t="n"/>
       <c r="X48" s="285" t="n"/>
-      <c r="Y48" s="1304" t="n"/>
-      <c r="Z48" s="285" t="inlineStr">
+      <c r="Y48" s="1448" t="n"/>
+      <c r="Z48" s="1304" t="n"/>
+      <c r="AA48" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14542,6 +14629,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J49" s="1448" t="n"/>
       <c r="K49" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14584,8 +14672,9 @@
       </c>
       <c r="W49" s="285" t="n"/>
       <c r="X49" s="285" t="n"/>
-      <c r="Y49" s="1304" t="n"/>
-      <c r="Z49" s="285" t="inlineStr">
+      <c r="Y49" s="1448" t="n"/>
+      <c r="Z49" s="1304" t="n"/>
+      <c r="AA49" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14625,6 +14714,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J50" s="1448" t="n"/>
       <c r="K50" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14667,8 +14757,9 @@
       </c>
       <c r="W50" s="285" t="n"/>
       <c r="X50" s="285" t="n"/>
-      <c r="Y50" s="1304" t="n"/>
-      <c r="Z50" s="285" t="inlineStr">
+      <c r="Y50" s="1448" t="n"/>
+      <c r="Z50" s="1304" t="n"/>
+      <c r="AA50" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14708,6 +14799,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J51" s="1448" t="n"/>
       <c r="K51" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14750,8 +14842,9 @@
       </c>
       <c r="W51" s="285" t="n"/>
       <c r="X51" s="285" t="n"/>
-      <c r="Y51" s="1304" t="n"/>
-      <c r="Z51" s="285" t="inlineStr">
+      <c r="Y51" s="1448" t="n"/>
+      <c r="Z51" s="1304" t="n"/>
+      <c r="AA51" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14791,6 +14884,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J52" s="1448" t="n"/>
       <c r="K52" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14833,8 +14927,9 @@
       </c>
       <c r="W52" s="285" t="n"/>
       <c r="X52" s="285" t="n"/>
-      <c r="Y52" s="1304" t="n"/>
-      <c r="Z52" s="285" t="inlineStr">
+      <c r="Y52" s="1448" t="n"/>
+      <c r="Z52" s="1304" t="n"/>
+      <c r="AA52" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14874,6 +14969,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J53" s="1448" t="n"/>
       <c r="K53" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14916,8 +15012,9 @@
       </c>
       <c r="W53" s="285" t="n"/>
       <c r="X53" s="285" t="n"/>
-      <c r="Y53" s="1304" t="n"/>
-      <c r="Z53" s="285" t="inlineStr">
+      <c r="Y53" s="1448" t="n"/>
+      <c r="Z53" s="1304" t="n"/>
+      <c r="AA53" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -14957,6 +15054,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J54" s="1448" t="n"/>
       <c r="K54" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14999,8 +15097,9 @@
       </c>
       <c r="W54" s="285" t="n"/>
       <c r="X54" s="285" t="n"/>
-      <c r="Y54" s="1304" t="n"/>
-      <c r="Z54" s="285" t="inlineStr">
+      <c r="Y54" s="1448" t="n"/>
+      <c r="Z54" s="1304" t="n"/>
+      <c r="AA54" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15040,6 +15139,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J55" s="1448" t="n"/>
       <c r="K55" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15082,8 +15182,9 @@
       </c>
       <c r="W55" s="285" t="n"/>
       <c r="X55" s="285" t="n"/>
-      <c r="Y55" s="1304" t="n"/>
-      <c r="Z55" s="285" t="inlineStr">
+      <c r="Y55" s="1448" t="n"/>
+      <c r="Z55" s="1304" t="n"/>
+      <c r="AA55" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15123,6 +15224,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J56" s="1448" t="n"/>
       <c r="K56" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15165,8 +15267,9 @@
       </c>
       <c r="W56" s="285" t="n"/>
       <c r="X56" s="285" t="n"/>
-      <c r="Y56" s="1304" t="n"/>
-      <c r="Z56" s="285" t="inlineStr">
+      <c r="Y56" s="1448" t="n"/>
+      <c r="Z56" s="1304" t="n"/>
+      <c r="AA56" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15206,6 +15309,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J57" s="1448" t="n"/>
       <c r="K57" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15248,8 +15352,9 @@
       </c>
       <c r="W57" s="285" t="n"/>
       <c r="X57" s="285" t="n"/>
-      <c r="Y57" s="1304" t="n"/>
-      <c r="Z57" s="285" t="inlineStr">
+      <c r="Y57" s="1448" t="n"/>
+      <c r="Z57" s="1304" t="n"/>
+      <c r="AA57" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15289,6 +15394,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J58" s="1448" t="n"/>
       <c r="K58" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15331,8 +15437,9 @@
       </c>
       <c r="W58" s="285" t="n"/>
       <c r="X58" s="285" t="n"/>
-      <c r="Y58" s="1304" t="n"/>
-      <c r="Z58" s="285" t="inlineStr">
+      <c r="Y58" s="1448" t="n"/>
+      <c r="Z58" s="1304" t="n"/>
+      <c r="AA58" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15372,6 +15479,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J59" s="1448" t="n"/>
       <c r="K59" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15414,8 +15522,9 @@
       </c>
       <c r="W59" s="285" t="n"/>
       <c r="X59" s="285" t="n"/>
-      <c r="Y59" s="1304" t="n"/>
-      <c r="Z59" s="285" t="inlineStr">
+      <c r="Y59" s="1448" t="n"/>
+      <c r="Z59" s="1304" t="n"/>
+      <c r="AA59" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15455,6 +15564,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J60" s="1448" t="n"/>
       <c r="K60" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15497,8 +15607,9 @@
       </c>
       <c r="W60" s="285" t="n"/>
       <c r="X60" s="285" t="n"/>
-      <c r="Y60" s="1304" t="n"/>
-      <c r="Z60" s="285" t="inlineStr">
+      <c r="Y60" s="1448" t="n"/>
+      <c r="Z60" s="1304" t="n"/>
+      <c r="AA60" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15538,6 +15649,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J61" s="1448" t="n"/>
       <c r="K61" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15580,8 +15692,9 @@
       </c>
       <c r="W61" s="285" t="n"/>
       <c r="X61" s="285" t="n"/>
-      <c r="Y61" s="1304" t="n"/>
-      <c r="Z61" s="285" t="inlineStr">
+      <c r="Y61" s="1448" t="n"/>
+      <c r="Z61" s="1304" t="n"/>
+      <c r="AA61" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15621,6 +15734,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J62" s="1448" t="n"/>
       <c r="K62" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15663,8 +15777,9 @@
       </c>
       <c r="W62" s="285" t="n"/>
       <c r="X62" s="285" t="n"/>
-      <c r="Y62" s="1304" t="n"/>
-      <c r="Z62" s="285" t="inlineStr">
+      <c r="Y62" s="1448" t="n"/>
+      <c r="Z62" s="1304" t="n"/>
+      <c r="AA62" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15704,6 +15819,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J63" s="1448" t="n"/>
       <c r="K63" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15746,8 +15862,9 @@
       </c>
       <c r="W63" s="285" t="n"/>
       <c r="X63" s="285" t="n"/>
-      <c r="Y63" s="1304" t="n"/>
-      <c r="Z63" s="285" t="inlineStr">
+      <c r="Y63" s="1448" t="n"/>
+      <c r="Z63" s="1304" t="n"/>
+      <c r="AA63" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15787,6 +15904,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J64" s="1448" t="n"/>
       <c r="K64" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15829,8 +15947,9 @@
       </c>
       <c r="W64" s="285" t="n"/>
       <c r="X64" s="285" t="n"/>
-      <c r="Y64" s="1304" t="n"/>
-      <c r="Z64" s="285" t="inlineStr">
+      <c r="Y64" s="1448" t="n"/>
+      <c r="Z64" s="1304" t="n"/>
+      <c r="AA64" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15870,6 +15989,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J65" s="1448" t="n"/>
       <c r="K65" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15912,8 +16032,9 @@
       </c>
       <c r="W65" s="285" t="n"/>
       <c r="X65" s="285" t="n"/>
-      <c r="Y65" s="1304" t="n"/>
-      <c r="Z65" s="285" t="inlineStr">
+      <c r="Y65" s="1448" t="n"/>
+      <c r="Z65" s="1304" t="n"/>
+      <c r="AA65" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -15953,6 +16074,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J66" s="1448" t="n"/>
       <c r="K66" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15995,8 +16117,9 @@
       </c>
       <c r="W66" s="285" t="n"/>
       <c r="X66" s="285" t="n"/>
-      <c r="Y66" s="1304" t="n"/>
-      <c r="Z66" s="285" t="inlineStr">
+      <c r="Y66" s="1448" t="n"/>
+      <c r="Z66" s="1304" t="n"/>
+      <c r="AA66" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16036,6 +16159,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J67" s="1448" t="n"/>
       <c r="K67" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16078,8 +16202,9 @@
       </c>
       <c r="W67" s="285" t="n"/>
       <c r="X67" s="285" t="n"/>
-      <c r="Y67" s="1304" t="n"/>
-      <c r="Z67" s="285" t="inlineStr">
+      <c r="Y67" s="1448" t="n"/>
+      <c r="Z67" s="1304" t="n"/>
+      <c r="AA67" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16119,6 +16244,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J68" s="1448" t="n"/>
       <c r="K68" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16161,8 +16287,9 @@
       </c>
       <c r="W68" s="285" t="n"/>
       <c r="X68" s="285" t="n"/>
-      <c r="Y68" s="1304" t="n"/>
-      <c r="Z68" s="285" t="inlineStr">
+      <c r="Y68" s="1448" t="n"/>
+      <c r="Z68" s="1304" t="n"/>
+      <c r="AA68" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16202,6 +16329,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J69" s="1448" t="n"/>
       <c r="K69" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16244,8 +16372,9 @@
       </c>
       <c r="W69" s="285" t="n"/>
       <c r="X69" s="285" t="n"/>
-      <c r="Y69" s="1304" t="n"/>
-      <c r="Z69" s="285" t="inlineStr">
+      <c r="Y69" s="1448" t="n"/>
+      <c r="Z69" s="1304" t="n"/>
+      <c r="AA69" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16285,6 +16414,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J70" s="1448" t="n"/>
       <c r="K70" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16327,8 +16457,9 @@
       </c>
       <c r="W70" s="285" t="n"/>
       <c r="X70" s="285" t="n"/>
-      <c r="Y70" s="1304" t="n"/>
-      <c r="Z70" s="285" t="inlineStr">
+      <c r="Y70" s="1448" t="n"/>
+      <c r="Z70" s="1304" t="n"/>
+      <c r="AA70" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16395,6 +16526,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J72" s="1448" t="n"/>
       <c r="K72" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16437,8 +16569,9 @@
       </c>
       <c r="W72" s="285" t="n"/>
       <c r="X72" s="285" t="n"/>
-      <c r="Y72" s="1304" t="n"/>
-      <c r="Z72" s="285" t="inlineStr">
+      <c r="Y72" s="1448" t="n"/>
+      <c r="Z72" s="1304" t="n"/>
+      <c r="AA72" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16478,6 +16611,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J73" s="1448" t="n"/>
       <c r="K73" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16520,8 +16654,9 @@
       </c>
       <c r="W73" s="285" t="n"/>
       <c r="X73" s="285" t="n"/>
-      <c r="Y73" s="1304" t="n"/>
-      <c r="Z73" s="285" t="inlineStr">
+      <c r="Y73" s="1448" t="n"/>
+      <c r="Z73" s="1304" t="n"/>
+      <c r="AA73" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16561,6 +16696,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J74" s="1448" t="n"/>
       <c r="K74" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16603,8 +16739,9 @@
       </c>
       <c r="W74" s="285" t="n"/>
       <c r="X74" s="285" t="n"/>
-      <c r="Y74" s="1304" t="n"/>
-      <c r="Z74" s="285" t="inlineStr">
+      <c r="Y74" s="1448" t="n"/>
+      <c r="Z74" s="1304" t="n"/>
+      <c r="AA74" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16644,6 +16781,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J75" s="1448" t="n"/>
       <c r="K75" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16686,8 +16824,9 @@
       </c>
       <c r="W75" s="285" t="n"/>
       <c r="X75" s="285" t="n"/>
-      <c r="Y75" s="1304" t="n"/>
-      <c r="Z75" s="285" t="inlineStr">
+      <c r="Y75" s="1448" t="n"/>
+      <c r="Z75" s="1304" t="n"/>
+      <c r="AA75" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16727,6 +16866,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J76" s="1448" t="n"/>
       <c r="K76" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16769,8 +16909,9 @@
       </c>
       <c r="W76" s="285" t="n"/>
       <c r="X76" s="285" t="n"/>
-      <c r="Y76" s="1304" t="n"/>
-      <c r="Z76" s="285" t="inlineStr">
+      <c r="Y76" s="1448" t="n"/>
+      <c r="Z76" s="1304" t="n"/>
+      <c r="AA76" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16810,6 +16951,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J77" s="1448" t="n"/>
       <c r="K77" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16852,8 +16994,9 @@
       </c>
       <c r="W77" s="285" t="n"/>
       <c r="X77" s="285" t="n"/>
-      <c r="Y77" s="1304" t="n"/>
-      <c r="Z77" s="285" t="inlineStr">
+      <c r="Y77" s="1448" t="n"/>
+      <c r="Z77" s="1304" t="n"/>
+      <c r="AA77" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16893,6 +17036,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J78" s="1448" t="n"/>
       <c r="K78" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16935,8 +17079,9 @@
       </c>
       <c r="W78" s="285" t="n"/>
       <c r="X78" s="285" t="n"/>
-      <c r="Y78" s="1304" t="n"/>
-      <c r="Z78" s="285" t="inlineStr">
+      <c r="Y78" s="1448" t="n"/>
+      <c r="Z78" s="1304" t="n"/>
+      <c r="AA78" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -16976,6 +17121,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J79" s="1448" t="n"/>
       <c r="K79" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17018,8 +17164,9 @@
       </c>
       <c r="W79" s="285" t="n"/>
       <c r="X79" s="285" t="n"/>
-      <c r="Y79" s="1304" t="n"/>
-      <c r="Z79" s="285" t="inlineStr">
+      <c r="Y79" s="1448" t="n"/>
+      <c r="Z79" s="1304" t="n"/>
+      <c r="AA79" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17059,6 +17206,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J80" s="1448" t="n"/>
       <c r="K80" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17101,8 +17249,9 @@
       </c>
       <c r="W80" s="285" t="n"/>
       <c r="X80" s="285" t="n"/>
-      <c r="Y80" s="1304" t="n"/>
-      <c r="Z80" s="285" t="inlineStr">
+      <c r="Y80" s="1448" t="n"/>
+      <c r="Z80" s="1304" t="n"/>
+      <c r="AA80" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17142,6 +17291,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J81" s="1448" t="n"/>
       <c r="K81" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17184,8 +17334,9 @@
       </c>
       <c r="W81" s="285" t="n"/>
       <c r="X81" s="285" t="n"/>
-      <c r="Y81" s="1304" t="n"/>
-      <c r="Z81" s="285" t="inlineStr">
+      <c r="Y81" s="1448" t="n"/>
+      <c r="Z81" s="1304" t="n"/>
+      <c r="AA81" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17225,6 +17376,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J82" s="1448" t="n"/>
       <c r="K82" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17267,8 +17419,9 @@
       </c>
       <c r="W82" s="285" t="n"/>
       <c r="X82" s="285" t="n"/>
-      <c r="Y82" s="1304" t="n"/>
-      <c r="Z82" s="285" t="inlineStr">
+      <c r="Y82" s="1448" t="n"/>
+      <c r="Z82" s="1304" t="n"/>
+      <c r="AA82" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17308,6 +17461,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J83" s="1448" t="n"/>
       <c r="K83" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17350,8 +17504,9 @@
       </c>
       <c r="W83" s="285" t="n"/>
       <c r="X83" s="285" t="n"/>
-      <c r="Y83" s="1304" t="n"/>
-      <c r="Z83" s="285" t="inlineStr">
+      <c r="Y83" s="1448" t="n"/>
+      <c r="Z83" s="1304" t="n"/>
+      <c r="AA83" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17391,6 +17546,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J84" s="1448" t="n"/>
       <c r="K84" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17433,8 +17589,9 @@
       </c>
       <c r="W84" s="285" t="n"/>
       <c r="X84" s="285" t="n"/>
-      <c r="Y84" s="1304" t="n"/>
-      <c r="Z84" s="285" t="inlineStr">
+      <c r="Y84" s="1448" t="n"/>
+      <c r="Z84" s="1304" t="n"/>
+      <c r="AA84" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17474,6 +17631,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J85" s="1448" t="n"/>
       <c r="K85" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17516,8 +17674,9 @@
       </c>
       <c r="W85" s="285" t="n"/>
       <c r="X85" s="285" t="n"/>
-      <c r="Y85" s="1304" t="n"/>
-      <c r="Z85" s="285" t="inlineStr">
+      <c r="Y85" s="1448" t="n"/>
+      <c r="Z85" s="1304" t="n"/>
+      <c r="AA85" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17557,6 +17716,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J86" s="1448" t="n"/>
       <c r="K86" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17599,8 +17759,9 @@
       </c>
       <c r="W86" s="285" t="n"/>
       <c r="X86" s="285" t="n"/>
-      <c r="Y86" s="1304" t="n"/>
-      <c r="Z86" s="285" t="inlineStr">
+      <c r="Y86" s="1448" t="n"/>
+      <c r="Z86" s="1304" t="n"/>
+      <c r="AA86" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17640,6 +17801,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J87" s="1448" t="n"/>
       <c r="K87" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17682,8 +17844,9 @@
       </c>
       <c r="W87" s="285" t="n"/>
       <c r="X87" s="285" t="n"/>
-      <c r="Y87" s="1304" t="n"/>
-      <c r="Z87" s="285" t="inlineStr">
+      <c r="Y87" s="1448" t="n"/>
+      <c r="Z87" s="1304" t="n"/>
+      <c r="AA87" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17723,6 +17886,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J88" s="1448" t="n"/>
       <c r="K88" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17765,8 +17929,9 @@
       </c>
       <c r="W88" s="285" t="n"/>
       <c r="X88" s="285" t="n"/>
-      <c r="Y88" s="1304" t="n"/>
-      <c r="Z88" s="285" t="inlineStr">
+      <c r="Y88" s="1448" t="n"/>
+      <c r="Z88" s="1304" t="n"/>
+      <c r="AA88" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17806,6 +17971,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J89" s="1448" t="n"/>
       <c r="K89" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17848,8 +18014,9 @@
       </c>
       <c r="W89" s="285" t="n"/>
       <c r="X89" s="285" t="n"/>
-      <c r="Y89" s="1304" t="n"/>
-      <c r="Z89" s="285" t="inlineStr">
+      <c r="Y89" s="1448" t="n"/>
+      <c r="Z89" s="1304" t="n"/>
+      <c r="AA89" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17889,6 +18056,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J90" s="1448" t="n"/>
       <c r="K90" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17931,8 +18099,9 @@
       </c>
       <c r="W90" s="285" t="n"/>
       <c r="X90" s="285" t="n"/>
-      <c r="Y90" s="1304" t="n"/>
-      <c r="Z90" s="285" t="inlineStr">
+      <c r="Y90" s="1448" t="n"/>
+      <c r="Z90" s="1304" t="n"/>
+      <c r="AA90" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -17972,6 +18141,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J91" s="1448" t="n"/>
       <c r="K91" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18014,8 +18184,9 @@
       </c>
       <c r="W91" s="285" t="n"/>
       <c r="X91" s="285" t="n"/>
-      <c r="Y91" s="1304" t="n"/>
-      <c r="Z91" s="285" t="inlineStr">
+      <c r="Y91" s="1448" t="n"/>
+      <c r="Z91" s="1304" t="n"/>
+      <c r="AA91" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18055,6 +18226,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J92" s="1448" t="n"/>
       <c r="K92" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18097,8 +18269,9 @@
       </c>
       <c r="W92" s="285" t="n"/>
       <c r="X92" s="285" t="n"/>
-      <c r="Y92" s="1304" t="n"/>
-      <c r="Z92" s="285" t="inlineStr">
+      <c r="Y92" s="1448" t="n"/>
+      <c r="Z92" s="1304" t="n"/>
+      <c r="AA92" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18138,6 +18311,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J93" s="1448" t="n"/>
       <c r="K93" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18180,8 +18354,9 @@
       </c>
       <c r="W93" s="285" t="n"/>
       <c r="X93" s="285" t="n"/>
-      <c r="Y93" s="1304" t="n"/>
-      <c r="Z93" s="285" t="inlineStr">
+      <c r="Y93" s="1448" t="n"/>
+      <c r="Z93" s="1304" t="n"/>
+      <c r="AA93" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18221,6 +18396,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J94" s="1448" t="n"/>
       <c r="K94" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18263,8 +18439,9 @@
       </c>
       <c r="W94" s="285" t="n"/>
       <c r="X94" s="285" t="n"/>
-      <c r="Y94" s="1304" t="n"/>
-      <c r="Z94" s="285" t="inlineStr">
+      <c r="Y94" s="1448" t="n"/>
+      <c r="Z94" s="1304" t="n"/>
+      <c r="AA94" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18304,6 +18481,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J95" s="1448" t="n"/>
       <c r="K95" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18346,8 +18524,9 @@
       </c>
       <c r="W95" s="285" t="n"/>
       <c r="X95" s="285" t="n"/>
-      <c r="Y95" s="1304" t="n"/>
-      <c r="Z95" s="285" t="inlineStr">
+      <c r="Y95" s="1448" t="n"/>
+      <c r="Z95" s="1304" t="n"/>
+      <c r="AA95" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18387,6 +18566,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J96" s="1448" t="n"/>
       <c r="K96" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18429,8 +18609,9 @@
       </c>
       <c r="W96" s="285" t="n"/>
       <c r="X96" s="285" t="n"/>
-      <c r="Y96" s="1304" t="n"/>
-      <c r="Z96" s="285" t="inlineStr">
+      <c r="Y96" s="1448" t="n"/>
+      <c r="Z96" s="1304" t="n"/>
+      <c r="AA96" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18470,6 +18651,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J97" s="1448" t="n"/>
       <c r="K97" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18512,8 +18694,9 @@
       </c>
       <c r="W97" s="285" t="n"/>
       <c r="X97" s="285" t="n"/>
-      <c r="Y97" s="1304" t="n"/>
-      <c r="Z97" s="285" t="inlineStr">
+      <c r="Y97" s="1448" t="n"/>
+      <c r="Z97" s="1304" t="n"/>
+      <c r="AA97" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18553,6 +18736,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J98" s="1448" t="n"/>
       <c r="K98" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18595,8 +18779,9 @@
       </c>
       <c r="W98" s="285" t="n"/>
       <c r="X98" s="285" t="n"/>
-      <c r="Y98" s="1304" t="n"/>
-      <c r="Z98" s="285" t="inlineStr">
+      <c r="Y98" s="1448" t="n"/>
+      <c r="Z98" s="1304" t="n"/>
+      <c r="AA98" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18636,6 +18821,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J99" s="1448" t="n"/>
       <c r="K99" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18678,8 +18864,9 @@
       </c>
       <c r="W99" s="285" t="n"/>
       <c r="X99" s="285" t="n"/>
-      <c r="Y99" s="1304" t="n"/>
-      <c r="Z99" s="285" t="inlineStr">
+      <c r="Y99" s="1448" t="n"/>
+      <c r="Z99" s="1304" t="n"/>
+      <c r="AA99" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18719,6 +18906,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J100" s="1448" t="n"/>
       <c r="K100" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18761,8 +18949,9 @@
       </c>
       <c r="W100" s="285" t="n"/>
       <c r="X100" s="285" t="n"/>
-      <c r="Y100" s="1304" t="n"/>
-      <c r="Z100" s="285" t="inlineStr">
+      <c r="Y100" s="1448" t="n"/>
+      <c r="Z100" s="1304" t="n"/>
+      <c r="AA100" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18802,6 +18991,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J101" s="1448" t="n"/>
       <c r="K101" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18844,8 +19034,9 @@
       </c>
       <c r="W101" s="285" t="n"/>
       <c r="X101" s="285" t="n"/>
-      <c r="Y101" s="1304" t="n"/>
-      <c r="Z101" s="285" t="inlineStr">
+      <c r="Y101" s="1448" t="n"/>
+      <c r="Z101" s="1304" t="n"/>
+      <c r="AA101" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18885,6 +19076,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J102" s="1448" t="n"/>
       <c r="K102" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18927,8 +19119,9 @@
       </c>
       <c r="W102" s="285" t="n"/>
       <c r="X102" s="285" t="n"/>
-      <c r="Y102" s="1304" t="n"/>
-      <c r="Z102" s="285" t="inlineStr">
+      <c r="Y102" s="1448" t="n"/>
+      <c r="Z102" s="1304" t="n"/>
+      <c r="AA102" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -18968,6 +19161,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J103" s="1448" t="n"/>
       <c r="K103" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19010,8 +19204,9 @@
       </c>
       <c r="W103" s="285" t="n"/>
       <c r="X103" s="285" t="n"/>
-      <c r="Y103" s="1304" t="n"/>
-      <c r="Z103" s="285" t="inlineStr">
+      <c r="Y103" s="1448" t="n"/>
+      <c r="Z103" s="1304" t="n"/>
+      <c r="AA103" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19051,6 +19246,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J104" s="1448" t="n"/>
       <c r="K104" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19093,8 +19289,9 @@
       </c>
       <c r="W104" s="285" t="n"/>
       <c r="X104" s="285" t="n"/>
-      <c r="Y104" s="1304" t="n"/>
-      <c r="Z104" s="285" t="inlineStr">
+      <c r="Y104" s="1448" t="n"/>
+      <c r="Z104" s="1304" t="n"/>
+      <c r="AA104" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19134,6 +19331,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J105" s="1448" t="n"/>
       <c r="K105" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19176,8 +19374,9 @@
       </c>
       <c r="W105" s="285" t="n"/>
       <c r="X105" s="285" t="n"/>
-      <c r="Y105" s="1304" t="n"/>
-      <c r="Z105" s="285" t="inlineStr">
+      <c r="Y105" s="1448" t="n"/>
+      <c r="Z105" s="1304" t="n"/>
+      <c r="AA105" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19217,6 +19416,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J106" s="1448" t="n"/>
       <c r="K106" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19259,8 +19459,9 @@
       </c>
       <c r="W106" s="285" t="n"/>
       <c r="X106" s="285" t="n"/>
-      <c r="Y106" s="1304" t="n"/>
-      <c r="Z106" s="285" t="inlineStr">
+      <c r="Y106" s="1448" t="n"/>
+      <c r="Z106" s="1304" t="n"/>
+      <c r="AA106" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19300,6 +19501,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J107" s="1448" t="n"/>
       <c r="K107" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19342,8 +19544,9 @@
       </c>
       <c r="W107" s="285" t="n"/>
       <c r="X107" s="285" t="n"/>
-      <c r="Y107" s="1304" t="n"/>
-      <c r="Z107" s="285" t="inlineStr">
+      <c r="Y107" s="1448" t="n"/>
+      <c r="Z107" s="1304" t="n"/>
+      <c r="AA107" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19383,6 +19586,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J108" s="1448" t="n"/>
       <c r="K108" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19425,8 +19629,9 @@
       </c>
       <c r="W108" s="285" t="n"/>
       <c r="X108" s="285" t="n"/>
-      <c r="Y108" s="1304" t="n"/>
-      <c r="Z108" s="285" t="inlineStr">
+      <c r="Y108" s="1448" t="n"/>
+      <c r="Z108" s="1304" t="n"/>
+      <c r="AA108" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19466,6 +19671,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J109" s="1448" t="n"/>
       <c r="K109" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19508,8 +19714,9 @@
       </c>
       <c r="W109" s="285" t="n"/>
       <c r="X109" s="285" t="n"/>
-      <c r="Y109" s="1304" t="n"/>
-      <c r="Z109" s="285" t="inlineStr">
+      <c r="Y109" s="1448" t="n"/>
+      <c r="Z109" s="1304" t="n"/>
+      <c r="AA109" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19549,6 +19756,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J110" s="1448" t="n"/>
       <c r="K110" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19591,8 +19799,9 @@
       </c>
       <c r="W110" s="285" t="n"/>
       <c r="X110" s="285" t="n"/>
-      <c r="Y110" s="1304" t="n"/>
-      <c r="Z110" s="285" t="inlineStr">
+      <c r="Y110" s="1448" t="n"/>
+      <c r="Z110" s="1304" t="n"/>
+      <c r="AA110" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19632,6 +19841,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J111" s="1448" t="n"/>
       <c r="K111" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19674,8 +19884,9 @@
       </c>
       <c r="W111" s="285" t="n"/>
       <c r="X111" s="285" t="n"/>
-      <c r="Y111" s="1304" t="n"/>
-      <c r="Z111" s="285" t="inlineStr">
+      <c r="Y111" s="1448" t="n"/>
+      <c r="Z111" s="1304" t="n"/>
+      <c r="AA111" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19715,6 +19926,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J112" s="1448" t="n"/>
       <c r="K112" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19757,8 +19969,9 @@
       </c>
       <c r="W112" s="285" t="n"/>
       <c r="X112" s="285" t="n"/>
-      <c r="Y112" s="1304" t="n"/>
-      <c r="Z112" s="285" t="inlineStr">
+      <c r="Y112" s="1448" t="n"/>
+      <c r="Z112" s="1304" t="n"/>
+      <c r="AA112" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19798,6 +20011,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J113" s="1448" t="n"/>
       <c r="K113" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19840,8 +20054,9 @@
       </c>
       <c r="W113" s="285" t="n"/>
       <c r="X113" s="285" t="n"/>
-      <c r="Y113" s="1304" t="n"/>
-      <c r="Z113" s="285" t="inlineStr">
+      <c r="Y113" s="1448" t="n"/>
+      <c r="Z113" s="1304" t="n"/>
+      <c r="AA113" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19881,6 +20096,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J114" s="1448" t="n"/>
       <c r="K114" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19923,8 +20139,9 @@
       </c>
       <c r="W114" s="285" t="n"/>
       <c r="X114" s="285" t="n"/>
-      <c r="Y114" s="1304" t="n"/>
-      <c r="Z114" s="285" t="inlineStr">
+      <c r="Y114" s="1448" t="n"/>
+      <c r="Z114" s="1304" t="n"/>
+      <c r="AA114" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -19964,6 +20181,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J115" s="1448" t="n"/>
       <c r="K115" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20006,8 +20224,9 @@
       </c>
       <c r="W115" s="285" t="n"/>
       <c r="X115" s="285" t="n"/>
-      <c r="Y115" s="1304" t="n"/>
-      <c r="Z115" s="285" t="inlineStr">
+      <c r="Y115" s="1448" t="n"/>
+      <c r="Z115" s="1304" t="n"/>
+      <c r="AA115" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20047,6 +20266,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J116" s="1448" t="n"/>
       <c r="K116" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20089,8 +20309,9 @@
       </c>
       <c r="W116" s="285" t="n"/>
       <c r="X116" s="285" t="n"/>
-      <c r="Y116" s="1304" t="n"/>
-      <c r="Z116" s="285" t="inlineStr">
+      <c r="Y116" s="1448" t="n"/>
+      <c r="Z116" s="1304" t="n"/>
+      <c r="AA116" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20130,6 +20351,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J117" s="1448" t="n"/>
       <c r="K117" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20172,8 +20394,9 @@
       </c>
       <c r="W117" s="285" t="n"/>
       <c r="X117" s="285" t="n"/>
-      <c r="Y117" s="1304" t="n"/>
-      <c r="Z117" s="285" t="inlineStr">
+      <c r="Y117" s="1448" t="n"/>
+      <c r="Z117" s="1304" t="n"/>
+      <c r="AA117" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20213,6 +20436,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J118" s="1448" t="n"/>
       <c r="K118" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20255,8 +20479,9 @@
       </c>
       <c r="W118" s="285" t="n"/>
       <c r="X118" s="285" t="n"/>
-      <c r="Y118" s="1304" t="n"/>
-      <c r="Z118" s="285" t="inlineStr">
+      <c r="Y118" s="1448" t="n"/>
+      <c r="Z118" s="1304" t="n"/>
+      <c r="AA118" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20296,6 +20521,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J119" s="1448" t="n"/>
       <c r="K119" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20338,8 +20564,9 @@
       </c>
       <c r="W119" s="285" t="n"/>
       <c r="X119" s="285" t="n"/>
-      <c r="Y119" s="1304" t="n"/>
-      <c r="Z119" s="285" t="inlineStr">
+      <c r="Y119" s="1448" t="n"/>
+      <c r="Z119" s="1304" t="n"/>
+      <c r="AA119" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20379,6 +20606,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J120" s="1448" t="n"/>
       <c r="K120" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20421,8 +20649,9 @@
       </c>
       <c r="W120" s="285" t="n"/>
       <c r="X120" s="285" t="n"/>
-      <c r="Y120" s="1304" t="n"/>
-      <c r="Z120" s="285" t="inlineStr">
+      <c r="Y120" s="1448" t="n"/>
+      <c r="Z120" s="1304" t="n"/>
+      <c r="AA120" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20462,6 +20691,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J121" s="1448" t="n"/>
       <c r="K121" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20504,8 +20734,9 @@
       </c>
       <c r="W121" s="285" t="n"/>
       <c r="X121" s="285" t="n"/>
-      <c r="Y121" s="1304" t="n"/>
-      <c r="Z121" s="285" t="inlineStr">
+      <c r="Y121" s="1448" t="n"/>
+      <c r="Z121" s="1304" t="n"/>
+      <c r="AA121" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20545,6 +20776,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J122" s="1448" t="n"/>
       <c r="K122" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20587,8 +20819,9 @@
       </c>
       <c r="W122" s="285" t="n"/>
       <c r="X122" s="285" t="n"/>
-      <c r="Y122" s="1304" t="n"/>
-      <c r="Z122" s="285" t="inlineStr">
+      <c r="Y122" s="1448" t="n"/>
+      <c r="Z122" s="1304" t="n"/>
+      <c r="AA122" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20628,6 +20861,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J123" s="1448" t="n"/>
       <c r="K123" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20670,8 +20904,9 @@
       </c>
       <c r="W123" s="285" t="n"/>
       <c r="X123" s="285" t="n"/>
-      <c r="Y123" s="1304" t="n"/>
-      <c r="Z123" s="285" t="inlineStr">
+      <c r="Y123" s="1448" t="n"/>
+      <c r="Z123" s="1304" t="n"/>
+      <c r="AA123" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20711,6 +20946,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J124" s="1448" t="n"/>
       <c r="K124" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20753,8 +20989,9 @@
       </c>
       <c r="W124" s="285" t="n"/>
       <c r="X124" s="285" t="n"/>
-      <c r="Y124" s="1304" t="n"/>
-      <c r="Z124" s="285" t="inlineStr">
+      <c r="Y124" s="1448" t="n"/>
+      <c r="Z124" s="1304" t="n"/>
+      <c r="AA124" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20794,6 +21031,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J125" s="1448" t="n"/>
       <c r="K125" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20836,8 +21074,9 @@
       </c>
       <c r="W125" s="285" t="n"/>
       <c r="X125" s="285" t="n"/>
-      <c r="Y125" s="1304" t="n"/>
-      <c r="Z125" s="285" t="inlineStr">
+      <c r="Y125" s="1448" t="n"/>
+      <c r="Z125" s="1304" t="n"/>
+      <c r="AA125" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20877,6 +21116,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J126" s="1448" t="n"/>
       <c r="K126" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20919,8 +21159,9 @@
       </c>
       <c r="W126" s="285" t="n"/>
       <c r="X126" s="285" t="n"/>
-      <c r="Y126" s="1304" t="n"/>
-      <c r="Z126" s="285" t="inlineStr">
+      <c r="Y126" s="1448" t="n"/>
+      <c r="Z126" s="1304" t="n"/>
+      <c r="AA126" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20960,6 +21201,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J127" s="1448" t="n"/>
       <c r="K127" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21002,8 +21244,9 @@
       </c>
       <c r="W127" s="285" t="n"/>
       <c r="X127" s="285" t="n"/>
-      <c r="Y127" s="1304" t="n"/>
-      <c r="Z127" s="285" t="inlineStr">
+      <c r="Y127" s="1448" t="n"/>
+      <c r="Z127" s="1304" t="n"/>
+      <c r="AA127" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21043,6 +21286,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J128" s="1448" t="n"/>
       <c r="K128" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21085,8 +21329,9 @@
       </c>
       <c r="W128" s="285" t="n"/>
       <c r="X128" s="285" t="n"/>
-      <c r="Y128" s="1304" t="n"/>
-      <c r="Z128" s="285" t="inlineStr">
+      <c r="Y128" s="1448" t="n"/>
+      <c r="Z128" s="1304" t="n"/>
+      <c r="AA128" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21126,6 +21371,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J129" s="1448" t="n"/>
       <c r="K129" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21168,8 +21414,9 @@
       </c>
       <c r="W129" s="285" t="n"/>
       <c r="X129" s="285" t="n"/>
-      <c r="Y129" s="1304" t="n"/>
-      <c r="Z129" s="285" t="inlineStr">
+      <c r="Y129" s="1448" t="n"/>
+      <c r="Z129" s="1304" t="n"/>
+      <c r="AA129" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21209,6 +21456,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J130" s="1448" t="n"/>
       <c r="K130" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21251,8 +21499,9 @@
       </c>
       <c r="W130" s="285" t="n"/>
       <c r="X130" s="285" t="n"/>
-      <c r="Y130" s="1304" t="n"/>
-      <c r="Z130" s="285" t="inlineStr">
+      <c r="Y130" s="1448" t="n"/>
+      <c r="Z130" s="1304" t="n"/>
+      <c r="AA130" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21292,6 +21541,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J131" s="1448" t="n"/>
       <c r="K131" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21334,8 +21584,9 @@
       </c>
       <c r="W131" s="285" t="n"/>
       <c r="X131" s="285" t="n"/>
-      <c r="Y131" s="1304" t="n"/>
-      <c r="Z131" s="285" t="inlineStr">
+      <c r="Y131" s="1448" t="n"/>
+      <c r="Z131" s="1304" t="n"/>
+      <c r="AA131" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21375,6 +21626,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J132" s="1448" t="n"/>
       <c r="K132" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21417,8 +21669,9 @@
       </c>
       <c r="W132" s="285" t="n"/>
       <c r="X132" s="285" t="n"/>
-      <c r="Y132" s="1304" t="n"/>
-      <c r="Z132" s="285" t="inlineStr">
+      <c r="Y132" s="1448" t="n"/>
+      <c r="Z132" s="1304" t="n"/>
+      <c r="AA132" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21458,6 +21711,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J133" s="1448" t="n"/>
       <c r="K133" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21500,8 +21754,9 @@
       </c>
       <c r="W133" s="285" t="n"/>
       <c r="X133" s="285" t="n"/>
-      <c r="Y133" s="1304" t="n"/>
-      <c r="Z133" s="285" t="inlineStr">
+      <c r="Y133" s="1448" t="n"/>
+      <c r="Z133" s="1304" t="n"/>
+      <c r="AA133" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21541,6 +21796,7 @@
           <t>ml</t>
         </is>
       </c>
+      <c r="J134" s="1448" t="n"/>
       <c r="K134" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21583,8 +21839,9 @@
       </c>
       <c r="W134" s="285" t="n"/>
       <c r="X134" s="285" t="n"/>
-      <c r="Y134" s="1304" t="n"/>
-      <c r="Z134" s="285" t="inlineStr">
+      <c r="Y134" s="1448" t="n"/>
+      <c r="Z134" s="1304" t="n"/>
+      <c r="AA134" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21624,6 +21881,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J135" s="1448" t="n"/>
       <c r="K135" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21666,8 +21924,9 @@
       </c>
       <c r="W135" s="285" t="n"/>
       <c r="X135" s="285" t="n"/>
-      <c r="Y135" s="1304" t="n"/>
-      <c r="Z135" s="285" t="inlineStr">
+      <c r="Y135" s="1448" t="n"/>
+      <c r="Z135" s="1304" t="n"/>
+      <c r="AA135" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21707,6 +21966,7 @@
           <t>m³</t>
         </is>
       </c>
+      <c r="J136" s="1448" t="n"/>
       <c r="K136" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21749,8 +22009,9 @@
       </c>
       <c r="W136" s="285" t="n"/>
       <c r="X136" s="285" t="n"/>
-      <c r="Y136" s="1304" t="n"/>
-      <c r="Z136" s="285" t="inlineStr">
+      <c r="Y136" s="1448" t="n"/>
+      <c r="Z136" s="1304" t="n"/>
+      <c r="AA136" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21790,6 +22051,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J137" s="1448" t="n"/>
       <c r="K137" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21832,8 +22094,9 @@
       </c>
       <c r="W137" s="285" t="n"/>
       <c r="X137" s="285" t="n"/>
-      <c r="Y137" s="1304" t="n"/>
-      <c r="Z137" s="285" t="inlineStr">
+      <c r="Y137" s="1448" t="n"/>
+      <c r="Z137" s="1304" t="n"/>
+      <c r="AA137" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21873,6 +22136,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J138" s="1448" t="n"/>
       <c r="K138" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21915,8 +22179,9 @@
       </c>
       <c r="W138" s="285" t="n"/>
       <c r="X138" s="285" t="n"/>
-      <c r="Y138" s="1304" t="n"/>
-      <c r="Z138" s="285" t="inlineStr">
+      <c r="Y138" s="1448" t="n"/>
+      <c r="Z138" s="1304" t="n"/>
+      <c r="AA138" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -21956,6 +22221,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J139" s="1448" t="n"/>
       <c r="K139" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21998,8 +22264,9 @@
       </c>
       <c r="W139" s="285" t="n"/>
       <c r="X139" s="285" t="n"/>
-      <c r="Y139" s="1304" t="n"/>
-      <c r="Z139" s="285" t="inlineStr">
+      <c r="Y139" s="1448" t="n"/>
+      <c r="Z139" s="1304" t="n"/>
+      <c r="AA139" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22039,6 +22306,7 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="J140" s="1448" t="n"/>
       <c r="K140" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22081,8 +22349,9 @@
       </c>
       <c r="W140" s="285" t="n"/>
       <c r="X140" s="285" t="n"/>
-      <c r="Y140" s="1304" t="n"/>
-      <c r="Z140" s="285" t="inlineStr">
+      <c r="Y140" s="1448" t="n"/>
+      <c r="Z140" s="1304" t="n"/>
+      <c r="AA140" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22122,6 +22391,7 @@
           <t>und</t>
         </is>
       </c>
+      <c r="J141" s="1448" t="n"/>
       <c r="K141" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22164,8 +22434,9 @@
       </c>
       <c r="W141" s="285" t="n"/>
       <c r="X141" s="285" t="n"/>
-      <c r="Y141" s="1304" t="n"/>
-      <c r="Z141" s="285" t="inlineStr">
+      <c r="Y141" s="1448" t="n"/>
+      <c r="Z141" s="1304" t="n"/>
+      <c r="AA141" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22205,6 +22476,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J142" s="1448" t="n"/>
       <c r="K142" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22247,8 +22519,9 @@
       </c>
       <c r="W142" s="285" t="n"/>
       <c r="X142" s="285" t="n"/>
-      <c r="Y142" s="1304" t="n"/>
-      <c r="Z142" s="285" t="inlineStr">
+      <c r="Y142" s="1448" t="n"/>
+      <c r="Z142" s="1304" t="n"/>
+      <c r="AA142" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22288,6 +22561,7 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J143" s="1448" t="n"/>
       <c r="K143" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22330,8 +22604,9 @@
       </c>
       <c r="W143" s="285" t="n"/>
       <c r="X143" s="285" t="n"/>
-      <c r="Y143" s="1304" t="n"/>
-      <c r="Z143" s="285" t="inlineStr">
+      <c r="Y143" s="1448" t="n"/>
+      <c r="Z143" s="1304" t="n"/>
+      <c r="AA143" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22371,6 +22646,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J144" s="1448" t="n"/>
       <c r="K144" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22413,8 +22689,9 @@
       </c>
       <c r="W144" s="285" t="n"/>
       <c r="X144" s="285" t="n"/>
-      <c r="Y144" s="1304" t="n"/>
-      <c r="Z144" s="285" t="inlineStr">
+      <c r="Y144" s="1448" t="n"/>
+      <c r="Z144" s="1304" t="n"/>
+      <c r="AA144" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22454,6 +22731,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J145" s="1448" t="n"/>
       <c r="K145" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22496,8 +22774,9 @@
       </c>
       <c r="W145" s="285" t="n"/>
       <c r="X145" s="285" t="n"/>
-      <c r="Y145" s="1304" t="n"/>
-      <c r="Z145" s="285" t="inlineStr">
+      <c r="Y145" s="1448" t="n"/>
+      <c r="Z145" s="1304" t="n"/>
+      <c r="AA145" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22537,6 +22816,7 @@
           <t>gl</t>
         </is>
       </c>
+      <c r="J146" s="1448" t="n"/>
       <c r="K146" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22579,8 +22859,9 @@
       </c>
       <c r="W146" s="285" t="n"/>
       <c r="X146" s="285" t="n"/>
-      <c r="Y146" s="1304" t="n"/>
-      <c r="Z146" s="285" t="inlineStr">
+      <c r="Y146" s="1448" t="n"/>
+      <c r="Z146" s="1304" t="n"/>
+      <c r="AA146" s="285" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -22616,7 +22897,7 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="Z147" s="336">
+      <c r="AA147" s="336">
         <f>I4</f>
         <v/>
       </c>
@@ -23311,16 +23592,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:Z169"/>
+  <autoFilter ref="A8:AA169"/>
   <mergeCells count="13">
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="L1:AA7"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L1:Z7"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="I7:K7"/>
@@ -34052,10 +34333,10 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E1:M1"/>
     <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="E1:M1"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -11140,7 +11140,7 @@
       </c>
       <c r="Q8" s="279" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Factor de desperdicio</t>
         </is>
       </c>
       <c r="R8" s="279" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="O8" s="296" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Factor de desperdicio</t>
         </is>
       </c>
       <c r="P8" s="296" t="inlineStr">
@@ -34333,10 +34333,10 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="E1:M1"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A23:M23"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$ &quot;#,##0"/>
@@ -32,8 +32,9 @@
     <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="\$\ #,##0"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
+    <numFmt numFmtId="173" formatCode="&quot;$ &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="167">
+  <fonts count="168">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1226,6 +1227,11 @@
       <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6702,7 +6708,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1449">
+  <cellXfs count="1470">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10302,6 +10308,43 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="422" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -10888,7 +10931,7 @@
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="615" min="1" max="1"/>
@@ -10973,7 +11016,7 @@
           <t>RYR-CO-005</t>
         </is>
       </c>
-      <c r="J4" s="1447" t="n"/>
+      <c r="J4" s="1468" t="n"/>
       <c r="K4" s="623" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="550">
@@ -11229,7 +11272,7 @@
           <t>m2</t>
         </is>
       </c>
-      <c r="J9" s="1448" t="n"/>
+      <c r="J9" s="1469" t="n"/>
       <c r="K9" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11272,7 +11315,7 @@
       </c>
       <c r="W9" s="285" t="n"/>
       <c r="X9" s="285" t="n"/>
-      <c r="Y9" s="1448" t="n"/>
+      <c r="Y9" s="1469" t="n"/>
       <c r="Z9" s="1304" t="n"/>
       <c r="AA9" s="285" t="inlineStr">
         <is>
@@ -11314,7 +11357,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J10" s="1448" t="n"/>
+      <c r="J10" s="1469" t="n"/>
       <c r="K10" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11357,7 +11400,7 @@
       </c>
       <c r="W10" s="285" t="n"/>
       <c r="X10" s="285" t="n"/>
-      <c r="Y10" s="1448" t="n"/>
+      <c r="Y10" s="1469" t="n"/>
       <c r="Z10" s="1304" t="n"/>
       <c r="AA10" s="285" t="inlineStr">
         <is>
@@ -11399,7 +11442,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J11" s="1448" t="n"/>
+      <c r="J11" s="1469" t="n"/>
       <c r="K11" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11442,7 +11485,7 @@
       </c>
       <c r="W11" s="285" t="n"/>
       <c r="X11" s="285" t="n"/>
-      <c r="Y11" s="1448" t="n"/>
+      <c r="Y11" s="1469" t="n"/>
       <c r="Z11" s="1304" t="n"/>
       <c r="AA11" s="285" t="inlineStr">
         <is>
@@ -11484,7 +11527,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J12" s="1448" t="n"/>
+      <c r="J12" s="1469" t="n"/>
       <c r="K12" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11527,7 +11570,7 @@
       </c>
       <c r="W12" s="285" t="n"/>
       <c r="X12" s="285" t="n"/>
-      <c r="Y12" s="1448" t="n"/>
+      <c r="Y12" s="1469" t="n"/>
       <c r="Z12" s="1304" t="n"/>
       <c r="AA12" s="285" t="inlineStr">
         <is>
@@ -11569,7 +11612,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J13" s="1448" t="n"/>
+      <c r="J13" s="1469" t="n"/>
       <c r="K13" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11612,7 +11655,7 @@
       </c>
       <c r="W13" s="285" t="n"/>
       <c r="X13" s="285" t="n"/>
-      <c r="Y13" s="1448" t="n"/>
+      <c r="Y13" s="1469" t="n"/>
       <c r="Z13" s="1304" t="n"/>
       <c r="AA13" s="285" t="inlineStr">
         <is>
@@ -11654,7 +11697,7 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="J14" s="1448" t="n"/>
+      <c r="J14" s="1469" t="n"/>
       <c r="K14" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11697,7 +11740,7 @@
       </c>
       <c r="W14" s="285" t="n"/>
       <c r="X14" s="285" t="n"/>
-      <c r="Y14" s="1448" t="n"/>
+      <c r="Y14" s="1469" t="n"/>
       <c r="Z14" s="1304" t="n"/>
       <c r="AA14" s="285" t="inlineStr">
         <is>
@@ -11739,7 +11782,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J15" s="1448" t="n"/>
+      <c r="J15" s="1469" t="n"/>
       <c r="K15" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11782,7 +11825,7 @@
       </c>
       <c r="W15" s="285" t="n"/>
       <c r="X15" s="285" t="n"/>
-      <c r="Y15" s="1448" t="n"/>
+      <c r="Y15" s="1469" t="n"/>
       <c r="Z15" s="1304" t="n"/>
       <c r="AA15" s="285" t="inlineStr">
         <is>
@@ -11824,7 +11867,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J16" s="1448" t="n"/>
+      <c r="J16" s="1469" t="n"/>
       <c r="K16" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11867,7 +11910,7 @@
       </c>
       <c r="W16" s="285" t="n"/>
       <c r="X16" s="285" t="n"/>
-      <c r="Y16" s="1448" t="n"/>
+      <c r="Y16" s="1469" t="n"/>
       <c r="Z16" s="1304" t="n"/>
       <c r="AA16" s="285" t="inlineStr">
         <is>
@@ -11909,7 +11952,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J17" s="1448" t="n"/>
+      <c r="J17" s="1469" t="n"/>
       <c r="K17" s="1438" t="n">
         <v>0</v>
       </c>
@@ -11952,7 +11995,7 @@
       </c>
       <c r="W17" s="285" t="n"/>
       <c r="X17" s="285" t="n"/>
-      <c r="Y17" s="1448" t="n"/>
+      <c r="Y17" s="1469" t="n"/>
       <c r="Z17" s="1304" t="n"/>
       <c r="AA17" s="285" t="inlineStr">
         <is>
@@ -11994,7 +12037,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J18" s="1448" t="n"/>
+      <c r="J18" s="1469" t="n"/>
       <c r="K18" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12037,7 +12080,7 @@
       </c>
       <c r="W18" s="285" t="n"/>
       <c r="X18" s="285" t="n"/>
-      <c r="Y18" s="1448" t="n"/>
+      <c r="Y18" s="1469" t="n"/>
       <c r="Z18" s="1304" t="n"/>
       <c r="AA18" s="285" t="inlineStr">
         <is>
@@ -12079,7 +12122,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J19" s="1448" t="n"/>
+      <c r="J19" s="1469" t="n"/>
       <c r="K19" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12122,7 +12165,7 @@
       </c>
       <c r="W19" s="285" t="n"/>
       <c r="X19" s="285" t="n"/>
-      <c r="Y19" s="1448" t="n"/>
+      <c r="Y19" s="1469" t="n"/>
       <c r="Z19" s="1304" t="n"/>
       <c r="AA19" s="285" t="inlineStr">
         <is>
@@ -12164,7 +12207,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J20" s="1448" t="n"/>
+      <c r="J20" s="1469" t="n"/>
       <c r="K20" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12207,7 +12250,7 @@
       </c>
       <c r="W20" s="285" t="n"/>
       <c r="X20" s="285" t="n"/>
-      <c r="Y20" s="1448" t="n"/>
+      <c r="Y20" s="1469" t="n"/>
       <c r="Z20" s="1304" t="n"/>
       <c r="AA20" s="285" t="inlineStr">
         <is>
@@ -12249,7 +12292,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J21" s="1448" t="n"/>
+      <c r="J21" s="1469" t="n"/>
       <c r="K21" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12292,7 +12335,7 @@
       </c>
       <c r="W21" s="285" t="n"/>
       <c r="X21" s="285" t="n"/>
-      <c r="Y21" s="1448" t="n"/>
+      <c r="Y21" s="1469" t="n"/>
       <c r="Z21" s="1304" t="n"/>
       <c r="AA21" s="285" t="inlineStr">
         <is>
@@ -12334,7 +12377,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J22" s="1448" t="n"/>
+      <c r="J22" s="1469" t="n"/>
       <c r="K22" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12377,7 +12420,7 @@
       </c>
       <c r="W22" s="285" t="n"/>
       <c r="X22" s="285" t="n"/>
-      <c r="Y22" s="1448" t="n"/>
+      <c r="Y22" s="1469" t="n"/>
       <c r="Z22" s="1304" t="n"/>
       <c r="AA22" s="285" t="inlineStr">
         <is>
@@ -12419,7 +12462,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J23" s="1448" t="n"/>
+      <c r="J23" s="1469" t="n"/>
       <c r="K23" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12462,7 +12505,7 @@
       </c>
       <c r="W23" s="285" t="n"/>
       <c r="X23" s="285" t="n"/>
-      <c r="Y23" s="1448" t="n"/>
+      <c r="Y23" s="1469" t="n"/>
       <c r="Z23" s="1304" t="n"/>
       <c r="AA23" s="285" t="inlineStr">
         <is>
@@ -12504,7 +12547,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J24" s="1448" t="n"/>
+      <c r="J24" s="1469" t="n"/>
       <c r="K24" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12547,7 +12590,7 @@
       </c>
       <c r="W24" s="285" t="n"/>
       <c r="X24" s="285" t="n"/>
-      <c r="Y24" s="1448" t="n"/>
+      <c r="Y24" s="1469" t="n"/>
       <c r="Z24" s="1304" t="n"/>
       <c r="AA24" s="285" t="inlineStr">
         <is>
@@ -12589,7 +12632,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J25" s="1448" t="n"/>
+      <c r="J25" s="1469" t="n"/>
       <c r="K25" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12632,7 +12675,7 @@
       </c>
       <c r="W25" s="285" t="n"/>
       <c r="X25" s="285" t="n"/>
-      <c r="Y25" s="1448" t="n"/>
+      <c r="Y25" s="1469" t="n"/>
       <c r="Z25" s="1304" t="n"/>
       <c r="AA25" s="285" t="inlineStr">
         <is>
@@ -12674,7 +12717,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J26" s="1448" t="n"/>
+      <c r="J26" s="1469" t="n"/>
       <c r="K26" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12717,7 +12760,7 @@
       </c>
       <c r="W26" s="285" t="n"/>
       <c r="X26" s="285" t="n"/>
-      <c r="Y26" s="1448" t="n"/>
+      <c r="Y26" s="1469" t="n"/>
       <c r="Z26" s="1304" t="n"/>
       <c r="AA26" s="285" t="inlineStr">
         <is>
@@ -12759,7 +12802,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J27" s="1448" t="n"/>
+      <c r="J27" s="1469" t="n"/>
       <c r="K27" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12802,7 +12845,7 @@
       </c>
       <c r="W27" s="285" t="n"/>
       <c r="X27" s="285" t="n"/>
-      <c r="Y27" s="1448" t="n"/>
+      <c r="Y27" s="1469" t="n"/>
       <c r="Z27" s="1304" t="n"/>
       <c r="AA27" s="285" t="inlineStr">
         <is>
@@ -12844,7 +12887,7 @@
           <t>m³</t>
         </is>
       </c>
-      <c r="J28" s="1448" t="n"/>
+      <c r="J28" s="1469" t="n"/>
       <c r="K28" s="1438" t="n">
         <v>0</v>
       </c>
@@ -12887,7 +12930,7 @@
       </c>
       <c r="W28" s="285" t="n"/>
       <c r="X28" s="285" t="n"/>
-      <c r="Y28" s="1448" t="n"/>
+      <c r="Y28" s="1469" t="n"/>
       <c r="Z28" s="1304" t="n"/>
       <c r="AA28" s="285" t="inlineStr">
         <is>
@@ -12895,10 +12938,10 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="29">
       <c r="A29" s="280" t="inlineStr">
         <is>
-          <t>MQ-021</t>
+          <t>MQ-011</t>
         </is>
       </c>
       <c r="B29" s="281" t="inlineStr">
@@ -12906,19 +12949,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C29" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D29" s="283" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
+      <c r="C29" s="282" t="n"/>
+      <c r="D29" s="283" t="n"/>
       <c r="E29" s="284" t="inlineStr">
         <is>
-          <t>Concreto de limpieza / solado</t>
+          <t>Concreto de f'c = 175 kg/cm² (2500 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="F29" s="285" t="n"/>
@@ -12926,64 +12961,34 @@
       <c r="H29" s="285" t="n"/>
       <c r="I29" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J29" s="1448" t="n"/>
-      <c r="K29" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J29" s="1469" t="n"/>
+      <c r="K29" s="1438" t="n"/>
+      <c r="L29" s="1438" t="n"/>
+      <c r="M29" s="1438" t="n"/>
+      <c r="N29" s="1438" t="n"/>
+      <c r="O29" s="1438" t="n"/>
+      <c r="P29" s="1438" t="n"/>
+      <c r="Q29" s="1438" t="n"/>
+      <c r="R29" s="1438" t="n"/>
+      <c r="S29" s="1303" t="n"/>
       <c r="T29" s="1438">
         <f>IF(I29="","",ROUND(IF(OR(I29="m²",I29="m2"),K29*IF(L29=0,1,L29)*IF(O29=0,1,O29)*IF(P29=0,1,P29)*Q29-R29,IF(OR(I29="m³",I29="m3"),K29*L29*M29*IF(O29=0,1,O29)*IF(P29=0,1,P29)*Q29-R29,IF(OR(I29="ml",I29="ML"),K29*IF(O29=0,1,O29)*IF(P29=0,1,P29)*Q29-R29,IF(OR(I29="und",I29="UND"),IF(O29=0,1,O29)*IF(P29=0,1,P29)*Q29-R29,IF(I29="kg",K29*IF(O29=0,1,O29)*IF(P29=0,1,P29)*Q29-R29,IF(OR(I29="gl",I29="GL",I29="gb",I29="GB",I29="Gl",I29="Gb"),IF(O29=0,1,O29)*IF(P29=0,1,P29)*Q29-R29,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U29" s="1438">
-        <f>IF(T29="","",ROUND(T29*(1+S29),3))</f>
-        <v/>
-      </c>
-      <c r="V29" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U29" s="1438" t="n"/>
+      <c r="V29" s="283" t="n"/>
       <c r="W29" s="285" t="n"/>
       <c r="X29" s="285" t="n"/>
-      <c r="Y29" s="1448" t="n"/>
+      <c r="Y29" s="1469" t="n"/>
       <c r="Z29" s="1304" t="n"/>
-      <c r="AA29" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="30">
       <c r="A30" s="280" t="inlineStr">
         <is>
-          <t>MQ-022</t>
+          <t>MQ-012</t>
         </is>
       </c>
       <c r="B30" s="281" t="inlineStr">
@@ -12991,19 +12996,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C30" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D30" s="283" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
+      <c r="C30" s="282" t="n"/>
+      <c r="D30" s="283" t="n"/>
       <c r="E30" s="284" t="inlineStr">
         <is>
-          <t>Concreto para zapatas</t>
+          <t>Concreto ciclópeo, incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="F30" s="285" t="n"/>
@@ -13011,64 +13008,34 @@
       <c r="H30" s="285" t="n"/>
       <c r="I30" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J30" s="1448" t="n"/>
-      <c r="K30" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J30" s="1469" t="n"/>
+      <c r="K30" s="1438" t="n"/>
+      <c r="L30" s="1438" t="n"/>
+      <c r="M30" s="1438" t="n"/>
+      <c r="N30" s="1438" t="n"/>
+      <c r="O30" s="1438" t="n"/>
+      <c r="P30" s="1438" t="n"/>
+      <c r="Q30" s="1438" t="n"/>
+      <c r="R30" s="1438" t="n"/>
+      <c r="S30" s="1303" t="n"/>
       <c r="T30" s="1438">
         <f>IF(I30="","",ROUND(IF(OR(I30="m²",I30="m2"),K30*IF(L30=0,1,L30)*IF(O30=0,1,O30)*IF(P30=0,1,P30)*Q30-R30,IF(OR(I30="m³",I30="m3"),K30*L30*M30*IF(O30=0,1,O30)*IF(P30=0,1,P30)*Q30-R30,IF(OR(I30="ml",I30="ML"),K30*IF(O30=0,1,O30)*IF(P30=0,1,P30)*Q30-R30,IF(OR(I30="und",I30="UND"),IF(O30=0,1,O30)*IF(P30=0,1,P30)*Q30-R30,IF(I30="kg",K30*IF(O30=0,1,O30)*IF(P30=0,1,P30)*Q30-R30,IF(OR(I30="gl",I30="GL",I30="gb",I30="GB",I30="Gl",I30="Gb"),IF(O30=0,1,O30)*IF(P30=0,1,P30)*Q30-R30,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U30" s="1438">
-        <f>IF(T30="","",ROUND(T30*(1+S30),3))</f>
-        <v/>
-      </c>
-      <c r="V30" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U30" s="1438" t="n"/>
+      <c r="V30" s="283" t="n"/>
       <c r="W30" s="285" t="n"/>
       <c r="X30" s="285" t="n"/>
-      <c r="Y30" s="1448" t="n"/>
+      <c r="Y30" s="1469" t="n"/>
       <c r="Z30" s="1304" t="n"/>
-      <c r="AA30" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="31">
       <c r="A31" s="280" t="inlineStr">
         <is>
-          <t>MQ-023</t>
+          <t>MQ-013</t>
         </is>
       </c>
       <c r="B31" s="281" t="inlineStr">
@@ -13076,19 +13043,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C31" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D31" s="283" t="inlineStr">
-        <is>
-          <t>03.01.03</t>
-        </is>
-      </c>
+      <c r="C31" s="282" t="n"/>
+      <c r="D31" s="283" t="n"/>
       <c r="E31" s="284" t="inlineStr">
         <is>
-          <t>Concreto para vigas de cimentación</t>
+          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado — Cimentaciones</t>
         </is>
       </c>
       <c r="F31" s="285" t="n"/>
@@ -13096,64 +13055,34 @@
       <c r="H31" s="285" t="n"/>
       <c r="I31" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J31" s="1448" t="n"/>
-      <c r="K31" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J31" s="1469" t="n"/>
+      <c r="K31" s="1438" t="n"/>
+      <c r="L31" s="1438" t="n"/>
+      <c r="M31" s="1438" t="n"/>
+      <c r="N31" s="1438" t="n"/>
+      <c r="O31" s="1438" t="n"/>
+      <c r="P31" s="1438" t="n"/>
+      <c r="Q31" s="1438" t="n"/>
+      <c r="R31" s="1438" t="n"/>
+      <c r="S31" s="1303" t="n"/>
       <c r="T31" s="1438">
         <f>IF(I31="","",ROUND(IF(OR(I31="m²",I31="m2"),K31*IF(L31=0,1,L31)*IF(O31=0,1,O31)*IF(P31=0,1,P31)*Q31-R31,IF(OR(I31="m³",I31="m3"),K31*L31*M31*IF(O31=0,1,O31)*IF(P31=0,1,P31)*Q31-R31,IF(OR(I31="ml",I31="ML"),K31*IF(O31=0,1,O31)*IF(P31=0,1,P31)*Q31-R31,IF(OR(I31="und",I31="UND"),IF(O31=0,1,O31)*IF(P31=0,1,P31)*Q31-R31,IF(I31="kg",K31*IF(O31=0,1,O31)*IF(P31=0,1,P31)*Q31-R31,IF(OR(I31="gl",I31="GL",I31="gb",I31="GB",I31="Gl",I31="Gb"),IF(O31=0,1,O31)*IF(P31=0,1,P31)*Q31-R31,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U31" s="1438">
-        <f>IF(T31="","",ROUND(T31*(1+S31),3))</f>
-        <v/>
-      </c>
-      <c r="V31" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U31" s="1438" t="n"/>
+      <c r="V31" s="283" t="n"/>
       <c r="W31" s="285" t="n"/>
       <c r="X31" s="285" t="n"/>
-      <c r="Y31" s="1448" t="n"/>
+      <c r="Y31" s="1469" t="n"/>
       <c r="Z31" s="1304" t="n"/>
-      <c r="AA31" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="32">
       <c r="A32" s="280" t="inlineStr">
         <is>
-          <t>MQ-024</t>
+          <t>MQ-014</t>
         </is>
       </c>
       <c r="B32" s="281" t="inlineStr">
@@ -13161,19 +13090,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C32" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D32" s="283" t="inlineStr">
-        <is>
-          <t>03.01.04</t>
-        </is>
-      </c>
+      <c r="C32" s="282" t="n"/>
+      <c r="D32" s="283" t="n"/>
       <c r="E32" s="284" t="inlineStr">
         <is>
-          <t>Concreto para losas de cimentación</t>
+          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado — Cimentaciones</t>
         </is>
       </c>
       <c r="F32" s="285" t="n"/>
@@ -13181,64 +13102,34 @@
       <c r="H32" s="285" t="n"/>
       <c r="I32" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J32" s="1448" t="n"/>
-      <c r="K32" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J32" s="1469" t="n"/>
+      <c r="K32" s="1438" t="n"/>
+      <c r="L32" s="1438" t="n"/>
+      <c r="M32" s="1438" t="n"/>
+      <c r="N32" s="1438" t="n"/>
+      <c r="O32" s="1438" t="n"/>
+      <c r="P32" s="1438" t="n"/>
+      <c r="Q32" s="1438" t="n"/>
+      <c r="R32" s="1438" t="n"/>
+      <c r="S32" s="1303" t="n"/>
       <c r="T32" s="1438">
         <f>IF(I32="","",ROUND(IF(OR(I32="m²",I32="m2"),K32*IF(L32=0,1,L32)*IF(O32=0,1,O32)*IF(P32=0,1,P32)*Q32-R32,IF(OR(I32="m³",I32="m3"),K32*L32*M32*IF(O32=0,1,O32)*IF(P32=0,1,P32)*Q32-R32,IF(OR(I32="ml",I32="ML"),K32*IF(O32=0,1,O32)*IF(P32=0,1,P32)*Q32-R32,IF(OR(I32="und",I32="UND"),IF(O32=0,1,O32)*IF(P32=0,1,P32)*Q32-R32,IF(I32="kg",K32*IF(O32=0,1,O32)*IF(P32=0,1,P32)*Q32-R32,IF(OR(I32="gl",I32="GL",I32="gb",I32="GB",I32="Gl",I32="Gb"),IF(O32=0,1,O32)*IF(P32=0,1,P32)*Q32-R32,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U32" s="1438">
-        <f>IF(T32="","",ROUND(T32*(1+S32),3))</f>
-        <v/>
-      </c>
-      <c r="V32" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U32" s="1438" t="n"/>
+      <c r="V32" s="283" t="n"/>
       <c r="W32" s="285" t="n"/>
       <c r="X32" s="285" t="n"/>
-      <c r="Y32" s="1448" t="n"/>
+      <c r="Y32" s="1469" t="n"/>
       <c r="Z32" s="1304" t="n"/>
-      <c r="AA32" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="33">
       <c r="A33" s="280" t="inlineStr">
         <is>
-          <t>MQ-025</t>
+          <t>MQ-015</t>
         </is>
       </c>
       <c r="B33" s="281" t="inlineStr">
@@ -13246,19 +13137,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C33" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D33" s="283" t="inlineStr">
-        <is>
-          <t>03.01.05</t>
-        </is>
-      </c>
+      <c r="C33" s="282" t="n"/>
+      <c r="D33" s="283" t="n"/>
       <c r="E33" s="284" t="inlineStr">
         <is>
-          <t>Concreto para pedestales</t>
+          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado — Cimentaciones</t>
         </is>
       </c>
       <c r="F33" s="285" t="n"/>
@@ -13266,64 +13149,34 @@
       <c r="H33" s="285" t="n"/>
       <c r="I33" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J33" s="1448" t="n"/>
-      <c r="K33" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J33" s="1469" t="n"/>
+      <c r="K33" s="1438" t="n"/>
+      <c r="L33" s="1438" t="n"/>
+      <c r="M33" s="1438" t="n"/>
+      <c r="N33" s="1438" t="n"/>
+      <c r="O33" s="1438" t="n"/>
+      <c r="P33" s="1438" t="n"/>
+      <c r="Q33" s="1438" t="n"/>
+      <c r="R33" s="1438" t="n"/>
+      <c r="S33" s="1303" t="n"/>
       <c r="T33" s="1438">
         <f>IF(I33="","",ROUND(IF(OR(I33="m²",I33="m2"),K33*IF(L33=0,1,L33)*IF(O33=0,1,O33)*IF(P33=0,1,P33)*Q33-R33,IF(OR(I33="m³",I33="m3"),K33*L33*M33*IF(O33=0,1,O33)*IF(P33=0,1,P33)*Q33-R33,IF(OR(I33="ml",I33="ML"),K33*IF(O33=0,1,O33)*IF(P33=0,1,P33)*Q33-R33,IF(OR(I33="und",I33="UND"),IF(O33=0,1,O33)*IF(P33=0,1,P33)*Q33-R33,IF(I33="kg",K33*IF(O33=0,1,O33)*IF(P33=0,1,P33)*Q33-R33,IF(OR(I33="gl",I33="GL",I33="gb",I33="GB",I33="Gl",I33="Gb"),IF(O33=0,1,O33)*IF(P33=0,1,P33)*Q33-R33,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U33" s="1438">
-        <f>IF(T33="","",ROUND(T33*(1+S33),3))</f>
-        <v/>
-      </c>
-      <c r="V33" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U33" s="1438" t="n"/>
+      <c r="V33" s="283" t="n"/>
       <c r="W33" s="285" t="n"/>
       <c r="X33" s="285" t="n"/>
-      <c r="Y33" s="1448" t="n"/>
+      <c r="Y33" s="1469" t="n"/>
       <c r="Z33" s="1304" t="n"/>
-      <c r="AA33" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="34">
       <c r="A34" s="280" t="inlineStr">
         <is>
-          <t>MQ-026</t>
+          <t>MQ-016</t>
         </is>
       </c>
       <c r="B34" s="281" t="inlineStr">
@@ -13331,19 +13184,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C34" s="282" t="inlineStr">
-        <is>
-          <t>Acero</t>
-        </is>
-      </c>
-      <c r="D34" s="283" t="inlineStr">
-        <is>
-          <t>03.02.01</t>
-        </is>
-      </c>
+      <c r="C34" s="282" t="n"/>
+      <c r="D34" s="283" t="n"/>
       <c r="E34" s="284" t="inlineStr">
         <is>
-          <t>Acero de refuerzo en cimentación</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI — Cimentaciones</t>
         </is>
       </c>
       <c r="F34" s="285" t="n"/>
@@ -13354,61 +13199,31 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="J34" s="1448" t="n"/>
-      <c r="K34" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1303" t="n">
-        <v>0</v>
-      </c>
+      <c r="J34" s="1469" t="n"/>
+      <c r="K34" s="1438" t="n"/>
+      <c r="L34" s="1438" t="n"/>
+      <c r="M34" s="1438" t="n"/>
+      <c r="N34" s="1438" t="n"/>
+      <c r="O34" s="1438" t="n"/>
+      <c r="P34" s="1438" t="n"/>
+      <c r="Q34" s="1438" t="n"/>
+      <c r="R34" s="1438" t="n"/>
+      <c r="S34" s="1303" t="n"/>
       <c r="T34" s="1438">
         <f>IF(I34="","",ROUND(IF(OR(I34="m²",I34="m2"),K34*IF(L34=0,1,L34)*IF(O34=0,1,O34)*IF(P34=0,1,P34)*Q34-R34,IF(OR(I34="m³",I34="m3"),K34*L34*M34*IF(O34=0,1,O34)*IF(P34=0,1,P34)*Q34-R34,IF(OR(I34="ml",I34="ML"),K34*IF(O34=0,1,O34)*IF(P34=0,1,P34)*Q34-R34,IF(OR(I34="und",I34="UND"),IF(O34=0,1,O34)*IF(P34=0,1,P34)*Q34-R34,IF(I34="kg",K34*IF(O34=0,1,O34)*IF(P34=0,1,P34)*Q34-R34,IF(OR(I34="gl",I34="GL",I34="gb",I34="GB",I34="Gl",I34="Gb"),IF(O34=0,1,O34)*IF(P34=0,1,P34)*Q34-R34,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U34" s="1438">
-        <f>IF(T34="","",ROUND(T34*(1+S34),3))</f>
-        <v/>
-      </c>
-      <c r="V34" s="283" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="U34" s="1438" t="n"/>
+      <c r="V34" s="283" t="n"/>
       <c r="W34" s="285" t="n"/>
       <c r="X34" s="285" t="n"/>
-      <c r="Y34" s="1448" t="n"/>
+      <c r="Y34" s="1469" t="n"/>
       <c r="Z34" s="1304" t="n"/>
-      <c r="AA34" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="35">
       <c r="A35" s="280" t="inlineStr">
         <is>
-          <t>MQ-027</t>
+          <t>MQ-017</t>
         </is>
       </c>
       <c r="B35" s="281" t="inlineStr">
@@ -13416,19 +13231,11 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C35" s="282" t="inlineStr">
-        <is>
-          <t>Formaleta</t>
-        </is>
-      </c>
-      <c r="D35" s="283" t="inlineStr">
-        <is>
-          <t>03.03.01</t>
-        </is>
-      </c>
+      <c r="C35" s="282" t="n"/>
+      <c r="D35" s="283" t="n"/>
       <c r="E35" s="284" t="inlineStr">
         <is>
-          <t>Formaleta para elementos de cimentación</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI — Cimentaciones</t>
         </is>
       </c>
       <c r="F35" s="285" t="n"/>
@@ -13436,84 +13243,54 @@
       <c r="H35" s="285" t="n"/>
       <c r="I35" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J35" s="1448" t="n"/>
-      <c r="K35" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="J35" s="1469" t="n"/>
+      <c r="K35" s="1438" t="n"/>
+      <c r="L35" s="1438" t="n"/>
+      <c r="M35" s="1438" t="n"/>
+      <c r="N35" s="1438" t="n"/>
+      <c r="O35" s="1438" t="n"/>
+      <c r="P35" s="1438" t="n"/>
+      <c r="Q35" s="1438" t="n"/>
+      <c r="R35" s="1438" t="n"/>
+      <c r="S35" s="1303" t="n"/>
       <c r="T35" s="1438">
         <f>IF(I35="","",ROUND(IF(OR(I35="m²",I35="m2"),K35*IF(L35=0,1,L35)*IF(O35=0,1,O35)*IF(P35=0,1,P35)*Q35-R35,IF(OR(I35="m³",I35="m3"),K35*L35*M35*IF(O35=0,1,O35)*IF(P35=0,1,P35)*Q35-R35,IF(OR(I35="ml",I35="ML"),K35*IF(O35=0,1,O35)*IF(P35=0,1,P35)*Q35-R35,IF(OR(I35="und",I35="UND"),IF(O35=0,1,O35)*IF(P35=0,1,P35)*Q35-R35,IF(I35="kg",K35*IF(O35=0,1,O35)*IF(P35=0,1,P35)*Q35-R35,IF(OR(I35="gl",I35="GL",I35="gb",I35="GB",I35="Gl",I35="Gb"),IF(O35=0,1,O35)*IF(P35=0,1,P35)*Q35-R35,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U35" s="1438">
-        <f>IF(T35="","",ROUND(T35*(1+S35),3))</f>
-        <v/>
-      </c>
-      <c r="V35" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="U35" s="1438" t="n"/>
+      <c r="V35" s="283" t="n"/>
       <c r="W35" s="285" t="n"/>
       <c r="X35" s="285" t="n"/>
-      <c r="Y35" s="1448" t="n"/>
+      <c r="Y35" s="1469" t="n"/>
       <c r="Z35" s="1304" t="n"/>
-      <c r="AA35" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A36" s="280" t="inlineStr">
         <is>
-          <t>MQ-028</t>
+          <t>MQ-027</t>
         </is>
       </c>
       <c r="B36" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>CIMENTACIONES</t>
         </is>
       </c>
       <c r="C36" s="282" t="inlineStr">
         <is>
-          <t>Concreto</t>
+          <t>Formaleta</t>
         </is>
       </c>
       <c r="D36" s="283" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.03.01</t>
         </is>
       </c>
       <c r="E36" s="284" t="inlineStr">
         <is>
-          <t>Concreto para columnas</t>
+          <t>Formaleta para elementos de cimentación</t>
         </is>
       </c>
       <c r="F36" s="285" t="n"/>
@@ -13521,10 +13298,10 @@
       <c r="H36" s="285" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J36" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J36" s="1469" t="n"/>
       <c r="K36" s="1438" t="n">
         <v>0</v>
       </c>
@@ -13562,12 +13339,12 @@
       </c>
       <c r="V36" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W36" s="285" t="n"/>
       <c r="X36" s="285" t="n"/>
-      <c r="Y36" s="1448" t="n"/>
+      <c r="Y36" s="1469" t="n"/>
       <c r="Z36" s="1304" t="n"/>
       <c r="AA36" s="285" t="inlineStr">
         <is>
@@ -13575,10 +13352,10 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="37">
       <c r="A37" s="280" t="inlineStr">
         <is>
-          <t>MQ-029</t>
+          <t>MQ-018</t>
         </is>
       </c>
       <c r="B37" s="281" t="inlineStr">
@@ -13586,19 +13363,11 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C37" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D37" s="283" t="inlineStr">
-        <is>
-          <t>04.01.02</t>
-        </is>
-      </c>
+      <c r="C37" s="282" t="n"/>
+      <c r="D37" s="283" t="n"/>
       <c r="E37" s="284" t="inlineStr">
         <is>
-          <t>Concreto para vigas</t>
+          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado — Estructura</t>
         </is>
       </c>
       <c r="F37" s="285" t="n"/>
@@ -13606,64 +13375,34 @@
       <c r="H37" s="285" t="n"/>
       <c r="I37" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J37" s="1448" t="n"/>
-      <c r="K37" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J37" s="1469" t="n"/>
+      <c r="K37" s="1438" t="n"/>
+      <c r="L37" s="1438" t="n"/>
+      <c r="M37" s="1438" t="n"/>
+      <c r="N37" s="1438" t="n"/>
+      <c r="O37" s="1438" t="n"/>
+      <c r="P37" s="1438" t="n"/>
+      <c r="Q37" s="1438" t="n"/>
+      <c r="R37" s="1438" t="n"/>
+      <c r="S37" s="1303" t="n"/>
       <c r="T37" s="1438">
         <f>IF(I37="","",ROUND(IF(OR(I37="m²",I37="m2"),K37*IF(L37=0,1,L37)*IF(O37=0,1,O37)*IF(P37=0,1,P37)*Q37-R37,IF(OR(I37="m³",I37="m3"),K37*L37*M37*IF(O37=0,1,O37)*IF(P37=0,1,P37)*Q37-R37,IF(OR(I37="ml",I37="ML"),K37*IF(O37=0,1,O37)*IF(P37=0,1,P37)*Q37-R37,IF(OR(I37="und",I37="UND"),IF(O37=0,1,O37)*IF(P37=0,1,P37)*Q37-R37,IF(I37="kg",K37*IF(O37=0,1,O37)*IF(P37=0,1,P37)*Q37-R37,IF(OR(I37="gl",I37="GL",I37="gb",I37="GB",I37="Gl",I37="Gb"),IF(O37=0,1,O37)*IF(P37=0,1,P37)*Q37-R37,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U37" s="1438">
-        <f>IF(T37="","",ROUND(T37*(1+S37),3))</f>
-        <v/>
-      </c>
-      <c r="V37" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U37" s="1438" t="n"/>
+      <c r="V37" s="283" t="n"/>
       <c r="W37" s="285" t="n"/>
       <c r="X37" s="285" t="n"/>
-      <c r="Y37" s="1448" t="n"/>
+      <c r="Y37" s="1469" t="n"/>
       <c r="Z37" s="1304" t="n"/>
-      <c r="AA37" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="38">
       <c r="A38" s="280" t="inlineStr">
         <is>
-          <t>MQ-030</t>
+          <t>MQ-019</t>
         </is>
       </c>
       <c r="B38" s="281" t="inlineStr">
@@ -13671,19 +13410,11 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C38" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D38" s="283" t="inlineStr">
-        <is>
-          <t>04.01.03</t>
-        </is>
-      </c>
+      <c r="C38" s="282" t="n"/>
+      <c r="D38" s="283" t="n"/>
       <c r="E38" s="284" t="inlineStr">
         <is>
-          <t>Concreto para losas</t>
+          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado — Estructura</t>
         </is>
       </c>
       <c r="F38" s="285" t="n"/>
@@ -13691,64 +13422,34 @@
       <c r="H38" s="285" t="n"/>
       <c r="I38" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J38" s="1448" t="n"/>
-      <c r="K38" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J38" s="1469" t="n"/>
+      <c r="K38" s="1438" t="n"/>
+      <c r="L38" s="1438" t="n"/>
+      <c r="M38" s="1438" t="n"/>
+      <c r="N38" s="1438" t="n"/>
+      <c r="O38" s="1438" t="n"/>
+      <c r="P38" s="1438" t="n"/>
+      <c r="Q38" s="1438" t="n"/>
+      <c r="R38" s="1438" t="n"/>
+      <c r="S38" s="1303" t="n"/>
       <c r="T38" s="1438">
         <f>IF(I38="","",ROUND(IF(OR(I38="m²",I38="m2"),K38*IF(L38=0,1,L38)*IF(O38=0,1,O38)*IF(P38=0,1,P38)*Q38-R38,IF(OR(I38="m³",I38="m3"),K38*L38*M38*IF(O38=0,1,O38)*IF(P38=0,1,P38)*Q38-R38,IF(OR(I38="ml",I38="ML"),K38*IF(O38=0,1,O38)*IF(P38=0,1,P38)*Q38-R38,IF(OR(I38="und",I38="UND"),IF(O38=0,1,O38)*IF(P38=0,1,P38)*Q38-R38,IF(I38="kg",K38*IF(O38=0,1,O38)*IF(P38=0,1,P38)*Q38-R38,IF(OR(I38="gl",I38="GL",I38="gb",I38="GB",I38="Gl",I38="Gb"),IF(O38=0,1,O38)*IF(P38=0,1,P38)*Q38-R38,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U38" s="1438">
-        <f>IF(T38="","",ROUND(T38*(1+S38),3))</f>
-        <v/>
-      </c>
-      <c r="V38" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U38" s="1438" t="n"/>
+      <c r="V38" s="283" t="n"/>
       <c r="W38" s="285" t="n"/>
       <c r="X38" s="285" t="n"/>
-      <c r="Y38" s="1448" t="n"/>
+      <c r="Y38" s="1469" t="n"/>
       <c r="Z38" s="1304" t="n"/>
-      <c r="AA38" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="39">
       <c r="A39" s="280" t="inlineStr">
         <is>
-          <t>MQ-031</t>
+          <t>MQ-020</t>
         </is>
       </c>
       <c r="B39" s="281" t="inlineStr">
@@ -13756,19 +13457,11 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C39" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D39" s="283" t="inlineStr">
-        <is>
-          <t>04.01.04</t>
-        </is>
-      </c>
+      <c r="C39" s="282" t="n"/>
+      <c r="D39" s="283" t="n"/>
       <c r="E39" s="284" t="inlineStr">
         <is>
-          <t>Concreto para escaleras</t>
+          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado — Estructura</t>
         </is>
       </c>
       <c r="F39" s="285" t="n"/>
@@ -13776,64 +13469,34 @@
       <c r="H39" s="285" t="n"/>
       <c r="I39" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J39" s="1448" t="n"/>
-      <c r="K39" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J39" s="1469" t="n"/>
+      <c r="K39" s="1438" t="n"/>
+      <c r="L39" s="1438" t="n"/>
+      <c r="M39" s="1438" t="n"/>
+      <c r="N39" s="1438" t="n"/>
+      <c r="O39" s="1438" t="n"/>
+      <c r="P39" s="1438" t="n"/>
+      <c r="Q39" s="1438" t="n"/>
+      <c r="R39" s="1438" t="n"/>
+      <c r="S39" s="1303" t="n"/>
       <c r="T39" s="1438">
         <f>IF(I39="","",ROUND(IF(OR(I39="m²",I39="m2"),K39*IF(L39=0,1,L39)*IF(O39=0,1,O39)*IF(P39=0,1,P39)*Q39-R39,IF(OR(I39="m³",I39="m3"),K39*L39*M39*IF(O39=0,1,O39)*IF(P39=0,1,P39)*Q39-R39,IF(OR(I39="ml",I39="ML"),K39*IF(O39=0,1,O39)*IF(P39=0,1,P39)*Q39-R39,IF(OR(I39="und",I39="UND"),IF(O39=0,1,O39)*IF(P39=0,1,P39)*Q39-R39,IF(I39="kg",K39*IF(O39=0,1,O39)*IF(P39=0,1,P39)*Q39-R39,IF(OR(I39="gl",I39="GL",I39="gb",I39="GB",I39="Gl",I39="Gb"),IF(O39=0,1,O39)*IF(P39=0,1,P39)*Q39-R39,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U39" s="1438">
-        <f>IF(T39="","",ROUND(T39*(1+S39),3))</f>
-        <v/>
-      </c>
-      <c r="V39" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U39" s="1438" t="n"/>
+      <c r="V39" s="283" t="n"/>
       <c r="W39" s="285" t="n"/>
       <c r="X39" s="285" t="n"/>
-      <c r="Y39" s="1448" t="n"/>
+      <c r="Y39" s="1469" t="n"/>
       <c r="Z39" s="1304" t="n"/>
-      <c r="AA39" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="40">
       <c r="A40" s="280" t="inlineStr">
         <is>
-          <t>MQ-032</t>
+          <t>MQ-021</t>
         </is>
       </c>
       <c r="B40" s="281" t="inlineStr">
@@ -13841,19 +13504,11 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C40" s="282" t="inlineStr">
-        <is>
-          <t>Concreto</t>
-        </is>
-      </c>
-      <c r="D40" s="283" t="inlineStr">
-        <is>
-          <t>04.01.05</t>
-        </is>
-      </c>
+      <c r="C40" s="282" t="n"/>
+      <c r="D40" s="283" t="n"/>
       <c r="E40" s="284" t="inlineStr">
         <is>
-          <t>Concreto para muros estructurales</t>
+          <t>Concreto de f'c = 420 kg/cm² (6000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="F40" s="285" t="n"/>
@@ -13861,64 +13516,34 @@
       <c r="H40" s="285" t="n"/>
       <c r="I40" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J40" s="1448" t="n"/>
-      <c r="K40" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1303" t="n">
-        <v>0</v>
-      </c>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="J40" s="1469" t="n"/>
+      <c r="K40" s="1438" t="n"/>
+      <c r="L40" s="1438" t="n"/>
+      <c r="M40" s="1438" t="n"/>
+      <c r="N40" s="1438" t="n"/>
+      <c r="O40" s="1438" t="n"/>
+      <c r="P40" s="1438" t="n"/>
+      <c r="Q40" s="1438" t="n"/>
+      <c r="R40" s="1438" t="n"/>
+      <c r="S40" s="1303" t="n"/>
       <c r="T40" s="1438">
         <f>IF(I40="","",ROUND(IF(OR(I40="m²",I40="m2"),K40*IF(L40=0,1,L40)*IF(O40=0,1,O40)*IF(P40=0,1,P40)*Q40-R40,IF(OR(I40="m³",I40="m3"),K40*L40*M40*IF(O40=0,1,O40)*IF(P40=0,1,P40)*Q40-R40,IF(OR(I40="ml",I40="ML"),K40*IF(O40=0,1,O40)*IF(P40=0,1,P40)*Q40-R40,IF(OR(I40="und",I40="UND"),IF(O40=0,1,O40)*IF(P40=0,1,P40)*Q40-R40,IF(I40="kg",K40*IF(O40=0,1,O40)*IF(P40=0,1,P40)*Q40-R40,IF(OR(I40="gl",I40="GL",I40="gb",I40="GB",I40="Gl",I40="Gb"),IF(O40=0,1,O40)*IF(P40=0,1,P40)*Q40-R40,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U40" s="1438">
-        <f>IF(T40="","",ROUND(T40*(1+S40),3))</f>
-        <v/>
-      </c>
-      <c r="V40" s="283" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="U40" s="1438" t="n"/>
+      <c r="V40" s="283" t="n"/>
       <c r="W40" s="285" t="n"/>
       <c r="X40" s="285" t="n"/>
-      <c r="Y40" s="1448" t="n"/>
+      <c r="Y40" s="1469" t="n"/>
       <c r="Z40" s="1304" t="n"/>
-      <c r="AA40" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="41">
       <c r="A41" s="280" t="inlineStr">
         <is>
-          <t>MQ-033</t>
+          <t>MQ-022</t>
         </is>
       </c>
       <c r="B41" s="281" t="inlineStr">
@@ -13926,19 +13551,11 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C41" s="282" t="inlineStr">
-        <is>
-          <t>Acero</t>
-        </is>
-      </c>
-      <c r="D41" s="283" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
+      <c r="C41" s="282" t="n"/>
+      <c r="D41" s="283" t="n"/>
       <c r="E41" s="284" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de columnas</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI — Estructura</t>
         </is>
       </c>
       <c r="F41" s="285" t="n"/>
@@ -13949,61 +13566,31 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="J41" s="1448" t="n"/>
-      <c r="K41" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="1303" t="n">
-        <v>0</v>
-      </c>
+      <c r="J41" s="1469" t="n"/>
+      <c r="K41" s="1438" t="n"/>
+      <c r="L41" s="1438" t="n"/>
+      <c r="M41" s="1438" t="n"/>
+      <c r="N41" s="1438" t="n"/>
+      <c r="O41" s="1438" t="n"/>
+      <c r="P41" s="1438" t="n"/>
+      <c r="Q41" s="1438" t="n"/>
+      <c r="R41" s="1438" t="n"/>
+      <c r="S41" s="1303" t="n"/>
       <c r="T41" s="1438">
         <f>IF(I41="","",ROUND(IF(OR(I41="m²",I41="m2"),K41*IF(L41=0,1,L41)*IF(O41=0,1,O41)*IF(P41=0,1,P41)*Q41-R41,IF(OR(I41="m³",I41="m3"),K41*L41*M41*IF(O41=0,1,O41)*IF(P41=0,1,P41)*Q41-R41,IF(OR(I41="ml",I41="ML"),K41*IF(O41=0,1,O41)*IF(P41=0,1,P41)*Q41-R41,IF(OR(I41="und",I41="UND"),IF(O41=0,1,O41)*IF(P41=0,1,P41)*Q41-R41,IF(I41="kg",K41*IF(O41=0,1,O41)*IF(P41=0,1,P41)*Q41-R41,IF(OR(I41="gl",I41="GL",I41="gb",I41="GB",I41="Gl",I41="Gb"),IF(O41=0,1,O41)*IF(P41=0,1,P41)*Q41-R41,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U41" s="1438">
-        <f>IF(T41="","",ROUND(T41*(1+S41),3))</f>
-        <v/>
-      </c>
-      <c r="V41" s="283" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="U41" s="1438" t="n"/>
+      <c r="V41" s="283" t="n"/>
       <c r="W41" s="285" t="n"/>
       <c r="X41" s="285" t="n"/>
-      <c r="Y41" s="1448" t="n"/>
+      <c r="Y41" s="1469" t="n"/>
       <c r="Z41" s="1304" t="n"/>
-      <c r="AA41" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="42">
       <c r="A42" s="280" t="inlineStr">
         <is>
-          <t>MQ-034</t>
+          <t>MQ-023</t>
         </is>
       </c>
       <c r="B42" s="281" t="inlineStr">
@@ -14011,19 +13598,11 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C42" s="282" t="inlineStr">
-        <is>
-          <t>Acero</t>
-        </is>
-      </c>
-      <c r="D42" s="283" t="inlineStr">
-        <is>
-          <t>04.02.02</t>
-        </is>
-      </c>
+      <c r="C42" s="282" t="n"/>
+      <c r="D42" s="283" t="n"/>
       <c r="E42" s="284" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de vigas</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI — Estructura</t>
         </is>
       </c>
       <c r="F42" s="285" t="n"/>
@@ -14034,61 +13613,31 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="J42" s="1448" t="n"/>
-      <c r="K42" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="1303" t="n">
-        <v>0</v>
-      </c>
+      <c r="J42" s="1469" t="n"/>
+      <c r="K42" s="1438" t="n"/>
+      <c r="L42" s="1438" t="n"/>
+      <c r="M42" s="1438" t="n"/>
+      <c r="N42" s="1438" t="n"/>
+      <c r="O42" s="1438" t="n"/>
+      <c r="P42" s="1438" t="n"/>
+      <c r="Q42" s="1438" t="n"/>
+      <c r="R42" s="1438" t="n"/>
+      <c r="S42" s="1303" t="n"/>
       <c r="T42" s="1438">
         <f>IF(I42="","",ROUND(IF(OR(I42="m²",I42="m2"),K42*IF(L42=0,1,L42)*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="m³",I42="m3"),K42*L42*M42*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="ml",I42="ML"),K42*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="und",I42="UND"),IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(I42="kg",K42*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="gl",I42="GL",I42="gb",I42="GB",I42="Gl",I42="Gb"),IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U42" s="1438">
-        <f>IF(T42="","",ROUND(T42*(1+S42),3))</f>
-        <v/>
-      </c>
-      <c r="V42" s="283" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="U42" s="1438" t="n"/>
+      <c r="V42" s="283" t="n"/>
       <c r="W42" s="285" t="n"/>
       <c r="X42" s="285" t="n"/>
-      <c r="Y42" s="1448" t="n"/>
+      <c r="Y42" s="1469" t="n"/>
       <c r="Z42" s="1304" t="n"/>
-      <c r="AA42" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
     </row>
     <row r="43" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A43" s="280" t="inlineStr">
         <is>
-          <t>MQ-035</t>
+          <t>MQ-036</t>
         </is>
       </c>
       <c r="B43" s="281" t="inlineStr">
@@ -14098,17 +13647,17 @@
       </c>
       <c r="C43" s="282" t="inlineStr">
         <is>
-          <t>Acero</t>
+          <t>Formaleta</t>
         </is>
       </c>
       <c r="D43" s="283" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E43" s="284" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de losas</t>
+          <t>Formaleta de columnas</t>
         </is>
       </c>
       <c r="F43" s="285" t="n"/>
@@ -14116,10 +13665,10 @@
       <c r="H43" s="285" t="n"/>
       <c r="I43" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="J43" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J43" s="1469" t="n"/>
       <c r="K43" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14157,12 +13706,12 @@
       </c>
       <c r="V43" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W43" s="285" t="n"/>
       <c r="X43" s="285" t="n"/>
-      <c r="Y43" s="1448" t="n"/>
+      <c r="Y43" s="1469" t="n"/>
       <c r="Z43" s="1304" t="n"/>
       <c r="AA43" s="285" t="inlineStr">
         <is>
@@ -14173,7 +13722,7 @@
     <row r="44" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A44" s="280" t="inlineStr">
         <is>
-          <t>MQ-036</t>
+          <t>MQ-037</t>
         </is>
       </c>
       <c r="B44" s="281" t="inlineStr">
@@ -14188,12 +13737,12 @@
       </c>
       <c r="D44" s="283" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="E44" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de columnas</t>
+          <t>Formaleta de vigas</t>
         </is>
       </c>
       <c r="F44" s="285" t="n"/>
@@ -14204,7 +13753,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J44" s="1448" t="n"/>
+      <c r="J44" s="1469" t="n"/>
       <c r="K44" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14247,7 +13796,7 @@
       </c>
       <c r="W44" s="285" t="n"/>
       <c r="X44" s="285" t="n"/>
-      <c r="Y44" s="1448" t="n"/>
+      <c r="Y44" s="1469" t="n"/>
       <c r="Z44" s="1304" t="n"/>
       <c r="AA44" s="285" t="inlineStr">
         <is>
@@ -14258,7 +13807,7 @@
     <row r="45" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A45" s="280" t="inlineStr">
         <is>
-          <t>MQ-037</t>
+          <t>MQ-038</t>
         </is>
       </c>
       <c r="B45" s="281" t="inlineStr">
@@ -14273,12 +13822,12 @@
       </c>
       <c r="D45" s="283" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="E45" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de vigas</t>
+          <t>Formaleta de losas</t>
         </is>
       </c>
       <c r="F45" s="285" t="n"/>
@@ -14289,7 +13838,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J45" s="1448" t="n"/>
+      <c r="J45" s="1469" t="n"/>
       <c r="K45" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14332,7 +13881,7 @@
       </c>
       <c r="W45" s="285" t="n"/>
       <c r="X45" s="285" t="n"/>
-      <c r="Y45" s="1448" t="n"/>
+      <c r="Y45" s="1469" t="n"/>
       <c r="Z45" s="1304" t="n"/>
       <c r="AA45" s="285" t="inlineStr">
         <is>
@@ -14343,7 +13892,7 @@
     <row r="46" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A46" s="280" t="inlineStr">
         <is>
-          <t>MQ-038</t>
+          <t>MQ-039</t>
         </is>
       </c>
       <c r="B46" s="281" t="inlineStr">
@@ -14358,12 +13907,12 @@
       </c>
       <c r="D46" s="283" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="E46" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de losas</t>
+          <t>Formaleta de escaleras</t>
         </is>
       </c>
       <c r="F46" s="285" t="n"/>
@@ -14374,7 +13923,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J46" s="1448" t="n"/>
+      <c r="J46" s="1469" t="n"/>
       <c r="K46" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14417,7 +13966,7 @@
       </c>
       <c r="W46" s="285" t="n"/>
       <c r="X46" s="285" t="n"/>
-      <c r="Y46" s="1448" t="n"/>
+      <c r="Y46" s="1469" t="n"/>
       <c r="Z46" s="1304" t="n"/>
       <c r="AA46" s="285" t="inlineStr">
         <is>
@@ -14428,7 +13977,7 @@
     <row r="47" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A47" s="280" t="inlineStr">
         <is>
-          <t>MQ-039</t>
+          <t>MQ-040</t>
         </is>
       </c>
       <c r="B47" s="281" t="inlineStr">
@@ -14438,17 +13987,17 @@
       </c>
       <c r="C47" s="282" t="inlineStr">
         <is>
-          <t>Formaleta</t>
+          <t>Estructura metálica</t>
         </is>
       </c>
       <c r="D47" s="283" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E47" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de escaleras</t>
+          <t>Suministro y montaje de perfiles metálicos</t>
         </is>
       </c>
       <c r="F47" s="285" t="n"/>
@@ -14456,10 +14005,10 @@
       <c r="H47" s="285" t="n"/>
       <c r="I47" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J47" s="1448" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="J47" s="1469" t="n"/>
       <c r="K47" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14497,12 +14046,12 @@
       </c>
       <c r="V47" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W47" s="285" t="n"/>
       <c r="X47" s="285" t="n"/>
-      <c r="Y47" s="1448" t="n"/>
+      <c r="Y47" s="1469" t="n"/>
       <c r="Z47" s="1304" t="n"/>
       <c r="AA47" s="285" t="inlineStr">
         <is>
@@ -14513,7 +14062,7 @@
     <row r="48" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A48" s="280" t="inlineStr">
         <is>
-          <t>MQ-040</t>
+          <t>MQ-041</t>
         </is>
       </c>
       <c r="B48" s="281" t="inlineStr">
@@ -14528,12 +14077,12 @@
       </c>
       <c r="D48" s="283" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="E48" s="284" t="inlineStr">
         <is>
-          <t>Suministro y montaje de perfiles metálicos</t>
+          <t>Placas, pernos y conexiones metálicas</t>
         </is>
       </c>
       <c r="F48" s="285" t="n"/>
@@ -14544,7 +14093,7 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="J48" s="1448" t="n"/>
+      <c r="J48" s="1469" t="n"/>
       <c r="K48" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14587,7 +14136,7 @@
       </c>
       <c r="W48" s="285" t="n"/>
       <c r="X48" s="285" t="n"/>
-      <c r="Y48" s="1448" t="n"/>
+      <c r="Y48" s="1469" t="n"/>
       <c r="Z48" s="1304" t="n"/>
       <c r="AA48" s="285" t="inlineStr">
         <is>
@@ -14598,27 +14147,27 @@
     <row r="49" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A49" s="280" t="inlineStr">
         <is>
-          <t>MQ-041</t>
+          <t>MQ-042</t>
         </is>
       </c>
       <c r="B49" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C49" s="282" t="inlineStr">
         <is>
-          <t>Estructura metálica</t>
+          <t>Muros</t>
         </is>
       </c>
       <c r="D49" s="283" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="E49" s="284" t="inlineStr">
         <is>
-          <t>Placas, pernos y conexiones metálicas</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="F49" s="285" t="n"/>
@@ -14626,10 +14175,10 @@
       <c r="H49" s="285" t="n"/>
       <c r="I49" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="J49" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J49" s="1469" t="n"/>
       <c r="K49" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14667,12 +14216,12 @@
       </c>
       <c r="V49" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W49" s="285" t="n"/>
       <c r="X49" s="285" t="n"/>
-      <c r="Y49" s="1448" t="n"/>
+      <c r="Y49" s="1469" t="n"/>
       <c r="Z49" s="1304" t="n"/>
       <c r="AA49" s="285" t="inlineStr">
         <is>
@@ -14683,7 +14232,7 @@
     <row r="50" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A50" s="280" t="inlineStr">
         <is>
-          <t>MQ-042</t>
+          <t>MQ-043</t>
         </is>
       </c>
       <c r="B50" s="281" t="inlineStr">
@@ -14698,12 +14247,12 @@
       </c>
       <c r="D50" s="283" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="E50" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en bloque de concreto</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="F50" s="285" t="n"/>
@@ -14714,7 +14263,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J50" s="1448" t="n"/>
+      <c r="J50" s="1469" t="n"/>
       <c r="K50" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14757,7 +14306,7 @@
       </c>
       <c r="W50" s="285" t="n"/>
       <c r="X50" s="285" t="n"/>
-      <c r="Y50" s="1448" t="n"/>
+      <c r="Y50" s="1469" t="n"/>
       <c r="Z50" s="1304" t="n"/>
       <c r="AA50" s="285" t="inlineStr">
         <is>
@@ -14768,7 +14317,7 @@
     <row r="51" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A51" s="280" t="inlineStr">
         <is>
-          <t>MQ-043</t>
+          <t>MQ-044</t>
         </is>
       </c>
       <c r="B51" s="281" t="inlineStr">
@@ -14783,12 +14332,12 @@
       </c>
       <c r="D51" s="283" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="E51" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="F51" s="285" t="n"/>
@@ -14799,7 +14348,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J51" s="1448" t="n"/>
+      <c r="J51" s="1469" t="n"/>
       <c r="K51" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14842,7 +14391,7 @@
       </c>
       <c r="W51" s="285" t="n"/>
       <c r="X51" s="285" t="n"/>
-      <c r="Y51" s="1448" t="n"/>
+      <c r="Y51" s="1469" t="n"/>
       <c r="Z51" s="1304" t="n"/>
       <c r="AA51" s="285" t="inlineStr">
         <is>
@@ -14853,7 +14402,7 @@
     <row r="52" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A52" s="280" t="inlineStr">
         <is>
-          <t>MQ-044</t>
+          <t>MQ-045</t>
         </is>
       </c>
       <c r="B52" s="281" t="inlineStr">
@@ -14868,12 +14417,12 @@
       </c>
       <c r="D52" s="283" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>05.01.04</t>
         </is>
       </c>
       <c r="E52" s="284" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="F52" s="285" t="n"/>
@@ -14884,7 +14433,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J52" s="1448" t="n"/>
+      <c r="J52" s="1469" t="n"/>
       <c r="K52" s="1438" t="n">
         <v>0</v>
       </c>
@@ -14927,7 +14476,7 @@
       </c>
       <c r="W52" s="285" t="n"/>
       <c r="X52" s="285" t="n"/>
-      <c r="Y52" s="1448" t="n"/>
+      <c r="Y52" s="1469" t="n"/>
       <c r="Z52" s="1304" t="n"/>
       <c r="AA52" s="285" t="inlineStr">
         <is>
@@ -14938,7 +14487,7 @@
     <row r="53" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A53" s="280" t="inlineStr">
         <is>
-          <t>MQ-045</t>
+          <t>MQ-046</t>
         </is>
       </c>
       <c r="B53" s="281" t="inlineStr">
@@ -14948,17 +14497,17 @@
       </c>
       <c r="C53" s="282" t="inlineStr">
         <is>
-          <t>Muros</t>
+          <t>Complementarios</t>
         </is>
       </c>
       <c r="D53" s="283" t="inlineStr">
         <is>
-          <t>05.01.04</t>
+          <t>05.02.01</t>
         </is>
       </c>
       <c r="E53" s="284" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Dinteles sobre vanos</t>
         </is>
       </c>
       <c r="F53" s="285" t="n"/>
@@ -14966,10 +14515,10 @@
       <c r="H53" s="285" t="n"/>
       <c r="I53" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J53" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J53" s="1469" t="n"/>
       <c r="K53" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15007,12 +14556,12 @@
       </c>
       <c r="V53" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W53" s="285" t="n"/>
       <c r="X53" s="285" t="n"/>
-      <c r="Y53" s="1448" t="n"/>
+      <c r="Y53" s="1469" t="n"/>
       <c r="Z53" s="1304" t="n"/>
       <c r="AA53" s="285" t="inlineStr">
         <is>
@@ -15023,7 +14572,7 @@
     <row r="54" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A54" s="280" t="inlineStr">
         <is>
-          <t>MQ-046</t>
+          <t>MQ-047</t>
         </is>
       </c>
       <c r="B54" s="281" t="inlineStr">
@@ -15038,12 +14587,12 @@
       </c>
       <c r="D54" s="283" t="inlineStr">
         <is>
-          <t>05.02.01</t>
+          <t>05.02.02</t>
         </is>
       </c>
       <c r="E54" s="284" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Alfajías y remates</t>
         </is>
       </c>
       <c r="F54" s="285" t="n"/>
@@ -15054,7 +14603,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J54" s="1448" t="n"/>
+      <c r="J54" s="1469" t="n"/>
       <c r="K54" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15097,7 +14646,7 @@
       </c>
       <c r="W54" s="285" t="n"/>
       <c r="X54" s="285" t="n"/>
-      <c r="Y54" s="1448" t="n"/>
+      <c r="Y54" s="1469" t="n"/>
       <c r="Z54" s="1304" t="n"/>
       <c r="AA54" s="285" t="inlineStr">
         <is>
@@ -15108,7 +14657,7 @@
     <row r="55" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A55" s="280" t="inlineStr">
         <is>
-          <t>MQ-047</t>
+          <t>MQ-048</t>
         </is>
       </c>
       <c r="B55" s="281" t="inlineStr">
@@ -15123,12 +14672,12 @@
       </c>
       <c r="D55" s="283" t="inlineStr">
         <is>
-          <t>05.02.02</t>
+          <t>05.02.03</t>
         </is>
       </c>
       <c r="E55" s="284" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="F55" s="285" t="n"/>
@@ -15136,10 +14685,10 @@
       <c r="H55" s="285" t="n"/>
       <c r="I55" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J55" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J55" s="1469" t="n"/>
       <c r="K55" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15177,12 +14726,12 @@
       </c>
       <c r="V55" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W55" s="285" t="n"/>
       <c r="X55" s="285" t="n"/>
-      <c r="Y55" s="1448" t="n"/>
+      <c r="Y55" s="1469" t="n"/>
       <c r="Z55" s="1304" t="n"/>
       <c r="AA55" s="285" t="inlineStr">
         <is>
@@ -15193,27 +14742,27 @@
     <row r="56" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A56" s="280" t="inlineStr">
         <is>
-          <t>MQ-048</t>
+          <t>MQ-049</t>
         </is>
       </c>
       <c r="B56" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C56" s="282" t="inlineStr">
         <is>
-          <t>Complementarios</t>
+          <t>Estructura</t>
         </is>
       </c>
       <c r="D56" s="283" t="inlineStr">
         <is>
-          <t>05.02.03</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="E56" s="284" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="F56" s="285" t="n"/>
@@ -15221,10 +14770,10 @@
       <c r="H56" s="285" t="n"/>
       <c r="I56" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J56" s="1448" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="J56" s="1469" t="n"/>
       <c r="K56" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15262,12 +14811,12 @@
       </c>
       <c r="V56" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W56" s="285" t="n"/>
       <c r="X56" s="285" t="n"/>
-      <c r="Y56" s="1448" t="n"/>
+      <c r="Y56" s="1469" t="n"/>
       <c r="Z56" s="1304" t="n"/>
       <c r="AA56" s="285" t="inlineStr">
         <is>
@@ -15278,7 +14827,7 @@
     <row r="57" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A57" s="280" t="inlineStr">
         <is>
-          <t>MQ-049</t>
+          <t>MQ-050</t>
         </is>
       </c>
       <c r="B57" s="281" t="inlineStr">
@@ -15293,12 +14842,12 @@
       </c>
       <c r="D57" s="283" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="E57" s="284" t="inlineStr">
         <is>
-          <t>Estructura metálica o de madera para cubierta</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="F57" s="285" t="n"/>
@@ -15309,7 +14858,7 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="J57" s="1448" t="n"/>
+      <c r="J57" s="1469" t="n"/>
       <c r="K57" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15352,7 +14901,7 @@
       </c>
       <c r="W57" s="285" t="n"/>
       <c r="X57" s="285" t="n"/>
-      <c r="Y57" s="1448" t="n"/>
+      <c r="Y57" s="1469" t="n"/>
       <c r="Z57" s="1304" t="n"/>
       <c r="AA57" s="285" t="inlineStr">
         <is>
@@ -15363,7 +14912,7 @@
     <row r="58" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A58" s="280" t="inlineStr">
         <is>
-          <t>MQ-050</t>
+          <t>MQ-051</t>
         </is>
       </c>
       <c r="B58" s="281" t="inlineStr">
@@ -15373,17 +14922,17 @@
       </c>
       <c r="C58" s="282" t="inlineStr">
         <is>
-          <t>Estructura</t>
+          <t>Cubierta</t>
         </is>
       </c>
       <c r="D58" s="283" t="inlineStr">
         <is>
-          <t>06.01.02</t>
+          <t>06.02.01</t>
         </is>
       </c>
       <c r="E58" s="284" t="inlineStr">
         <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="F58" s="285" t="n"/>
@@ -15391,10 +14940,10 @@
       <c r="H58" s="285" t="n"/>
       <c r="I58" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="J58" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J58" s="1469" t="n"/>
       <c r="K58" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15432,12 +14981,12 @@
       </c>
       <c r="V58" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W58" s="285" t="n"/>
       <c r="X58" s="285" t="n"/>
-      <c r="Y58" s="1448" t="n"/>
+      <c r="Y58" s="1469" t="n"/>
       <c r="Z58" s="1304" t="n"/>
       <c r="AA58" s="285" t="inlineStr">
         <is>
@@ -15448,7 +14997,7 @@
     <row r="59" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A59" s="280" t="inlineStr">
         <is>
-          <t>MQ-051</t>
+          <t>MQ-052</t>
         </is>
       </c>
       <c r="B59" s="281" t="inlineStr">
@@ -15463,12 +15012,12 @@
       </c>
       <c r="D59" s="283" t="inlineStr">
         <is>
-          <t>06.02.01</t>
+          <t>06.02.02</t>
         </is>
       </c>
       <c r="E59" s="284" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Impermeabilización de cubierta</t>
         </is>
       </c>
       <c r="F59" s="285" t="n"/>
@@ -15479,7 +15028,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J59" s="1448" t="n"/>
+      <c r="J59" s="1469" t="n"/>
       <c r="K59" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15522,7 +15071,7 @@
       </c>
       <c r="W59" s="285" t="n"/>
       <c r="X59" s="285" t="n"/>
-      <c r="Y59" s="1448" t="n"/>
+      <c r="Y59" s="1469" t="n"/>
       <c r="Z59" s="1304" t="n"/>
       <c r="AA59" s="285" t="inlineStr">
         <is>
@@ -15533,7 +15082,7 @@
     <row r="60" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A60" s="280" t="inlineStr">
         <is>
-          <t>MQ-052</t>
+          <t>MQ-053</t>
         </is>
       </c>
       <c r="B60" s="281" t="inlineStr">
@@ -15548,12 +15097,12 @@
       </c>
       <c r="D60" s="283" t="inlineStr">
         <is>
-          <t>06.02.02</t>
+          <t>06.02.03</t>
         </is>
       </c>
       <c r="E60" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de cubierta</t>
+          <t>Aislamiento térmico/acústico</t>
         </is>
       </c>
       <c r="F60" s="285" t="n"/>
@@ -15564,7 +15113,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J60" s="1448" t="n"/>
+      <c r="J60" s="1469" t="n"/>
       <c r="K60" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15607,7 +15156,7 @@
       </c>
       <c r="W60" s="285" t="n"/>
       <c r="X60" s="285" t="n"/>
-      <c r="Y60" s="1448" t="n"/>
+      <c r="Y60" s="1469" t="n"/>
       <c r="Z60" s="1304" t="n"/>
       <c r="AA60" s="285" t="inlineStr">
         <is>
@@ -15618,7 +15167,7 @@
     <row r="61" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A61" s="280" t="inlineStr">
         <is>
-          <t>MQ-053</t>
+          <t>MQ-054</t>
         </is>
       </c>
       <c r="B61" s="281" t="inlineStr">
@@ -15628,17 +15177,17 @@
       </c>
       <c r="C61" s="282" t="inlineStr">
         <is>
-          <t>Cubierta</t>
+          <t>Canales</t>
         </is>
       </c>
       <c r="D61" s="283" t="inlineStr">
         <is>
-          <t>06.02.03</t>
+          <t>06.03.01</t>
         </is>
       </c>
       <c r="E61" s="284" t="inlineStr">
         <is>
-          <t>Aislamiento térmico/acústico</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="F61" s="285" t="n"/>
@@ -15646,10 +15195,10 @@
       <c r="H61" s="285" t="n"/>
       <c r="I61" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J61" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J61" s="1469" t="n"/>
       <c r="K61" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15687,12 +15236,12 @@
       </c>
       <c r="V61" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W61" s="285" t="n"/>
       <c r="X61" s="285" t="n"/>
-      <c r="Y61" s="1448" t="n"/>
+      <c r="Y61" s="1469" t="n"/>
       <c r="Z61" s="1304" t="n"/>
       <c r="AA61" s="285" t="inlineStr">
         <is>
@@ -15703,7 +15252,7 @@
     <row r="62" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A62" s="280" t="inlineStr">
         <is>
-          <t>MQ-054</t>
+          <t>MQ-055</t>
         </is>
       </c>
       <c r="B62" s="281" t="inlineStr">
@@ -15718,12 +15267,12 @@
       </c>
       <c r="D62" s="283" t="inlineStr">
         <is>
-          <t>06.03.01</t>
+          <t>06.03.02</t>
         </is>
       </c>
       <c r="E62" s="284" t="inlineStr">
         <is>
-          <t>Canales de aguas lluvias</t>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="F62" s="285" t="n"/>
@@ -15734,7 +15283,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J62" s="1448" t="n"/>
+      <c r="J62" s="1469" t="n"/>
       <c r="K62" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15777,7 +15326,7 @@
       </c>
       <c r="W62" s="285" t="n"/>
       <c r="X62" s="285" t="n"/>
-      <c r="Y62" s="1448" t="n"/>
+      <c r="Y62" s="1469" t="n"/>
       <c r="Z62" s="1304" t="n"/>
       <c r="AA62" s="285" t="inlineStr">
         <is>
@@ -15788,27 +15337,27 @@
     <row r="63" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A63" s="280" t="inlineStr">
         <is>
-          <t>MQ-055</t>
+          <t>MQ-056</t>
         </is>
       </c>
       <c r="B63" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C63" s="282" t="inlineStr">
         <is>
-          <t>Canales</t>
+          <t>Superficies</t>
         </is>
       </c>
       <c r="D63" s="283" t="inlineStr">
         <is>
-          <t>06.03.02</t>
+          <t>07.01.01</t>
         </is>
       </c>
       <c r="E63" s="284" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="F63" s="285" t="n"/>
@@ -15816,10 +15365,10 @@
       <c r="H63" s="285" t="n"/>
       <c r="I63" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J63" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J63" s="1469" t="n"/>
       <c r="K63" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15857,12 +15406,12 @@
       </c>
       <c r="V63" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W63" s="285" t="n"/>
       <c r="X63" s="285" t="n"/>
-      <c r="Y63" s="1448" t="n"/>
+      <c r="Y63" s="1469" t="n"/>
       <c r="Z63" s="1304" t="n"/>
       <c r="AA63" s="285" t="inlineStr">
         <is>
@@ -15873,7 +15422,7 @@
     <row r="64" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A64" s="280" t="inlineStr">
         <is>
-          <t>MQ-056</t>
+          <t>MQ-057</t>
         </is>
       </c>
       <c r="B64" s="281" t="inlineStr">
@@ -15888,12 +15437,12 @@
       </c>
       <c r="D64" s="283" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="E64" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de losas y terrazas</t>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="F64" s="285" t="n"/>
@@ -15904,7 +15453,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J64" s="1448" t="n"/>
+      <c r="J64" s="1469" t="n"/>
       <c r="K64" s="1438" t="n">
         <v>0</v>
       </c>
@@ -15947,7 +15496,7 @@
       </c>
       <c r="W64" s="285" t="n"/>
       <c r="X64" s="285" t="n"/>
-      <c r="Y64" s="1448" t="n"/>
+      <c r="Y64" s="1469" t="n"/>
       <c r="Z64" s="1304" t="n"/>
       <c r="AA64" s="285" t="inlineStr">
         <is>
@@ -15958,7 +15507,7 @@
     <row r="65" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A65" s="280" t="inlineStr">
         <is>
-          <t>MQ-057</t>
+          <t>MQ-058</t>
         </is>
       </c>
       <c r="B65" s="281" t="inlineStr">
@@ -15973,12 +15522,12 @@
       </c>
       <c r="D65" s="283" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="E65" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de muros</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="F65" s="285" t="n"/>
@@ -15989,7 +15538,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J65" s="1448" t="n"/>
+      <c r="J65" s="1469" t="n"/>
       <c r="K65" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16032,7 +15581,7 @@
       </c>
       <c r="W65" s="285" t="n"/>
       <c r="X65" s="285" t="n"/>
-      <c r="Y65" s="1448" t="n"/>
+      <c r="Y65" s="1469" t="n"/>
       <c r="Z65" s="1304" t="n"/>
       <c r="AA65" s="285" t="inlineStr">
         <is>
@@ -16043,27 +15592,27 @@
     <row r="66" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A66" s="280" t="inlineStr">
         <is>
-          <t>MQ-058</t>
+          <t>MQ-059</t>
         </is>
       </c>
       <c r="B66" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
+          <t>PAÑETES Y REVOQUES</t>
         </is>
       </c>
       <c r="C66" s="282" t="inlineStr">
         <is>
-          <t>Superficies</t>
+          <t>Pañetes</t>
         </is>
       </c>
       <c r="D66" s="283" t="inlineStr">
         <is>
-          <t>07.01.03</t>
+          <t>08.01.01</t>
         </is>
       </c>
       <c r="E66" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="F66" s="285" t="n"/>
@@ -16074,7 +15623,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J66" s="1448" t="n"/>
+      <c r="J66" s="1469" t="n"/>
       <c r="K66" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16117,7 +15666,7 @@
       </c>
       <c r="W66" s="285" t="n"/>
       <c r="X66" s="285" t="n"/>
-      <c r="Y66" s="1448" t="n"/>
+      <c r="Y66" s="1469" t="n"/>
       <c r="Z66" s="1304" t="n"/>
       <c r="AA66" s="285" t="inlineStr">
         <is>
@@ -16128,7 +15677,7 @@
     <row r="67" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A67" s="280" t="inlineStr">
         <is>
-          <t>MQ-059</t>
+          <t>MQ-060</t>
         </is>
       </c>
       <c r="B67" s="281" t="inlineStr">
@@ -16143,12 +15692,12 @@
       </c>
       <c r="D67" s="283" t="inlineStr">
         <is>
-          <t>08.01.01</t>
+          <t>08.01.02</t>
         </is>
       </c>
       <c r="E67" s="284" t="inlineStr">
         <is>
-          <t>Pañete / revoque interior</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="F67" s="285" t="n"/>
@@ -16159,7 +15708,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J67" s="1448" t="n"/>
+      <c r="J67" s="1469" t="n"/>
       <c r="K67" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16202,7 +15751,7 @@
       </c>
       <c r="W67" s="285" t="n"/>
       <c r="X67" s="285" t="n"/>
-      <c r="Y67" s="1448" t="n"/>
+      <c r="Y67" s="1469" t="n"/>
       <c r="Z67" s="1304" t="n"/>
       <c r="AA67" s="285" t="inlineStr">
         <is>
@@ -16213,7 +15762,7 @@
     <row r="68" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A68" s="280" t="inlineStr">
         <is>
-          <t>MQ-060</t>
+          <t>MQ-061</t>
         </is>
       </c>
       <c r="B68" s="281" t="inlineStr">
@@ -16228,12 +15777,12 @@
       </c>
       <c r="D68" s="283" t="inlineStr">
         <is>
-          <t>08.01.02</t>
+          <t>08.01.03</t>
         </is>
       </c>
       <c r="E68" s="284" t="inlineStr">
         <is>
-          <t>Pañete / revoque exterior</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="F68" s="285" t="n"/>
@@ -16244,7 +15793,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J68" s="1448" t="n"/>
+      <c r="J68" s="1469" t="n"/>
       <c r="K68" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16287,7 +15836,7 @@
       </c>
       <c r="W68" s="285" t="n"/>
       <c r="X68" s="285" t="n"/>
-      <c r="Y68" s="1448" t="n"/>
+      <c r="Y68" s="1469" t="n"/>
       <c r="Z68" s="1304" t="n"/>
       <c r="AA68" s="285" t="inlineStr">
         <is>
@@ -16298,12 +15847,12 @@
     <row r="69" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A69" s="280" t="inlineStr">
         <is>
-          <t>MQ-061</t>
+          <t>MQ-062</t>
         </is>
       </c>
       <c r="B69" s="281" t="inlineStr">
         <is>
-          <t>PAÑETES Y REVOQUES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C69" s="282" t="inlineStr">
@@ -16313,12 +15862,12 @@
       </c>
       <c r="D69" s="283" t="inlineStr">
         <is>
-          <t>08.01.03</t>
+          <t>08.01.04</t>
         </is>
       </c>
       <c r="E69" s="284" t="inlineStr">
         <is>
-          <t>Pañete impermeabilizado</t>
+          <t>Estuco plástico</t>
         </is>
       </c>
       <c r="F69" s="285" t="n"/>
@@ -16329,7 +15878,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J69" s="1448" t="n"/>
+      <c r="J69" s="1469" t="n"/>
       <c r="K69" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16372,7 +15921,7 @@
       </c>
       <c r="W69" s="285" t="n"/>
       <c r="X69" s="285" t="n"/>
-      <c r="Y69" s="1448" t="n"/>
+      <c r="Y69" s="1469" t="n"/>
       <c r="Z69" s="1304" t="n"/>
       <c r="AA69" s="285" t="inlineStr">
         <is>
@@ -16380,10 +15929,10 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="70">
       <c r="A70" s="280" t="inlineStr">
         <is>
-          <t>MQ-062</t>
+          <t>MQ-062B</t>
         </is>
       </c>
       <c r="B70" s="281" t="inlineStr">
@@ -16391,19 +15940,11 @@
           <t>PINTURA</t>
         </is>
       </c>
-      <c r="C70" s="282" t="inlineStr">
-        <is>
-          <t>Pañetes</t>
-        </is>
-      </c>
-      <c r="D70" s="283" t="inlineStr">
-        <is>
-          <t>08.01.04</t>
-        </is>
-      </c>
+      <c r="C70" s="282" t="n"/>
+      <c r="D70" s="283" t="n"/>
       <c r="E70" s="284" t="inlineStr">
         <is>
-          <t>Estuco plástico</t>
+          <t>Estuco tradicional</t>
         </is>
       </c>
       <c r="F70" s="285" t="n"/>
@@ -16414,73 +15955,31 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J70" s="1448" t="n"/>
-      <c r="K70" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="1438">
-        <f>IF(I70="","",ROUND(IF(OR(I70="m²",I70="m2"),K70*IF(L70=0,1,L70)*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="m³",I70="m3"),K70*L70*M70*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="ml",I70="ML"),K70*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="und",I70="UND"),IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(I70="kg",K70*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="gl",I70="GL",I70="gb",I70="GB",I70="Gl",I70="Gb"),IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="U70" s="1438">
-        <f>IF(T70="","",ROUND(T70*(1+S70),3))</f>
-        <v/>
-      </c>
-      <c r="V70" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="W70" s="285" t="n"/>
-      <c r="X70" s="285" t="n"/>
-      <c r="Y70" s="1448" t="n"/>
-      <c r="Z70" s="1304" t="n"/>
-      <c r="AA70" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A71" s="280" t="inlineStr">
         <is>
-          <t>MQ-062B</t>
+          <t>MQ-063</t>
         </is>
       </c>
       <c r="B71" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="C71" s="282" t="n"/>
-      <c r="D71" s="283" t="n"/>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C71" s="282" t="inlineStr">
+        <is>
+          <t>Pisos</t>
+        </is>
+      </c>
+      <c r="D71" s="283" t="inlineStr">
+        <is>
+          <t>09.01.01</t>
+        </is>
+      </c>
       <c r="E71" s="284" t="inlineStr">
         <is>
-          <t>Estuco tradicional</t>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="F71" s="285" t="n"/>
@@ -16491,11 +15990,61 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J71" s="1469" t="n"/>
+      <c r="K71" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="1438">
+        <f>IF(I71="","",ROUND(IF(OR(I71="m²",I71="m2"),K71*IF(L71=0,1,L71)*IF(O71=0,1,O71)*IF(P71=0,1,P71)*Q71-R71,IF(OR(I71="m³",I71="m3"),K71*L71*M71*IF(O71=0,1,O71)*IF(P71=0,1,P71)*Q71-R71,IF(OR(I71="ml",I71="ML"),K71*IF(O71=0,1,O71)*IF(P71=0,1,P71)*Q71-R71,IF(OR(I71="und",I71="UND"),IF(O71=0,1,O71)*IF(P71=0,1,P71)*Q71-R71,IF(I71="kg",K71*IF(O71=0,1,O71)*IF(P71=0,1,P71)*Q71-R71,IF(OR(I71="gl",I71="GL",I71="gb",I71="GB",I71="Gl",I71="Gb"),IF(O71=0,1,O71)*IF(P71=0,1,P71)*Q71-R71,0)))))),3))</f>
+        <v/>
+      </c>
+      <c r="U71" s="1438">
+        <f>IF(T71="","",ROUND(T71*(1+S71),3))</f>
+        <v/>
+      </c>
+      <c r="V71" s="283" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="W71" s="285" t="n"/>
+      <c r="X71" s="285" t="n"/>
+      <c r="Y71" s="1469" t="n"/>
+      <c r="Z71" s="1304" t="n"/>
+      <c r="AA71" s="285" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A72" s="280" t="inlineStr">
         <is>
-          <t>MQ-063</t>
+          <t>MQ-064</t>
         </is>
       </c>
       <c r="B72" s="281" t="inlineStr">
@@ -16510,12 +16059,12 @@
       </c>
       <c r="D72" s="283" t="inlineStr">
         <is>
-          <t>09.01.01</t>
+          <t>09.01.02</t>
         </is>
       </c>
       <c r="E72" s="284" t="inlineStr">
         <is>
-          <t>Mortero de nivelación</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="F72" s="285" t="n"/>
@@ -16526,7 +16075,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J72" s="1448" t="n"/>
+      <c r="J72" s="1469" t="n"/>
       <c r="K72" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16569,7 +16118,7 @@
       </c>
       <c r="W72" s="285" t="n"/>
       <c r="X72" s="285" t="n"/>
-      <c r="Y72" s="1448" t="n"/>
+      <c r="Y72" s="1469" t="n"/>
       <c r="Z72" s="1304" t="n"/>
       <c r="AA72" s="285" t="inlineStr">
         <is>
@@ -16580,7 +16129,7 @@
     <row r="73" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A73" s="280" t="inlineStr">
         <is>
-          <t>MQ-064</t>
+          <t>MQ-065</t>
         </is>
       </c>
       <c r="B73" s="281" t="inlineStr">
@@ -16595,12 +16144,12 @@
       </c>
       <c r="D73" s="283" t="inlineStr">
         <is>
-          <t>09.01.02</t>
+          <t>09.01.03</t>
         </is>
       </c>
       <c r="E73" s="284" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="F73" s="285" t="n"/>
@@ -16611,7 +16160,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J73" s="1448" t="n"/>
+      <c r="J73" s="1469" t="n"/>
       <c r="K73" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16654,7 +16203,7 @@
       </c>
       <c r="W73" s="285" t="n"/>
       <c r="X73" s="285" t="n"/>
-      <c r="Y73" s="1448" t="n"/>
+      <c r="Y73" s="1469" t="n"/>
       <c r="Z73" s="1304" t="n"/>
       <c r="AA73" s="285" t="inlineStr">
         <is>
@@ -16665,7 +16214,7 @@
     <row r="74" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A74" s="280" t="inlineStr">
         <is>
-          <t>MQ-065</t>
+          <t>MQ-066</t>
         </is>
       </c>
       <c r="B74" s="281" t="inlineStr">
@@ -16680,12 +16229,12 @@
       </c>
       <c r="D74" s="283" t="inlineStr">
         <is>
-          <t>09.01.03</t>
+          <t>09.01.04</t>
         </is>
       </c>
       <c r="E74" s="284" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="F74" s="285" t="n"/>
@@ -16696,7 +16245,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J74" s="1448" t="n"/>
+      <c r="J74" s="1469" t="n"/>
       <c r="K74" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16739,7 +16288,7 @@
       </c>
       <c r="W74" s="285" t="n"/>
       <c r="X74" s="285" t="n"/>
-      <c r="Y74" s="1448" t="n"/>
+      <c r="Y74" s="1469" t="n"/>
       <c r="Z74" s="1304" t="n"/>
       <c r="AA74" s="285" t="inlineStr">
         <is>
@@ -16750,7 +16299,7 @@
     <row r="75" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A75" s="280" t="inlineStr">
         <is>
-          <t>MQ-066</t>
+          <t>MQ-067</t>
         </is>
       </c>
       <c r="B75" s="281" t="inlineStr">
@@ -16765,12 +16314,12 @@
       </c>
       <c r="D75" s="283" t="inlineStr">
         <is>
-          <t>09.01.04</t>
+          <t>09.01.05</t>
         </is>
       </c>
       <c r="E75" s="284" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="F75" s="285" t="n"/>
@@ -16781,7 +16330,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J75" s="1448" t="n"/>
+      <c r="J75" s="1469" t="n"/>
       <c r="K75" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16824,7 +16373,7 @@
       </c>
       <c r="W75" s="285" t="n"/>
       <c r="X75" s="285" t="n"/>
-      <c r="Y75" s="1448" t="n"/>
+      <c r="Y75" s="1469" t="n"/>
       <c r="Z75" s="1304" t="n"/>
       <c r="AA75" s="285" t="inlineStr">
         <is>
@@ -16835,7 +16384,7 @@
     <row r="76" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A76" s="280" t="inlineStr">
         <is>
-          <t>MQ-067</t>
+          <t>MQ-068</t>
         </is>
       </c>
       <c r="B76" s="281" t="inlineStr">
@@ -16845,17 +16394,17 @@
       </c>
       <c r="C76" s="282" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>Enchapes</t>
         </is>
       </c>
       <c r="D76" s="283" t="inlineStr">
         <is>
-          <t>09.01.05</t>
+          <t>09.02.01</t>
         </is>
       </c>
       <c r="E76" s="284" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="F76" s="285" t="n"/>
@@ -16866,7 +16415,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J76" s="1448" t="n"/>
+      <c r="J76" s="1469" t="n"/>
       <c r="K76" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16909,7 +16458,7 @@
       </c>
       <c r="W76" s="285" t="n"/>
       <c r="X76" s="285" t="n"/>
-      <c r="Y76" s="1448" t="n"/>
+      <c r="Y76" s="1469" t="n"/>
       <c r="Z76" s="1304" t="n"/>
       <c r="AA76" s="285" t="inlineStr">
         <is>
@@ -16920,7 +16469,7 @@
     <row r="77" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A77" s="280" t="inlineStr">
         <is>
-          <t>MQ-068</t>
+          <t>MQ-069</t>
         </is>
       </c>
       <c r="B77" s="281" t="inlineStr">
@@ -16935,12 +16484,12 @@
       </c>
       <c r="D77" s="283" t="inlineStr">
         <is>
-          <t>09.02.01</t>
+          <t>09.02.02</t>
         </is>
       </c>
       <c r="E77" s="284" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="F77" s="285" t="n"/>
@@ -16948,10 +16497,10 @@
       <c r="H77" s="285" t="n"/>
       <c r="I77" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J77" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J77" s="1469" t="n"/>
       <c r="K77" s="1438" t="n">
         <v>0</v>
       </c>
@@ -16989,12 +16538,12 @@
       </c>
       <c r="V77" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W77" s="285" t="n"/>
       <c r="X77" s="285" t="n"/>
-      <c r="Y77" s="1448" t="n"/>
+      <c r="Y77" s="1469" t="n"/>
       <c r="Z77" s="1304" t="n"/>
       <c r="AA77" s="285" t="inlineStr">
         <is>
@@ -17005,7 +16554,7 @@
     <row r="78" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A78" s="280" t="inlineStr">
         <is>
-          <t>MQ-069</t>
+          <t>MQ-070</t>
         </is>
       </c>
       <c r="B78" s="281" t="inlineStr">
@@ -17020,12 +16569,12 @@
       </c>
       <c r="D78" s="283" t="inlineStr">
         <is>
-          <t>09.02.02</t>
+          <t>09.02.03</t>
         </is>
       </c>
       <c r="E78" s="284" t="inlineStr">
         <is>
-          <t>Guardaescoba</t>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="F78" s="285" t="n"/>
@@ -17036,7 +16585,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J78" s="1448" t="n"/>
+      <c r="J78" s="1469" t="n"/>
       <c r="K78" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17079,7 +16628,7 @@
       </c>
       <c r="W78" s="285" t="n"/>
       <c r="X78" s="285" t="n"/>
-      <c r="Y78" s="1448" t="n"/>
+      <c r="Y78" s="1469" t="n"/>
       <c r="Z78" s="1304" t="n"/>
       <c r="AA78" s="285" t="inlineStr">
         <is>
@@ -17090,27 +16639,27 @@
     <row r="79" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A79" s="280" t="inlineStr">
         <is>
-          <t>MQ-070</t>
+          <t>MQ-071</t>
         </is>
       </c>
       <c r="B79" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C79" s="282" t="inlineStr">
         <is>
-          <t>Enchapes</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D79" s="283" t="inlineStr">
         <is>
-          <t>09.02.03</t>
+          <t>10.01.01</t>
         </is>
       </c>
       <c r="E79" s="284" t="inlineStr">
         <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="F79" s="285" t="n"/>
@@ -17118,10 +16667,10 @@
       <c r="H79" s="285" t="n"/>
       <c r="I79" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J79" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J79" s="1469" t="n"/>
       <c r="K79" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17159,12 +16708,12 @@
       </c>
       <c r="V79" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W79" s="285" t="n"/>
       <c r="X79" s="285" t="n"/>
-      <c r="Y79" s="1448" t="n"/>
+      <c r="Y79" s="1469" t="n"/>
       <c r="Z79" s="1304" t="n"/>
       <c r="AA79" s="285" t="inlineStr">
         <is>
@@ -17175,7 +16724,7 @@
     <row r="80" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A80" s="280" t="inlineStr">
         <is>
-          <t>MQ-071</t>
+          <t>MQ-072</t>
         </is>
       </c>
       <c r="B80" s="281" t="inlineStr">
@@ -17190,12 +16739,12 @@
       </c>
       <c r="D80" s="283" t="inlineStr">
         <is>
-          <t>10.01.01</t>
+          <t>10.01.02</t>
         </is>
       </c>
       <c r="E80" s="284" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="F80" s="285" t="n"/>
@@ -17206,7 +16755,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J80" s="1448" t="n"/>
+      <c r="J80" s="1469" t="n"/>
       <c r="K80" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17249,7 +16798,7 @@
       </c>
       <c r="W80" s="285" t="n"/>
       <c r="X80" s="285" t="n"/>
-      <c r="Y80" s="1448" t="n"/>
+      <c r="Y80" s="1469" t="n"/>
       <c r="Z80" s="1304" t="n"/>
       <c r="AA80" s="285" t="inlineStr">
         <is>
@@ -17260,7 +16809,7 @@
     <row r="81" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A81" s="280" t="inlineStr">
         <is>
-          <t>MQ-072</t>
+          <t>MQ-073</t>
         </is>
       </c>
       <c r="B81" s="281" t="inlineStr">
@@ -17275,12 +16824,12 @@
       </c>
       <c r="D81" s="283" t="inlineStr">
         <is>
-          <t>10.01.02</t>
+          <t>10.01.03</t>
         </is>
       </c>
       <c r="E81" s="284" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="F81" s="285" t="n"/>
@@ -17291,7 +16840,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J81" s="1448" t="n"/>
+      <c r="J81" s="1469" t="n"/>
       <c r="K81" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17334,7 +16883,7 @@
       </c>
       <c r="W81" s="285" t="n"/>
       <c r="X81" s="285" t="n"/>
-      <c r="Y81" s="1448" t="n"/>
+      <c r="Y81" s="1469" t="n"/>
       <c r="Z81" s="1304" t="n"/>
       <c r="AA81" s="285" t="inlineStr">
         <is>
@@ -17345,7 +16894,7 @@
     <row r="82" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A82" s="280" t="inlineStr">
         <is>
-          <t>MQ-073</t>
+          <t>MQ-074</t>
         </is>
       </c>
       <c r="B82" s="281" t="inlineStr">
@@ -17360,12 +16909,12 @@
       </c>
       <c r="D82" s="283" t="inlineStr">
         <is>
-          <t>10.01.03</t>
+          <t>10.01.04</t>
         </is>
       </c>
       <c r="E82" s="284" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="F82" s="285" t="n"/>
@@ -17376,7 +16925,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J82" s="1448" t="n"/>
+      <c r="J82" s="1469" t="n"/>
       <c r="K82" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17419,7 +16968,7 @@
       </c>
       <c r="W82" s="285" t="n"/>
       <c r="X82" s="285" t="n"/>
-      <c r="Y82" s="1448" t="n"/>
+      <c r="Y82" s="1469" t="n"/>
       <c r="Z82" s="1304" t="n"/>
       <c r="AA82" s="285" t="inlineStr">
         <is>
@@ -17430,7 +16979,7 @@
     <row r="83" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A83" s="280" t="inlineStr">
         <is>
-          <t>MQ-074</t>
+          <t>MQ-075</t>
         </is>
       </c>
       <c r="B83" s="281" t="inlineStr">
@@ -17445,12 +16994,12 @@
       </c>
       <c r="D83" s="283" t="inlineStr">
         <is>
-          <t>10.01.04</t>
+          <t>10.01.05</t>
         </is>
       </c>
       <c r="E83" s="284" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Sellador / imprimante</t>
         </is>
       </c>
       <c r="F83" s="285" t="n"/>
@@ -17461,7 +17010,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J83" s="1448" t="n"/>
+      <c r="J83" s="1469" t="n"/>
       <c r="K83" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17504,7 +17053,7 @@
       </c>
       <c r="W83" s="285" t="n"/>
       <c r="X83" s="285" t="n"/>
-      <c r="Y83" s="1448" t="n"/>
+      <c r="Y83" s="1469" t="n"/>
       <c r="Z83" s="1304" t="n"/>
       <c r="AA83" s="285" t="inlineStr">
         <is>
@@ -17515,27 +17064,27 @@
     <row r="84" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A84" s="280" t="inlineStr">
         <is>
-          <t>MQ-075</t>
+          <t>MQ-076</t>
         </is>
       </c>
       <c r="B84" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C84" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Madera</t>
         </is>
       </c>
       <c r="D84" s="283" t="inlineStr">
         <is>
-          <t>10.01.05</t>
+          <t>11.01.01</t>
         </is>
       </c>
       <c r="E84" s="284" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="F84" s="285" t="n"/>
@@ -17543,10 +17092,10 @@
       <c r="H84" s="285" t="n"/>
       <c r="I84" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J84" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J84" s="1469" t="n"/>
       <c r="K84" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17584,12 +17133,12 @@
       </c>
       <c r="V84" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W84" s="285" t="n"/>
       <c r="X84" s="285" t="n"/>
-      <c r="Y84" s="1448" t="n"/>
+      <c r="Y84" s="1469" t="n"/>
       <c r="Z84" s="1304" t="n"/>
       <c r="AA84" s="285" t="inlineStr">
         <is>
@@ -17600,7 +17149,7 @@
     <row r="85" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A85" s="280" t="inlineStr">
         <is>
-          <t>MQ-076</t>
+          <t>MQ-077</t>
         </is>
       </c>
       <c r="B85" s="281" t="inlineStr">
@@ -17615,12 +17164,12 @@
       </c>
       <c r="D85" s="283" t="inlineStr">
         <is>
-          <t>11.01.01</t>
+          <t>11.01.02</t>
         </is>
       </c>
       <c r="E85" s="284" t="inlineStr">
         <is>
-          <t>Puertas de madera</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="F85" s="285" t="n"/>
@@ -17628,10 +17177,10 @@
       <c r="H85" s="285" t="n"/>
       <c r="I85" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J85" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J85" s="1469" t="n"/>
       <c r="K85" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17669,12 +17218,12 @@
       </c>
       <c r="V85" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W85" s="285" t="n"/>
       <c r="X85" s="285" t="n"/>
-      <c r="Y85" s="1448" t="n"/>
+      <c r="Y85" s="1469" t="n"/>
       <c r="Z85" s="1304" t="n"/>
       <c r="AA85" s="285" t="inlineStr">
         <is>
@@ -17685,7 +17234,7 @@
     <row r="86" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A86" s="280" t="inlineStr">
         <is>
-          <t>MQ-077</t>
+          <t>MQ-078</t>
         </is>
       </c>
       <c r="B86" s="281" t="inlineStr">
@@ -17695,17 +17244,17 @@
       </c>
       <c r="C86" s="282" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>Metálica</t>
         </is>
       </c>
       <c r="D86" s="283" t="inlineStr">
         <is>
-          <t>11.01.02</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="E86" s="284" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="F86" s="285" t="n"/>
@@ -17713,10 +17262,10 @@
       <c r="H86" s="285" t="n"/>
       <c r="I86" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J86" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J86" s="1469" t="n"/>
       <c r="K86" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17754,12 +17303,12 @@
       </c>
       <c r="V86" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W86" s="285" t="n"/>
       <c r="X86" s="285" t="n"/>
-      <c r="Y86" s="1448" t="n"/>
+      <c r="Y86" s="1469" t="n"/>
       <c r="Z86" s="1304" t="n"/>
       <c r="AA86" s="285" t="inlineStr">
         <is>
@@ -17770,7 +17319,7 @@
     <row r="87" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A87" s="280" t="inlineStr">
         <is>
-          <t>MQ-078</t>
+          <t>MQ-079</t>
         </is>
       </c>
       <c r="B87" s="281" t="inlineStr">
@@ -17785,12 +17334,12 @@
       </c>
       <c r="D87" s="283" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>11.02.02</t>
         </is>
       </c>
       <c r="E87" s="284" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="F87" s="285" t="n"/>
@@ -17798,10 +17347,10 @@
       <c r="H87" s="285" t="n"/>
       <c r="I87" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J87" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J87" s="1469" t="n"/>
       <c r="K87" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17839,12 +17388,12 @@
       </c>
       <c r="V87" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W87" s="285" t="n"/>
       <c r="X87" s="285" t="n"/>
-      <c r="Y87" s="1448" t="n"/>
+      <c r="Y87" s="1469" t="n"/>
       <c r="Z87" s="1304" t="n"/>
       <c r="AA87" s="285" t="inlineStr">
         <is>
@@ -17855,7 +17404,7 @@
     <row r="88" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A88" s="280" t="inlineStr">
         <is>
-          <t>MQ-079</t>
+          <t>MQ-080</t>
         </is>
       </c>
       <c r="B88" s="281" t="inlineStr">
@@ -17870,12 +17419,12 @@
       </c>
       <c r="D88" s="283" t="inlineStr">
         <is>
-          <t>11.02.02</t>
+          <t>11.02.03</t>
         </is>
       </c>
       <c r="E88" s="284" t="inlineStr">
         <is>
-          <t>Barandas metálicas</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="F88" s="285" t="n"/>
@@ -17886,7 +17435,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J88" s="1448" t="n"/>
+      <c r="J88" s="1469" t="n"/>
       <c r="K88" s="1438" t="n">
         <v>0</v>
       </c>
@@ -17929,7 +17478,7 @@
       </c>
       <c r="W88" s="285" t="n"/>
       <c r="X88" s="285" t="n"/>
-      <c r="Y88" s="1448" t="n"/>
+      <c r="Y88" s="1469" t="n"/>
       <c r="Z88" s="1304" t="n"/>
       <c r="AA88" s="285" t="inlineStr">
         <is>
@@ -17940,7 +17489,7 @@
     <row r="89" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A89" s="280" t="inlineStr">
         <is>
-          <t>MQ-080</t>
+          <t>MQ-081</t>
         </is>
       </c>
       <c r="B89" s="281" t="inlineStr">
@@ -17950,17 +17499,17 @@
       </c>
       <c r="C89" s="282" t="inlineStr">
         <is>
-          <t>Metálica</t>
+          <t>Aluminio</t>
         </is>
       </c>
       <c r="D89" s="283" t="inlineStr">
         <is>
-          <t>11.02.03</t>
+          <t>11.03.01</t>
         </is>
       </c>
       <c r="E89" s="284" t="inlineStr">
         <is>
-          <t>Pasamanos</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="F89" s="285" t="n"/>
@@ -17968,10 +17517,10 @@
       <c r="H89" s="285" t="n"/>
       <c r="I89" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J89" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J89" s="1469" t="n"/>
       <c r="K89" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18009,12 +17558,12 @@
       </c>
       <c r="V89" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W89" s="285" t="n"/>
       <c r="X89" s="285" t="n"/>
-      <c r="Y89" s="1448" t="n"/>
+      <c r="Y89" s="1469" t="n"/>
       <c r="Z89" s="1304" t="n"/>
       <c r="AA89" s="285" t="inlineStr">
         <is>
@@ -18025,7 +17574,7 @@
     <row r="90" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A90" s="280" t="inlineStr">
         <is>
-          <t>MQ-081</t>
+          <t>MQ-082</t>
         </is>
       </c>
       <c r="B90" s="281" t="inlineStr">
@@ -18040,12 +17589,12 @@
       </c>
       <c r="D90" s="283" t="inlineStr">
         <is>
-          <t>11.03.01</t>
+          <t>11.03.02</t>
         </is>
       </c>
       <c r="E90" s="284" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="F90" s="285" t="n"/>
@@ -18056,7 +17605,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J90" s="1448" t="n"/>
+      <c r="J90" s="1469" t="n"/>
       <c r="K90" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18099,7 +17648,7 @@
       </c>
       <c r="W90" s="285" t="n"/>
       <c r="X90" s="285" t="n"/>
-      <c r="Y90" s="1448" t="n"/>
+      <c r="Y90" s="1469" t="n"/>
       <c r="Z90" s="1304" t="n"/>
       <c r="AA90" s="285" t="inlineStr">
         <is>
@@ -18110,27 +17659,27 @@
     <row r="91" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A91" s="280" t="inlineStr">
         <is>
-          <t>MQ-082</t>
+          <t>MQ-083</t>
         </is>
       </c>
       <c r="B91" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>VIDRIOS</t>
         </is>
       </c>
       <c r="C91" s="282" t="inlineStr">
         <is>
-          <t>Aluminio</t>
+          <t>Vidriería</t>
         </is>
       </c>
       <c r="D91" s="283" t="inlineStr">
         <is>
-          <t>11.03.02</t>
+          <t>12.01.01</t>
         </is>
       </c>
       <c r="E91" s="284" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="F91" s="285" t="n"/>
@@ -18141,7 +17690,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J91" s="1448" t="n"/>
+      <c r="J91" s="1469" t="n"/>
       <c r="K91" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18184,7 +17733,7 @@
       </c>
       <c r="W91" s="285" t="n"/>
       <c r="X91" s="285" t="n"/>
-      <c r="Y91" s="1448" t="n"/>
+      <c r="Y91" s="1469" t="n"/>
       <c r="Z91" s="1304" t="n"/>
       <c r="AA91" s="285" t="inlineStr">
         <is>
@@ -18195,7 +17744,7 @@
     <row r="92" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A92" s="280" t="inlineStr">
         <is>
-          <t>MQ-083</t>
+          <t>MQ-084</t>
         </is>
       </c>
       <c r="B92" s="281" t="inlineStr">
@@ -18210,12 +17759,12 @@
       </c>
       <c r="D92" s="283" t="inlineStr">
         <is>
-          <t>12.01.01</t>
+          <t>12.01.02</t>
         </is>
       </c>
       <c r="E92" s="284" t="inlineStr">
         <is>
-          <t>Vidrio templado</t>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="F92" s="285" t="n"/>
@@ -18226,7 +17775,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J92" s="1448" t="n"/>
+      <c r="J92" s="1469" t="n"/>
       <c r="K92" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18269,7 +17818,7 @@
       </c>
       <c r="W92" s="285" t="n"/>
       <c r="X92" s="285" t="n"/>
-      <c r="Y92" s="1448" t="n"/>
+      <c r="Y92" s="1469" t="n"/>
       <c r="Z92" s="1304" t="n"/>
       <c r="AA92" s="285" t="inlineStr">
         <is>
@@ -18280,7 +17829,7 @@
     <row r="93" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A93" s="280" t="inlineStr">
         <is>
-          <t>MQ-084</t>
+          <t>MQ-085</t>
         </is>
       </c>
       <c r="B93" s="281" t="inlineStr">
@@ -18295,12 +17844,12 @@
       </c>
       <c r="D93" s="283" t="inlineStr">
         <is>
-          <t>12.01.02</t>
+          <t>12.01.03</t>
         </is>
       </c>
       <c r="E93" s="284" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="F93" s="285" t="n"/>
@@ -18311,7 +17860,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J93" s="1448" t="n"/>
+      <c r="J93" s="1469" t="n"/>
       <c r="K93" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18354,7 +17903,7 @@
       </c>
       <c r="W93" s="285" t="n"/>
       <c r="X93" s="285" t="n"/>
-      <c r="Y93" s="1448" t="n"/>
+      <c r="Y93" s="1469" t="n"/>
       <c r="Z93" s="1304" t="n"/>
       <c r="AA93" s="285" t="inlineStr">
         <is>
@@ -18365,7 +17914,7 @@
     <row r="94" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A94" s="280" t="inlineStr">
         <is>
-          <t>MQ-085</t>
+          <t>MQ-086</t>
         </is>
       </c>
       <c r="B94" s="281" t="inlineStr">
@@ -18380,12 +17929,12 @@
       </c>
       <c r="D94" s="283" t="inlineStr">
         <is>
-          <t>12.01.03</t>
+          <t>12.01.04</t>
         </is>
       </c>
       <c r="E94" s="284" t="inlineStr">
         <is>
-          <t>Espejos</t>
+          <t>Sellos y silicona</t>
         </is>
       </c>
       <c r="F94" s="285" t="n"/>
@@ -18393,10 +17942,10 @@
       <c r="H94" s="285" t="n"/>
       <c r="I94" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J94" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J94" s="1469" t="n"/>
       <c r="K94" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18434,12 +17983,12 @@
       </c>
       <c r="V94" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W94" s="285" t="n"/>
       <c r="X94" s="285" t="n"/>
-      <c r="Y94" s="1448" t="n"/>
+      <c r="Y94" s="1469" t="n"/>
       <c r="Z94" s="1304" t="n"/>
       <c r="AA94" s="285" t="inlineStr">
         <is>
@@ -18450,27 +17999,27 @@
     <row r="95" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A95" s="280" t="inlineStr">
         <is>
-          <t>MQ-086</t>
+          <t>MQ-087</t>
         </is>
       </c>
       <c r="B95" s="281" t="inlineStr">
         <is>
-          <t>VIDRIOS</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C95" s="282" t="inlineStr">
         <is>
-          <t>Vidriería</t>
+          <t>Agua potable</t>
         </is>
       </c>
       <c r="D95" s="283" t="inlineStr">
         <is>
-          <t>12.01.04</t>
+          <t>13.01.01</t>
         </is>
       </c>
       <c r="E95" s="284" t="inlineStr">
         <is>
-          <t>Sellos y silicona</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="F95" s="285" t="n"/>
@@ -18481,7 +18030,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J95" s="1448" t="n"/>
+      <c r="J95" s="1469" t="n"/>
       <c r="K95" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18524,7 +18073,7 @@
       </c>
       <c r="W95" s="285" t="n"/>
       <c r="X95" s="285" t="n"/>
-      <c r="Y95" s="1448" t="n"/>
+      <c r="Y95" s="1469" t="n"/>
       <c r="Z95" s="1304" t="n"/>
       <c r="AA95" s="285" t="inlineStr">
         <is>
@@ -18535,7 +18084,7 @@
     <row r="96" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A96" s="280" t="inlineStr">
         <is>
-          <t>MQ-087</t>
+          <t>MQ-088</t>
         </is>
       </c>
       <c r="B96" s="281" t="inlineStr">
@@ -18550,12 +18099,12 @@
       </c>
       <c r="D96" s="283" t="inlineStr">
         <is>
-          <t>13.01.01</t>
+          <t>13.01.02</t>
         </is>
       </c>
       <c r="E96" s="284" t="inlineStr">
         <is>
-          <t>Tubería de agua fría</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="F96" s="285" t="n"/>
@@ -18566,7 +18115,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J96" s="1448" t="n"/>
+      <c r="J96" s="1469" t="n"/>
       <c r="K96" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18609,7 +18158,7 @@
       </c>
       <c r="W96" s="285" t="n"/>
       <c r="X96" s="285" t="n"/>
-      <c r="Y96" s="1448" t="n"/>
+      <c r="Y96" s="1469" t="n"/>
       <c r="Z96" s="1304" t="n"/>
       <c r="AA96" s="285" t="inlineStr">
         <is>
@@ -18620,7 +18169,7 @@
     <row r="97" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A97" s="280" t="inlineStr">
         <is>
-          <t>MQ-088</t>
+          <t>MQ-089</t>
         </is>
       </c>
       <c r="B97" s="281" t="inlineStr">
@@ -18635,12 +18184,12 @@
       </c>
       <c r="D97" s="283" t="inlineStr">
         <is>
-          <t>13.01.02</t>
+          <t>13.01.03</t>
         </is>
       </c>
       <c r="E97" s="284" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="F97" s="285" t="n"/>
@@ -18648,10 +18197,10 @@
       <c r="H97" s="285" t="n"/>
       <c r="I97" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J97" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J97" s="1469" t="n"/>
       <c r="K97" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18689,12 +18238,12 @@
       </c>
       <c r="V97" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W97" s="285" t="n"/>
       <c r="X97" s="285" t="n"/>
-      <c r="Y97" s="1448" t="n"/>
+      <c r="Y97" s="1469" t="n"/>
       <c r="Z97" s="1304" t="n"/>
       <c r="AA97" s="285" t="inlineStr">
         <is>
@@ -18705,7 +18254,7 @@
     <row r="98" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A98" s="280" t="inlineStr">
         <is>
-          <t>MQ-089</t>
+          <t>MQ-090</t>
         </is>
       </c>
       <c r="B98" s="281" t="inlineStr">
@@ -18715,17 +18264,17 @@
       </c>
       <c r="C98" s="282" t="inlineStr">
         <is>
-          <t>Agua potable</t>
+          <t>Desagües</t>
         </is>
       </c>
       <c r="D98" s="283" t="inlineStr">
         <is>
-          <t>13.01.03</t>
+          <t>13.02.01</t>
         </is>
       </c>
       <c r="E98" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios hidrosanitarios</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="F98" s="285" t="n"/>
@@ -18733,10 +18282,10 @@
       <c r="H98" s="285" t="n"/>
       <c r="I98" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J98" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J98" s="1469" t="n"/>
       <c r="K98" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18774,12 +18323,12 @@
       </c>
       <c r="V98" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W98" s="285" t="n"/>
       <c r="X98" s="285" t="n"/>
-      <c r="Y98" s="1448" t="n"/>
+      <c r="Y98" s="1469" t="n"/>
       <c r="Z98" s="1304" t="n"/>
       <c r="AA98" s="285" t="inlineStr">
         <is>
@@ -18790,7 +18339,7 @@
     <row r="99" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A99" s="280" t="inlineStr">
         <is>
-          <t>MQ-090</t>
+          <t>MQ-091</t>
         </is>
       </c>
       <c r="B99" s="281" t="inlineStr">
@@ -18805,12 +18354,12 @@
       </c>
       <c r="D99" s="283" t="inlineStr">
         <is>
-          <t>13.02.01</t>
+          <t>13.02.02</t>
         </is>
       </c>
       <c r="E99" s="284" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="F99" s="285" t="n"/>
@@ -18821,7 +18370,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J99" s="1448" t="n"/>
+      <c r="J99" s="1469" t="n"/>
       <c r="K99" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18864,7 +18413,7 @@
       </c>
       <c r="W99" s="285" t="n"/>
       <c r="X99" s="285" t="n"/>
-      <c r="Y99" s="1448" t="n"/>
+      <c r="Y99" s="1469" t="n"/>
       <c r="Z99" s="1304" t="n"/>
       <c r="AA99" s="285" t="inlineStr">
         <is>
@@ -18875,7 +18424,7 @@
     <row r="100" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A100" s="280" t="inlineStr">
         <is>
-          <t>MQ-091</t>
+          <t>MQ-092</t>
         </is>
       </c>
       <c r="B100" s="281" t="inlineStr">
@@ -18890,12 +18439,12 @@
       </c>
       <c r="D100" s="283" t="inlineStr">
         <is>
-          <t>13.02.02</t>
+          <t>13.02.03</t>
         </is>
       </c>
       <c r="E100" s="284" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="F100" s="285" t="n"/>
@@ -18903,10 +18452,10 @@
       <c r="H100" s="285" t="n"/>
       <c r="I100" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J100" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J100" s="1469" t="n"/>
       <c r="K100" s="1438" t="n">
         <v>0</v>
       </c>
@@ -18944,12 +18493,12 @@
       </c>
       <c r="V100" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W100" s="285" t="n"/>
       <c r="X100" s="285" t="n"/>
-      <c r="Y100" s="1448" t="n"/>
+      <c r="Y100" s="1469" t="n"/>
       <c r="Z100" s="1304" t="n"/>
       <c r="AA100" s="285" t="inlineStr">
         <is>
@@ -18960,7 +18509,7 @@
     <row r="101" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A101" s="280" t="inlineStr">
         <is>
-          <t>MQ-092</t>
+          <t>MQ-093</t>
         </is>
       </c>
       <c r="B101" s="281" t="inlineStr">
@@ -18970,17 +18519,17 @@
       </c>
       <c r="C101" s="282" t="inlineStr">
         <is>
-          <t>Desagües</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D101" s="283" t="inlineStr">
         <is>
-          <t>13.02.03</t>
+          <t>13.03.01</t>
         </is>
       </c>
       <c r="E101" s="284" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="F101" s="285" t="n"/>
@@ -18991,7 +18540,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J101" s="1448" t="n"/>
+      <c r="J101" s="1469" t="n"/>
       <c r="K101" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19034,7 +18583,7 @@
       </c>
       <c r="W101" s="285" t="n"/>
       <c r="X101" s="285" t="n"/>
-      <c r="Y101" s="1448" t="n"/>
+      <c r="Y101" s="1469" t="n"/>
       <c r="Z101" s="1304" t="n"/>
       <c r="AA101" s="285" t="inlineStr">
         <is>
@@ -19045,7 +18594,7 @@
     <row r="102" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A102" s="280" t="inlineStr">
         <is>
-          <t>MQ-093</t>
+          <t>MQ-094</t>
         </is>
       </c>
       <c r="B102" s="281" t="inlineStr">
@@ -19060,12 +18609,12 @@
       </c>
       <c r="D102" s="283" t="inlineStr">
         <is>
-          <t>13.03.01</t>
+          <t>13.03.02</t>
         </is>
       </c>
       <c r="E102" s="284" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="F102" s="285" t="n"/>
@@ -19076,7 +18625,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J102" s="1448" t="n"/>
+      <c r="J102" s="1469" t="n"/>
       <c r="K102" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19119,7 +18668,7 @@
       </c>
       <c r="W102" s="285" t="n"/>
       <c r="X102" s="285" t="n"/>
-      <c r="Y102" s="1448" t="n"/>
+      <c r="Y102" s="1469" t="n"/>
       <c r="Z102" s="1304" t="n"/>
       <c r="AA102" s="285" t="inlineStr">
         <is>
@@ -19130,7 +18679,7 @@
     <row r="103" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A103" s="280" t="inlineStr">
         <is>
-          <t>MQ-094</t>
+          <t>MQ-095</t>
         </is>
       </c>
       <c r="B103" s="281" t="inlineStr">
@@ -19145,12 +18694,12 @@
       </c>
       <c r="D103" s="283" t="inlineStr">
         <is>
-          <t>13.03.02</t>
+          <t>13.03.03</t>
         </is>
       </c>
       <c r="E103" s="284" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="F103" s="285" t="n"/>
@@ -19161,7 +18710,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J103" s="1448" t="n"/>
+      <c r="J103" s="1469" t="n"/>
       <c r="K103" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19204,7 +18753,7 @@
       </c>
       <c r="W103" s="285" t="n"/>
       <c r="X103" s="285" t="n"/>
-      <c r="Y103" s="1448" t="n"/>
+      <c r="Y103" s="1469" t="n"/>
       <c r="Z103" s="1304" t="n"/>
       <c r="AA103" s="285" t="inlineStr">
         <is>
@@ -19215,7 +18764,7 @@
     <row r="104" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A104" s="280" t="inlineStr">
         <is>
-          <t>MQ-095</t>
+          <t>MQ-096</t>
         </is>
       </c>
       <c r="B104" s="281" t="inlineStr">
@@ -19230,12 +18779,12 @@
       </c>
       <c r="D104" s="283" t="inlineStr">
         <is>
-          <t>13.03.03</t>
+          <t>13.03.04</t>
         </is>
       </c>
       <c r="E104" s="284" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="F104" s="285" t="n"/>
@@ -19246,7 +18795,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J104" s="1448" t="n"/>
+      <c r="J104" s="1469" t="n"/>
       <c r="K104" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19289,7 +18838,7 @@
       </c>
       <c r="W104" s="285" t="n"/>
       <c r="X104" s="285" t="n"/>
-      <c r="Y104" s="1448" t="n"/>
+      <c r="Y104" s="1469" t="n"/>
       <c r="Z104" s="1304" t="n"/>
       <c r="AA104" s="285" t="inlineStr">
         <is>
@@ -19300,7 +18849,7 @@
     <row r="105" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A105" s="280" t="inlineStr">
         <is>
-          <t>MQ-096</t>
+          <t>MQ-097</t>
         </is>
       </c>
       <c r="B105" s="281" t="inlineStr">
@@ -19310,17 +18859,17 @@
       </c>
       <c r="C105" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D105" s="283" t="inlineStr">
         <is>
-          <t>13.03.04</t>
+          <t>13.04.01</t>
         </is>
       </c>
       <c r="E105" s="284" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="F105" s="285" t="n"/>
@@ -19328,10 +18877,10 @@
       <c r="H105" s="285" t="n"/>
       <c r="I105" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J105" s="1448" t="n"/>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="J105" s="1469" t="n"/>
       <c r="K105" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19369,12 +18918,12 @@
       </c>
       <c r="V105" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W105" s="285" t="n"/>
       <c r="X105" s="285" t="n"/>
-      <c r="Y105" s="1448" t="n"/>
+      <c r="Y105" s="1469" t="n"/>
       <c r="Z105" s="1304" t="n"/>
       <c r="AA105" s="285" t="inlineStr">
         <is>
@@ -19385,27 +18934,27 @@
     <row r="106" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A106" s="280" t="inlineStr">
         <is>
-          <t>MQ-097</t>
+          <t>MQ-098</t>
         </is>
       </c>
       <c r="B106" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C106" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Canalizaciones</t>
         </is>
       </c>
       <c r="D106" s="283" t="inlineStr">
         <is>
-          <t>13.04.01</t>
+          <t>14.01.01</t>
         </is>
       </c>
       <c r="E106" s="284" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="F106" s="285" t="n"/>
@@ -19413,10 +18962,10 @@
       <c r="H106" s="285" t="n"/>
       <c r="I106" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J106" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J106" s="1469" t="n"/>
       <c r="K106" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19454,12 +19003,12 @@
       </c>
       <c r="V106" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W106" s="285" t="n"/>
       <c r="X106" s="285" t="n"/>
-      <c r="Y106" s="1448" t="n"/>
+      <c r="Y106" s="1469" t="n"/>
       <c r="Z106" s="1304" t="n"/>
       <c r="AA106" s="285" t="inlineStr">
         <is>
@@ -19470,7 +19019,7 @@
     <row r="107" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A107" s="280" t="inlineStr">
         <is>
-          <t>MQ-098</t>
+          <t>MQ-099</t>
         </is>
       </c>
       <c r="B107" s="281" t="inlineStr">
@@ -19485,12 +19034,12 @@
       </c>
       <c r="D107" s="283" t="inlineStr">
         <is>
-          <t>14.01.01</t>
+          <t>14.01.02</t>
         </is>
       </c>
       <c r="E107" s="284" t="inlineStr">
         <is>
-          <t>Tubería/conduit eléctrica</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="F107" s="285" t="n"/>
@@ -19501,7 +19050,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J107" s="1448" t="n"/>
+      <c r="J107" s="1469" t="n"/>
       <c r="K107" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19544,7 +19093,7 @@
       </c>
       <c r="W107" s="285" t="n"/>
       <c r="X107" s="285" t="n"/>
-      <c r="Y107" s="1448" t="n"/>
+      <c r="Y107" s="1469" t="n"/>
       <c r="Z107" s="1304" t="n"/>
       <c r="AA107" s="285" t="inlineStr">
         <is>
@@ -19555,7 +19104,7 @@
     <row r="108" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A108" s="280" t="inlineStr">
         <is>
-          <t>MQ-099</t>
+          <t>MQ-100</t>
         </is>
       </c>
       <c r="B108" s="281" t="inlineStr">
@@ -19570,12 +19119,12 @@
       </c>
       <c r="D108" s="283" t="inlineStr">
         <is>
-          <t>14.01.02</t>
+          <t>14.01.03</t>
         </is>
       </c>
       <c r="E108" s="284" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="F108" s="285" t="n"/>
@@ -19583,10 +19132,10 @@
       <c r="H108" s="285" t="n"/>
       <c r="I108" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J108" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J108" s="1469" t="n"/>
       <c r="K108" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19624,12 +19173,12 @@
       </c>
       <c r="V108" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W108" s="285" t="n"/>
       <c r="X108" s="285" t="n"/>
-      <c r="Y108" s="1448" t="n"/>
+      <c r="Y108" s="1469" t="n"/>
       <c r="Z108" s="1304" t="n"/>
       <c r="AA108" s="285" t="inlineStr">
         <is>
@@ -19640,7 +19189,7 @@
     <row r="109" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A109" s="280" t="inlineStr">
         <is>
-          <t>MQ-100</t>
+          <t>MQ-101</t>
         </is>
       </c>
       <c r="B109" s="281" t="inlineStr">
@@ -19650,17 +19199,17 @@
       </c>
       <c r="C109" s="282" t="inlineStr">
         <is>
-          <t>Canalizaciones</t>
+          <t>Cableado</t>
         </is>
       </c>
       <c r="D109" s="283" t="inlineStr">
         <is>
-          <t>14.01.03</t>
+          <t>14.02.01</t>
         </is>
       </c>
       <c r="E109" s="284" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="F109" s="285" t="n"/>
@@ -19668,10 +19217,10 @@
       <c r="H109" s="285" t="n"/>
       <c r="I109" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J109" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J109" s="1469" t="n"/>
       <c r="K109" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19709,12 +19258,12 @@
       </c>
       <c r="V109" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W109" s="285" t="n"/>
       <c r="X109" s="285" t="n"/>
-      <c r="Y109" s="1448" t="n"/>
+      <c r="Y109" s="1469" t="n"/>
       <c r="Z109" s="1304" t="n"/>
       <c r="AA109" s="285" t="inlineStr">
         <is>
@@ -19725,7 +19274,7 @@
     <row r="110" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A110" s="280" t="inlineStr">
         <is>
-          <t>MQ-101</t>
+          <t>MQ-102</t>
         </is>
       </c>
       <c r="B110" s="281" t="inlineStr">
@@ -19740,12 +19289,12 @@
       </c>
       <c r="D110" s="283" t="inlineStr">
         <is>
-          <t>14.02.01</t>
+          <t>14.02.02</t>
         </is>
       </c>
       <c r="E110" s="284" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="F110" s="285" t="n"/>
@@ -19756,7 +19305,7 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="J110" s="1448" t="n"/>
+      <c r="J110" s="1469" t="n"/>
       <c r="K110" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19799,7 +19348,7 @@
       </c>
       <c r="W110" s="285" t="n"/>
       <c r="X110" s="285" t="n"/>
-      <c r="Y110" s="1448" t="n"/>
+      <c r="Y110" s="1469" t="n"/>
       <c r="Z110" s="1304" t="n"/>
       <c r="AA110" s="285" t="inlineStr">
         <is>
@@ -19810,7 +19359,7 @@
     <row r="111" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A111" s="280" t="inlineStr">
         <is>
-          <t>MQ-102</t>
+          <t>MQ-103</t>
         </is>
       </c>
       <c r="B111" s="281" t="inlineStr">
@@ -19825,12 +19374,12 @@
       </c>
       <c r="D111" s="283" t="inlineStr">
         <is>
-          <t>14.02.02</t>
+          <t>14.02.03</t>
         </is>
       </c>
       <c r="E111" s="284" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="F111" s="285" t="n"/>
@@ -19838,10 +19387,10 @@
       <c r="H111" s="285" t="n"/>
       <c r="I111" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J111" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J111" s="1469" t="n"/>
       <c r="K111" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19879,12 +19428,12 @@
       </c>
       <c r="V111" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W111" s="285" t="n"/>
       <c r="X111" s="285" t="n"/>
-      <c r="Y111" s="1448" t="n"/>
+      <c r="Y111" s="1469" t="n"/>
       <c r="Z111" s="1304" t="n"/>
       <c r="AA111" s="285" t="inlineStr">
         <is>
@@ -19895,7 +19444,7 @@
     <row r="112" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A112" s="280" t="inlineStr">
         <is>
-          <t>MQ-103</t>
+          <t>MQ-104</t>
         </is>
       </c>
       <c r="B112" s="281" t="inlineStr">
@@ -19905,17 +19454,17 @@
       </c>
       <c r="C112" s="282" t="inlineStr">
         <is>
-          <t>Cableado</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D112" s="283" t="inlineStr">
         <is>
-          <t>14.02.03</t>
+          <t>14.03.01</t>
         </is>
       </c>
       <c r="E112" s="284" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="F112" s="285" t="n"/>
@@ -19926,7 +19475,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J112" s="1448" t="n"/>
+      <c r="J112" s="1469" t="n"/>
       <c r="K112" s="1438" t="n">
         <v>0</v>
       </c>
@@ -19969,7 +19518,7 @@
       </c>
       <c r="W112" s="285" t="n"/>
       <c r="X112" s="285" t="n"/>
-      <c r="Y112" s="1448" t="n"/>
+      <c r="Y112" s="1469" t="n"/>
       <c r="Z112" s="1304" t="n"/>
       <c r="AA112" s="285" t="inlineStr">
         <is>
@@ -19980,7 +19529,7 @@
     <row r="113" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A113" s="280" t="inlineStr">
         <is>
-          <t>MQ-104</t>
+          <t>MQ-105</t>
         </is>
       </c>
       <c r="B113" s="281" t="inlineStr">
@@ -19995,12 +19544,12 @@
       </c>
       <c r="D113" s="283" t="inlineStr">
         <is>
-          <t>14.03.01</t>
+          <t>14.03.02</t>
         </is>
       </c>
       <c r="E113" s="284" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="F113" s="285" t="n"/>
@@ -20011,7 +19560,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J113" s="1448" t="n"/>
+      <c r="J113" s="1469" t="n"/>
       <c r="K113" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20054,7 +19603,7 @@
       </c>
       <c r="W113" s="285" t="n"/>
       <c r="X113" s="285" t="n"/>
-      <c r="Y113" s="1448" t="n"/>
+      <c r="Y113" s="1469" t="n"/>
       <c r="Z113" s="1304" t="n"/>
       <c r="AA113" s="285" t="inlineStr">
         <is>
@@ -20065,7 +19614,7 @@
     <row r="114" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A114" s="280" t="inlineStr">
         <is>
-          <t>MQ-105</t>
+          <t>MQ-106</t>
         </is>
       </c>
       <c r="B114" s="281" t="inlineStr">
@@ -20080,12 +19629,12 @@
       </c>
       <c r="D114" s="283" t="inlineStr">
         <is>
-          <t>14.03.02</t>
+          <t>14.03.03</t>
         </is>
       </c>
       <c r="E114" s="284" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="F114" s="285" t="n"/>
@@ -20096,7 +19645,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J114" s="1448" t="n"/>
+      <c r="J114" s="1469" t="n"/>
       <c r="K114" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20139,7 +19688,7 @@
       </c>
       <c r="W114" s="285" t="n"/>
       <c r="X114" s="285" t="n"/>
-      <c r="Y114" s="1448" t="n"/>
+      <c r="Y114" s="1469" t="n"/>
       <c r="Z114" s="1304" t="n"/>
       <c r="AA114" s="285" t="inlineStr">
         <is>
@@ -20150,7 +19699,7 @@
     <row r="115" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A115" s="280" t="inlineStr">
         <is>
-          <t>MQ-106</t>
+          <t>MQ-107</t>
         </is>
       </c>
       <c r="B115" s="281" t="inlineStr">
@@ -20160,17 +19709,17 @@
       </c>
       <c r="C115" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Puesta a tierra</t>
         </is>
       </c>
       <c r="D115" s="283" t="inlineStr">
         <is>
-          <t>14.03.03</t>
+          <t>14.04.01</t>
         </is>
       </c>
       <c r="E115" s="284" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="F115" s="285" t="n"/>
@@ -20178,10 +19727,10 @@
       <c r="H115" s="285" t="n"/>
       <c r="I115" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J115" s="1448" t="n"/>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="J115" s="1469" t="n"/>
       <c r="K115" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20219,12 +19768,12 @@
       </c>
       <c r="V115" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W115" s="285" t="n"/>
       <c r="X115" s="285" t="n"/>
-      <c r="Y115" s="1448" t="n"/>
+      <c r="Y115" s="1469" t="n"/>
       <c r="Z115" s="1304" t="n"/>
       <c r="AA115" s="285" t="inlineStr">
         <is>
@@ -20235,7 +19784,7 @@
     <row r="116" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A116" s="280" t="inlineStr">
         <is>
-          <t>MQ-107</t>
+          <t>MQ-108</t>
         </is>
       </c>
       <c r="B116" s="281" t="inlineStr">
@@ -20245,17 +19794,17 @@
       </c>
       <c r="C116" s="282" t="inlineStr">
         <is>
-          <t>Puesta a tierra</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D116" s="283" t="inlineStr">
         <is>
-          <t>14.04.01</t>
+          <t>14.05.01</t>
         </is>
       </c>
       <c r="E116" s="284" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Pruebas y certificaciones</t>
         </is>
       </c>
       <c r="F116" s="285" t="n"/>
@@ -20266,7 +19815,7 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="J116" s="1448" t="n"/>
+      <c r="J116" s="1469" t="n"/>
       <c r="K116" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20309,7 +19858,7 @@
       </c>
       <c r="W116" s="285" t="n"/>
       <c r="X116" s="285" t="n"/>
-      <c r="Y116" s="1448" t="n"/>
+      <c r="Y116" s="1469" t="n"/>
       <c r="Z116" s="1304" t="n"/>
       <c r="AA116" s="285" t="inlineStr">
         <is>
@@ -20320,27 +19869,27 @@
     <row r="117" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A117" s="280" t="inlineStr">
         <is>
-          <t>MQ-108</t>
+          <t>MQ-109</t>
         </is>
       </c>
       <c r="B117" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C117" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Datos</t>
         </is>
       </c>
       <c r="D117" s="283" t="inlineStr">
         <is>
-          <t>14.05.01</t>
+          <t>15.01.01</t>
         </is>
       </c>
       <c r="E117" s="284" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="F117" s="285" t="n"/>
@@ -20348,10 +19897,10 @@
       <c r="H117" s="285" t="n"/>
       <c r="I117" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J117" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J117" s="1469" t="n"/>
       <c r="K117" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20389,12 +19938,12 @@
       </c>
       <c r="V117" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W117" s="285" t="n"/>
       <c r="X117" s="285" t="n"/>
-      <c r="Y117" s="1448" t="n"/>
+      <c r="Y117" s="1469" t="n"/>
       <c r="Z117" s="1304" t="n"/>
       <c r="AA117" s="285" t="inlineStr">
         <is>
@@ -20405,7 +19954,7 @@
     <row r="118" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A118" s="280" t="inlineStr">
         <is>
-          <t>MQ-109</t>
+          <t>MQ-110</t>
         </is>
       </c>
       <c r="B118" s="281" t="inlineStr">
@@ -20420,12 +19969,12 @@
       </c>
       <c r="D118" s="283" t="inlineStr">
         <is>
-          <t>15.01.01</t>
+          <t>15.01.02</t>
         </is>
       </c>
       <c r="E118" s="284" t="inlineStr">
         <is>
-          <t>Cableado estructurado de datos</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="F118" s="285" t="n"/>
@@ -20433,10 +19982,10 @@
       <c r="H118" s="285" t="n"/>
       <c r="I118" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J118" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J118" s="1469" t="n"/>
       <c r="K118" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20474,12 +20023,12 @@
       </c>
       <c r="V118" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W118" s="285" t="n"/>
       <c r="X118" s="285" t="n"/>
-      <c r="Y118" s="1448" t="n"/>
+      <c r="Y118" s="1469" t="n"/>
       <c r="Z118" s="1304" t="n"/>
       <c r="AA118" s="285" t="inlineStr">
         <is>
@@ -20490,7 +20039,7 @@
     <row r="119" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A119" s="280" t="inlineStr">
         <is>
-          <t>MQ-110</t>
+          <t>MQ-111</t>
         </is>
       </c>
       <c r="B119" s="281" t="inlineStr">
@@ -20500,17 +20049,17 @@
       </c>
       <c r="C119" s="282" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D119" s="283" t="inlineStr">
         <is>
-          <t>15.01.02</t>
+          <t>15.02.01</t>
         </is>
       </c>
       <c r="E119" s="284" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="F119" s="285" t="n"/>
@@ -20521,7 +20070,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J119" s="1448" t="n"/>
+      <c r="J119" s="1469" t="n"/>
       <c r="K119" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20564,7 +20113,7 @@
       </c>
       <c r="W119" s="285" t="n"/>
       <c r="X119" s="285" t="n"/>
-      <c r="Y119" s="1448" t="n"/>
+      <c r="Y119" s="1469" t="n"/>
       <c r="Z119" s="1304" t="n"/>
       <c r="AA119" s="285" t="inlineStr">
         <is>
@@ -20575,7 +20124,7 @@
     <row r="120" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A120" s="280" t="inlineStr">
         <is>
-          <t>MQ-111</t>
+          <t>MQ-112</t>
         </is>
       </c>
       <c r="B120" s="281" t="inlineStr">
@@ -20590,12 +20139,12 @@
       </c>
       <c r="D120" s="283" t="inlineStr">
         <is>
-          <t>15.02.01</t>
+          <t>15.02.02</t>
         </is>
       </c>
       <c r="E120" s="284" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="F120" s="285" t="n"/>
@@ -20606,7 +20155,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J120" s="1448" t="n"/>
+      <c r="J120" s="1469" t="n"/>
       <c r="K120" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20649,7 +20198,7 @@
       </c>
       <c r="W120" s="285" t="n"/>
       <c r="X120" s="285" t="n"/>
-      <c r="Y120" s="1448" t="n"/>
+      <c r="Y120" s="1469" t="n"/>
       <c r="Z120" s="1304" t="n"/>
       <c r="AA120" s="285" t="inlineStr">
         <is>
@@ -20660,7 +20209,7 @@
     <row r="121" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A121" s="280" t="inlineStr">
         <is>
-          <t>MQ-112</t>
+          <t>MQ-113</t>
         </is>
       </c>
       <c r="B121" s="281" t="inlineStr">
@@ -20675,12 +20224,12 @@
       </c>
       <c r="D121" s="283" t="inlineStr">
         <is>
-          <t>15.02.02</t>
+          <t>15.02.03</t>
         </is>
       </c>
       <c r="E121" s="284" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="F121" s="285" t="n"/>
@@ -20691,7 +20240,7 @@
           <t>und</t>
         </is>
       </c>
-      <c r="J121" s="1448" t="n"/>
+      <c r="J121" s="1469" t="n"/>
       <c r="K121" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20734,7 +20283,7 @@
       </c>
       <c r="W121" s="285" t="n"/>
       <c r="X121" s="285" t="n"/>
-      <c r="Y121" s="1448" t="n"/>
+      <c r="Y121" s="1469" t="n"/>
       <c r="Z121" s="1304" t="n"/>
       <c r="AA121" s="285" t="inlineStr">
         <is>
@@ -20745,7 +20294,7 @@
     <row r="122" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A122" s="280" t="inlineStr">
         <is>
-          <t>MQ-113</t>
+          <t>MQ-114</t>
         </is>
       </c>
       <c r="B122" s="281" t="inlineStr">
@@ -20755,17 +20304,17 @@
       </c>
       <c r="C122" s="282" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Detección</t>
         </is>
       </c>
       <c r="D122" s="283" t="inlineStr">
         <is>
-          <t>15.02.03</t>
+          <t>15.03.01</t>
         </is>
       </c>
       <c r="E122" s="284" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Sistema de detección de incendios</t>
         </is>
       </c>
       <c r="F122" s="285" t="n"/>
@@ -20773,10 +20322,10 @@
       <c r="H122" s="285" t="n"/>
       <c r="I122" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J122" s="1448" t="n"/>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="J122" s="1469" t="n"/>
       <c r="K122" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20814,12 +20363,12 @@
       </c>
       <c r="V122" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W122" s="285" t="n"/>
       <c r="X122" s="285" t="n"/>
-      <c r="Y122" s="1448" t="n"/>
+      <c r="Y122" s="1469" t="n"/>
       <c r="Z122" s="1304" t="n"/>
       <c r="AA122" s="285" t="inlineStr">
         <is>
@@ -20830,27 +20379,27 @@
     <row r="123" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A123" s="280" t="inlineStr">
         <is>
-          <t>MQ-114</t>
+          <t>MQ-115</t>
         </is>
       </c>
       <c r="B123" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C123" s="282" t="inlineStr">
         <is>
-          <t>Detección</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D123" s="283" t="inlineStr">
         <is>
-          <t>15.03.01</t>
+          <t>16.01.01</t>
         </is>
       </c>
       <c r="E123" s="284" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="F123" s="285" t="n"/>
@@ -20858,10 +20407,10 @@
       <c r="H123" s="285" t="n"/>
       <c r="I123" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J123" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J123" s="1469" t="n"/>
       <c r="K123" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20899,12 +20448,12 @@
       </c>
       <c r="V123" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W123" s="285" t="n"/>
       <c r="X123" s="285" t="n"/>
-      <c r="Y123" s="1448" t="n"/>
+      <c r="Y123" s="1469" t="n"/>
       <c r="Z123" s="1304" t="n"/>
       <c r="AA123" s="285" t="inlineStr">
         <is>
@@ -20915,7 +20464,7 @@
     <row r="124" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A124" s="280" t="inlineStr">
         <is>
-          <t>MQ-115</t>
+          <t>MQ-116</t>
         </is>
       </c>
       <c r="B124" s="281" t="inlineStr">
@@ -20930,12 +20479,12 @@
       </c>
       <c r="D124" s="283" t="inlineStr">
         <is>
-          <t>16.01.01</t>
+          <t>16.01.02</t>
         </is>
       </c>
       <c r="E124" s="284" t="inlineStr">
         <is>
-          <t>Equipos de aire acondicionado</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="F124" s="285" t="n"/>
@@ -20943,10 +20492,10 @@
       <c r="H124" s="285" t="n"/>
       <c r="I124" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J124" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J124" s="1469" t="n"/>
       <c r="K124" s="1438" t="n">
         <v>0</v>
       </c>
@@ -20984,12 +20533,12 @@
       </c>
       <c r="V124" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W124" s="285" t="n"/>
       <c r="X124" s="285" t="n"/>
-      <c r="Y124" s="1448" t="n"/>
+      <c r="Y124" s="1469" t="n"/>
       <c r="Z124" s="1304" t="n"/>
       <c r="AA124" s="285" t="inlineStr">
         <is>
@@ -21000,7 +20549,7 @@
     <row r="125" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A125" s="280" t="inlineStr">
         <is>
-          <t>MQ-116</t>
+          <t>MQ-117</t>
         </is>
       </c>
       <c r="B125" s="281" t="inlineStr">
@@ -21015,12 +20564,12 @@
       </c>
       <c r="D125" s="283" t="inlineStr">
         <is>
-          <t>16.01.02</t>
+          <t>16.01.03</t>
         </is>
       </c>
       <c r="E125" s="284" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="F125" s="285" t="n"/>
@@ -21028,10 +20577,10 @@
       <c r="H125" s="285" t="n"/>
       <c r="I125" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J125" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J125" s="1469" t="n"/>
       <c r="K125" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21069,12 +20618,12 @@
       </c>
       <c r="V125" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W125" s="285" t="n"/>
       <c r="X125" s="285" t="n"/>
-      <c r="Y125" s="1448" t="n"/>
+      <c r="Y125" s="1469" t="n"/>
       <c r="Z125" s="1304" t="n"/>
       <c r="AA125" s="285" t="inlineStr">
         <is>
@@ -21085,7 +20634,7 @@
     <row r="126" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A126" s="280" t="inlineStr">
         <is>
-          <t>MQ-117</t>
+          <t>MQ-118</t>
         </is>
       </c>
       <c r="B126" s="281" t="inlineStr">
@@ -21100,12 +20649,12 @@
       </c>
       <c r="D126" s="283" t="inlineStr">
         <is>
-          <t>16.01.03</t>
+          <t>16.01.04</t>
         </is>
       </c>
       <c r="E126" s="284" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Rejillas y difusores</t>
         </is>
       </c>
       <c r="F126" s="285" t="n"/>
@@ -21113,10 +20662,10 @@
       <c r="H126" s="285" t="n"/>
       <c r="I126" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J126" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J126" s="1469" t="n"/>
       <c r="K126" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21154,12 +20703,12 @@
       </c>
       <c r="V126" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W126" s="285" t="n"/>
       <c r="X126" s="285" t="n"/>
-      <c r="Y126" s="1448" t="n"/>
+      <c r="Y126" s="1469" t="n"/>
       <c r="Z126" s="1304" t="n"/>
       <c r="AA126" s="285" t="inlineStr">
         <is>
@@ -21170,27 +20719,27 @@
     <row r="127" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A127" s="280" t="inlineStr">
         <is>
-          <t>MQ-118</t>
+          <t>MQ-119</t>
         </is>
       </c>
       <c r="B127" s="281" t="inlineStr">
         <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="C127" s="282" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Red de gas</t>
         </is>
       </c>
       <c r="D127" s="283" t="inlineStr">
         <is>
-          <t>16.01.04</t>
+          <t>17.01.01</t>
         </is>
       </c>
       <c r="E127" s="284" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="F127" s="285" t="n"/>
@@ -21198,10 +20747,10 @@
       <c r="H127" s="285" t="n"/>
       <c r="I127" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J127" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J127" s="1469" t="n"/>
       <c r="K127" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21239,12 +20788,12 @@
       </c>
       <c r="V127" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W127" s="285" t="n"/>
       <c r="X127" s="285" t="n"/>
-      <c r="Y127" s="1448" t="n"/>
+      <c r="Y127" s="1469" t="n"/>
       <c r="Z127" s="1304" t="n"/>
       <c r="AA127" s="285" t="inlineStr">
         <is>
@@ -21255,7 +20804,7 @@
     <row r="128" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A128" s="280" t="inlineStr">
         <is>
-          <t>MQ-119</t>
+          <t>MQ-120</t>
         </is>
       </c>
       <c r="B128" s="281" t="inlineStr">
@@ -21270,12 +20819,12 @@
       </c>
       <c r="D128" s="283" t="inlineStr">
         <is>
-          <t>17.01.01</t>
+          <t>17.01.02</t>
         </is>
       </c>
       <c r="E128" s="284" t="inlineStr">
         <is>
-          <t>Red interna de gas</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="F128" s="285" t="n"/>
@@ -21283,10 +20832,10 @@
       <c r="H128" s="285" t="n"/>
       <c r="I128" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J128" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J128" s="1469" t="n"/>
       <c r="K128" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21324,12 +20873,12 @@
       </c>
       <c r="V128" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W128" s="285" t="n"/>
       <c r="X128" s="285" t="n"/>
-      <c r="Y128" s="1448" t="n"/>
+      <c r="Y128" s="1469" t="n"/>
       <c r="Z128" s="1304" t="n"/>
       <c r="AA128" s="285" t="inlineStr">
         <is>
@@ -21340,7 +20889,7 @@
     <row r="129" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A129" s="280" t="inlineStr">
         <is>
-          <t>MQ-120</t>
+          <t>MQ-121</t>
         </is>
       </c>
       <c r="B129" s="281" t="inlineStr">
@@ -21355,12 +20904,12 @@
       </c>
       <c r="D129" s="283" t="inlineStr">
         <is>
-          <t>17.01.02</t>
+          <t>17.01.03</t>
         </is>
       </c>
       <c r="E129" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios de gas</t>
+          <t>Pruebas y certificación</t>
         </is>
       </c>
       <c r="F129" s="285" t="n"/>
@@ -21368,10 +20917,10 @@
       <c r="H129" s="285" t="n"/>
       <c r="I129" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J129" s="1448" t="n"/>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="J129" s="1469" t="n"/>
       <c r="K129" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21409,12 +20958,12 @@
       </c>
       <c r="V129" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W129" s="285" t="n"/>
       <c r="X129" s="285" t="n"/>
-      <c r="Y129" s="1448" t="n"/>
+      <c r="Y129" s="1469" t="n"/>
       <c r="Z129" s="1304" t="n"/>
       <c r="AA129" s="285" t="inlineStr">
         <is>
@@ -21425,27 +20974,27 @@
     <row r="130" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A130" s="280" t="inlineStr">
         <is>
-          <t>MQ-121</t>
+          <t>MQ-122</t>
         </is>
       </c>
       <c r="B130" s="281" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C130" s="282" t="inlineStr">
         <is>
-          <t>Red de gas</t>
+          <t>Pavimentos</t>
         </is>
       </c>
       <c r="D130" s="283" t="inlineStr">
         <is>
-          <t>17.01.03</t>
+          <t>18.01.01</t>
         </is>
       </c>
       <c r="E130" s="284" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="F130" s="285" t="n"/>
@@ -21453,10 +21002,10 @@
       <c r="H130" s="285" t="n"/>
       <c r="I130" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J130" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J130" s="1469" t="n"/>
       <c r="K130" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21494,12 +21043,12 @@
       </c>
       <c r="V130" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W130" s="285" t="n"/>
       <c r="X130" s="285" t="n"/>
-      <c r="Y130" s="1448" t="n"/>
+      <c r="Y130" s="1469" t="n"/>
       <c r="Z130" s="1304" t="n"/>
       <c r="AA130" s="285" t="inlineStr">
         <is>
@@ -21510,7 +21059,7 @@
     <row r="131" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A131" s="280" t="inlineStr">
         <is>
-          <t>MQ-122</t>
+          <t>MQ-123</t>
         </is>
       </c>
       <c r="B131" s="281" t="inlineStr">
@@ -21525,12 +21074,12 @@
       </c>
       <c r="D131" s="283" t="inlineStr">
         <is>
-          <t>18.01.01</t>
+          <t>18.01.02</t>
         </is>
       </c>
       <c r="E131" s="284" t="inlineStr">
         <is>
-          <t>Construcción de andenes</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="F131" s="285" t="n"/>
@@ -21538,10 +21087,10 @@
       <c r="H131" s="285" t="n"/>
       <c r="I131" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J131" s="1448" t="n"/>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="J131" s="1469" t="n"/>
       <c r="K131" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21579,12 +21128,12 @@
       </c>
       <c r="V131" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="W131" s="285" t="n"/>
       <c r="X131" s="285" t="n"/>
-      <c r="Y131" s="1448" t="n"/>
+      <c r="Y131" s="1469" t="n"/>
       <c r="Z131" s="1304" t="n"/>
       <c r="AA131" s="285" t="inlineStr">
         <is>
@@ -21595,7 +21144,7 @@
     <row r="132" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A132" s="280" t="inlineStr">
         <is>
-          <t>MQ-123</t>
+          <t>MQ-124</t>
         </is>
       </c>
       <c r="B132" s="281" t="inlineStr">
@@ -21610,12 +21159,12 @@
       </c>
       <c r="D132" s="283" t="inlineStr">
         <is>
-          <t>18.01.02</t>
+          <t>18.01.03</t>
         </is>
       </c>
       <c r="E132" s="284" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="F132" s="285" t="n"/>
@@ -21623,10 +21172,10 @@
       <c r="H132" s="285" t="n"/>
       <c r="I132" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J132" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J132" s="1469" t="n"/>
       <c r="K132" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21664,12 +21213,12 @@
       </c>
       <c r="V132" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W132" s="285" t="n"/>
       <c r="X132" s="285" t="n"/>
-      <c r="Y132" s="1448" t="n"/>
+      <c r="Y132" s="1469" t="n"/>
       <c r="Z132" s="1304" t="n"/>
       <c r="AA132" s="285" t="inlineStr">
         <is>
@@ -21680,7 +21229,7 @@
     <row r="133" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A133" s="280" t="inlineStr">
         <is>
-          <t>MQ-124</t>
+          <t>MQ-125</t>
         </is>
       </c>
       <c r="B133" s="281" t="inlineStr">
@@ -21690,17 +21239,17 @@
       </c>
       <c r="C133" s="282" t="inlineStr">
         <is>
-          <t>Pavimentos</t>
+          <t>Bordillos</t>
         </is>
       </c>
       <c r="D133" s="283" t="inlineStr">
         <is>
-          <t>18.01.03</t>
+          <t>18.02.01</t>
         </is>
       </c>
       <c r="E133" s="284" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="F133" s="285" t="n"/>
@@ -21708,10 +21257,10 @@
       <c r="H133" s="285" t="n"/>
       <c r="I133" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J133" s="1448" t="n"/>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="J133" s="1469" t="n"/>
       <c r="K133" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21749,12 +21298,12 @@
       </c>
       <c r="V133" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W133" s="285" t="n"/>
       <c r="X133" s="285" t="n"/>
-      <c r="Y133" s="1448" t="n"/>
+      <c r="Y133" s="1469" t="n"/>
       <c r="Z133" s="1304" t="n"/>
       <c r="AA133" s="285" t="inlineStr">
         <is>
@@ -21765,7 +21314,7 @@
     <row r="134" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A134" s="280" t="inlineStr">
         <is>
-          <t>MQ-125</t>
+          <t>MQ-126</t>
         </is>
       </c>
       <c r="B134" s="281" t="inlineStr">
@@ -21775,17 +21324,17 @@
       </c>
       <c r="C134" s="282" t="inlineStr">
         <is>
-          <t>Bordillos</t>
+          <t>Drenajes</t>
         </is>
       </c>
       <c r="D134" s="283" t="inlineStr">
         <is>
-          <t>18.02.01</t>
+          <t>18.03.01</t>
         </is>
       </c>
       <c r="E134" s="284" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="F134" s="285" t="n"/>
@@ -21793,10 +21342,10 @@
       <c r="H134" s="285" t="n"/>
       <c r="I134" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="J134" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J134" s="1469" t="n"/>
       <c r="K134" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21834,12 +21383,12 @@
       </c>
       <c r="V134" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W134" s="285" t="n"/>
       <c r="X134" s="285" t="n"/>
-      <c r="Y134" s="1448" t="n"/>
+      <c r="Y134" s="1469" t="n"/>
       <c r="Z134" s="1304" t="n"/>
       <c r="AA134" s="285" t="inlineStr">
         <is>
@@ -21850,7 +21399,7 @@
     <row r="135" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A135" s="280" t="inlineStr">
         <is>
-          <t>MQ-126</t>
+          <t>MQ-127</t>
         </is>
       </c>
       <c r="B135" s="281" t="inlineStr">
@@ -21860,17 +21409,17 @@
       </c>
       <c r="C135" s="282" t="inlineStr">
         <is>
-          <t>Drenajes</t>
+          <t>Paisajismo</t>
         </is>
       </c>
       <c r="D135" s="283" t="inlineStr">
         <is>
-          <t>18.03.01</t>
+          <t>18.04.01</t>
         </is>
       </c>
       <c r="E135" s="284" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="F135" s="285" t="n"/>
@@ -21878,10 +21427,10 @@
       <c r="H135" s="285" t="n"/>
       <c r="I135" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J135" s="1448" t="n"/>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="J135" s="1469" t="n"/>
       <c r="K135" s="1438" t="n">
         <v>0</v>
       </c>
@@ -21919,12 +21468,12 @@
       </c>
       <c r="V135" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="W135" s="285" t="n"/>
       <c r="X135" s="285" t="n"/>
-      <c r="Y135" s="1448" t="n"/>
+      <c r="Y135" s="1469" t="n"/>
       <c r="Z135" s="1304" t="n"/>
       <c r="AA135" s="285" t="inlineStr">
         <is>
@@ -21935,7 +21484,7 @@
     <row r="136" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A136" s="280" t="inlineStr">
         <is>
-          <t>MQ-127</t>
+          <t>MQ-128</t>
         </is>
       </c>
       <c r="B136" s="281" t="inlineStr">
@@ -21950,12 +21499,12 @@
       </c>
       <c r="D136" s="283" t="inlineStr">
         <is>
-          <t>18.04.01</t>
+          <t>18.04.02</t>
         </is>
       </c>
       <c r="E136" s="284" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="F136" s="285" t="n"/>
@@ -21963,10 +21512,10 @@
       <c r="H136" s="285" t="n"/>
       <c r="I136" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="J136" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J136" s="1469" t="n"/>
       <c r="K136" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22004,12 +21553,12 @@
       </c>
       <c r="V136" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W136" s="285" t="n"/>
       <c r="X136" s="285" t="n"/>
-      <c r="Y136" s="1448" t="n"/>
+      <c r="Y136" s="1469" t="n"/>
       <c r="Z136" s="1304" t="n"/>
       <c r="AA136" s="285" t="inlineStr">
         <is>
@@ -22020,27 +21569,27 @@
     <row r="137" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A137" s="280" t="inlineStr">
         <is>
-          <t>MQ-128</t>
+          <t>MQ-129</t>
         </is>
       </c>
       <c r="B137" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C137" s="282" t="inlineStr">
         <is>
-          <t>Paisajismo</t>
+          <t>Metálicas</t>
         </is>
       </c>
       <c r="D137" s="283" t="inlineStr">
         <is>
-          <t>18.04.02</t>
+          <t>19.01.01</t>
         </is>
       </c>
       <c r="E137" s="284" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="F137" s="285" t="n"/>
@@ -22051,7 +21600,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J137" s="1448" t="n"/>
+      <c r="J137" s="1469" t="n"/>
       <c r="K137" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22094,7 +21643,7 @@
       </c>
       <c r="W137" s="285" t="n"/>
       <c r="X137" s="285" t="n"/>
-      <c r="Y137" s="1448" t="n"/>
+      <c r="Y137" s="1469" t="n"/>
       <c r="Z137" s="1304" t="n"/>
       <c r="AA137" s="285" t="inlineStr">
         <is>
@@ -22105,7 +21654,7 @@
     <row r="138" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A138" s="280" t="inlineStr">
         <is>
-          <t>MQ-129</t>
+          <t>MQ-130</t>
         </is>
       </c>
       <c r="B138" s="281" t="inlineStr">
@@ -22120,12 +21669,12 @@
       </c>
       <c r="D138" s="283" t="inlineStr">
         <is>
-          <t>19.01.01</t>
+          <t>19.01.02</t>
         </is>
       </c>
       <c r="E138" s="284" t="inlineStr">
         <is>
-          <t>Rejas metálicas</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="F138" s="285" t="n"/>
@@ -22133,10 +21682,10 @@
       <c r="H138" s="285" t="n"/>
       <c r="I138" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J138" s="1448" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="J138" s="1469" t="n"/>
       <c r="K138" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22174,12 +21723,12 @@
       </c>
       <c r="V138" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W138" s="285" t="n"/>
       <c r="X138" s="285" t="n"/>
-      <c r="Y138" s="1448" t="n"/>
+      <c r="Y138" s="1469" t="n"/>
       <c r="Z138" s="1304" t="n"/>
       <c r="AA138" s="285" t="inlineStr">
         <is>
@@ -22190,7 +21739,7 @@
     <row r="139" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A139" s="280" t="inlineStr">
         <is>
-          <t>MQ-130</t>
+          <t>MQ-131</t>
         </is>
       </c>
       <c r="B139" s="281" t="inlineStr">
@@ -22205,12 +21754,12 @@
       </c>
       <c r="D139" s="283" t="inlineStr">
         <is>
-          <t>19.01.02</t>
+          <t>19.01.03</t>
         </is>
       </c>
       <c r="E139" s="284" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="F139" s="285" t="n"/>
@@ -22221,7 +21770,7 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="J139" s="1448" t="n"/>
+      <c r="J139" s="1469" t="n"/>
       <c r="K139" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22264,7 +21813,7 @@
       </c>
       <c r="W139" s="285" t="n"/>
       <c r="X139" s="285" t="n"/>
-      <c r="Y139" s="1448" t="n"/>
+      <c r="Y139" s="1469" t="n"/>
       <c r="Z139" s="1304" t="n"/>
       <c r="AA139" s="285" t="inlineStr">
         <is>
@@ -22275,7 +21824,7 @@
     <row r="140" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A140" s="280" t="inlineStr">
         <is>
-          <t>MQ-131</t>
+          <t>MQ-132</t>
         </is>
       </c>
       <c r="B140" s="281" t="inlineStr">
@@ -22285,17 +21834,17 @@
       </c>
       <c r="C140" s="282" t="inlineStr">
         <is>
-          <t>Metálicas</t>
+          <t>Mobiliario</t>
         </is>
       </c>
       <c r="D140" s="283" t="inlineStr">
         <is>
-          <t>19.01.03</t>
+          <t>19.02.01</t>
         </is>
       </c>
       <c r="E140" s="284" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Mobiliario fijo de obra</t>
         </is>
       </c>
       <c r="F140" s="285" t="n"/>
@@ -22303,10 +21852,10 @@
       <c r="H140" s="285" t="n"/>
       <c r="I140" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="J140" s="1448" t="n"/>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J140" s="1469" t="n"/>
       <c r="K140" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22344,12 +21893,12 @@
       </c>
       <c r="V140" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W140" s="285" t="n"/>
       <c r="X140" s="285" t="n"/>
-      <c r="Y140" s="1448" t="n"/>
+      <c r="Y140" s="1469" t="n"/>
       <c r="Z140" s="1304" t="n"/>
       <c r="AA140" s="285" t="inlineStr">
         <is>
@@ -22360,27 +21909,27 @@
     <row r="141" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A141" s="280" t="inlineStr">
         <is>
-          <t>MQ-132</t>
+          <t>MQ-133</t>
         </is>
       </c>
       <c r="B141" s="281" t="inlineStr">
         <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C141" s="282" t="inlineStr">
         <is>
-          <t>Mobiliario</t>
+          <t>Limpieza</t>
         </is>
       </c>
       <c r="D141" s="283" t="inlineStr">
         <is>
-          <t>19.02.01</t>
+          <t>20.01.01</t>
         </is>
       </c>
       <c r="E141" s="284" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="F141" s="285" t="n"/>
@@ -22388,10 +21937,10 @@
       <c r="H141" s="285" t="n"/>
       <c r="I141" s="283" t="inlineStr">
         <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J141" s="1448" t="n"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="J141" s="1469" t="n"/>
       <c r="K141" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22429,12 +21978,12 @@
       </c>
       <c r="V141" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W141" s="285" t="n"/>
       <c r="X141" s="285" t="n"/>
-      <c r="Y141" s="1448" t="n"/>
+      <c r="Y141" s="1469" t="n"/>
       <c r="Z141" s="1304" t="n"/>
       <c r="AA141" s="285" t="inlineStr">
         <is>
@@ -22445,7 +21994,7 @@
     <row r="142" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A142" s="280" t="inlineStr">
         <is>
-          <t>MQ-133</t>
+          <t>MQ-134</t>
         </is>
       </c>
       <c r="B142" s="281" t="inlineStr">
@@ -22460,12 +22009,12 @@
       </c>
       <c r="D142" s="283" t="inlineStr">
         <is>
-          <t>20.01.01</t>
+          <t>20.01.02</t>
         </is>
       </c>
       <c r="E142" s="284" t="inlineStr">
         <is>
-          <t>Limpieza gruesa y fina de obra</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="F142" s="285" t="n"/>
@@ -22476,7 +22025,7 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J142" s="1448" t="n"/>
+      <c r="J142" s="1469" t="n"/>
       <c r="K142" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22519,7 +22068,7 @@
       </c>
       <c r="W142" s="285" t="n"/>
       <c r="X142" s="285" t="n"/>
-      <c r="Y142" s="1448" t="n"/>
+      <c r="Y142" s="1469" t="n"/>
       <c r="Z142" s="1304" t="n"/>
       <c r="AA142" s="285" t="inlineStr">
         <is>
@@ -22530,7 +22079,7 @@
     <row r="143" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A143" s="280" t="inlineStr">
         <is>
-          <t>MQ-134</t>
+          <t>MQ-135</t>
         </is>
       </c>
       <c r="B143" s="281" t="inlineStr">
@@ -22540,17 +22089,17 @@
       </c>
       <c r="C143" s="282" t="inlineStr">
         <is>
-          <t>Limpieza</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D143" s="283" t="inlineStr">
         <is>
-          <t>20.01.02</t>
+          <t>20.02.01</t>
         </is>
       </c>
       <c r="E143" s="284" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="F143" s="285" t="n"/>
@@ -22558,10 +22107,10 @@
       <c r="H143" s="285" t="n"/>
       <c r="I143" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J143" s="1448" t="n"/>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="J143" s="1469" t="n"/>
       <c r="K143" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22599,12 +22148,12 @@
       </c>
       <c r="V143" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W143" s="285" t="n"/>
       <c r="X143" s="285" t="n"/>
-      <c r="Y143" s="1448" t="n"/>
+      <c r="Y143" s="1469" t="n"/>
       <c r="Z143" s="1304" t="n"/>
       <c r="AA143" s="285" t="inlineStr">
         <is>
@@ -22615,7 +22164,7 @@
     <row r="144" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A144" s="280" t="inlineStr">
         <is>
-          <t>MQ-135</t>
+          <t>MQ-136</t>
         </is>
       </c>
       <c r="B144" s="281" t="inlineStr">
@@ -22625,7 +22174,7 @@
       </c>
       <c r="C144" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D144" s="283" t="inlineStr">
@@ -22635,7 +22184,7 @@
       </c>
       <c r="E144" s="284" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="F144" s="285" t="n"/>
@@ -22646,7 +22195,7 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="J144" s="1448" t="n"/>
+      <c r="J144" s="1469" t="n"/>
       <c r="K144" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22689,7 +22238,7 @@
       </c>
       <c r="W144" s="285" t="n"/>
       <c r="X144" s="285" t="n"/>
-      <c r="Y144" s="1448" t="n"/>
+      <c r="Y144" s="1469" t="n"/>
       <c r="Z144" s="1304" t="n"/>
       <c r="AA144" s="285" t="inlineStr">
         <is>
@@ -22700,7 +22249,7 @@
     <row r="145" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A145" s="280" t="inlineStr">
         <is>
-          <t>MQ-136</t>
+          <t>MQ-137</t>
         </is>
       </c>
       <c r="B145" s="281" t="inlineStr">
@@ -22710,17 +22259,17 @@
       </c>
       <c r="C145" s="282" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Entrega</t>
         </is>
       </c>
       <c r="D145" s="283" t="inlineStr">
         <is>
-          <t>20.02.01</t>
+          <t>20.02.02</t>
         </is>
       </c>
       <c r="E145" s="284" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Entrega, manuales y acta de recibo</t>
         </is>
       </c>
       <c r="F145" s="285" t="n"/>
@@ -22731,7 +22280,7 @@
           <t>gl</t>
         </is>
       </c>
-      <c r="J145" s="1448" t="n"/>
+      <c r="J145" s="1469" t="n"/>
       <c r="K145" s="1438" t="n">
         <v>0</v>
       </c>
@@ -22774,7 +22323,7 @@
       </c>
       <c r="W145" s="285" t="n"/>
       <c r="X145" s="285" t="n"/>
-      <c r="Y145" s="1448" t="n"/>
+      <c r="Y145" s="1469" t="n"/>
       <c r="Z145" s="1304" t="n"/>
       <c r="AA145" s="285" t="inlineStr">
         <is>
@@ -22782,30 +22331,26 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="146">
       <c r="A146" s="280" t="inlineStr">
         <is>
-          <t>MQ-137</t>
+          <t>MQ-138</t>
         </is>
       </c>
       <c r="B146" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C146" s="282" t="inlineStr">
-        <is>
-          <t>Entrega</t>
-        </is>
-      </c>
+          <t>PRELIMINARES</t>
+        </is>
+      </c>
+      <c r="C146" s="282" t="n"/>
       <c r="D146" s="283" t="inlineStr">
         <is>
-          <t>20.02.02</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E146" s="284" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Desmantelamiento de estructuras metálicas existentes</t>
         </is>
       </c>
       <c r="F146" s="285" t="n"/>
@@ -22813,80 +22358,34 @@
       <c r="H146" s="285" t="n"/>
       <c r="I146" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J146" s="1448" t="n"/>
-      <c r="K146" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P146" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q146" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R146" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" s="1438">
-        <f>IF(I146="","",ROUND(IF(OR(I146="m²",I146="m2"),K146*IF(L146=0,1,L146)*IF(O146=0,1,O146)*IF(P146=0,1,P146)*Q146-R146,IF(OR(I146="m³",I146="m3"),K146*L146*M146*IF(O146=0,1,O146)*IF(P146=0,1,P146)*Q146-R146,IF(OR(I146="ml",I146="ML"),K146*IF(O146=0,1,O146)*IF(P146=0,1,P146)*Q146-R146,IF(OR(I146="und",I146="UND"),IF(O146=0,1,O146)*IF(P146=0,1,P146)*Q146-R146,IF(I146="kg",K146*IF(O146=0,1,O146)*IF(P146=0,1,P146)*Q146-R146,IF(OR(I146="gl",I146="GL",I146="gb",I146="GB",I146="Gl",I146="Gb"),IF(O146=0,1,O146)*IF(P146=0,1,P146)*Q146-R146,0)))))),3))</f>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA146" s="336">
+        <f>I4</f>
         <v/>
-      </c>
-      <c r="U146" s="1438">
-        <f>IF(T146="","",ROUND(T146*(1+S146),3))</f>
-        <v/>
-      </c>
-      <c r="V146" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="W146" s="285" t="n"/>
-      <c r="X146" s="285" t="n"/>
-      <c r="Y146" s="1448" t="n"/>
-      <c r="Z146" s="1304" t="n"/>
-      <c r="AA146" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="280" t="inlineStr">
         <is>
-          <t>MQ-138</t>
+          <t>MQ-139</t>
         </is>
       </c>
       <c r="B147" s="281" t="inlineStr">
         <is>
-          <t>PRELIMINARES</t>
+          <t>ESTRUCTURA</t>
         </is>
       </c>
       <c r="C147" s="282" t="n"/>
       <c r="D147" s="283" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="E147" s="284" t="inlineStr">
         <is>
-          <t>Desmantelamiento de estructuras metálicas existentes</t>
+          <t>Grouting cementoso para reparación estructural</t>
         </is>
       </c>
       <c r="F147" s="285" t="n"/>
@@ -22894,18 +22393,14 @@
       <c r="H147" s="285" t="n"/>
       <c r="I147" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA147" s="336">
-        <f>I4</f>
-        <v/>
+          <t>m2</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="280" t="inlineStr">
         <is>
-          <t>MQ-139</t>
+          <t>MQ-140</t>
         </is>
       </c>
       <c r="B148" s="281" t="inlineStr">
@@ -22916,12 +22411,12 @@
       <c r="C148" s="282" t="n"/>
       <c r="D148" s="283" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E148" s="284" t="inlineStr">
         <is>
-          <t>Grouting cementoso para reparación estructural</t>
+          <t>Grouting epóxico para reparación estructural</t>
         </is>
       </c>
       <c r="F148" s="285" t="n"/>
@@ -22936,23 +22431,23 @@
     <row r="149">
       <c r="A149" s="280" t="inlineStr">
         <is>
-          <t>MQ-140</t>
+          <t>MQ-141</t>
         </is>
       </c>
       <c r="B149" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C149" s="282" t="n"/>
       <c r="D149" s="283" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="E149" s="284" t="inlineStr">
         <is>
-          <t>Grouting epóxico para reparación estructural</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="F149" s="285" t="n"/>
@@ -22967,7 +22462,7 @@
     <row r="150">
       <c r="A150" s="280" t="inlineStr">
         <is>
-          <t>MQ-141</t>
+          <t>MQ-142</t>
         </is>
       </c>
       <c r="B150" s="281" t="inlineStr">
@@ -22978,12 +22473,12 @@
       <c r="C150" s="282" t="n"/>
       <c r="D150" s="283" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="E150" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
         </is>
       </c>
       <c r="F150" s="285" t="n"/>
@@ -22998,23 +22493,23 @@
     <row r="151">
       <c r="A151" s="280" t="inlineStr">
         <is>
-          <t>MQ-142</t>
+          <t>MQ-143</t>
         </is>
       </c>
       <c r="B151" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C151" s="282" t="n"/>
       <c r="D151" s="283" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="E151" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="F151" s="285" t="n"/>
@@ -23029,7 +22524,7 @@
     <row r="152">
       <c r="A152" s="280" t="inlineStr">
         <is>
-          <t>MQ-143</t>
+          <t>MQ-144</t>
         </is>
       </c>
       <c r="B152" s="281" t="inlineStr">
@@ -23040,12 +22535,12 @@
       <c r="C152" s="282" t="n"/>
       <c r="D152" s="283" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="E152" s="284" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
         </is>
       </c>
       <c r="F152" s="285" t="n"/>
@@ -23060,23 +22555,23 @@
     <row r="153">
       <c r="A153" s="280" t="inlineStr">
         <is>
-          <t>MQ-144</t>
+          <t>MQ-145</t>
         </is>
       </c>
       <c r="B153" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C153" s="282" t="n"/>
       <c r="D153" s="283" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E153" s="284" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
         </is>
       </c>
       <c r="F153" s="285" t="n"/>
@@ -23091,23 +22586,23 @@
     <row r="154">
       <c r="A154" s="280" t="inlineStr">
         <is>
-          <t>MQ-145</t>
+          <t>MQ-146</t>
         </is>
       </c>
       <c r="B154" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C154" s="282" t="n"/>
       <c r="D154" s="283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="E154" s="284" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="F154" s="285" t="n"/>
@@ -23122,7 +22617,7 @@
     <row r="155">
       <c r="A155" s="280" t="inlineStr">
         <is>
-          <t>MQ-146</t>
+          <t>MQ-147</t>
         </is>
       </c>
       <c r="B155" s="281" t="inlineStr">
@@ -23133,12 +22628,12 @@
       <c r="C155" s="282" t="n"/>
       <c r="D155" s="283" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="E155" s="284" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="F155" s="285" t="n"/>
@@ -23153,7 +22648,7 @@
     <row r="156">
       <c r="A156" s="280" t="inlineStr">
         <is>
-          <t>MQ-147</t>
+          <t>MQ-148</t>
         </is>
       </c>
       <c r="B156" s="281" t="inlineStr">
@@ -23164,12 +22659,12 @@
       <c r="C156" s="282" t="n"/>
       <c r="D156" s="283" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="E156" s="284" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Enchape en granito pulido</t>
         </is>
       </c>
       <c r="F156" s="285" t="n"/>
@@ -23184,23 +22679,23 @@
     <row r="157">
       <c r="A157" s="280" t="inlineStr">
         <is>
-          <t>MQ-148</t>
+          <t>MQ-149</t>
         </is>
       </c>
       <c r="B157" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C157" s="282" t="n"/>
       <c r="D157" s="283" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="E157" s="284" t="inlineStr">
         <is>
-          <t>Enchape en granito pulido</t>
+          <t>Puerta antipánico</t>
         </is>
       </c>
       <c r="F157" s="285" t="n"/>
@@ -23208,30 +22703,30 @@
       <c r="H157" s="285" t="n"/>
       <c r="I157" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="280" t="inlineStr">
         <is>
-          <t>MQ-149</t>
+          <t>MQ-150</t>
         </is>
       </c>
       <c r="B158" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C158" s="282" t="n"/>
       <c r="D158" s="283" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="E158" s="284" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Orinal institucional</t>
         </is>
       </c>
       <c r="F158" s="285" t="n"/>
@@ -23246,23 +22741,23 @@
     <row r="159">
       <c r="A159" s="280" t="inlineStr">
         <is>
-          <t>MQ-150</t>
+          <t>MQ-151</t>
         </is>
       </c>
       <c r="B159" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C159" s="282" t="n"/>
       <c r="D159" s="283" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="E159" s="284" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="F159" s="285" t="n"/>
@@ -23270,14 +22765,14 @@
       <c r="H159" s="285" t="n"/>
       <c r="I159" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="280" t="inlineStr">
         <is>
-          <t>MQ-151</t>
+          <t>MQ-152</t>
         </is>
       </c>
       <c r="B160" s="281" t="inlineStr">
@@ -23288,12 +22783,12 @@
       <c r="C160" s="282" t="n"/>
       <c r="D160" s="283" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="E160" s="284" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="F160" s="285" t="n"/>
@@ -23301,14 +22796,14 @@
       <c r="H160" s="285" t="n"/>
       <c r="I160" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="280" t="inlineStr">
         <is>
-          <t>MQ-152</t>
+          <t>MQ-153</t>
         </is>
       </c>
       <c r="B161" s="281" t="inlineStr">
@@ -23319,12 +22814,12 @@
       <c r="C161" s="282" t="n"/>
       <c r="D161" s="283" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="E161" s="284" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="F161" s="285" t="n"/>
@@ -23332,14 +22827,14 @@
       <c r="H161" s="285" t="n"/>
       <c r="I161" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="280" t="inlineStr">
         <is>
-          <t>MQ-153</t>
+          <t>MQ-154</t>
         </is>
       </c>
       <c r="B162" s="281" t="inlineStr">
@@ -23350,12 +22845,12 @@
       <c r="C162" s="282" t="n"/>
       <c r="D162" s="283" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="E162" s="284" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Revegetalización / empradización</t>
         </is>
       </c>
       <c r="F162" s="285" t="n"/>
@@ -23363,30 +22858,30 @@
       <c r="H162" s="285" t="n"/>
       <c r="I162" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="280" t="inlineStr">
         <is>
-          <t>MQ-154</t>
+          <t>MQ-155</t>
         </is>
       </c>
       <c r="B163" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>ESTRUCTURA</t>
         </is>
       </c>
       <c r="C163" s="282" t="n"/>
       <c r="D163" s="283" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="E163" s="284" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Concreto premezclado o de planta (suministro)</t>
         </is>
       </c>
       <c r="F163" s="285" t="n"/>
@@ -23394,30 +22889,30 @@
       <c r="H163" s="285" t="n"/>
       <c r="I163" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="280" t="inlineStr">
         <is>
-          <t>MQ-155</t>
+          <t>MQ-157</t>
         </is>
       </c>
       <c r="B164" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C164" s="282" t="n"/>
       <c r="D164" s="283" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="E164" s="284" t="inlineStr">
         <is>
-          <t>Concreto premezclado o de planta (suministro)</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="F164" s="285" t="n"/>
@@ -23425,14 +22920,14 @@
       <c r="H164" s="285" t="n"/>
       <c r="I164" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>gl</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="280" t="inlineStr">
         <is>
-          <t>MQ-157</t>
+          <t>MQ-158</t>
         </is>
       </c>
       <c r="B165" s="281" t="inlineStr">
@@ -23443,12 +22938,12 @@
       <c r="C165" s="282" t="n"/>
       <c r="D165" s="283" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="E165" s="284" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="F165" s="285" t="n"/>
@@ -23463,7 +22958,7 @@
     <row r="166">
       <c r="A166" s="280" t="inlineStr">
         <is>
-          <t>MQ-158</t>
+          <t>MQ-159</t>
         </is>
       </c>
       <c r="B166" s="281" t="inlineStr">
@@ -23474,12 +22969,12 @@
       <c r="C166" s="282" t="n"/>
       <c r="D166" s="283" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E166" s="284" t="inlineStr">
         <is>
-          <t>Estudio de suelos y geotecnia</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="F166" s="285" t="n"/>
@@ -23494,7 +22989,7 @@
     <row r="167">
       <c r="A167" s="280" t="inlineStr">
         <is>
-          <t>MQ-159</t>
+          <t>MQ-160</t>
         </is>
       </c>
       <c r="B167" s="281" t="inlineStr">
@@ -23505,12 +23000,12 @@
       <c r="C167" s="282" t="n"/>
       <c r="D167" s="283" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="E167" s="284" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
         </is>
       </c>
       <c r="F167" s="285" t="n"/>
@@ -23525,23 +23020,23 @@
     <row r="168">
       <c r="A168" s="280" t="inlineStr">
         <is>
-          <t>MQ-160</t>
+          <t>MQ-161</t>
         </is>
       </c>
       <c r="B168" s="281" t="inlineStr">
         <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+          <t>ASCENSORES</t>
         </is>
       </c>
       <c r="C168" s="282" t="n"/>
       <c r="D168" s="283" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="E168" s="284" t="inlineStr">
         <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+          <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
       <c r="F168" s="285" t="n"/>
@@ -23549,43 +23044,12 @@
       <c r="H168" s="285" t="n"/>
       <c r="I168" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="280" t="inlineStr">
-        <is>
-          <t>MQ-161</t>
-        </is>
-      </c>
-      <c r="B169" s="281" t="inlineStr">
-        <is>
-          <t>ASCENSORES</t>
-        </is>
-      </c>
-      <c r="C169" s="282" t="n"/>
-      <c r="D169" s="283" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="E169" s="284" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
-        </is>
-      </c>
-      <c r="F169" s="285" t="n"/>
-      <c r="G169" s="285" t="n"/>
-      <c r="H169" s="285" t="n"/>
-      <c r="I169" s="283" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1446" t="inlineStr">
+      <c r="A169" s="1446" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
@@ -34333,10 +33797,10 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E1:M1"/>
     <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="E1:M1"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>

--- a/public/plantilla-cantidades.xlsx
+++ b/public/plantilla-cantidades.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructivo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$AA$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cantidades de Obra'!$A$8:$AA$164</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -10931,7 +10931,7 @@
     <tabColor rgb="FF1565C0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB169"/>
+  <dimension ref="A1:AB164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="615" min="1" max="1"/>
@@ -12953,7 +12953,7 @@
       <c r="D29" s="283" t="n"/>
       <c r="E29" s="284" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 175 kg/cm² (2500 PSI), incluye vaciado y vibrado</t>
+          <t>Concreto de f'c = 175 kg/cm² (2500 PSI), incluye vaciado</t>
         </is>
       </c>
       <c r="F29" s="285" t="n"/>
@@ -13000,7 +13000,7 @@
       <c r="D30" s="283" t="n"/>
       <c r="E30" s="284" t="inlineStr">
         <is>
-          <t>Concreto ciclópeo, incluye vaciado y vibrado</t>
+          <t>Concreto ciclópeo, incluye vaciado</t>
         </is>
       </c>
       <c r="F30" s="285" t="n"/>
@@ -13267,30 +13267,22 @@
       <c r="Y35" s="1469" t="n"/>
       <c r="Z35" s="1304" t="n"/>
     </row>
-    <row r="36" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="36">
       <c r="A36" s="280" t="inlineStr">
         <is>
-          <t>MQ-027</t>
+          <t>MQ-018</t>
         </is>
       </c>
       <c r="B36" s="281" t="inlineStr">
         <is>
-          <t>CIMENTACIONES</t>
-        </is>
-      </c>
-      <c r="C36" s="282" t="inlineStr">
-        <is>
-          <t>Formaleta</t>
-        </is>
-      </c>
-      <c r="D36" s="283" t="inlineStr">
-        <is>
-          <t>03.03.01</t>
-        </is>
-      </c>
+          <t>ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C36" s="282" t="n"/>
+      <c r="D36" s="283" t="n"/>
       <c r="E36" s="284" t="inlineStr">
         <is>
-          <t>Formaleta para elementos de cimentación</t>
+          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado — Estructura</t>
         </is>
       </c>
       <c r="F36" s="285" t="n"/>
@@ -13298,64 +13290,34 @@
       <c r="H36" s="285" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="J36" s="1469" t="n"/>
-      <c r="K36" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1303" t="n">
-        <v>0</v>
-      </c>
+      <c r="K36" s="1438" t="n"/>
+      <c r="L36" s="1438" t="n"/>
+      <c r="M36" s="1438" t="n"/>
+      <c r="N36" s="1438" t="n"/>
+      <c r="O36" s="1438" t="n"/>
+      <c r="P36" s="1438" t="n"/>
+      <c r="Q36" s="1438" t="n"/>
+      <c r="R36" s="1438" t="n"/>
+      <c r="S36" s="1303" t="n"/>
       <c r="T36" s="1438">
         <f>IF(I36="","",ROUND(IF(OR(I36="m²",I36="m2"),K36*IF(L36=0,1,L36)*IF(O36=0,1,O36)*IF(P36=0,1,P36)*Q36-R36,IF(OR(I36="m³",I36="m3"),K36*L36*M36*IF(O36=0,1,O36)*IF(P36=0,1,P36)*Q36-R36,IF(OR(I36="ml",I36="ML"),K36*IF(O36=0,1,O36)*IF(P36=0,1,P36)*Q36-R36,IF(OR(I36="und",I36="UND"),IF(O36=0,1,O36)*IF(P36=0,1,P36)*Q36-R36,IF(I36="kg",K36*IF(O36=0,1,O36)*IF(P36=0,1,P36)*Q36-R36,IF(OR(I36="gl",I36="GL",I36="gb",I36="GB",I36="Gl",I36="Gb"),IF(O36=0,1,O36)*IF(P36=0,1,P36)*Q36-R36,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U36" s="1438">
-        <f>IF(T36="","",ROUND(T36*(1+S36),3))</f>
-        <v/>
-      </c>
-      <c r="V36" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="U36" s="1438" t="n"/>
+      <c r="V36" s="283" t="n"/>
       <c r="W36" s="285" t="n"/>
       <c r="X36" s="285" t="n"/>
       <c r="Y36" s="1469" t="n"/>
       <c r="Z36" s="1304" t="n"/>
-      <c r="AA36" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="280" t="inlineStr">
         <is>
-          <t>MQ-018</t>
+          <t>MQ-019</t>
         </is>
       </c>
       <c r="B37" s="281" t="inlineStr">
@@ -13367,7 +13329,7 @@
       <c r="D37" s="283" t="n"/>
       <c r="E37" s="284" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado — Estructura</t>
+          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado — Estructura</t>
         </is>
       </c>
       <c r="F37" s="285" t="n"/>
@@ -13402,7 +13364,7 @@
     <row r="38">
       <c r="A38" s="280" t="inlineStr">
         <is>
-          <t>MQ-019</t>
+          <t>MQ-020</t>
         </is>
       </c>
       <c r="B38" s="281" t="inlineStr">
@@ -13414,7 +13376,7 @@
       <c r="D38" s="283" t="n"/>
       <c r="E38" s="284" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado — Estructura</t>
+          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado — Estructura</t>
         </is>
       </c>
       <c r="F38" s="285" t="n"/>
@@ -13449,7 +13411,7 @@
     <row r="39">
       <c r="A39" s="280" t="inlineStr">
         <is>
-          <t>MQ-020</t>
+          <t>MQ-021</t>
         </is>
       </c>
       <c r="B39" s="281" t="inlineStr">
@@ -13461,7 +13423,7 @@
       <c r="D39" s="283" t="n"/>
       <c r="E39" s="284" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado — Estructura</t>
+          <t>Concreto de f'c = 420 kg/cm² (6000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="F39" s="285" t="n"/>
@@ -13496,7 +13458,7 @@
     <row r="40">
       <c r="A40" s="280" t="inlineStr">
         <is>
-          <t>MQ-021</t>
+          <t>MQ-022</t>
         </is>
       </c>
       <c r="B40" s="281" t="inlineStr">
@@ -13508,7 +13470,7 @@
       <c r="D40" s="283" t="n"/>
       <c r="E40" s="284" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 420 kg/cm² (6000 PSI), incluye vaciado y vibrado</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI — Estructura</t>
         </is>
       </c>
       <c r="F40" s="285" t="n"/>
@@ -13516,7 +13478,7 @@
       <c r="H40" s="285" t="n"/>
       <c r="I40" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J40" s="1469" t="n"/>
@@ -13543,7 +13505,7 @@
     <row r="41">
       <c r="A41" s="280" t="inlineStr">
         <is>
-          <t>MQ-022</t>
+          <t>MQ-023</t>
         </is>
       </c>
       <c r="B41" s="281" t="inlineStr">
@@ -13555,7 +13517,7 @@
       <c r="D41" s="283" t="n"/>
       <c r="E41" s="284" t="inlineStr">
         <is>
-          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI — Estructura</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI — Estructura</t>
         </is>
       </c>
       <c r="F41" s="285" t="n"/>
@@ -13587,10 +13549,10 @@
       <c r="Y41" s="1469" t="n"/>
       <c r="Z41" s="1304" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A42" s="280" t="inlineStr">
         <is>
-          <t>MQ-023</t>
+          <t>MQ-040</t>
         </is>
       </c>
       <c r="B42" s="281" t="inlineStr">
@@ -13598,11 +13560,19 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C42" s="282" t="n"/>
-      <c r="D42" s="283" t="n"/>
+      <c r="C42" s="282" t="inlineStr">
+        <is>
+          <t>Estructura metálica</t>
+        </is>
+      </c>
+      <c r="D42" s="283" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
       <c r="E42" s="284" t="inlineStr">
         <is>
-          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI — Estructura</t>
+          <t>Suministro y montaje de perfiles metálicos</t>
         </is>
       </c>
       <c r="F42" s="285" t="n"/>
@@ -13614,30 +13584,60 @@
         </is>
       </c>
       <c r="J42" s="1469" t="n"/>
-      <c r="K42" s="1438" t="n"/>
-      <c r="L42" s="1438" t="n"/>
-      <c r="M42" s="1438" t="n"/>
-      <c r="N42" s="1438" t="n"/>
-      <c r="O42" s="1438" t="n"/>
-      <c r="P42" s="1438" t="n"/>
-      <c r="Q42" s="1438" t="n"/>
-      <c r="R42" s="1438" t="n"/>
-      <c r="S42" s="1303" t="n"/>
+      <c r="K42" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1303" t="n">
+        <v>0</v>
+      </c>
       <c r="T42" s="1438">
         <f>IF(I42="","",ROUND(IF(OR(I42="m²",I42="m2"),K42*IF(L42=0,1,L42)*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="m³",I42="m3"),K42*L42*M42*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="ml",I42="ML"),K42*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="und",I42="UND"),IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(I42="kg",K42*IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,IF(OR(I42="gl",I42="GL",I42="gb",I42="GB",I42="Gl",I42="Gb"),IF(O42=0,1,O42)*IF(P42=0,1,P42)*Q42-R42,0)))))),3))</f>
         <v/>
       </c>
-      <c r="U42" s="1438" t="n"/>
-      <c r="V42" s="283" t="n"/>
+      <c r="U42" s="1438">
+        <f>IF(T42="","",ROUND(T42*(1+S42),3))</f>
+        <v/>
+      </c>
+      <c r="V42" s="283" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="W42" s="285" t="n"/>
       <c r="X42" s="285" t="n"/>
       <c r="Y42" s="1469" t="n"/>
       <c r="Z42" s="1304" t="n"/>
+      <c r="AA42" s="285" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A43" s="280" t="inlineStr">
         <is>
-          <t>MQ-036</t>
+          <t>MQ-041</t>
         </is>
       </c>
       <c r="B43" s="281" t="inlineStr">
@@ -13647,17 +13647,17 @@
       </c>
       <c r="C43" s="282" t="inlineStr">
         <is>
-          <t>Formaleta</t>
+          <t>Estructura metálica</t>
         </is>
       </c>
       <c r="D43" s="283" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="E43" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de columnas</t>
+          <t>Placas, pernos y conexiones metálicas</t>
         </is>
       </c>
       <c r="F43" s="285" t="n"/>
@@ -13665,7 +13665,7 @@
       <c r="H43" s="285" t="n"/>
       <c r="I43" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J43" s="1469" t="n"/>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="V43" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W43" s="285" t="n"/>
@@ -13722,27 +13722,27 @@
     <row r="44" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A44" s="280" t="inlineStr">
         <is>
-          <t>MQ-037</t>
+          <t>MQ-042</t>
         </is>
       </c>
       <c r="B44" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C44" s="282" t="inlineStr">
         <is>
-          <t>Formaleta</t>
+          <t>Muros</t>
         </is>
       </c>
       <c r="D44" s="283" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="E44" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de vigas</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="F44" s="285" t="n"/>
@@ -13807,27 +13807,27 @@
     <row r="45" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A45" s="280" t="inlineStr">
         <is>
-          <t>MQ-038</t>
+          <t>MQ-043</t>
         </is>
       </c>
       <c r="B45" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C45" s="282" t="inlineStr">
         <is>
-          <t>Formaleta</t>
+          <t>Muros</t>
         </is>
       </c>
       <c r="D45" s="283" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="E45" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de losas</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="F45" s="285" t="n"/>
@@ -13892,27 +13892,27 @@
     <row r="46" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A46" s="280" t="inlineStr">
         <is>
-          <t>MQ-039</t>
+          <t>MQ-044</t>
         </is>
       </c>
       <c r="B46" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C46" s="282" t="inlineStr">
         <is>
-          <t>Formaleta</t>
+          <t>Muros</t>
         </is>
       </c>
       <c r="D46" s="283" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="E46" s="284" t="inlineStr">
         <is>
-          <t>Formaleta de escaleras</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="F46" s="285" t="n"/>
@@ -13977,27 +13977,27 @@
     <row r="47" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A47" s="280" t="inlineStr">
         <is>
-          <t>MQ-040</t>
+          <t>MQ-045</t>
         </is>
       </c>
       <c r="B47" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C47" s="282" t="inlineStr">
         <is>
-          <t>Estructura metálica</t>
+          <t>Muros</t>
         </is>
       </c>
       <c r="D47" s="283" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>05.01.04</t>
         </is>
       </c>
       <c r="E47" s="284" t="inlineStr">
         <is>
-          <t>Suministro y montaje de perfiles metálicos</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="F47" s="285" t="n"/>
@@ -14005,7 +14005,7 @@
       <c r="H47" s="285" t="n"/>
       <c r="I47" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J47" s="1469" t="n"/>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="V47" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W47" s="285" t="n"/>
@@ -14062,27 +14062,27 @@
     <row r="48" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A48" s="280" t="inlineStr">
         <is>
-          <t>MQ-041</t>
+          <t>MQ-046</t>
         </is>
       </c>
       <c r="B48" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>MAMPOSTERÍA</t>
         </is>
       </c>
       <c r="C48" s="282" t="inlineStr">
         <is>
-          <t>Estructura metálica</t>
+          <t>Complementarios</t>
         </is>
       </c>
       <c r="D48" s="283" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>05.02.01</t>
         </is>
       </c>
       <c r="E48" s="284" t="inlineStr">
         <is>
-          <t>Placas, pernos y conexiones metálicas</t>
+          <t>Dinteles sobre vanos</t>
         </is>
       </c>
       <c r="F48" s="285" t="n"/>
@@ -14090,7 +14090,7 @@
       <c r="H48" s="285" t="n"/>
       <c r="I48" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J48" s="1469" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="V48" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W48" s="285" t="n"/>
@@ -14147,7 +14147,7 @@
     <row r="49" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A49" s="280" t="inlineStr">
         <is>
-          <t>MQ-042</t>
+          <t>MQ-047</t>
         </is>
       </c>
       <c r="B49" s="281" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="C49" s="282" t="inlineStr">
         <is>
-          <t>Muros</t>
+          <t>Complementarios</t>
         </is>
       </c>
       <c r="D49" s="283" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>05.02.02</t>
         </is>
       </c>
       <c r="E49" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en bloque de concreto</t>
+          <t>Alfajías y remates</t>
         </is>
       </c>
       <c r="F49" s="285" t="n"/>
@@ -14175,7 +14175,7 @@
       <c r="H49" s="285" t="n"/>
       <c r="I49" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J49" s="1469" t="n"/>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="V49" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W49" s="285" t="n"/>
@@ -14232,7 +14232,7 @@
     <row r="50" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A50" s="280" t="inlineStr">
         <is>
-          <t>MQ-043</t>
+          <t>MQ-048</t>
         </is>
       </c>
       <c r="B50" s="281" t="inlineStr">
@@ -14242,17 +14242,17 @@
       </c>
       <c r="C50" s="282" t="inlineStr">
         <is>
-          <t>Muros</t>
+          <t>Complementarios</t>
         </is>
       </c>
       <c r="D50" s="283" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>05.02.03</t>
         </is>
       </c>
       <c r="E50" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="F50" s="285" t="n"/>
@@ -14260,7 +14260,7 @@
       <c r="H50" s="285" t="n"/>
       <c r="I50" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J50" s="1469" t="n"/>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="V50" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W50" s="285" t="n"/>
@@ -14317,27 +14317,27 @@
     <row r="51" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A51" s="280" t="inlineStr">
         <is>
-          <t>MQ-044</t>
+          <t>MQ-049</t>
         </is>
       </c>
       <c r="B51" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C51" s="282" t="inlineStr">
         <is>
-          <t>Muros</t>
+          <t>Estructura</t>
         </is>
       </c>
       <c r="D51" s="283" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="E51" s="284" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="F51" s="285" t="n"/>
@@ -14345,7 +14345,7 @@
       <c r="H51" s="285" t="n"/>
       <c r="I51" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J51" s="1469" t="n"/>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="V51" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W51" s="285" t="n"/>
@@ -14402,27 +14402,27 @@
     <row r="52" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A52" s="280" t="inlineStr">
         <is>
-          <t>MQ-045</t>
+          <t>MQ-050</t>
         </is>
       </c>
       <c r="B52" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C52" s="282" t="inlineStr">
         <is>
-          <t>Muros</t>
+          <t>Estructura</t>
         </is>
       </c>
       <c r="D52" s="283" t="inlineStr">
         <is>
-          <t>05.01.04</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="E52" s="284" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="F52" s="285" t="n"/>
@@ -14430,7 +14430,7 @@
       <c r="H52" s="285" t="n"/>
       <c r="I52" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J52" s="1469" t="n"/>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="V52" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W52" s="285" t="n"/>
@@ -14487,27 +14487,27 @@
     <row r="53" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A53" s="280" t="inlineStr">
         <is>
-          <t>MQ-046</t>
+          <t>MQ-051</t>
         </is>
       </c>
       <c r="B53" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C53" s="282" t="inlineStr">
         <is>
-          <t>Complementarios</t>
+          <t>Cubierta</t>
         </is>
       </c>
       <c r="D53" s="283" t="inlineStr">
         <is>
-          <t>05.02.01</t>
+          <t>06.02.01</t>
         </is>
       </c>
       <c r="E53" s="284" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="F53" s="285" t="n"/>
@@ -14515,7 +14515,7 @@
       <c r="H53" s="285" t="n"/>
       <c r="I53" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J53" s="1469" t="n"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="V53" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W53" s="285" t="n"/>
@@ -14572,27 +14572,27 @@
     <row r="54" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A54" s="280" t="inlineStr">
         <is>
-          <t>MQ-047</t>
+          <t>MQ-052</t>
         </is>
       </c>
       <c r="B54" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C54" s="282" t="inlineStr">
         <is>
-          <t>Complementarios</t>
+          <t>Cubierta</t>
         </is>
       </c>
       <c r="D54" s="283" t="inlineStr">
         <is>
-          <t>05.02.02</t>
+          <t>06.02.02</t>
         </is>
       </c>
       <c r="E54" s="284" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Impermeabilización de cubierta</t>
         </is>
       </c>
       <c r="F54" s="285" t="n"/>
@@ -14600,7 +14600,7 @@
       <c r="H54" s="285" t="n"/>
       <c r="I54" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J54" s="1469" t="n"/>
@@ -14641,7 +14641,7 @@
       </c>
       <c r="V54" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W54" s="285" t="n"/>
@@ -14657,27 +14657,27 @@
     <row r="55" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A55" s="280" t="inlineStr">
         <is>
-          <t>MQ-048</t>
+          <t>MQ-053</t>
         </is>
       </c>
       <c r="B55" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C55" s="282" t="inlineStr">
         <is>
-          <t>Complementarios</t>
+          <t>Cubierta</t>
         </is>
       </c>
       <c r="D55" s="283" t="inlineStr">
         <is>
-          <t>05.02.03</t>
+          <t>06.02.03</t>
         </is>
       </c>
       <c r="E55" s="284" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Aislamiento térmico/acústico</t>
         </is>
       </c>
       <c r="F55" s="285" t="n"/>
@@ -14685,7 +14685,7 @@
       <c r="H55" s="285" t="n"/>
       <c r="I55" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J55" s="1469" t="n"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="V55" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W55" s="285" t="n"/>
@@ -14742,7 +14742,7 @@
     <row r="56" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A56" s="280" t="inlineStr">
         <is>
-          <t>MQ-049</t>
+          <t>MQ-054</t>
         </is>
       </c>
       <c r="B56" s="281" t="inlineStr">
@@ -14752,17 +14752,17 @@
       </c>
       <c r="C56" s="282" t="inlineStr">
         <is>
-          <t>Estructura</t>
+          <t>Canales</t>
         </is>
       </c>
       <c r="D56" s="283" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>06.03.01</t>
         </is>
       </c>
       <c r="E56" s="284" t="inlineStr">
         <is>
-          <t>Estructura metálica o de madera para cubierta</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="F56" s="285" t="n"/>
@@ -14770,7 +14770,7 @@
       <c r="H56" s="285" t="n"/>
       <c r="I56" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J56" s="1469" t="n"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="V56" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W56" s="285" t="n"/>
@@ -14827,7 +14827,7 @@
     <row r="57" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A57" s="280" t="inlineStr">
         <is>
-          <t>MQ-050</t>
+          <t>MQ-055</t>
         </is>
       </c>
       <c r="B57" s="281" t="inlineStr">
@@ -14837,17 +14837,17 @@
       </c>
       <c r="C57" s="282" t="inlineStr">
         <is>
-          <t>Estructura</t>
+          <t>Canales</t>
         </is>
       </c>
       <c r="D57" s="283" t="inlineStr">
         <is>
-          <t>06.01.02</t>
+          <t>06.03.02</t>
         </is>
       </c>
       <c r="E57" s="284" t="inlineStr">
         <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="F57" s="285" t="n"/>
@@ -14855,7 +14855,7 @@
       <c r="H57" s="285" t="n"/>
       <c r="I57" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J57" s="1469" t="n"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="V57" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W57" s="285" t="n"/>
@@ -14912,27 +14912,27 @@
     <row r="58" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A58" s="280" t="inlineStr">
         <is>
-          <t>MQ-051</t>
+          <t>MQ-056</t>
         </is>
       </c>
       <c r="B58" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C58" s="282" t="inlineStr">
         <is>
-          <t>Cubierta</t>
+          <t>Superficies</t>
         </is>
       </c>
       <c r="D58" s="283" t="inlineStr">
         <is>
-          <t>06.02.01</t>
+          <t>07.01.01</t>
         </is>
       </c>
       <c r="E58" s="284" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="F58" s="285" t="n"/>
@@ -14997,27 +14997,27 @@
     <row r="59" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A59" s="280" t="inlineStr">
         <is>
-          <t>MQ-052</t>
+          <t>MQ-057</t>
         </is>
       </c>
       <c r="B59" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C59" s="282" t="inlineStr">
         <is>
-          <t>Cubierta</t>
+          <t>Superficies</t>
         </is>
       </c>
       <c r="D59" s="283" t="inlineStr">
         <is>
-          <t>06.02.02</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="E59" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de cubierta</t>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="F59" s="285" t="n"/>
@@ -15082,27 +15082,27 @@
     <row r="60" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A60" s="280" t="inlineStr">
         <is>
-          <t>MQ-053</t>
+          <t>MQ-058</t>
         </is>
       </c>
       <c r="B60" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C60" s="282" t="inlineStr">
         <is>
-          <t>Cubierta</t>
+          <t>Superficies</t>
         </is>
       </c>
       <c r="D60" s="283" t="inlineStr">
         <is>
-          <t>06.02.03</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="E60" s="284" t="inlineStr">
         <is>
-          <t>Aislamiento térmico/acústico</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="F60" s="285" t="n"/>
@@ -15167,27 +15167,27 @@
     <row r="61" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A61" s="280" t="inlineStr">
         <is>
-          <t>MQ-054</t>
+          <t>MQ-059</t>
         </is>
       </c>
       <c r="B61" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>PAÑETES Y REVOQUES</t>
         </is>
       </c>
       <c r="C61" s="282" t="inlineStr">
         <is>
-          <t>Canales</t>
+          <t>Pañetes</t>
         </is>
       </c>
       <c r="D61" s="283" t="inlineStr">
         <is>
-          <t>06.03.01</t>
+          <t>08.01.01</t>
         </is>
       </c>
       <c r="E61" s="284" t="inlineStr">
         <is>
-          <t>Canales de aguas lluvias</t>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="F61" s="285" t="n"/>
@@ -15195,7 +15195,7 @@
       <c r="H61" s="285" t="n"/>
       <c r="I61" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J61" s="1469" t="n"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="V61" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W61" s="285" t="n"/>
@@ -15252,27 +15252,27 @@
     <row r="62" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A62" s="280" t="inlineStr">
         <is>
-          <t>MQ-055</t>
+          <t>MQ-060</t>
         </is>
       </c>
       <c r="B62" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>PAÑETES Y REVOQUES</t>
         </is>
       </c>
       <c r="C62" s="282" t="inlineStr">
         <is>
-          <t>Canales</t>
+          <t>Pañetes</t>
         </is>
       </c>
       <c r="D62" s="283" t="inlineStr">
         <is>
-          <t>06.03.02</t>
+          <t>08.01.02</t>
         </is>
       </c>
       <c r="E62" s="284" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="F62" s="285" t="n"/>
@@ -15280,7 +15280,7 @@
       <c r="H62" s="285" t="n"/>
       <c r="I62" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J62" s="1469" t="n"/>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="V62" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W62" s="285" t="n"/>
@@ -15337,27 +15337,27 @@
     <row r="63" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A63" s="280" t="inlineStr">
         <is>
-          <t>MQ-056</t>
+          <t>MQ-061</t>
         </is>
       </c>
       <c r="B63" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
+          <t>PAÑETES Y REVOQUES</t>
         </is>
       </c>
       <c r="C63" s="282" t="inlineStr">
         <is>
-          <t>Superficies</t>
+          <t>Pañetes</t>
         </is>
       </c>
       <c r="D63" s="283" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>08.01.03</t>
         </is>
       </c>
       <c r="E63" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de losas y terrazas</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="F63" s="285" t="n"/>
@@ -15422,27 +15422,27 @@
     <row r="64" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A64" s="280" t="inlineStr">
         <is>
-          <t>MQ-057</t>
+          <t>MQ-062</t>
         </is>
       </c>
       <c r="B64" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C64" s="282" t="inlineStr">
         <is>
-          <t>Superficies</t>
+          <t>Pañetes</t>
         </is>
       </c>
       <c r="D64" s="283" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>08.01.04</t>
         </is>
       </c>
       <c r="E64" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de muros</t>
+          <t>Estuco plástico</t>
         </is>
       </c>
       <c r="F64" s="285" t="n"/>
@@ -15504,30 +15504,22 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="65">
       <c r="A65" s="280" t="inlineStr">
         <is>
-          <t>MQ-058</t>
+          <t>MQ-062B</t>
         </is>
       </c>
       <c r="B65" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
-      <c r="C65" s="282" t="inlineStr">
-        <is>
-          <t>Superficies</t>
-        </is>
-      </c>
-      <c r="D65" s="283" t="inlineStr">
-        <is>
-          <t>07.01.03</t>
-        </is>
-      </c>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="C65" s="282" t="n"/>
+      <c r="D65" s="283" t="n"/>
       <c r="E65" s="284" t="inlineStr">
         <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>Estuco tradicional</t>
         </is>
       </c>
       <c r="F65" s="285" t="n"/>
@@ -15538,81 +15530,31 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="J65" s="1469" t="n"/>
-      <c r="K65" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1438">
-        <f>IF(I65="","",ROUND(IF(OR(I65="m²",I65="m2"),K65*IF(L65=0,1,L65)*IF(O65=0,1,O65)*IF(P65=0,1,P65)*Q65-R65,IF(OR(I65="m³",I65="m3"),K65*L65*M65*IF(O65=0,1,O65)*IF(P65=0,1,P65)*Q65-R65,IF(OR(I65="ml",I65="ML"),K65*IF(O65=0,1,O65)*IF(P65=0,1,P65)*Q65-R65,IF(OR(I65="und",I65="UND"),IF(O65=0,1,O65)*IF(P65=0,1,P65)*Q65-R65,IF(I65="kg",K65*IF(O65=0,1,O65)*IF(P65=0,1,P65)*Q65-R65,IF(OR(I65="gl",I65="GL",I65="gb",I65="GB",I65="Gl",I65="Gb"),IF(O65=0,1,O65)*IF(P65=0,1,P65)*Q65-R65,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="U65" s="1438">
-        <f>IF(T65="","",ROUND(T65*(1+S65),3))</f>
-        <v/>
-      </c>
-      <c r="V65" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="W65" s="285" t="n"/>
-      <c r="X65" s="285" t="n"/>
-      <c r="Y65" s="1469" t="n"/>
-      <c r="Z65" s="1304" t="n"/>
-      <c r="AA65" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
     </row>
     <row r="66" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A66" s="280" t="inlineStr">
         <is>
-          <t>MQ-059</t>
+          <t>MQ-063</t>
         </is>
       </c>
       <c r="B66" s="281" t="inlineStr">
         <is>
-          <t>PAÑETES Y REVOQUES</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C66" s="282" t="inlineStr">
         <is>
-          <t>Pañetes</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="D66" s="283" t="inlineStr">
         <is>
-          <t>08.01.01</t>
+          <t>09.01.01</t>
         </is>
       </c>
       <c r="E66" s="284" t="inlineStr">
         <is>
-          <t>Pañete / revoque interior</t>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="F66" s="285" t="n"/>
@@ -15677,27 +15619,27 @@
     <row r="67" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A67" s="280" t="inlineStr">
         <is>
-          <t>MQ-060</t>
+          <t>MQ-064</t>
         </is>
       </c>
       <c r="B67" s="281" t="inlineStr">
         <is>
-          <t>PAÑETES Y REVOQUES</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C67" s="282" t="inlineStr">
         <is>
-          <t>Pañetes</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="D67" s="283" t="inlineStr">
         <is>
-          <t>08.01.02</t>
+          <t>09.01.02</t>
         </is>
       </c>
       <c r="E67" s="284" t="inlineStr">
         <is>
-          <t>Pañete / revoque exterior</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="F67" s="285" t="n"/>
@@ -15762,27 +15704,27 @@
     <row r="68" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A68" s="280" t="inlineStr">
         <is>
-          <t>MQ-061</t>
+          <t>MQ-065</t>
         </is>
       </c>
       <c r="B68" s="281" t="inlineStr">
         <is>
-          <t>PAÑETES Y REVOQUES</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C68" s="282" t="inlineStr">
         <is>
-          <t>Pañetes</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="D68" s="283" t="inlineStr">
         <is>
-          <t>08.01.03</t>
+          <t>09.01.03</t>
         </is>
       </c>
       <c r="E68" s="284" t="inlineStr">
         <is>
-          <t>Pañete impermeabilizado</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="F68" s="285" t="n"/>
@@ -15847,27 +15789,27 @@
     <row r="69" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A69" s="280" t="inlineStr">
         <is>
-          <t>MQ-062</t>
+          <t>MQ-066</t>
         </is>
       </c>
       <c r="B69" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C69" s="282" t="inlineStr">
         <is>
-          <t>Pañetes</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="D69" s="283" t="inlineStr">
         <is>
-          <t>08.01.04</t>
+          <t>09.01.04</t>
         </is>
       </c>
       <c r="E69" s="284" t="inlineStr">
         <is>
-          <t>Estuco plástico</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="F69" s="285" t="n"/>
@@ -15929,22 +15871,30 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A70" s="280" t="inlineStr">
         <is>
-          <t>MQ-062B</t>
+          <t>MQ-067</t>
         </is>
       </c>
       <c r="B70" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="C70" s="282" t="n"/>
-      <c r="D70" s="283" t="n"/>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C70" s="282" t="inlineStr">
+        <is>
+          <t>Pisos</t>
+        </is>
+      </c>
+      <c r="D70" s="283" t="inlineStr">
+        <is>
+          <t>09.01.05</t>
+        </is>
+      </c>
       <c r="E70" s="284" t="inlineStr">
         <is>
-          <t>Estuco tradicional</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="F70" s="285" t="n"/>
@@ -15955,11 +15905,61 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="J70" s="1469" t="n"/>
+      <c r="K70" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="1438" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1438">
+        <f>IF(I70="","",ROUND(IF(OR(I70="m²",I70="m2"),K70*IF(L70=0,1,L70)*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="m³",I70="m3"),K70*L70*M70*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="ml",I70="ML"),K70*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="und",I70="UND"),IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(I70="kg",K70*IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,IF(OR(I70="gl",I70="GL",I70="gb",I70="GB",I70="Gl",I70="Gb"),IF(O70=0,1,O70)*IF(P70=0,1,P70)*Q70-R70,0)))))),3))</f>
+        <v/>
+      </c>
+      <c r="U70" s="1438">
+        <f>IF(T70="","",ROUND(T70*(1+S70),3))</f>
+        <v/>
+      </c>
+      <c r="V70" s="283" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="W70" s="285" t="n"/>
+      <c r="X70" s="285" t="n"/>
+      <c r="Y70" s="1469" t="n"/>
+      <c r="Z70" s="1304" t="n"/>
+      <c r="AA70" s="285" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A71" s="280" t="inlineStr">
         <is>
-          <t>MQ-063</t>
+          <t>MQ-068</t>
         </is>
       </c>
       <c r="B71" s="281" t="inlineStr">
@@ -15969,17 +15969,17 @@
       </c>
       <c r="C71" s="282" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>Enchapes</t>
         </is>
       </c>
       <c r="D71" s="283" t="inlineStr">
         <is>
-          <t>09.01.01</t>
+          <t>09.02.01</t>
         </is>
       </c>
       <c r="E71" s="284" t="inlineStr">
         <is>
-          <t>Mortero de nivelación</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="F71" s="285" t="n"/>
@@ -16044,7 +16044,7 @@
     <row r="72" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A72" s="280" t="inlineStr">
         <is>
-          <t>MQ-064</t>
+          <t>MQ-069</t>
         </is>
       </c>
       <c r="B72" s="281" t="inlineStr">
@@ -16054,17 +16054,17 @@
       </c>
       <c r="C72" s="282" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>Enchapes</t>
         </is>
       </c>
       <c r="D72" s="283" t="inlineStr">
         <is>
-          <t>09.01.02</t>
+          <t>09.02.02</t>
         </is>
       </c>
       <c r="E72" s="284" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="F72" s="285" t="n"/>
@@ -16072,7 +16072,7 @@
       <c r="H72" s="285" t="n"/>
       <c r="I72" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J72" s="1469" t="n"/>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="V72" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W72" s="285" t="n"/>
@@ -16129,7 +16129,7 @@
     <row r="73" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A73" s="280" t="inlineStr">
         <is>
-          <t>MQ-065</t>
+          <t>MQ-070</t>
         </is>
       </c>
       <c r="B73" s="281" t="inlineStr">
@@ -16139,17 +16139,17 @@
       </c>
       <c r="C73" s="282" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>Enchapes</t>
         </is>
       </c>
       <c r="D73" s="283" t="inlineStr">
         <is>
-          <t>09.01.03</t>
+          <t>09.02.03</t>
         </is>
       </c>
       <c r="E73" s="284" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="F73" s="285" t="n"/>
@@ -16157,7 +16157,7 @@
       <c r="H73" s="285" t="n"/>
       <c r="I73" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J73" s="1469" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="V73" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W73" s="285" t="n"/>
@@ -16214,27 +16214,27 @@
     <row r="74" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A74" s="280" t="inlineStr">
         <is>
-          <t>MQ-066</t>
+          <t>MQ-071</t>
         </is>
       </c>
       <c r="B74" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C74" s="282" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D74" s="283" t="inlineStr">
         <is>
-          <t>09.01.04</t>
+          <t>10.01.01</t>
         </is>
       </c>
       <c r="E74" s="284" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="F74" s="285" t="n"/>
@@ -16299,27 +16299,27 @@
     <row r="75" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A75" s="280" t="inlineStr">
         <is>
-          <t>MQ-067</t>
+          <t>MQ-072</t>
         </is>
       </c>
       <c r="B75" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C75" s="282" t="inlineStr">
         <is>
-          <t>Pisos</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D75" s="283" t="inlineStr">
         <is>
-          <t>09.01.05</t>
+          <t>10.01.02</t>
         </is>
       </c>
       <c r="E75" s="284" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="F75" s="285" t="n"/>
@@ -16384,27 +16384,27 @@
     <row r="76" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A76" s="280" t="inlineStr">
         <is>
-          <t>MQ-068</t>
+          <t>MQ-073</t>
         </is>
       </c>
       <c r="B76" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C76" s="282" t="inlineStr">
         <is>
-          <t>Enchapes</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D76" s="283" t="inlineStr">
         <is>
-          <t>09.02.01</t>
+          <t>10.01.03</t>
         </is>
       </c>
       <c r="E76" s="284" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="F76" s="285" t="n"/>
@@ -16469,27 +16469,27 @@
     <row r="77" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A77" s="280" t="inlineStr">
         <is>
-          <t>MQ-069</t>
+          <t>MQ-074</t>
         </is>
       </c>
       <c r="B77" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C77" s="282" t="inlineStr">
         <is>
-          <t>Enchapes</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D77" s="283" t="inlineStr">
         <is>
-          <t>09.02.02</t>
+          <t>10.01.04</t>
         </is>
       </c>
       <c r="E77" s="284" t="inlineStr">
         <is>
-          <t>Guardaescoba</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="F77" s="285" t="n"/>
@@ -16497,7 +16497,7 @@
       <c r="H77" s="285" t="n"/>
       <c r="I77" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J77" s="1469" t="n"/>
@@ -16538,7 +16538,7 @@
       </c>
       <c r="V77" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W77" s="285" t="n"/>
@@ -16554,27 +16554,27 @@
     <row r="78" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A78" s="280" t="inlineStr">
         <is>
-          <t>MQ-070</t>
+          <t>MQ-075</t>
         </is>
       </c>
       <c r="B78" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="C78" s="282" t="inlineStr">
         <is>
-          <t>Enchapes</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="D78" s="283" t="inlineStr">
         <is>
-          <t>09.02.03</t>
+          <t>10.01.05</t>
         </is>
       </c>
       <c r="E78" s="284" t="inlineStr">
         <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>Sellador / imprimante</t>
         </is>
       </c>
       <c r="F78" s="285" t="n"/>
@@ -16582,7 +16582,7 @@
       <c r="H78" s="285" t="n"/>
       <c r="I78" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J78" s="1469" t="n"/>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="V78" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W78" s="285" t="n"/>
@@ -16639,27 +16639,27 @@
     <row r="79" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A79" s="280" t="inlineStr">
         <is>
-          <t>MQ-071</t>
+          <t>MQ-076</t>
         </is>
       </c>
       <c r="B79" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C79" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Madera</t>
         </is>
       </c>
       <c r="D79" s="283" t="inlineStr">
         <is>
-          <t>10.01.01</t>
+          <t>11.01.01</t>
         </is>
       </c>
       <c r="E79" s="284" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="F79" s="285" t="n"/>
@@ -16667,7 +16667,7 @@
       <c r="H79" s="285" t="n"/>
       <c r="I79" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J79" s="1469" t="n"/>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="V79" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W79" s="285" t="n"/>
@@ -16724,27 +16724,27 @@
     <row r="80" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A80" s="280" t="inlineStr">
         <is>
-          <t>MQ-072</t>
+          <t>MQ-077</t>
         </is>
       </c>
       <c r="B80" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C80" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Madera</t>
         </is>
       </c>
       <c r="D80" s="283" t="inlineStr">
         <is>
-          <t>10.01.02</t>
+          <t>11.01.02</t>
         </is>
       </c>
       <c r="E80" s="284" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="F80" s="285" t="n"/>
@@ -16752,7 +16752,7 @@
       <c r="H80" s="285" t="n"/>
       <c r="I80" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J80" s="1469" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="V80" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W80" s="285" t="n"/>
@@ -16809,27 +16809,27 @@
     <row r="81" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A81" s="280" t="inlineStr">
         <is>
-          <t>MQ-073</t>
+          <t>MQ-078</t>
         </is>
       </c>
       <c r="B81" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C81" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Metálica</t>
         </is>
       </c>
       <c r="D81" s="283" t="inlineStr">
         <is>
-          <t>10.01.03</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="E81" s="284" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="F81" s="285" t="n"/>
@@ -16837,7 +16837,7 @@
       <c r="H81" s="285" t="n"/>
       <c r="I81" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J81" s="1469" t="n"/>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="V81" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W81" s="285" t="n"/>
@@ -16894,27 +16894,27 @@
     <row r="82" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A82" s="280" t="inlineStr">
         <is>
-          <t>MQ-074</t>
+          <t>MQ-079</t>
         </is>
       </c>
       <c r="B82" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C82" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Metálica</t>
         </is>
       </c>
       <c r="D82" s="283" t="inlineStr">
         <is>
-          <t>10.01.04</t>
+          <t>11.02.02</t>
         </is>
       </c>
       <c r="E82" s="284" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="F82" s="285" t="n"/>
@@ -16922,7 +16922,7 @@
       <c r="H82" s="285" t="n"/>
       <c r="I82" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J82" s="1469" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="V82" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W82" s="285" t="n"/>
@@ -16979,27 +16979,27 @@
     <row r="83" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A83" s="280" t="inlineStr">
         <is>
-          <t>MQ-075</t>
+          <t>MQ-080</t>
         </is>
       </c>
       <c r="B83" s="281" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C83" s="282" t="inlineStr">
         <is>
-          <t>Pintura</t>
+          <t>Metálica</t>
         </is>
       </c>
       <c r="D83" s="283" t="inlineStr">
         <is>
-          <t>10.01.05</t>
+          <t>11.02.03</t>
         </is>
       </c>
       <c r="E83" s="284" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="F83" s="285" t="n"/>
@@ -17007,7 +17007,7 @@
       <c r="H83" s="285" t="n"/>
       <c r="I83" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J83" s="1469" t="n"/>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="V83" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W83" s="285" t="n"/>
@@ -17064,7 +17064,7 @@
     <row r="84" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A84" s="280" t="inlineStr">
         <is>
-          <t>MQ-076</t>
+          <t>MQ-081</t>
         </is>
       </c>
       <c r="B84" s="281" t="inlineStr">
@@ -17074,17 +17074,17 @@
       </c>
       <c r="C84" s="282" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>Aluminio</t>
         </is>
       </c>
       <c r="D84" s="283" t="inlineStr">
         <is>
-          <t>11.01.01</t>
+          <t>11.03.01</t>
         </is>
       </c>
       <c r="E84" s="284" t="inlineStr">
         <is>
-          <t>Puertas de madera</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="F84" s="285" t="n"/>
@@ -17092,7 +17092,7 @@
       <c r="H84" s="285" t="n"/>
       <c r="I84" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J84" s="1469" t="n"/>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="V84" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W84" s="285" t="n"/>
@@ -17149,7 +17149,7 @@
     <row r="85" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A85" s="280" t="inlineStr">
         <is>
-          <t>MQ-077</t>
+          <t>MQ-082</t>
         </is>
       </c>
       <c r="B85" s="281" t="inlineStr">
@@ -17159,17 +17159,17 @@
       </c>
       <c r="C85" s="282" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>Aluminio</t>
         </is>
       </c>
       <c r="D85" s="283" t="inlineStr">
         <is>
-          <t>11.01.02</t>
+          <t>11.03.02</t>
         </is>
       </c>
       <c r="E85" s="284" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="F85" s="285" t="n"/>
@@ -17177,7 +17177,7 @@
       <c r="H85" s="285" t="n"/>
       <c r="I85" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J85" s="1469" t="n"/>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="V85" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W85" s="285" t="n"/>
@@ -17234,27 +17234,27 @@
     <row r="86" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A86" s="280" t="inlineStr">
         <is>
-          <t>MQ-078</t>
+          <t>MQ-083</t>
         </is>
       </c>
       <c r="B86" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>VIDRIOS</t>
         </is>
       </c>
       <c r="C86" s="282" t="inlineStr">
         <is>
-          <t>Metálica</t>
+          <t>Vidriería</t>
         </is>
       </c>
       <c r="D86" s="283" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>12.01.01</t>
         </is>
       </c>
       <c r="E86" s="284" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="F86" s="285" t="n"/>
@@ -17262,7 +17262,7 @@
       <c r="H86" s="285" t="n"/>
       <c r="I86" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J86" s="1469" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="V86" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W86" s="285" t="n"/>
@@ -17319,27 +17319,27 @@
     <row r="87" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A87" s="280" t="inlineStr">
         <is>
-          <t>MQ-079</t>
+          <t>MQ-084</t>
         </is>
       </c>
       <c r="B87" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>VIDRIOS</t>
         </is>
       </c>
       <c r="C87" s="282" t="inlineStr">
         <is>
-          <t>Metálica</t>
+          <t>Vidriería</t>
         </is>
       </c>
       <c r="D87" s="283" t="inlineStr">
         <is>
-          <t>11.02.02</t>
+          <t>12.01.02</t>
         </is>
       </c>
       <c r="E87" s="284" t="inlineStr">
         <is>
-          <t>Barandas metálicas</t>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="F87" s="285" t="n"/>
@@ -17347,7 +17347,7 @@
       <c r="H87" s="285" t="n"/>
       <c r="I87" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J87" s="1469" t="n"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="V87" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W87" s="285" t="n"/>
@@ -17404,27 +17404,27 @@
     <row r="88" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A88" s="280" t="inlineStr">
         <is>
-          <t>MQ-080</t>
+          <t>MQ-085</t>
         </is>
       </c>
       <c r="B88" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>VIDRIOS</t>
         </is>
       </c>
       <c r="C88" s="282" t="inlineStr">
         <is>
-          <t>Metálica</t>
+          <t>Vidriería</t>
         </is>
       </c>
       <c r="D88" s="283" t="inlineStr">
         <is>
-          <t>11.02.03</t>
+          <t>12.01.03</t>
         </is>
       </c>
       <c r="E88" s="284" t="inlineStr">
         <is>
-          <t>Pasamanos</t>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="F88" s="285" t="n"/>
@@ -17432,7 +17432,7 @@
       <c r="H88" s="285" t="n"/>
       <c r="I88" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J88" s="1469" t="n"/>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="V88" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W88" s="285" t="n"/>
@@ -17489,27 +17489,27 @@
     <row r="89" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A89" s="280" t="inlineStr">
         <is>
-          <t>MQ-081</t>
+          <t>MQ-086</t>
         </is>
       </c>
       <c r="B89" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>VIDRIOS</t>
         </is>
       </c>
       <c r="C89" s="282" t="inlineStr">
         <is>
-          <t>Aluminio</t>
+          <t>Vidriería</t>
         </is>
       </c>
       <c r="D89" s="283" t="inlineStr">
         <is>
-          <t>11.03.01</t>
+          <t>12.01.04</t>
         </is>
       </c>
       <c r="E89" s="284" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Sellos y silicona</t>
         </is>
       </c>
       <c r="F89" s="285" t="n"/>
@@ -17517,7 +17517,7 @@
       <c r="H89" s="285" t="n"/>
       <c r="I89" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J89" s="1469" t="n"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="V89" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W89" s="285" t="n"/>
@@ -17574,27 +17574,27 @@
     <row r="90" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A90" s="280" t="inlineStr">
         <is>
-          <t>MQ-082</t>
+          <t>MQ-087</t>
         </is>
       </c>
       <c r="B90" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C90" s="282" t="inlineStr">
         <is>
-          <t>Aluminio</t>
+          <t>Agua potable</t>
         </is>
       </c>
       <c r="D90" s="283" t="inlineStr">
         <is>
-          <t>11.03.02</t>
+          <t>13.01.01</t>
         </is>
       </c>
       <c r="E90" s="284" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="F90" s="285" t="n"/>
@@ -17602,7 +17602,7 @@
       <c r="H90" s="285" t="n"/>
       <c r="I90" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J90" s="1469" t="n"/>
@@ -17643,7 +17643,7 @@
       </c>
       <c r="V90" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W90" s="285" t="n"/>
@@ -17659,27 +17659,27 @@
     <row r="91" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A91" s="280" t="inlineStr">
         <is>
-          <t>MQ-083</t>
+          <t>MQ-088</t>
         </is>
       </c>
       <c r="B91" s="281" t="inlineStr">
         <is>
-          <t>VIDRIOS</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C91" s="282" t="inlineStr">
         <is>
-          <t>Vidriería</t>
+          <t>Agua potable</t>
         </is>
       </c>
       <c r="D91" s="283" t="inlineStr">
         <is>
-          <t>12.01.01</t>
+          <t>13.01.02</t>
         </is>
       </c>
       <c r="E91" s="284" t="inlineStr">
         <is>
-          <t>Vidrio templado</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="F91" s="285" t="n"/>
@@ -17687,7 +17687,7 @@
       <c r="H91" s="285" t="n"/>
       <c r="I91" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J91" s="1469" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="V91" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W91" s="285" t="n"/>
@@ -17744,27 +17744,27 @@
     <row r="92" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A92" s="280" t="inlineStr">
         <is>
-          <t>MQ-084</t>
+          <t>MQ-089</t>
         </is>
       </c>
       <c r="B92" s="281" t="inlineStr">
         <is>
-          <t>VIDRIOS</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C92" s="282" t="inlineStr">
         <is>
-          <t>Vidriería</t>
+          <t>Agua potable</t>
         </is>
       </c>
       <c r="D92" s="283" t="inlineStr">
         <is>
-          <t>12.01.02</t>
+          <t>13.01.03</t>
         </is>
       </c>
       <c r="E92" s="284" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="F92" s="285" t="n"/>
@@ -17772,7 +17772,7 @@
       <c r="H92" s="285" t="n"/>
       <c r="I92" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J92" s="1469" t="n"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="V92" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W92" s="285" t="n"/>
@@ -17829,27 +17829,27 @@
     <row r="93" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A93" s="280" t="inlineStr">
         <is>
-          <t>MQ-085</t>
+          <t>MQ-090</t>
         </is>
       </c>
       <c r="B93" s="281" t="inlineStr">
         <is>
-          <t>VIDRIOS</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C93" s="282" t="inlineStr">
         <is>
-          <t>Vidriería</t>
+          <t>Desagües</t>
         </is>
       </c>
       <c r="D93" s="283" t="inlineStr">
         <is>
-          <t>12.01.03</t>
+          <t>13.02.01</t>
         </is>
       </c>
       <c r="E93" s="284" t="inlineStr">
         <is>
-          <t>Espejos</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="F93" s="285" t="n"/>
@@ -17857,7 +17857,7 @@
       <c r="H93" s="285" t="n"/>
       <c r="I93" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J93" s="1469" t="n"/>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="V93" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W93" s="285" t="n"/>
@@ -17914,27 +17914,27 @@
     <row r="94" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A94" s="280" t="inlineStr">
         <is>
-          <t>MQ-086</t>
+          <t>MQ-091</t>
         </is>
       </c>
       <c r="B94" s="281" t="inlineStr">
         <is>
-          <t>VIDRIOS</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C94" s="282" t="inlineStr">
         <is>
-          <t>Vidriería</t>
+          <t>Desagües</t>
         </is>
       </c>
       <c r="D94" s="283" t="inlineStr">
         <is>
-          <t>12.01.04</t>
+          <t>13.02.02</t>
         </is>
       </c>
       <c r="E94" s="284" t="inlineStr">
         <is>
-          <t>Sellos y silicona</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="F94" s="285" t="n"/>
@@ -17999,7 +17999,7 @@
     <row r="95" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A95" s="280" t="inlineStr">
         <is>
-          <t>MQ-087</t>
+          <t>MQ-092</t>
         </is>
       </c>
       <c r="B95" s="281" t="inlineStr">
@@ -18009,17 +18009,17 @@
       </c>
       <c r="C95" s="282" t="inlineStr">
         <is>
-          <t>Agua potable</t>
+          <t>Desagües</t>
         </is>
       </c>
       <c r="D95" s="283" t="inlineStr">
         <is>
-          <t>13.01.01</t>
+          <t>13.02.03</t>
         </is>
       </c>
       <c r="E95" s="284" t="inlineStr">
         <is>
-          <t>Tubería de agua fría</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="F95" s="285" t="n"/>
@@ -18027,7 +18027,7 @@
       <c r="H95" s="285" t="n"/>
       <c r="I95" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J95" s="1469" t="n"/>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="V95" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W95" s="285" t="n"/>
@@ -18084,7 +18084,7 @@
     <row r="96" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A96" s="280" t="inlineStr">
         <is>
-          <t>MQ-088</t>
+          <t>MQ-093</t>
         </is>
       </c>
       <c r="B96" s="281" t="inlineStr">
@@ -18094,17 +18094,17 @@
       </c>
       <c r="C96" s="282" t="inlineStr">
         <is>
-          <t>Agua potable</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D96" s="283" t="inlineStr">
         <is>
-          <t>13.01.02</t>
+          <t>13.03.01</t>
         </is>
       </c>
       <c r="E96" s="284" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="F96" s="285" t="n"/>
@@ -18112,7 +18112,7 @@
       <c r="H96" s="285" t="n"/>
       <c r="I96" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J96" s="1469" t="n"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="V96" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W96" s="285" t="n"/>
@@ -18169,7 +18169,7 @@
     <row r="97" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A97" s="280" t="inlineStr">
         <is>
-          <t>MQ-089</t>
+          <t>MQ-094</t>
         </is>
       </c>
       <c r="B97" s="281" t="inlineStr">
@@ -18179,17 +18179,17 @@
       </c>
       <c r="C97" s="282" t="inlineStr">
         <is>
-          <t>Agua potable</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D97" s="283" t="inlineStr">
         <is>
-          <t>13.01.03</t>
+          <t>13.03.02</t>
         </is>
       </c>
       <c r="E97" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios hidrosanitarios</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="F97" s="285" t="n"/>
@@ -18254,7 +18254,7 @@
     <row r="98" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A98" s="280" t="inlineStr">
         <is>
-          <t>MQ-090</t>
+          <t>MQ-095</t>
         </is>
       </c>
       <c r="B98" s="281" t="inlineStr">
@@ -18264,17 +18264,17 @@
       </c>
       <c r="C98" s="282" t="inlineStr">
         <is>
-          <t>Desagües</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D98" s="283" t="inlineStr">
         <is>
-          <t>13.02.01</t>
+          <t>13.03.03</t>
         </is>
       </c>
       <c r="E98" s="284" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="F98" s="285" t="n"/>
@@ -18282,7 +18282,7 @@
       <c r="H98" s="285" t="n"/>
       <c r="I98" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J98" s="1469" t="n"/>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="V98" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W98" s="285" t="n"/>
@@ -18339,7 +18339,7 @@
     <row r="99" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A99" s="280" t="inlineStr">
         <is>
-          <t>MQ-091</t>
+          <t>MQ-096</t>
         </is>
       </c>
       <c r="B99" s="281" t="inlineStr">
@@ -18349,17 +18349,17 @@
       </c>
       <c r="C99" s="282" t="inlineStr">
         <is>
-          <t>Desagües</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D99" s="283" t="inlineStr">
         <is>
-          <t>13.02.02</t>
+          <t>13.03.04</t>
         </is>
       </c>
       <c r="E99" s="284" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="F99" s="285" t="n"/>
@@ -18367,7 +18367,7 @@
       <c r="H99" s="285" t="n"/>
       <c r="I99" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J99" s="1469" t="n"/>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="V99" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W99" s="285" t="n"/>
@@ -18424,7 +18424,7 @@
     <row r="100" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A100" s="280" t="inlineStr">
         <is>
-          <t>MQ-092</t>
+          <t>MQ-097</t>
         </is>
       </c>
       <c r="B100" s="281" t="inlineStr">
@@ -18434,17 +18434,17 @@
       </c>
       <c r="C100" s="282" t="inlineStr">
         <is>
-          <t>Desagües</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D100" s="283" t="inlineStr">
         <is>
-          <t>13.02.03</t>
+          <t>13.04.01</t>
         </is>
       </c>
       <c r="E100" s="284" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="F100" s="285" t="n"/>
@@ -18452,7 +18452,7 @@
       <c r="H100" s="285" t="n"/>
       <c r="I100" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J100" s="1469" t="n"/>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="V100" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W100" s="285" t="n"/>
@@ -18509,27 +18509,27 @@
     <row r="101" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A101" s="280" t="inlineStr">
         <is>
-          <t>MQ-093</t>
+          <t>MQ-098</t>
         </is>
       </c>
       <c r="B101" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C101" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Canalizaciones</t>
         </is>
       </c>
       <c r="D101" s="283" t="inlineStr">
         <is>
-          <t>13.03.01</t>
+          <t>14.01.01</t>
         </is>
       </c>
       <c r="E101" s="284" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="F101" s="285" t="n"/>
@@ -18537,7 +18537,7 @@
       <c r="H101" s="285" t="n"/>
       <c r="I101" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J101" s="1469" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="V101" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W101" s="285" t="n"/>
@@ -18594,27 +18594,27 @@
     <row r="102" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A102" s="280" t="inlineStr">
         <is>
-          <t>MQ-094</t>
+          <t>MQ-099</t>
         </is>
       </c>
       <c r="B102" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C102" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Canalizaciones</t>
         </is>
       </c>
       <c r="D102" s="283" t="inlineStr">
         <is>
-          <t>13.03.02</t>
+          <t>14.01.02</t>
         </is>
       </c>
       <c r="E102" s="284" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="F102" s="285" t="n"/>
@@ -18622,7 +18622,7 @@
       <c r="H102" s="285" t="n"/>
       <c r="I102" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J102" s="1469" t="n"/>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="V102" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W102" s="285" t="n"/>
@@ -18679,27 +18679,27 @@
     <row r="103" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A103" s="280" t="inlineStr">
         <is>
-          <t>MQ-095</t>
+          <t>MQ-100</t>
         </is>
       </c>
       <c r="B103" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C103" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Canalizaciones</t>
         </is>
       </c>
       <c r="D103" s="283" t="inlineStr">
         <is>
-          <t>13.03.03</t>
+          <t>14.01.03</t>
         </is>
       </c>
       <c r="E103" s="284" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="F103" s="285" t="n"/>
@@ -18764,27 +18764,27 @@
     <row r="104" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A104" s="280" t="inlineStr">
         <is>
-          <t>MQ-096</t>
+          <t>MQ-101</t>
         </is>
       </c>
       <c r="B104" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C104" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Cableado</t>
         </is>
       </c>
       <c r="D104" s="283" t="inlineStr">
         <is>
-          <t>13.03.04</t>
+          <t>14.02.01</t>
         </is>
       </c>
       <c r="E104" s="284" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="F104" s="285" t="n"/>
@@ -18792,7 +18792,7 @@
       <c r="H104" s="285" t="n"/>
       <c r="I104" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J104" s="1469" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="V104" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W104" s="285" t="n"/>
@@ -18849,27 +18849,27 @@
     <row r="105" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A105" s="280" t="inlineStr">
         <is>
-          <t>MQ-097</t>
+          <t>MQ-102</t>
         </is>
       </c>
       <c r="B105" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
       <c r="C105" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Cableado</t>
         </is>
       </c>
       <c r="D105" s="283" t="inlineStr">
         <is>
-          <t>13.04.01</t>
+          <t>14.02.02</t>
         </is>
       </c>
       <c r="E105" s="284" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="F105" s="285" t="n"/>
@@ -18877,7 +18877,7 @@
       <c r="H105" s="285" t="n"/>
       <c r="I105" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J105" s="1469" t="n"/>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="V105" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W105" s="285" t="n"/>
@@ -18934,7 +18934,7 @@
     <row r="106" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A106" s="280" t="inlineStr">
         <is>
-          <t>MQ-098</t>
+          <t>MQ-103</t>
         </is>
       </c>
       <c r="B106" s="281" t="inlineStr">
@@ -18944,17 +18944,17 @@
       </c>
       <c r="C106" s="282" t="inlineStr">
         <is>
-          <t>Canalizaciones</t>
+          <t>Cableado</t>
         </is>
       </c>
       <c r="D106" s="283" t="inlineStr">
         <is>
-          <t>14.01.01</t>
+          <t>14.02.03</t>
         </is>
       </c>
       <c r="E106" s="284" t="inlineStr">
         <is>
-          <t>Tubería/conduit eléctrica</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="F106" s="285" t="n"/>
@@ -18962,7 +18962,7 @@
       <c r="H106" s="285" t="n"/>
       <c r="I106" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J106" s="1469" t="n"/>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="V106" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W106" s="285" t="n"/>
@@ -19019,7 +19019,7 @@
     <row r="107" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A107" s="280" t="inlineStr">
         <is>
-          <t>MQ-099</t>
+          <t>MQ-104</t>
         </is>
       </c>
       <c r="B107" s="281" t="inlineStr">
@@ -19029,17 +19029,17 @@
       </c>
       <c r="C107" s="282" t="inlineStr">
         <is>
-          <t>Canalizaciones</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D107" s="283" t="inlineStr">
         <is>
-          <t>14.01.02</t>
+          <t>14.03.01</t>
         </is>
       </c>
       <c r="E107" s="284" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="F107" s="285" t="n"/>
@@ -19047,7 +19047,7 @@
       <c r="H107" s="285" t="n"/>
       <c r="I107" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J107" s="1469" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="V107" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W107" s="285" t="n"/>
@@ -19104,7 +19104,7 @@
     <row r="108" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A108" s="280" t="inlineStr">
         <is>
-          <t>MQ-100</t>
+          <t>MQ-105</t>
         </is>
       </c>
       <c r="B108" s="281" t="inlineStr">
@@ -19114,17 +19114,17 @@
       </c>
       <c r="C108" s="282" t="inlineStr">
         <is>
-          <t>Canalizaciones</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D108" s="283" t="inlineStr">
         <is>
-          <t>14.01.03</t>
+          <t>14.03.02</t>
         </is>
       </c>
       <c r="E108" s="284" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="F108" s="285" t="n"/>
@@ -19189,7 +19189,7 @@
     <row r="109" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A109" s="280" t="inlineStr">
         <is>
-          <t>MQ-101</t>
+          <t>MQ-106</t>
         </is>
       </c>
       <c r="B109" s="281" t="inlineStr">
@@ -19199,17 +19199,17 @@
       </c>
       <c r="C109" s="282" t="inlineStr">
         <is>
-          <t>Cableado</t>
+          <t>Aparatos</t>
         </is>
       </c>
       <c r="D109" s="283" t="inlineStr">
         <is>
-          <t>14.02.01</t>
+          <t>14.03.03</t>
         </is>
       </c>
       <c r="E109" s="284" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="F109" s="285" t="n"/>
@@ -19217,7 +19217,7 @@
       <c r="H109" s="285" t="n"/>
       <c r="I109" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J109" s="1469" t="n"/>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="V109" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W109" s="285" t="n"/>
@@ -19274,7 +19274,7 @@
     <row r="110" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A110" s="280" t="inlineStr">
         <is>
-          <t>MQ-102</t>
+          <t>MQ-107</t>
         </is>
       </c>
       <c r="B110" s="281" t="inlineStr">
@@ -19284,17 +19284,17 @@
       </c>
       <c r="C110" s="282" t="inlineStr">
         <is>
-          <t>Cableado</t>
+          <t>Puesta a tierra</t>
         </is>
       </c>
       <c r="D110" s="283" t="inlineStr">
         <is>
-          <t>14.02.02</t>
+          <t>14.04.01</t>
         </is>
       </c>
       <c r="E110" s="284" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="F110" s="285" t="n"/>
@@ -19302,7 +19302,7 @@
       <c r="H110" s="285" t="n"/>
       <c r="I110" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J110" s="1469" t="n"/>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="V110" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W110" s="285" t="n"/>
@@ -19359,7 +19359,7 @@
     <row r="111" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A111" s="280" t="inlineStr">
         <is>
-          <t>MQ-103</t>
+          <t>MQ-108</t>
         </is>
       </c>
       <c r="B111" s="281" t="inlineStr">
@@ -19369,17 +19369,17 @@
       </c>
       <c r="C111" s="282" t="inlineStr">
         <is>
-          <t>Cableado</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D111" s="283" t="inlineStr">
         <is>
-          <t>14.02.03</t>
+          <t>14.05.01</t>
         </is>
       </c>
       <c r="E111" s="284" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Pruebas y certificaciones</t>
         </is>
       </c>
       <c r="F111" s="285" t="n"/>
@@ -19387,7 +19387,7 @@
       <c r="H111" s="285" t="n"/>
       <c r="I111" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J111" s="1469" t="n"/>
@@ -19428,7 +19428,7 @@
       </c>
       <c r="V111" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W111" s="285" t="n"/>
@@ -19444,27 +19444,27 @@
     <row r="112" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A112" s="280" t="inlineStr">
         <is>
-          <t>MQ-104</t>
+          <t>MQ-109</t>
         </is>
       </c>
       <c r="B112" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C112" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Datos</t>
         </is>
       </c>
       <c r="D112" s="283" t="inlineStr">
         <is>
-          <t>14.03.01</t>
+          <t>15.01.01</t>
         </is>
       </c>
       <c r="E112" s="284" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="F112" s="285" t="n"/>
@@ -19472,7 +19472,7 @@
       <c r="H112" s="285" t="n"/>
       <c r="I112" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J112" s="1469" t="n"/>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="V112" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W112" s="285" t="n"/>
@@ -19529,27 +19529,27 @@
     <row r="113" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A113" s="280" t="inlineStr">
         <is>
-          <t>MQ-105</t>
+          <t>MQ-110</t>
         </is>
       </c>
       <c r="B113" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C113" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Datos</t>
         </is>
       </c>
       <c r="D113" s="283" t="inlineStr">
         <is>
-          <t>14.03.02</t>
+          <t>15.01.02</t>
         </is>
       </c>
       <c r="E113" s="284" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="F113" s="285" t="n"/>
@@ -19614,27 +19614,27 @@
     <row r="114" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A114" s="280" t="inlineStr">
         <is>
-          <t>MQ-106</t>
+          <t>MQ-111</t>
         </is>
       </c>
       <c r="B114" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C114" s="282" t="inlineStr">
         <is>
-          <t>Aparatos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D114" s="283" t="inlineStr">
         <is>
-          <t>14.03.03</t>
+          <t>15.02.01</t>
         </is>
       </c>
       <c r="E114" s="284" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="F114" s="285" t="n"/>
@@ -19699,27 +19699,27 @@
     <row r="115" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A115" s="280" t="inlineStr">
         <is>
-          <t>MQ-107</t>
+          <t>MQ-112</t>
         </is>
       </c>
       <c r="B115" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C115" s="282" t="inlineStr">
         <is>
-          <t>Puesta a tierra</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D115" s="283" t="inlineStr">
         <is>
-          <t>14.04.01</t>
+          <t>15.02.02</t>
         </is>
       </c>
       <c r="E115" s="284" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="F115" s="285" t="n"/>
@@ -19727,7 +19727,7 @@
       <c r="H115" s="285" t="n"/>
       <c r="I115" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J115" s="1469" t="n"/>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="V115" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W115" s="285" t="n"/>
@@ -19784,27 +19784,27 @@
     <row r="116" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A116" s="280" t="inlineStr">
         <is>
-          <t>MQ-108</t>
+          <t>MQ-113</t>
         </is>
       </c>
       <c r="B116" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
       <c r="C116" s="282" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D116" s="283" t="inlineStr">
         <is>
-          <t>14.05.01</t>
+          <t>15.02.03</t>
         </is>
       </c>
       <c r="E116" s="284" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="F116" s="285" t="n"/>
@@ -19812,7 +19812,7 @@
       <c r="H116" s="285" t="n"/>
       <c r="I116" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J116" s="1469" t="n"/>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="V116" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W116" s="285" t="n"/>
@@ -19869,7 +19869,7 @@
     <row r="117" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A117" s="280" t="inlineStr">
         <is>
-          <t>MQ-109</t>
+          <t>MQ-114</t>
         </is>
       </c>
       <c r="B117" s="281" t="inlineStr">
@@ -19879,17 +19879,17 @@
       </c>
       <c r="C117" s="282" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Detección</t>
         </is>
       </c>
       <c r="D117" s="283" t="inlineStr">
         <is>
-          <t>15.01.01</t>
+          <t>15.03.01</t>
         </is>
       </c>
       <c r="E117" s="284" t="inlineStr">
         <is>
-          <t>Cableado estructurado de datos</t>
+          <t>Sistema de detección de incendios</t>
         </is>
       </c>
       <c r="F117" s="285" t="n"/>
@@ -19897,7 +19897,7 @@
       <c r="H117" s="285" t="n"/>
       <c r="I117" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J117" s="1469" t="n"/>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="V117" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W117" s="285" t="n"/>
@@ -19954,27 +19954,27 @@
     <row r="118" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A118" s="280" t="inlineStr">
         <is>
-          <t>MQ-110</t>
+          <t>MQ-115</t>
         </is>
       </c>
       <c r="B118" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C118" s="282" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D118" s="283" t="inlineStr">
         <is>
-          <t>15.01.02</t>
+          <t>16.01.01</t>
         </is>
       </c>
       <c r="E118" s="284" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="F118" s="285" t="n"/>
@@ -20039,27 +20039,27 @@
     <row r="119" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A119" s="280" t="inlineStr">
         <is>
-          <t>MQ-111</t>
+          <t>MQ-116</t>
         </is>
       </c>
       <c r="B119" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C119" s="282" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D119" s="283" t="inlineStr">
         <is>
-          <t>15.02.01</t>
+          <t>16.01.02</t>
         </is>
       </c>
       <c r="E119" s="284" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="F119" s="285" t="n"/>
@@ -20067,7 +20067,7 @@
       <c r="H119" s="285" t="n"/>
       <c r="I119" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J119" s="1469" t="n"/>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="V119" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W119" s="285" t="n"/>
@@ -20124,27 +20124,27 @@
     <row r="120" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A120" s="280" t="inlineStr">
         <is>
-          <t>MQ-112</t>
+          <t>MQ-117</t>
         </is>
       </c>
       <c r="B120" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C120" s="282" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D120" s="283" t="inlineStr">
         <is>
-          <t>15.02.02</t>
+          <t>16.01.03</t>
         </is>
       </c>
       <c r="E120" s="284" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="F120" s="285" t="n"/>
@@ -20152,7 +20152,7 @@
       <c r="H120" s="285" t="n"/>
       <c r="I120" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J120" s="1469" t="n"/>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="V120" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W120" s="285" t="n"/>
@@ -20209,27 +20209,27 @@
     <row r="121" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A121" s="280" t="inlineStr">
         <is>
-          <t>MQ-113</t>
+          <t>MQ-118</t>
         </is>
       </c>
       <c r="B121" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
       <c r="C121" s="282" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D121" s="283" t="inlineStr">
         <is>
-          <t>15.02.03</t>
+          <t>16.01.04</t>
         </is>
       </c>
       <c r="E121" s="284" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Rejillas y difusores</t>
         </is>
       </c>
       <c r="F121" s="285" t="n"/>
@@ -20294,27 +20294,27 @@
     <row r="122" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A122" s="280" t="inlineStr">
         <is>
-          <t>MQ-114</t>
+          <t>MQ-119</t>
         </is>
       </c>
       <c r="B122" s="281" t="inlineStr">
         <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="C122" s="282" t="inlineStr">
         <is>
-          <t>Detección</t>
+          <t>Red de gas</t>
         </is>
       </c>
       <c r="D122" s="283" t="inlineStr">
         <is>
-          <t>15.03.01</t>
+          <t>17.01.01</t>
         </is>
       </c>
       <c r="E122" s="284" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="F122" s="285" t="n"/>
@@ -20322,7 +20322,7 @@
       <c r="H122" s="285" t="n"/>
       <c r="I122" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J122" s="1469" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="V122" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W122" s="285" t="n"/>
@@ -20379,27 +20379,27 @@
     <row r="123" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A123" s="280" t="inlineStr">
         <is>
-          <t>MQ-115</t>
+          <t>MQ-120</t>
         </is>
       </c>
       <c r="B123" s="281" t="inlineStr">
         <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="C123" s="282" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Red de gas</t>
         </is>
       </c>
       <c r="D123" s="283" t="inlineStr">
         <is>
-          <t>16.01.01</t>
+          <t>17.01.02</t>
         </is>
       </c>
       <c r="E123" s="284" t="inlineStr">
         <is>
-          <t>Equipos de aire acondicionado</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="F123" s="285" t="n"/>
@@ -20464,27 +20464,27 @@
     <row r="124" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A124" s="280" t="inlineStr">
         <is>
-          <t>MQ-116</t>
+          <t>MQ-121</t>
         </is>
       </c>
       <c r="B124" s="281" t="inlineStr">
         <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="C124" s="282" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Red de gas</t>
         </is>
       </c>
       <c r="D124" s="283" t="inlineStr">
         <is>
-          <t>16.01.02</t>
+          <t>17.01.03</t>
         </is>
       </c>
       <c r="E124" s="284" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Pruebas y certificación</t>
         </is>
       </c>
       <c r="F124" s="285" t="n"/>
@@ -20492,7 +20492,7 @@
       <c r="H124" s="285" t="n"/>
       <c r="I124" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J124" s="1469" t="n"/>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="V124" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W124" s="285" t="n"/>
@@ -20549,27 +20549,27 @@
     <row r="125" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A125" s="280" t="inlineStr">
         <is>
-          <t>MQ-117</t>
+          <t>MQ-122</t>
         </is>
       </c>
       <c r="B125" s="281" t="inlineStr">
         <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C125" s="282" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Pavimentos</t>
         </is>
       </c>
       <c r="D125" s="283" t="inlineStr">
         <is>
-          <t>16.01.03</t>
+          <t>18.01.01</t>
         </is>
       </c>
       <c r="E125" s="284" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="F125" s="285" t="n"/>
@@ -20577,7 +20577,7 @@
       <c r="H125" s="285" t="n"/>
       <c r="I125" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J125" s="1469" t="n"/>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="V125" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W125" s="285" t="n"/>
@@ -20634,27 +20634,27 @@
     <row r="126" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A126" s="280" t="inlineStr">
         <is>
-          <t>MQ-118</t>
+          <t>MQ-123</t>
         </is>
       </c>
       <c r="B126" s="281" t="inlineStr">
         <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C126" s="282" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Pavimentos</t>
         </is>
       </c>
       <c r="D126" s="283" t="inlineStr">
         <is>
-          <t>16.01.04</t>
+          <t>18.01.02</t>
         </is>
       </c>
       <c r="E126" s="284" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="F126" s="285" t="n"/>
@@ -20662,7 +20662,7 @@
       <c r="H126" s="285" t="n"/>
       <c r="I126" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="J126" s="1469" t="n"/>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="V126" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="W126" s="285" t="n"/>
@@ -20719,27 +20719,27 @@
     <row r="127" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A127" s="280" t="inlineStr">
         <is>
-          <t>MQ-119</t>
+          <t>MQ-124</t>
         </is>
       </c>
       <c r="B127" s="281" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C127" s="282" t="inlineStr">
         <is>
-          <t>Red de gas</t>
+          <t>Pavimentos</t>
         </is>
       </c>
       <c r="D127" s="283" t="inlineStr">
         <is>
-          <t>17.01.01</t>
+          <t>18.01.03</t>
         </is>
       </c>
       <c r="E127" s="284" t="inlineStr">
         <is>
-          <t>Red interna de gas</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="F127" s="285" t="n"/>
@@ -20747,7 +20747,7 @@
       <c r="H127" s="285" t="n"/>
       <c r="I127" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J127" s="1469" t="n"/>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="V127" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W127" s="285" t="n"/>
@@ -20804,27 +20804,27 @@
     <row r="128" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A128" s="280" t="inlineStr">
         <is>
-          <t>MQ-120</t>
+          <t>MQ-125</t>
         </is>
       </c>
       <c r="B128" s="281" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C128" s="282" t="inlineStr">
         <is>
-          <t>Red de gas</t>
+          <t>Bordillos</t>
         </is>
       </c>
       <c r="D128" s="283" t="inlineStr">
         <is>
-          <t>17.01.02</t>
+          <t>18.02.01</t>
         </is>
       </c>
       <c r="E128" s="284" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios de gas</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="F128" s="285" t="n"/>
@@ -20832,7 +20832,7 @@
       <c r="H128" s="285" t="n"/>
       <c r="I128" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="J128" s="1469" t="n"/>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="V128" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W128" s="285" t="n"/>
@@ -20889,27 +20889,27 @@
     <row r="129" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A129" s="280" t="inlineStr">
         <is>
-          <t>MQ-121</t>
+          <t>MQ-126</t>
         </is>
       </c>
       <c r="B129" s="281" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C129" s="282" t="inlineStr">
         <is>
-          <t>Red de gas</t>
+          <t>Drenajes</t>
         </is>
       </c>
       <c r="D129" s="283" t="inlineStr">
         <is>
-          <t>17.01.03</t>
+          <t>18.03.01</t>
         </is>
       </c>
       <c r="E129" s="284" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="F129" s="285" t="n"/>
@@ -20917,7 +20917,7 @@
       <c r="H129" s="285" t="n"/>
       <c r="I129" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J129" s="1469" t="n"/>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="V129" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W129" s="285" t="n"/>
@@ -20974,7 +20974,7 @@
     <row r="130" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A130" s="280" t="inlineStr">
         <is>
-          <t>MQ-122</t>
+          <t>MQ-127</t>
         </is>
       </c>
       <c r="B130" s="281" t="inlineStr">
@@ -20984,17 +20984,17 @@
       </c>
       <c r="C130" s="282" t="inlineStr">
         <is>
-          <t>Pavimentos</t>
+          <t>Paisajismo</t>
         </is>
       </c>
       <c r="D130" s="283" t="inlineStr">
         <is>
-          <t>18.01.01</t>
+          <t>18.04.01</t>
         </is>
       </c>
       <c r="E130" s="284" t="inlineStr">
         <is>
-          <t>Construcción de andenes</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="F130" s="285" t="n"/>
@@ -21002,7 +21002,7 @@
       <c r="H130" s="285" t="n"/>
       <c r="I130" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="J130" s="1469" t="n"/>
@@ -21043,7 +21043,7 @@
       </c>
       <c r="V130" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="W130" s="285" t="n"/>
@@ -21059,7 +21059,7 @@
     <row r="131" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A131" s="280" t="inlineStr">
         <is>
-          <t>MQ-123</t>
+          <t>MQ-128</t>
         </is>
       </c>
       <c r="B131" s="281" t="inlineStr">
@@ -21069,17 +21069,17 @@
       </c>
       <c r="C131" s="282" t="inlineStr">
         <is>
-          <t>Pavimentos</t>
+          <t>Paisajismo</t>
         </is>
       </c>
       <c r="D131" s="283" t="inlineStr">
         <is>
-          <t>18.01.02</t>
+          <t>18.04.02</t>
         </is>
       </c>
       <c r="E131" s="284" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="F131" s="285" t="n"/>
@@ -21087,7 +21087,7 @@
       <c r="H131" s="285" t="n"/>
       <c r="I131" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="J131" s="1469" t="n"/>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="V131" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="W131" s="285" t="n"/>
@@ -21144,27 +21144,27 @@
     <row r="132" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A132" s="280" t="inlineStr">
         <is>
-          <t>MQ-124</t>
+          <t>MQ-129</t>
         </is>
       </c>
       <c r="B132" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C132" s="282" t="inlineStr">
         <is>
-          <t>Pavimentos</t>
+          <t>Metálicas</t>
         </is>
       </c>
       <c r="D132" s="283" t="inlineStr">
         <is>
-          <t>18.01.03</t>
+          <t>19.01.01</t>
         </is>
       </c>
       <c r="E132" s="284" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="F132" s="285" t="n"/>
@@ -21229,27 +21229,27 @@
     <row r="133" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A133" s="280" t="inlineStr">
         <is>
-          <t>MQ-125</t>
+          <t>MQ-130</t>
         </is>
       </c>
       <c r="B133" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C133" s="282" t="inlineStr">
         <is>
-          <t>Bordillos</t>
+          <t>Metálicas</t>
         </is>
       </c>
       <c r="D133" s="283" t="inlineStr">
         <is>
-          <t>18.02.01</t>
+          <t>19.01.02</t>
         </is>
       </c>
       <c r="E133" s="284" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="F133" s="285" t="n"/>
@@ -21257,7 +21257,7 @@
       <c r="H133" s="285" t="n"/>
       <c r="I133" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J133" s="1469" t="n"/>
@@ -21298,7 +21298,7 @@
       </c>
       <c r="V133" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W133" s="285" t="n"/>
@@ -21314,27 +21314,27 @@
     <row r="134" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A134" s="280" t="inlineStr">
         <is>
-          <t>MQ-126</t>
+          <t>MQ-131</t>
         </is>
       </c>
       <c r="B134" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C134" s="282" t="inlineStr">
         <is>
-          <t>Drenajes</t>
+          <t>Metálicas</t>
         </is>
       </c>
       <c r="D134" s="283" t="inlineStr">
         <is>
-          <t>18.03.01</t>
+          <t>19.01.03</t>
         </is>
       </c>
       <c r="E134" s="284" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="F134" s="285" t="n"/>
@@ -21342,7 +21342,7 @@
       <c r="H134" s="285" t="n"/>
       <c r="I134" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="J134" s="1469" t="n"/>
@@ -21383,7 +21383,7 @@
       </c>
       <c r="V134" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="W134" s="285" t="n"/>
@@ -21399,27 +21399,27 @@
     <row r="135" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A135" s="280" t="inlineStr">
         <is>
-          <t>MQ-127</t>
+          <t>MQ-132</t>
         </is>
       </c>
       <c r="B135" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
       <c r="C135" s="282" t="inlineStr">
         <is>
-          <t>Paisajismo</t>
+          <t>Mobiliario</t>
         </is>
       </c>
       <c r="D135" s="283" t="inlineStr">
         <is>
-          <t>18.04.01</t>
+          <t>19.02.01</t>
         </is>
       </c>
       <c r="E135" s="284" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Mobiliario fijo de obra</t>
         </is>
       </c>
       <c r="F135" s="285" t="n"/>
@@ -21427,7 +21427,7 @@
       <c r="H135" s="285" t="n"/>
       <c r="I135" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J135" s="1469" t="n"/>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="V135" s="283" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>und</t>
         </is>
       </c>
       <c r="W135" s="285" t="n"/>
@@ -21484,27 +21484,27 @@
     <row r="136" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A136" s="280" t="inlineStr">
         <is>
-          <t>MQ-128</t>
+          <t>MQ-133</t>
         </is>
       </c>
       <c r="B136" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C136" s="282" t="inlineStr">
         <is>
-          <t>Paisajismo</t>
+          <t>Limpieza</t>
         </is>
       </c>
       <c r="D136" s="283" t="inlineStr">
         <is>
-          <t>18.04.02</t>
+          <t>20.01.01</t>
         </is>
       </c>
       <c r="E136" s="284" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="F136" s="285" t="n"/>
@@ -21569,27 +21569,27 @@
     <row r="137" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A137" s="280" t="inlineStr">
         <is>
-          <t>MQ-129</t>
+          <t>MQ-134</t>
         </is>
       </c>
       <c r="B137" s="281" t="inlineStr">
         <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C137" s="282" t="inlineStr">
         <is>
-          <t>Metálicas</t>
+          <t>Limpieza</t>
         </is>
       </c>
       <c r="D137" s="283" t="inlineStr">
         <is>
-          <t>19.01.01</t>
+          <t>20.01.02</t>
         </is>
       </c>
       <c r="E137" s="284" t="inlineStr">
         <is>
-          <t>Rejas metálicas</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="F137" s="285" t="n"/>
@@ -21654,27 +21654,27 @@
     <row r="138" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A138" s="280" t="inlineStr">
         <is>
-          <t>MQ-130</t>
+          <t>MQ-135</t>
         </is>
       </c>
       <c r="B138" s="281" t="inlineStr">
         <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C138" s="282" t="inlineStr">
         <is>
-          <t>Metálicas</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D138" s="283" t="inlineStr">
         <is>
-          <t>19.01.02</t>
+          <t>20.02.01</t>
         </is>
       </c>
       <c r="E138" s="284" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="F138" s="285" t="n"/>
@@ -21682,7 +21682,7 @@
       <c r="H138" s="285" t="n"/>
       <c r="I138" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J138" s="1469" t="n"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="V138" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W138" s="285" t="n"/>
@@ -21739,27 +21739,27 @@
     <row r="139" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A139" s="280" t="inlineStr">
         <is>
-          <t>MQ-131</t>
+          <t>MQ-136</t>
         </is>
       </c>
       <c r="B139" s="281" t="inlineStr">
         <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C139" s="282" t="inlineStr">
         <is>
-          <t>Metálicas</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D139" s="283" t="inlineStr">
         <is>
-          <t>19.01.03</t>
+          <t>20.02.01</t>
         </is>
       </c>
       <c r="E139" s="284" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="F139" s="285" t="n"/>
@@ -21767,7 +21767,7 @@
       <c r="H139" s="285" t="n"/>
       <c r="I139" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J139" s="1469" t="n"/>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="V139" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W139" s="285" t="n"/>
@@ -21824,27 +21824,27 @@
     <row r="140" ht="15" customFormat="1" customHeight="1" s="685">
       <c r="A140" s="280" t="inlineStr">
         <is>
-          <t>MQ-132</t>
+          <t>MQ-137</t>
         </is>
       </c>
       <c r="B140" s="281" t="inlineStr">
         <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
+          <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C140" s="282" t="inlineStr">
         <is>
-          <t>Mobiliario</t>
+          <t>Entrega</t>
         </is>
       </c>
       <c r="D140" s="283" t="inlineStr">
         <is>
-          <t>19.02.01</t>
+          <t>20.02.02</t>
         </is>
       </c>
       <c r="E140" s="284" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Entrega, manuales y acta de recibo</t>
         </is>
       </c>
       <c r="F140" s="285" t="n"/>
@@ -21852,7 +21852,7 @@
       <c r="H140" s="285" t="n"/>
       <c r="I140" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="J140" s="1469" t="n"/>
@@ -21893,7 +21893,7 @@
       </c>
       <c r="V140" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>gl</t>
         </is>
       </c>
       <c r="W140" s="285" t="n"/>
@@ -21906,30 +21906,26 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="15" customFormat="1" customHeight="1" s="685">
+    <row r="141">
       <c r="A141" s="280" t="inlineStr">
         <is>
-          <t>MQ-133</t>
+          <t>MQ-138</t>
         </is>
       </c>
       <c r="B141" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C141" s="282" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
+          <t>PRELIMINARES</t>
+        </is>
+      </c>
+      <c r="C141" s="282" t="n"/>
       <c r="D141" s="283" t="inlineStr">
         <is>
-          <t>20.01.01</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E141" s="284" t="inlineStr">
         <is>
-          <t>Limpieza gruesa y fina de obra</t>
+          <t>Desmantelamiento de estructuras metálicas existentes</t>
         </is>
       </c>
       <c r="F141" s="285" t="n"/>
@@ -21937,84 +21933,34 @@
       <c r="H141" s="285" t="n"/>
       <c r="I141" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J141" s="1469" t="n"/>
-      <c r="K141" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P141" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q141" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R141" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" s="1438">
-        <f>IF(I141="","",ROUND(IF(OR(I141="m²",I141="m2"),K141*IF(L141=0,1,L141)*IF(O141=0,1,O141)*IF(P141=0,1,P141)*Q141-R141,IF(OR(I141="m³",I141="m3"),K141*L141*M141*IF(O141=0,1,O141)*IF(P141=0,1,P141)*Q141-R141,IF(OR(I141="ml",I141="ML"),K141*IF(O141=0,1,O141)*IF(P141=0,1,P141)*Q141-R141,IF(OR(I141="und",I141="UND"),IF(O141=0,1,O141)*IF(P141=0,1,P141)*Q141-R141,IF(I141="kg",K141*IF(O141=0,1,O141)*IF(P141=0,1,P141)*Q141-R141,IF(OR(I141="gl",I141="GL",I141="gb",I141="GB",I141="Gl",I141="Gb"),IF(O141=0,1,O141)*IF(P141=0,1,P141)*Q141-R141,0)))))),3))</f>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA141" s="336">
+        <f>I4</f>
         <v/>
       </c>
-      <c r="U141" s="1438">
-        <f>IF(T141="","",ROUND(T141*(1+S141),3))</f>
-        <v/>
-      </c>
-      <c r="V141" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="W141" s="285" t="n"/>
-      <c r="X141" s="285" t="n"/>
-      <c r="Y141" s="1469" t="n"/>
-      <c r="Z141" s="1304" t="n"/>
-      <c r="AA141" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15" customFormat="1" customHeight="1" s="685">
+    </row>
+    <row r="142">
       <c r="A142" s="280" t="inlineStr">
         <is>
-          <t>MQ-134</t>
+          <t>MQ-139</t>
         </is>
       </c>
       <c r="B142" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C142" s="282" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
+          <t>ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C142" s="282" t="n"/>
       <c r="D142" s="283" t="inlineStr">
         <is>
-          <t>20.01.02</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="E142" s="284" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Grouting cementoso para reparación estructural</t>
         </is>
       </c>
       <c r="F142" s="285" t="n"/>
@@ -22022,84 +21968,30 @@
       <c r="H142" s="285" t="n"/>
       <c r="I142" s="283" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="J142" s="1469" t="n"/>
-      <c r="K142" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P142" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q142" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R142" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="1438">
-        <f>IF(I142="","",ROUND(IF(OR(I142="m²",I142="m2"),K142*IF(L142=0,1,L142)*IF(O142=0,1,O142)*IF(P142=0,1,P142)*Q142-R142,IF(OR(I142="m³",I142="m3"),K142*L142*M142*IF(O142=0,1,O142)*IF(P142=0,1,P142)*Q142-R142,IF(OR(I142="ml",I142="ML"),K142*IF(O142=0,1,O142)*IF(P142=0,1,P142)*Q142-R142,IF(OR(I142="und",I142="UND"),IF(O142=0,1,O142)*IF(P142=0,1,P142)*Q142-R142,IF(I142="kg",K142*IF(O142=0,1,O142)*IF(P142=0,1,P142)*Q142-R142,IF(OR(I142="gl",I142="GL",I142="gb",I142="GB",I142="Gl",I142="Gb"),IF(O142=0,1,O142)*IF(P142=0,1,P142)*Q142-R142,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="U142" s="1438">
-        <f>IF(T142="","",ROUND(T142*(1+S142),3))</f>
-        <v/>
-      </c>
-      <c r="V142" s="283" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="W142" s="285" t="n"/>
-      <c r="X142" s="285" t="n"/>
-      <c r="Y142" s="1469" t="n"/>
-      <c r="Z142" s="1304" t="n"/>
-      <c r="AA142" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="15" customFormat="1" customHeight="1" s="685">
+          <t>m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
       <c r="A143" s="280" t="inlineStr">
         <is>
-          <t>MQ-135</t>
+          <t>MQ-140</t>
         </is>
       </c>
       <c r="B143" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C143" s="282" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
+          <t>ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C143" s="282" t="n"/>
       <c r="D143" s="283" t="inlineStr">
         <is>
-          <t>20.02.01</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E143" s="284" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Grouting epóxico para reparación estructural</t>
         </is>
       </c>
       <c r="F143" s="285" t="n"/>
@@ -22107,84 +21999,30 @@
       <c r="H143" s="285" t="n"/>
       <c r="I143" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J143" s="1469" t="n"/>
-      <c r="K143" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P143" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q143" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R143" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" s="1438">
-        <f>IF(I143="","",ROUND(IF(OR(I143="m²",I143="m2"),K143*IF(L143=0,1,L143)*IF(O143=0,1,O143)*IF(P143=0,1,P143)*Q143-R143,IF(OR(I143="m³",I143="m3"),K143*L143*M143*IF(O143=0,1,O143)*IF(P143=0,1,P143)*Q143-R143,IF(OR(I143="ml",I143="ML"),K143*IF(O143=0,1,O143)*IF(P143=0,1,P143)*Q143-R143,IF(OR(I143="und",I143="UND"),IF(O143=0,1,O143)*IF(P143=0,1,P143)*Q143-R143,IF(I143="kg",K143*IF(O143=0,1,O143)*IF(P143=0,1,P143)*Q143-R143,IF(OR(I143="gl",I143="GL",I143="gb",I143="GB",I143="Gl",I143="Gb"),IF(O143=0,1,O143)*IF(P143=0,1,P143)*Q143-R143,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="U143" s="1438">
-        <f>IF(T143="","",ROUND(T143*(1+S143),3))</f>
-        <v/>
-      </c>
-      <c r="V143" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="W143" s="285" t="n"/>
-      <c r="X143" s="285" t="n"/>
-      <c r="Y143" s="1469" t="n"/>
-      <c r="Z143" s="1304" t="n"/>
-      <c r="AA143" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="15" customFormat="1" customHeight="1" s="685">
+          <t>m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
       <c r="A144" s="280" t="inlineStr">
         <is>
-          <t>MQ-136</t>
+          <t>MQ-141</t>
         </is>
       </c>
       <c r="B144" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C144" s="282" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
+          <t>MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C144" s="282" t="n"/>
       <c r="D144" s="283" t="inlineStr">
         <is>
-          <t>20.02.01</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="E144" s="284" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="F144" s="285" t="n"/>
@@ -22192,84 +22030,30 @@
       <c r="H144" s="285" t="n"/>
       <c r="I144" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J144" s="1469" t="n"/>
-      <c r="K144" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P144" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q144" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R144" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" s="1438">
-        <f>IF(I144="","",ROUND(IF(OR(I144="m²",I144="m2"),K144*IF(L144=0,1,L144)*IF(O144=0,1,O144)*IF(P144=0,1,P144)*Q144-R144,IF(OR(I144="m³",I144="m3"),K144*L144*M144*IF(O144=0,1,O144)*IF(P144=0,1,P144)*Q144-R144,IF(OR(I144="ml",I144="ML"),K144*IF(O144=0,1,O144)*IF(P144=0,1,P144)*Q144-R144,IF(OR(I144="und",I144="UND"),IF(O144=0,1,O144)*IF(P144=0,1,P144)*Q144-R144,IF(I144="kg",K144*IF(O144=0,1,O144)*IF(P144=0,1,P144)*Q144-R144,IF(OR(I144="gl",I144="GL",I144="gb",I144="GB",I144="Gl",I144="Gb"),IF(O144=0,1,O144)*IF(P144=0,1,P144)*Q144-R144,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="U144" s="1438">
-        <f>IF(T144="","",ROUND(T144*(1+S144),3))</f>
-        <v/>
-      </c>
-      <c r="V144" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="W144" s="285" t="n"/>
-      <c r="X144" s="285" t="n"/>
-      <c r="Y144" s="1469" t="n"/>
-      <c r="Z144" s="1304" t="n"/>
-      <c r="AA144" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15" customFormat="1" customHeight="1" s="685">
+          <t>m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
       <c r="A145" s="280" t="inlineStr">
         <is>
-          <t>MQ-137</t>
+          <t>MQ-142</t>
         </is>
       </c>
       <c r="B145" s="281" t="inlineStr">
         <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C145" s="282" t="inlineStr">
-        <is>
-          <t>Entrega</t>
-        </is>
-      </c>
+          <t>MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C145" s="282" t="n"/>
       <c r="D145" s="283" t="inlineStr">
         <is>
-          <t>20.02.02</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="E145" s="284" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
         </is>
       </c>
       <c r="F145" s="285" t="n"/>
@@ -22277,80 +22061,30 @@
       <c r="H145" s="285" t="n"/>
       <c r="I145" s="283" t="inlineStr">
         <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="J145" s="1469" t="n"/>
-      <c r="K145" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="P145" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q145" s="1438" t="n">
-        <v>1</v>
-      </c>
-      <c r="R145" s="1438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" s="1303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" s="1438">
-        <f>IF(I145="","",ROUND(IF(OR(I145="m²",I145="m2"),K145*IF(L145=0,1,L145)*IF(O145=0,1,O145)*IF(P145=0,1,P145)*Q145-R145,IF(OR(I145="m³",I145="m3"),K145*L145*M145*IF(O145=0,1,O145)*IF(P145=0,1,P145)*Q145-R145,IF(OR(I145="ml",I145="ML"),K145*IF(O145=0,1,O145)*IF(P145=0,1,P145)*Q145-R145,IF(OR(I145="und",I145="UND"),IF(O145=0,1,O145)*IF(P145=0,1,P145)*Q145-R145,IF(I145="kg",K145*IF(O145=0,1,O145)*IF(P145=0,1,P145)*Q145-R145,IF(OR(I145="gl",I145="GL",I145="gb",I145="GB",I145="Gl",I145="Gb"),IF(O145=0,1,O145)*IF(P145=0,1,P145)*Q145-R145,0)))))),3))</f>
-        <v/>
-      </c>
-      <c r="U145" s="1438">
-        <f>IF(T145="","",ROUND(T145*(1+S145),3))</f>
-        <v/>
-      </c>
-      <c r="V145" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="W145" s="285" t="n"/>
-      <c r="X145" s="285" t="n"/>
-      <c r="Y145" s="1469" t="n"/>
-      <c r="Z145" s="1304" t="n"/>
-      <c r="AA145" s="285" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="280" t="inlineStr">
         <is>
-          <t>MQ-138</t>
+          <t>MQ-143</t>
         </is>
       </c>
       <c r="B146" s="281" t="inlineStr">
         <is>
-          <t>PRELIMINARES</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C146" s="282" t="n"/>
       <c r="D146" s="283" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="E146" s="284" t="inlineStr">
         <is>
-          <t>Desmantelamiento de estructuras metálicas existentes</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="F146" s="285" t="n"/>
@@ -22358,34 +22092,30 @@
       <c r="H146" s="285" t="n"/>
       <c r="I146" s="283" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA146" s="336">
-        <f>I4</f>
-        <v/>
+          <t>m2</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="280" t="inlineStr">
         <is>
-          <t>MQ-139</t>
+          <t>MQ-144</t>
         </is>
       </c>
       <c r="B147" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>CUBIERTAS</t>
         </is>
       </c>
       <c r="C147" s="282" t="n"/>
       <c r="D147" s="283" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="E147" s="284" t="inlineStr">
         <is>
-          <t>Grouting cementoso para reparación estructural</t>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
         </is>
       </c>
       <c r="F147" s="285" t="n"/>
@@ -22400,23 +22130,23 @@
     <row r="148">
       <c r="A148" s="280" t="inlineStr">
         <is>
-          <t>MQ-140</t>
+          <t>MQ-145</t>
         </is>
       </c>
       <c r="B148" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
       <c r="C148" s="282" t="n"/>
       <c r="D148" s="283" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E148" s="284" t="inlineStr">
         <is>
-          <t>Grouting epóxico para reparación estructural</t>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
         </is>
       </c>
       <c r="F148" s="285" t="n"/>
@@ -22431,23 +22161,23 @@
     <row r="149">
       <c r="A149" s="280" t="inlineStr">
         <is>
-          <t>MQ-141</t>
+          <t>MQ-146</t>
         </is>
       </c>
       <c r="B149" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C149" s="282" t="n"/>
       <c r="D149" s="283" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="E149" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="F149" s="285" t="n"/>
@@ -22462,23 +22192,23 @@
     <row r="150">
       <c r="A150" s="280" t="inlineStr">
         <is>
-          <t>MQ-142</t>
+          <t>MQ-147</t>
         </is>
       </c>
       <c r="B150" s="281" t="inlineStr">
         <is>
-          <t>MAMPOSTERÍA</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C150" s="282" t="n"/>
       <c r="D150" s="283" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="E150" s="284" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="F150" s="285" t="n"/>
@@ -22493,23 +22223,23 @@
     <row r="151">
       <c r="A151" s="280" t="inlineStr">
         <is>
-          <t>MQ-143</t>
+          <t>MQ-148</t>
         </is>
       </c>
       <c r="B151" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C151" s="282" t="n"/>
       <c r="D151" s="283" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="E151" s="284" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Enchape en granito pulido</t>
         </is>
       </c>
       <c r="F151" s="285" t="n"/>
@@ -22524,23 +22254,23 @@
     <row r="152">
       <c r="A152" s="280" t="inlineStr">
         <is>
-          <t>MQ-144</t>
+          <t>MQ-149</t>
         </is>
       </c>
       <c r="B152" s="281" t="inlineStr">
         <is>
-          <t>CUBIERTAS</t>
+          <t>CARPINTERÍA</t>
         </is>
       </c>
       <c r="C152" s="282" t="n"/>
       <c r="D152" s="283" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="E152" s="284" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Puerta antipánico</t>
         </is>
       </c>
       <c r="F152" s="285" t="n"/>
@@ -22548,30 +22278,30 @@
       <c r="H152" s="285" t="n"/>
       <c r="I152" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="280" t="inlineStr">
         <is>
-          <t>MQ-145</t>
+          <t>MQ-150</t>
         </is>
       </c>
       <c r="B153" s="281" t="inlineStr">
         <is>
-          <t>IMPERMEABILIZACIONES</t>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
       <c r="C153" s="282" t="n"/>
       <c r="D153" s="283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="E153" s="284" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Orinal institucional</t>
         </is>
       </c>
       <c r="F153" s="285" t="n"/>
@@ -22579,30 +22309,30 @@
       <c r="H153" s="285" t="n"/>
       <c r="I153" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="280" t="inlineStr">
         <is>
-          <t>MQ-146</t>
+          <t>MQ-151</t>
         </is>
       </c>
       <c r="B154" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C154" s="282" t="n"/>
       <c r="D154" s="283" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="E154" s="284" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="F154" s="285" t="n"/>
@@ -22617,23 +22347,23 @@
     <row r="155">
       <c r="A155" s="280" t="inlineStr">
         <is>
-          <t>MQ-147</t>
+          <t>MQ-152</t>
         </is>
       </c>
       <c r="B155" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C155" s="282" t="n"/>
       <c r="D155" s="283" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="E155" s="284" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="F155" s="285" t="n"/>
@@ -22641,30 +22371,30 @@
       <c r="H155" s="285" t="n"/>
       <c r="I155" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="280" t="inlineStr">
         <is>
-          <t>MQ-148</t>
+          <t>MQ-153</t>
         </is>
       </c>
       <c r="B156" s="281" t="inlineStr">
         <is>
-          <t>PISOS Y ENCHAPES</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C156" s="282" t="n"/>
       <c r="D156" s="283" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="E156" s="284" t="inlineStr">
         <is>
-          <t>Enchape en granito pulido</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="F156" s="285" t="n"/>
@@ -22672,30 +22402,30 @@
       <c r="H156" s="285" t="n"/>
       <c r="I156" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="280" t="inlineStr">
         <is>
-          <t>MQ-149</t>
+          <t>MQ-154</t>
         </is>
       </c>
       <c r="B157" s="281" t="inlineStr">
         <is>
-          <t>CARPINTERÍA</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C157" s="282" t="n"/>
       <c r="D157" s="283" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="E157" s="284" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Revegetalización / empradización</t>
         </is>
       </c>
       <c r="F157" s="285" t="n"/>
@@ -22703,30 +22433,30 @@
       <c r="H157" s="285" t="n"/>
       <c r="I157" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="280" t="inlineStr">
         <is>
-          <t>MQ-150</t>
+          <t>MQ-155</t>
         </is>
       </c>
       <c r="B158" s="281" t="inlineStr">
         <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
+          <t>ESTRUCTURA</t>
         </is>
       </c>
       <c r="C158" s="282" t="n"/>
       <c r="D158" s="283" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="E158" s="284" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Concreto premezclado o de planta (suministro)</t>
         </is>
       </c>
       <c r="F158" s="285" t="n"/>
@@ -22734,30 +22464,30 @@
       <c r="H158" s="285" t="n"/>
       <c r="I158" s="283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="280" t="inlineStr">
         <is>
-          <t>MQ-151</t>
+          <t>MQ-157</t>
         </is>
       </c>
       <c r="B159" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C159" s="282" t="n"/>
       <c r="D159" s="283" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="E159" s="284" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="F159" s="285" t="n"/>
@@ -22765,30 +22495,30 @@
       <c r="H159" s="285" t="n"/>
       <c r="I159" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>gl</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="280" t="inlineStr">
         <is>
-          <t>MQ-152</t>
+          <t>MQ-158</t>
         </is>
       </c>
       <c r="B160" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C160" s="282" t="n"/>
       <c r="D160" s="283" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="E160" s="284" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="F160" s="285" t="n"/>
@@ -22796,30 +22526,30 @@
       <c r="H160" s="285" t="n"/>
       <c r="I160" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>gl</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="280" t="inlineStr">
         <is>
-          <t>MQ-153</t>
+          <t>MQ-159</t>
         </is>
       </c>
       <c r="B161" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C161" s="282" t="n"/>
       <c r="D161" s="283" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E161" s="284" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="F161" s="285" t="n"/>
@@ -22827,30 +22557,30 @@
       <c r="H161" s="285" t="n"/>
       <c r="I161" s="283" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>gl</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="280" t="inlineStr">
         <is>
-          <t>MQ-154</t>
+          <t>MQ-160</t>
         </is>
       </c>
       <c r="B162" s="281" t="inlineStr">
         <is>
-          <t>URBANISMO Y EXTERIORES</t>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C162" s="282" t="n"/>
       <c r="D162" s="283" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="E162" s="284" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
         </is>
       </c>
       <c r="F162" s="285" t="n"/>
@@ -22858,30 +22588,30 @@
       <c r="H162" s="285" t="n"/>
       <c r="I162" s="283" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>gl</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="280" t="inlineStr">
         <is>
-          <t>MQ-155</t>
+          <t>MQ-161</t>
         </is>
       </c>
       <c r="B163" s="281" t="inlineStr">
         <is>
-          <t>ESTRUCTURA</t>
+          <t>ASCENSORES</t>
         </is>
       </c>
       <c r="C163" s="282" t="n"/>
       <c r="D163" s="283" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="E163" s="284" t="inlineStr">
         <is>
-          <t>Concreto premezclado o de planta (suministro)</t>
+          <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
       <c r="F163" s="285" t="n"/>
@@ -22889,174 +22619,19 @@
       <c r="H163" s="285" t="n"/>
       <c r="I163" s="283" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="280" t="inlineStr">
-        <is>
-          <t>MQ-157</t>
-        </is>
-      </c>
-      <c r="B164" s="281" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C164" s="282" t="n"/>
-      <c r="D164" s="283" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="E164" s="284" t="inlineStr">
-        <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
-        </is>
-      </c>
-      <c r="F164" s="285" t="n"/>
-      <c r="G164" s="285" t="n"/>
-      <c r="H164" s="285" t="n"/>
-      <c r="I164" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="280" t="inlineStr">
-        <is>
-          <t>MQ-158</t>
-        </is>
-      </c>
-      <c r="B165" s="281" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C165" s="282" t="n"/>
-      <c r="D165" s="283" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="E165" s="284" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="F165" s="285" t="n"/>
-      <c r="G165" s="285" t="n"/>
-      <c r="H165" s="285" t="n"/>
-      <c r="I165" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="280" t="inlineStr">
-        <is>
-          <t>MQ-159</t>
-        </is>
-      </c>
-      <c r="B166" s="281" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C166" s="282" t="n"/>
-      <c r="D166" s="283" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="E166" s="284" t="inlineStr">
-        <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
-        </is>
-      </c>
-      <c r="F166" s="285" t="n"/>
-      <c r="G166" s="285" t="n"/>
-      <c r="H166" s="285" t="n"/>
-      <c r="I166" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="280" t="inlineStr">
-        <is>
-          <t>MQ-160</t>
-        </is>
-      </c>
-      <c r="B167" s="281" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C167" s="282" t="n"/>
-      <c r="D167" s="283" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="E167" s="284" t="inlineStr">
-        <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
-        </is>
-      </c>
-      <c r="F167" s="285" t="n"/>
-      <c r="G167" s="285" t="n"/>
-      <c r="H167" s="285" t="n"/>
-      <c r="I167" s="283" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="280" t="inlineStr">
-        <is>
-          <t>MQ-161</t>
-        </is>
-      </c>
-      <c r="B168" s="281" t="inlineStr">
-        <is>
-          <t>ASCENSORES</t>
-        </is>
-      </c>
-      <c r="C168" s="282" t="n"/>
-      <c r="D168" s="283" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="E168" s="284" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
-        </is>
-      </c>
-      <c r="F168" s="285" t="n"/>
-      <c r="G168" s="285" t="n"/>
-      <c r="H168" s="285" t="n"/>
-      <c r="I168" s="283" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="1446" t="inlineStr">
+      <c r="A164" s="1446" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:AA169"/>
+  <autoFilter ref="A8:AA164"/>
   <mergeCells count="13">
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="C1:K1"/>
@@ -33797,10 +33372,10 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="E1:M1"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A23:M23"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A17:M17"/>
